--- a/docs/downloads/2026-10-19/bursa-report-2026-10-19.xlsx
+++ b/docs/downloads/2026-10-19/bursa-report-2026-10-19.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-19" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-19'!$A$1:$M$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-19'!$A$1:$M$70</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -78,12 +78,12 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -543,39 +543,39 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.31</v>
+        <v>0.92</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0.0333</v>
+        <v>0.0222</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>15576000</v>
+        <v>22748800</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>1.91</v>
+        <v>0.34</v>
       </c>
       <c r="H2" t="n">
-        <v>58.29</v>
+        <v>68.37</v>
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.3</v>
+        <v>0.83</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0.28</v>
+        <v>0.737</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" s="7" t="inlineStr"/>
@@ -588,39 +588,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.44</v>
+        <v>0.135</v>
       </c>
       <c r="E3" s="8" t="n">
-        <v>-0.0222</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>1510900</v>
+        <v>19411100</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.04</v>
+        <v>0.28</v>
       </c>
       <c r="H3" t="n">
-        <v>37.57</v>
-      </c>
-      <c r="I3" s="6" t="inlineStr">
+        <v>40.3</v>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.478</v>
+        <v>0.158</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.482</v>
+        <v>0.139</v>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" s="7" t="inlineStr"/>
@@ -633,39 +633,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.645</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>0.0157</v>
+        <v>0.325</v>
+      </c>
+      <c r="E4" s="8" t="n">
+        <v>-0.0441</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>1455300</v>
+        <v>16224400</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.65</v>
+        <v>0.21</v>
       </c>
       <c r="H4" t="n">
-        <v>56.76</v>
+        <v>61.81</v>
       </c>
       <c r="I4" s="9" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.638</v>
+        <v>0.303</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.623</v>
+        <v>0.257</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" s="7" t="inlineStr"/>
@@ -678,39 +678,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.335</v>
+        <v>0.415</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>-0.0147</v>
+        <v>-0.0119</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>1441700</v>
+        <v>10000200</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.02</v>
+        <v>0.29</v>
       </c>
       <c r="H5" t="n">
-        <v>66.22</v>
-      </c>
-      <c r="I5" s="9" t="inlineStr">
+        <v>71.66</v>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.304</v>
+        <v>0.382</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.257</v>
+        <v>0.277</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="7" t="inlineStr"/>
@@ -723,39 +723,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5932</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BPURI</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.215</v>
-      </c>
-      <c r="E6" s="10" t="n">
-        <v>0</v>
+        <v>0.285</v>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>-0.0806</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>1203100</v>
+        <v>8461900</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>1.76</v>
+        <v>0.97</v>
       </c>
       <c r="H6" t="n">
-        <v>41.08</v>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
+        <v>45.31</v>
+      </c>
+      <c r="I6" s="9" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.224</v>
+        <v>0.299</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.232</v>
+        <v>0.28</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="7" t="inlineStr"/>
@@ -768,39 +768,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.665</v>
+        <v>4.74</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>-0.0075</v>
+        <v>-0.0186</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>1153000</v>
+        <v>7832700</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.05</v>
+        <v>0.42</v>
       </c>
       <c r="H7" t="n">
-        <v>72.77</v>
-      </c>
-      <c r="I7" s="9" t="inlineStr">
+        <v>49.11</v>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.615</v>
+        <v>4.731</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.531</v>
+        <v>4.848</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="7" t="inlineStr"/>
@@ -813,39 +813,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>0081</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>REKATECH</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.955</v>
+        <v>0.035</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>-0.0052</v>
+        <v>-0.2222</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1120300</v>
+        <v>7785200</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.19</v>
+        <v>21.05</v>
       </c>
       <c r="H8" t="n">
-        <v>63.1</v>
-      </c>
-      <c r="I8" s="9" t="inlineStr">
+        <v>62.28</v>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.924</v>
+        <v>0.026</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.876</v>
+        <v>0.023</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="7" t="inlineStr"/>
@@ -858,40 +858,33 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>SLG</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="E9" s="8" t="n">
-        <v>-0.0062</v>
+        <v>0.25</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>883300</v>
+        <v>6773100</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="H9" t="n">
-        <v>54.37</v>
+        <v>0.27</v>
       </c>
       <c r="I9" s="9" t="inlineStr">
         <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="n">
-        <v>4.737</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>4.849</v>
-      </c>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="n"/>
+      <c r="K9" s="2" t="n"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="7" t="inlineStr"/>
     </row>
@@ -903,45 +896,2734 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="E10" s="8" t="n">
-        <v>-0.0111</v>
+        <v>0.67</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>530300</v>
+        <v>6058000</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.01</v>
+        <v>0.24</v>
       </c>
       <c r="H10" t="n">
-        <v>64.16</v>
-      </c>
-      <c r="I10" s="9" t="inlineStr">
+        <v>75.19</v>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.827</v>
+        <v>0.616</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0.736</v>
+        <v>0.531</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="7" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>3891</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>MUIIND</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E11" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>5898300</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="H11" t="n">
+        <v>46.69</v>
+      </c>
+      <c r="I11" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" s="7" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>5259</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>AVANGAAD</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>5874500</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="H12" t="n">
+        <v>49.08</v>
+      </c>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" s="7" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>4251</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>IBHD</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>0.0682</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>4984100</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>17.11</v>
+      </c>
+      <c r="H13" t="n">
+        <v>71.83</v>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>0.217</v>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" s="7" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>7106</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>SUPERMX</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>0.0112</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>4604100</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H14" t="n">
+        <v>60.13</v>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>0.424</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" s="7" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>4456</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>DNEX</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>0.445</v>
+      </c>
+      <c r="E15" s="8" t="n">
+        <v>-0.0111</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>4602500</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H15" t="n">
+        <v>38.75</v>
+      </c>
+      <c r="I15" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>0.478</v>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>0.482</v>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" s="7" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0270</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NATGATE</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="E16" s="8" t="n">
+        <v>-0.0347</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>3267500</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H16" t="n">
+        <v>54.64</v>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>1.923</v>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>1.739</v>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" s="7" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>5168</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>HARTA</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>0.0091</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>3192300</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H17" t="n">
+        <v>55.57</v>
+      </c>
+      <c r="I17" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="K17" s="2" t="n">
+        <v>1.046</v>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" s="7" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0457</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>PENTECH</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="E18" s="8" t="n">
+        <v>-0.0147</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>3057200</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H18" t="n">
+        <v>47.31</v>
+      </c>
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="n">
+        <v>0.346</v>
+      </c>
+      <c r="K18" s="2" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" s="7" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>5199</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>HIBISCS</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>0.0218</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>2875100</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="H19" t="n">
+        <v>60.87</v>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="n">
+        <v>2.226</v>
+      </c>
+      <c r="K19" s="2" t="n">
+        <v>2.167</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" s="7" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1171</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>MBSB</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="E20" s="8" t="n">
+        <v>-0.0187</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>2770400</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="H20" t="n">
+        <v>36.53</v>
+      </c>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="n">
+        <v>0.544</v>
+      </c>
+      <c r="K20" s="2" t="n">
+        <v>0.572</v>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" s="7" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>0198</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>GDB</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>0.0247</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>2685200</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="H21" t="n">
+        <v>45.72</v>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="n">
+        <v>0.416</v>
+      </c>
+      <c r="K21" s="2" t="n">
+        <v>0.434</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" s="7" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>0477</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ECOSYS</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="E22" s="8" t="n">
+        <v>-0.0127</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>2641400</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="n"/>
+      <c r="K22" s="2" t="n"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" s="7" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>0455</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>BUSCAP</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="E23" s="8" t="n">
+        <v>-0.0556</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>2599300</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="H23" t="n">
+        <v>67.29000000000001</v>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="n">
+        <v>0.843</v>
+      </c>
+      <c r="K23" s="2" t="n">
+        <v>0.573</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" s="7" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>5161</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>JCY</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="E24" s="8" t="n">
+        <v>-0.027</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>1969900</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H24" t="n">
+        <v>45.4</v>
+      </c>
+      <c r="I24" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="n">
+        <v>0.572</v>
+      </c>
+      <c r="K24" s="2" t="n">
+        <v>0.541</v>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" s="7" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>4677</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>YTL</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" s="8" t="n">
+        <v>-0.0148</v>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>1956500</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H25" t="n">
+        <v>31.84</v>
+      </c>
+      <c r="I25" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="n">
+        <v>2.146</v>
+      </c>
+      <c r="K25" s="2" t="n">
+        <v>2.233</v>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" s="7" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>0181</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>AEMULUS</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>0.425</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>0.0119</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>1924900</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H26" t="n">
+        <v>51.3</v>
+      </c>
+      <c r="I26" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="n">
+        <v>0.424</v>
+      </c>
+      <c r="K26" s="2" t="n">
+        <v>0.416</v>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" s="7" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>5151</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>HEXTAR</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="E27" s="8" t="n">
+        <v>-0.0064</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>1875200</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H27" t="n">
+        <v>49.91</v>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="K27" s="2" t="n">
+        <v>0.776</v>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" s="7" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>7153</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>KOSSAN</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>0.0169</v>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>1860300</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H28" t="n">
+        <v>54.72</v>
+      </c>
+      <c r="I28" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="n">
+        <v>1.172</v>
+      </c>
+      <c r="K28" s="2" t="n">
+        <v>1.137</v>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" s="7" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>0339</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>CBHB</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>0.009899999999999999</v>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>1768200</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H29" t="n">
+        <v>47.53</v>
+      </c>
+      <c r="I29" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="n">
+        <v>1.052</v>
+      </c>
+      <c r="K29" s="2" t="n">
+        <v>0.959</v>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" s="7" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>0166</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>INARI</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="E30" s="8" t="n">
+        <v>-0.0226</v>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>1752600</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H30" t="n">
+        <v>48.48</v>
+      </c>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="n">
+        <v>2.645</v>
+      </c>
+      <c r="K30" s="2" t="n">
+        <v>2.554</v>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" s="7" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>0112</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>MIKROMB</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="E31" s="8" t="n">
+        <v>-0.007900000000000001</v>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>1700000</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="H31" t="n">
+        <v>47.67</v>
+      </c>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="n">
+        <v>0.637</v>
+      </c>
+      <c r="K31" s="2" t="n">
+        <v>0.622</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" s="7" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>4324</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>HENGYUAN</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>0.0269</v>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>1687500</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H32" t="n">
+        <v>58.32</v>
+      </c>
+      <c r="I32" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>3.008</v>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" s="7" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>8869</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>PMETAL</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>6.61</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>0.0169</v>
+      </c>
+      <c r="F33" s="4" t="n">
+        <v>1667700</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H33" t="n">
+        <v>25.41</v>
+      </c>
+      <c r="I33" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="n">
+        <v>7.202</v>
+      </c>
+      <c r="K33" s="2" t="n">
+        <v>7.605</v>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" s="7" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>0248</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>YEWLEE</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E34" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>1614900</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H34" t="n">
+        <v>56.82</v>
+      </c>
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="n">
+        <v>0.617</v>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" s="7" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>0338</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>KOPI</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>0.835</v>
+      </c>
+      <c r="E35" s="8" t="n">
+        <v>-0.0457</v>
+      </c>
+      <c r="F35" s="4" t="n">
+        <v>1607900</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="H35" t="n">
+        <v>28.22</v>
+      </c>
+      <c r="I35" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="n">
+        <v>0.897</v>
+      </c>
+      <c r="K35" s="2" t="n">
+        <v>0.953</v>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" s="7" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>5243</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>VELESTO</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>0.0345</v>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>1412500</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H36" t="n">
+        <v>42.77</v>
+      </c>
+      <c r="I36" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="n">
+        <v>0.218</v>
+      </c>
+      <c r="K36" s="2" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" s="7" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>0345</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>SUNLOGY</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="E37" s="8" t="n">
+        <v>-0.0238</v>
+      </c>
+      <c r="F37" s="4" t="n">
+        <v>1382800</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H37" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="I37" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="n">
+        <v>0.438</v>
+      </c>
+      <c r="K37" s="2" t="n">
+        <v>0.434</v>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" s="7" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>0236</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>RAMSSOL</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>0.745</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>0.0136</v>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>1359900</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H38" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="I38" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="n">
+        <v>0.769</v>
+      </c>
+      <c r="K38" s="2" t="n">
+        <v>0.771</v>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" s="7" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>0318</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>ELRIDGE</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="E39" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="4" t="n">
+        <v>1317700</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H39" t="n">
+        <v>65.06</v>
+      </c>
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="n">
+        <v>0.924</v>
+      </c>
+      <c r="K39" s="2" t="n">
+        <v>0.877</v>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" s="7" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>0083</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>NOTION</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="E40" s="8" t="n">
+        <v>-0.0336</v>
+      </c>
+      <c r="F40" s="4" t="n">
+        <v>1295300</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H40" t="n">
+        <v>37.01</v>
+      </c>
+      <c r="I40" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="n">
+        <v>0.648</v>
+      </c>
+      <c r="K40" s="2" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" s="7" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>6742</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>YTLPOWR</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="E41" s="8" t="n">
+        <v>-0.0155</v>
+      </c>
+      <c r="F41" s="4" t="n">
+        <v>1276000</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H41" t="n">
+        <v>33.09</v>
+      </c>
+      <c r="I41" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="K41" s="2" t="n">
+        <v>5.447</v>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" s="7" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>5238</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>AAGB</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>0.445</v>
+      </c>
+      <c r="E42" s="8" t="n">
+        <v>-0.022</v>
+      </c>
+      <c r="F42" s="4" t="n">
+        <v>1267800</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H42" t="n">
+        <v>26.49</v>
+      </c>
+      <c r="I42" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="n">
+        <v>0.506</v>
+      </c>
+      <c r="K42" s="2" t="n">
+        <v>0.677</v>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" s="7" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>5148</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>UEMS</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="E43" s="8" t="n">
+        <v>-0.0215</v>
+      </c>
+      <c r="F43" s="4" t="n">
+        <v>1264500</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H43" t="n">
+        <v>28.78</v>
+      </c>
+      <c r="I43" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="n">
+        <v>0.498</v>
+      </c>
+      <c r="K43" s="2" t="n">
+        <v>0.556</v>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" s="7" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>0251</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>SFPTECH</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="E44" s="8" t="n">
+        <v>-0.0189</v>
+      </c>
+      <c r="F44" s="4" t="n">
+        <v>1250200</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H44" t="n">
+        <v>42.45</v>
+      </c>
+      <c r="I44" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="n">
+        <v>0.273</v>
+      </c>
+      <c r="K44" s="2" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" s="7" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>5932</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>BPURI</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="E45" s="8" t="n">
+        <v>-0.0233</v>
+      </c>
+      <c r="F45" s="4" t="n">
+        <v>1233100</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H45" t="n">
+        <v>38.22</v>
+      </c>
+      <c r="I45" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="n">
+        <v>0.223</v>
+      </c>
+      <c r="K45" s="2" t="n">
+        <v>0.232</v>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" s="7" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>3182</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>GENTING</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="E46" s="8" t="n">
+        <v>-0.0069</v>
+      </c>
+      <c r="F46" s="4" t="n">
+        <v>1174600</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H46" t="n">
+        <v>22.12</v>
+      </c>
+      <c r="I46" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="n">
+        <v>1.693</v>
+      </c>
+      <c r="K46" s="2" t="n">
+        <v>1.945</v>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" s="7" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>0469</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>GTA</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>0.245</v>
+      </c>
+      <c r="E47" s="8" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="F47" s="4" t="n">
+        <v>1120300</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H47" t="n">
+        <v>16.72</v>
+      </c>
+      <c r="I47" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="n">
+        <v>0.272</v>
+      </c>
+      <c r="K47" s="2" t="n"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" s="7" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>5301</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>CTOS</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="E48" s="8" t="n">
+        <v>-0.0235</v>
+      </c>
+      <c r="F48" s="4" t="n">
+        <v>1114900</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H48" t="n">
+        <v>23.04</v>
+      </c>
+      <c r="I48" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="n">
+        <v>0.527</v>
+      </c>
+      <c r="K48" s="2" t="n">
+        <v>0.614</v>
+      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" s="7" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>7204</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>D&amp;O</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="E49" s="8" t="n">
+        <v>-0.019</v>
+      </c>
+      <c r="F49" s="4" t="n">
+        <v>1070600</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H49" t="n">
+        <v>51.37</v>
+      </c>
+      <c r="I49" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="K49" s="2" t="n">
+        <v>0.461</v>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" s="7" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>0471</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>PIONEER</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="E50" s="8" t="n">
+        <v>-0.0274</v>
+      </c>
+      <c r="F50" s="4" t="n">
+        <v>1065900</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H50" t="n">
+        <v>60.83</v>
+      </c>
+      <c r="I50" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="K50" s="2" t="n"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" s="7" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>0127</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>JHM</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E51" s="8" t="n">
+        <v>-0.0351</v>
+      </c>
+      <c r="F51" s="4" t="n">
+        <v>1046200</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H51" t="n">
+        <v>49.98</v>
+      </c>
+      <c r="I51" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="K51" s="2" t="n">
+        <v>0.516</v>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" s="7" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>0450</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>MFGROUP</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="E52" s="8" t="n">
+        <v>-0.0175</v>
+      </c>
+      <c r="F52" s="4" t="n">
+        <v>1006700</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="H52" t="n">
+        <v>55.75</v>
+      </c>
+      <c r="I52" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="n">
+        <v>0.276</v>
+      </c>
+      <c r="K52" s="2" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" s="7" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>0240</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>CORAZA</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="E53" s="8" t="n">
+        <v>-0.0301</v>
+      </c>
+      <c r="F53" s="4" t="n">
+        <v>998800</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="H53" t="n">
+        <v>55.19</v>
+      </c>
+      <c r="I53" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="n">
+        <v>1.259</v>
+      </c>
+      <c r="K53" s="2" t="n">
+        <v>1.173</v>
+      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" s="7" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>7121</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="E54" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" s="4" t="n">
+        <v>992500</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H54" t="n">
+        <v>57.16</v>
+      </c>
+      <c r="I54" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="n">
+        <v>0.8139999999999999</v>
+      </c>
+      <c r="K54" s="2" t="n">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" s="7" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>0368</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>OXB</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>0.585</v>
+      </c>
+      <c r="E55" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" s="4" t="n">
+        <v>875800</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H55" t="n">
+        <v>68.69</v>
+      </c>
+      <c r="I55" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="n">
+        <v>0.509</v>
+      </c>
+      <c r="K55" s="2" t="n">
+        <v>0.468</v>
+      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" s="7" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>5327</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>MEGAFB</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="E56" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" s="4" t="n">
+        <v>822000</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H56" t="n">
+        <v>82.09</v>
+      </c>
+      <c r="I56" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="n">
+        <v>2.827</v>
+      </c>
+      <c r="K56" s="2" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" s="7" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>0459</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>SUM</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="n">
+        <v>0.735</v>
+      </c>
+      <c r="E57" s="8" t="n">
+        <v>-0.0329</v>
+      </c>
+      <c r="F57" s="4" t="n">
+        <v>807300</v>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H57" t="n">
+        <v>48.09</v>
+      </c>
+      <c r="I57" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="n">
+        <v>0.761</v>
+      </c>
+      <c r="K57" s="2" t="n">
+        <v>0.6850000000000001</v>
+      </c>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" s="7" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>0275</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>OPPSTAR</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="E58" s="8" t="n">
+        <v>-0.0155</v>
+      </c>
+      <c r="F58" s="4" t="n">
+        <v>755200</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H58" t="n">
+        <v>40.95</v>
+      </c>
+      <c r="I58" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="n">
+        <v>0.678</v>
+      </c>
+      <c r="K58" s="2" t="n">
+        <v>0.6889999999999999</v>
+      </c>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" s="7" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>4715</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>GENM</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="E59" s="8" t="n">
+        <v>-0.0236</v>
+      </c>
+      <c r="F59" s="4" t="n">
+        <v>741100</v>
+      </c>
+      <c r="G59" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H59" t="n">
+        <v>24.69</v>
+      </c>
+      <c r="I59" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="n">
+        <v>1.394</v>
+      </c>
+      <c r="K59" s="2" t="n">
+        <v>1.561</v>
+      </c>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" s="7" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>0246</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>CNERGEN</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="E60" s="8" t="n">
+        <v>-0.027</v>
+      </c>
+      <c r="F60" s="4" t="n">
+        <v>724400</v>
+      </c>
+      <c r="G60" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H60" t="n">
+        <v>55.63</v>
+      </c>
+      <c r="I60" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="n">
+        <v>1.052</v>
+      </c>
+      <c r="K60" s="2" t="n">
+        <v>0.913</v>
+      </c>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" s="7" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>0217</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>PWRWELL</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="E61" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" s="4" t="n">
+        <v>720100</v>
+      </c>
+      <c r="G61" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H61" t="n">
+        <v>52.61</v>
+      </c>
+      <c r="I61" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="K61" s="2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" s="7" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>3336</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>IJM</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="E62" s="8" t="n">
+        <v>-0.0114</v>
+      </c>
+      <c r="F62" s="4" t="n">
+        <v>683200</v>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H62" t="n">
+        <v>37.72</v>
+      </c>
+      <c r="I62" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="n">
+        <v>2.754</v>
+      </c>
+      <c r="K62" s="2" t="n">
+        <v>2.737</v>
+      </c>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" s="7" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>7579</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>AWC</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="E63" s="8" t="n">
+        <v>-0.0219</v>
+      </c>
+      <c r="F63" s="4" t="n">
+        <v>679800</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H63" t="n">
+        <v>59.56</v>
+      </c>
+      <c r="I63" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="n">
+        <v>0.647</v>
+      </c>
+      <c r="K63" s="2" t="n">
+        <v>0.5570000000000001</v>
+      </c>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" s="7" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>0453</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>EIPOWER</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E64" s="8" t="n">
+        <v>-0.0168</v>
+      </c>
+      <c r="F64" s="4" t="n">
+        <v>679100</v>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H64" t="n">
+        <v>44.55</v>
+      </c>
+      <c r="I64" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="n">
+        <v>0.929</v>
+      </c>
+      <c r="K64" s="2" t="n">
+        <v>0.847</v>
+      </c>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" s="7" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>5398</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>GAMUDA</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="E65" s="8" t="n">
+        <v>-0.0104</v>
+      </c>
+      <c r="F65" s="4" t="n">
+        <v>673400</v>
+      </c>
+      <c r="G65" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H65" t="n">
+        <v>43.41</v>
+      </c>
+      <c r="I65" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="n">
+        <v>4.894</v>
+      </c>
+      <c r="K65" s="2" t="n">
+        <v>4.727</v>
+      </c>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" s="7" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>5352</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>MTTSL</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>0.007900000000000001</v>
+      </c>
+      <c r="F66" s="4" t="n">
+        <v>613200</v>
+      </c>
+      <c r="G66" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H66" t="n">
+        <v>62.51</v>
+      </c>
+      <c r="I66" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="n">
+        <v>1.198</v>
+      </c>
+      <c r="K66" s="2" t="n">
+        <v>1.188</v>
+      </c>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" s="7" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>CIMB</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="n">
+        <v>7.21</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>0.0014</v>
+      </c>
+      <c r="F67" s="4" t="n">
+        <v>611100</v>
+      </c>
+      <c r="G67" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H67" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="I67" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="n">
+        <v>7.51</v>
+      </c>
+      <c r="K67" s="2" t="n">
+        <v>7.685</v>
+      </c>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" s="7" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>0196</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>QES</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="E68" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" s="4" t="n">
+        <v>610200</v>
+      </c>
+      <c r="G68" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H68" t="n">
+        <v>49.06</v>
+      </c>
+      <c r="I68" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="n">
+        <v>0.598</v>
+      </c>
+      <c r="K68" s="2" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" s="7" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>0390</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>ISF</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="n">
+        <v>0.845</v>
+      </c>
+      <c r="E69" s="8" t="n">
+        <v>-0.0059</v>
+      </c>
+      <c r="F69" s="4" t="n">
+        <v>604700</v>
+      </c>
+      <c r="G69" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H69" t="n">
+        <v>55.12</v>
+      </c>
+      <c r="I69" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="n">
+        <v>0.828</v>
+      </c>
+      <c r="K69" s="2" t="n">
+        <v>0.782</v>
+      </c>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" s="7" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>5555</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>SUNMED</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="E70" s="8" t="n">
+        <v>-0.0095</v>
+      </c>
+      <c r="F70" s="4" t="n">
+        <v>507500</v>
+      </c>
+      <c r="G70" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H70" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="I70" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="n">
+        <v>2.107</v>
+      </c>
+      <c r="K70" s="2" t="n">
+        <v>2.101</v>
+      </c>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M10"/>
+  <autoFilter ref="A1:M70"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-19/bursa-report-2026-10-19.xlsx
+++ b/docs/downloads/2026-10-19/bursa-report-2026-10-19.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-19" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-19'!$A$1:$M$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-19'!$A$1:$M$100</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M70"/>
+  <dimension ref="A1:M100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -552,19 +552,19 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.92</v>
+        <v>0.915</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0.0222</v>
+        <v>0.0167</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>22748800</v>
+        <v>31591100</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.34</v>
+        <v>0.47</v>
       </c>
       <c r="H2" t="n">
-        <v>68.37</v>
+        <v>67.87</v>
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
@@ -588,28 +588,28 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.135</v>
+        <v>0.325</v>
       </c>
       <c r="E3" s="8" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-0.0441</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>19411100</v>
+        <v>27017700</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.28</v>
+        <v>0.35</v>
       </c>
       <c r="H3" t="n">
-        <v>40.3</v>
+        <v>61.81</v>
       </c>
       <c r="I3" s="9" t="inlineStr">
         <is>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.158</v>
+        <v>0.303</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.139</v>
+        <v>0.257</v>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" s="7" t="inlineStr"/>
@@ -633,28 +633,28 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.325</v>
+        <v>0.13</v>
       </c>
       <c r="E4" s="8" t="n">
-        <v>-0.0441</v>
+        <v>-0.1034</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>16224400</v>
+        <v>24671900</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.21</v>
+        <v>0.36</v>
       </c>
       <c r="H4" t="n">
-        <v>61.81</v>
+        <v>38.6</v>
       </c>
       <c r="I4" s="9" t="inlineStr">
         <is>
@@ -662,10 +662,10 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.303</v>
+        <v>0.158</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.257</v>
+        <v>0.139</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" s="7" t="inlineStr"/>
@@ -678,39 +678,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>0138</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>ZETRIX</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.415</v>
+        <v>0.05</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>-0.0119</v>
+        <v>-0.09089999999999999</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>10000200</v>
+        <v>15008400</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.29</v>
+        <v>0.04</v>
       </c>
       <c r="H5" t="n">
-        <v>71.66</v>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>22.63</v>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.382</v>
+        <v>0.123</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.277</v>
+        <v>0.322</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="7" t="inlineStr"/>
@@ -723,39 +723,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.285</v>
-      </c>
-      <c r="E6" s="8" t="n">
-        <v>-0.0806</v>
+        <v>0.42</v>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>8461900</v>
+        <v>11693500</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.97</v>
+        <v>0.34</v>
       </c>
       <c r="H6" t="n">
-        <v>45.31</v>
-      </c>
-      <c r="I6" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>74.48999999999999</v>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.299</v>
+        <v>0.382</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.28</v>
+        <v>0.277</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="7" t="inlineStr"/>
@@ -768,28 +768,28 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>4.74</v>
-      </c>
-      <c r="E7" s="8" t="n">
-        <v>-0.0186</v>
+        <v>0.67</v>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>7832700</v>
+        <v>11249400</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.42</v>
+        <v>0.45</v>
       </c>
       <c r="H7" t="n">
-        <v>49.11</v>
+        <v>75.19</v>
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
@@ -797,10 +797,10 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>4.731</v>
+        <v>0.616</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>4.848</v>
+        <v>0.531</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="7" t="inlineStr"/>
@@ -813,39 +813,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0081</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>REKATECH</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.035</v>
+        <v>0.285</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>-0.2222</v>
+        <v>-0.0806</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>7785200</v>
+        <v>10467300</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>21.05</v>
+        <v>1.2</v>
       </c>
       <c r="H8" t="n">
-        <v>62.28</v>
-      </c>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.31</v>
+      </c>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.026</v>
+        <v>0.299</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.023</v>
+        <v>0.28</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="7" t="inlineStr"/>
@@ -858,33 +858,40 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>4251</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SLG</t>
+          <t>IBHD</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E9" s="10" t="n">
-        <v>0</v>
+        <v>0.205</v>
+      </c>
+      <c r="E9" s="8" t="n">
+        <v>-0.0682</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>6773100</v>
+        <v>9266700</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="I9" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="n"/>
-      <c r="K9" s="2" t="n"/>
+        <v>31.82</v>
+      </c>
+      <c r="H9" t="n">
+        <v>42.78</v>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>0.211</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>0.217</v>
+      </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="7" t="inlineStr"/>
     </row>
@@ -896,28 +903,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="E10" s="10" t="n">
-        <v>0</v>
+        <v>4.75</v>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>-0.0166</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>6058000</v>
+        <v>9029700</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.24</v>
+        <v>0.48</v>
       </c>
       <c r="H10" t="n">
-        <v>75.19</v>
+        <v>49.91</v>
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
@@ -925,10 +932,10 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.616</v>
+        <v>4.732</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0.531</v>
+        <v>4.848</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="7" t="inlineStr"/>
@@ -941,39 +948,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>3891</t>
+          <t>0081</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MUIIND</t>
+          <t>REKATECH</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="E11" s="10" t="n">
-        <v>0</v>
+        <v>0.035</v>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>-0.2222</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>5898300</v>
+        <v>7785200</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>3.48</v>
+        <v>21.05</v>
       </c>
       <c r="H11" t="n">
-        <v>46.69</v>
-      </c>
-      <c r="I11" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.28</v>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.041</v>
+        <v>0.026</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0.042</v>
+        <v>0.023</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="7" t="inlineStr"/>
@@ -986,28 +993,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E12" s="10" t="n">
-        <v>0</v>
+        <v>0.44</v>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>-0.0222</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>5874500</v>
+        <v>7550600</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>1.89</v>
+        <v>0.21</v>
       </c>
       <c r="H12" t="n">
-        <v>49.08</v>
+        <v>37.57</v>
       </c>
       <c r="I12" s="9" t="inlineStr">
         <is>
@@ -1015,10 +1022,10 @@
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.295</v>
+        <v>0.478</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0.295</v>
+        <v>0.482</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="7" t="inlineStr"/>
@@ -1031,40 +1038,33 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>4251</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>IBHD</t>
+          <t>SLG</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0.235</v>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>0.0682</v>
+        <v>0.245</v>
+      </c>
+      <c r="E13" s="8" t="n">
+        <v>-0.02</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>4984100</v>
+        <v>6774700</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>17.11</v>
-      </c>
-      <c r="H13" t="n">
-        <v>71.83</v>
-      </c>
-      <c r="I13" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="n">
-        <v>0.214</v>
-      </c>
-      <c r="K13" s="2" t="n">
-        <v>0.217</v>
-      </c>
+        <v>0.27</v>
+      </c>
+      <c r="I13" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="n"/>
+      <c r="K13" s="2" t="n"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="7" t="inlineStr"/>
     </row>
@@ -1091,10 +1091,10 @@
         <v>0.0112</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>4604100</v>
+        <v>6299100</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.23</v>
+        <v>0.31</v>
       </c>
       <c r="H14" t="n">
         <v>60.13</v>
@@ -1121,28 +1121,28 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0.445</v>
-      </c>
-      <c r="E15" s="8" t="n">
-        <v>-0.0111</v>
+        <v>0.295</v>
+      </c>
+      <c r="E15" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>4602500</v>
+        <v>6072500</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.13</v>
+        <v>1.95</v>
       </c>
       <c r="H15" t="n">
-        <v>38.75</v>
+        <v>49.08</v>
       </c>
       <c r="I15" s="9" t="inlineStr">
         <is>
@@ -1150,10 +1150,10 @@
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.478</v>
+        <v>0.295</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0.482</v>
+        <v>0.295</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="7" t="inlineStr"/>
@@ -1166,39 +1166,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>3891</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>MUIIND</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="E16" s="8" t="n">
-        <v>-0.0347</v>
+        <v>0.04</v>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>3267500</v>
+        <v>5900400</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.11</v>
+        <v>3.48</v>
       </c>
       <c r="H16" t="n">
-        <v>54.64</v>
-      </c>
-      <c r="I16" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.69</v>
+      </c>
+      <c r="I16" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.923</v>
+        <v>0.041</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>1.739</v>
+        <v>0.042</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="7" t="inlineStr"/>
@@ -1211,39 +1211,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="E17" s="3" t="n">
-        <v>0.0091</v>
+        <v>1.94</v>
+      </c>
+      <c r="E17" s="8" t="n">
+        <v>-0.0396</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>3192300</v>
+        <v>4846100</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.33</v>
+        <v>0.17</v>
       </c>
       <c r="H17" t="n">
-        <v>55.57</v>
-      </c>
-      <c r="I17" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.02</v>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1.08</v>
+        <v>1.922</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>1.046</v>
+        <v>1.739</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="7" t="inlineStr"/>
@@ -1256,28 +1256,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>0.335</v>
-      </c>
-      <c r="E18" s="8" t="n">
-        <v>-0.0147</v>
+        <v>1.1</v>
+      </c>
+      <c r="E18" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>3057200</v>
+        <v>4105400</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.32</v>
+        <v>0.43</v>
       </c>
       <c r="H18" t="n">
-        <v>47.31</v>
+        <v>54.23</v>
       </c>
       <c r="I18" s="9" t="inlineStr">
         <is>
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.346</v>
+        <v>1.079</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0.334</v>
+        <v>1.045</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="7" t="inlineStr"/>
@@ -1301,39 +1301,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>2.34</v>
+        <v>0.43</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>0.0218</v>
+        <v>0.0238</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>2875100</v>
+        <v>3922900</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="H19" t="n">
-        <v>60.87</v>
-      </c>
-      <c r="I19" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.5</v>
+      </c>
+      <c r="I19" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>2.226</v>
+        <v>0.424</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>2.167</v>
+        <v>0.416</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="7" t="inlineStr"/>
@@ -1346,39 +1346,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0.525</v>
-      </c>
-      <c r="E20" s="8" t="n">
-        <v>-0.0187</v>
+        <v>0.31</v>
+      </c>
+      <c r="E20" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>2770400</v>
+        <v>3688400</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>1.12</v>
+        <v>0.19</v>
       </c>
       <c r="H20" t="n">
-        <v>36.53</v>
-      </c>
-      <c r="I20" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.55</v>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.544</v>
+        <v>0.309</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0.572</v>
+        <v>0.3</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="7" t="inlineStr"/>
@@ -1391,28 +1391,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>0.415</v>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>0.0247</v>
+        <v>2.56</v>
+      </c>
+      <c r="E21" s="8" t="n">
+        <v>-0.03759999999999999</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>2685200</v>
+        <v>3592300</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>1.38</v>
+        <v>0.2</v>
       </c>
       <c r="H21" t="n">
-        <v>45.72</v>
+        <v>46.31</v>
       </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
@@ -1420,10 +1420,10 @@
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.416</v>
+        <v>2.641</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0.434</v>
+        <v>2.553</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="7" t="inlineStr"/>
@@ -1436,33 +1436,40 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0477</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ECOSYS</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>0.775</v>
+        <v>0.535</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>-0.0127</v>
+        <v>-0.036</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>2641400</v>
+        <v>3520400</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="I22" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="n"/>
-      <c r="K22" s="2" t="n"/>
+        <v>0.17</v>
+      </c>
+      <c r="H22" t="n">
+        <v>44.62</v>
+      </c>
+      <c r="I22" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="n">
+        <v>0.572</v>
+      </c>
+      <c r="K22" s="2" t="n">
+        <v>0.541</v>
+      </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="7" t="inlineStr"/>
     </row>
@@ -1474,28 +1481,28 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="E23" s="8" t="n">
-        <v>-0.0556</v>
+        <v>2.37</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>0.0349</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>2599300</v>
+        <v>3481300</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.66</v>
+        <v>0.98</v>
       </c>
       <c r="H23" t="n">
-        <v>67.29000000000001</v>
+        <v>62.65</v>
       </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
@@ -1503,10 +1510,10 @@
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.843</v>
+        <v>2.229</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0.573</v>
+        <v>2.167</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="7" t="inlineStr"/>
@@ -1519,28 +1526,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>0.54</v>
+        <v>0.335</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>-0.027</v>
+        <v>-0.0147</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1969900</v>
+        <v>3327400</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.1</v>
+        <v>0.35</v>
       </c>
       <c r="H24" t="n">
-        <v>45.4</v>
+        <v>47.31</v>
       </c>
       <c r="I24" s="9" t="inlineStr">
         <is>
@@ -1548,10 +1555,10 @@
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.572</v>
+        <v>0.346</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0.541</v>
+        <v>0.334</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="7" t="inlineStr"/>
@@ -1564,40 +1571,33 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>0477</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>ECOSYS</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>2</v>
+        <v>0.775</v>
       </c>
       <c r="E25" s="8" t="n">
-        <v>-0.0148</v>
+        <v>-0.0127</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1956500</v>
+        <v>3171100</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="H25" t="n">
-        <v>31.84</v>
-      </c>
-      <c r="I25" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="n">
-        <v>2.146</v>
-      </c>
-      <c r="K25" s="2" t="n">
-        <v>2.233</v>
-      </c>
+        <v>0.04</v>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="n"/>
+      <c r="K25" s="2" t="n"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="7" t="inlineStr"/>
     </row>
@@ -1609,39 +1609,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>0.425</v>
-      </c>
-      <c r="E26" s="3" t="n">
-        <v>0.0119</v>
+        <v>1.19</v>
+      </c>
+      <c r="E26" s="8" t="n">
+        <v>-0.0325</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>1924900</v>
+        <v>3162100</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.28</v>
+        <v>0.42</v>
       </c>
       <c r="H26" t="n">
-        <v>51.3</v>
-      </c>
-      <c r="I26" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>38.78</v>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.424</v>
+        <v>1.235</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0.416</v>
+        <v>1.323</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="7" t="inlineStr"/>
@@ -1654,28 +1654,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E27" s="8" t="n">
-        <v>-0.0064</v>
+        <v>0.625</v>
+      </c>
+      <c r="E27" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>1875200</v>
+        <v>3081600</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.12</v>
+        <v>0.28</v>
       </c>
       <c r="H27" t="n">
-        <v>49.91</v>
+        <v>56.82</v>
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.775</v>
+        <v>0.617</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0.776</v>
+        <v>0.615</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="7" t="inlineStr"/>
@@ -1699,39 +1699,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="E28" s="3" t="n">
-        <v>0.0169</v>
+        <v>0.77</v>
+      </c>
+      <c r="E28" s="8" t="n">
+        <v>-0.0128</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>1860300</v>
+        <v>3059900</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="H28" t="n">
-        <v>54.72</v>
-      </c>
-      <c r="I28" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.74</v>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>1.172</v>
+        <v>0.775</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>1.137</v>
+        <v>0.776</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="7" t="inlineStr"/>
@@ -1744,39 +1744,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="E29" s="3" t="n">
-        <v>0.009899999999999999</v>
+        <v>0.375</v>
+      </c>
+      <c r="E29" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>1768200</v>
+        <v>2974600</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.22</v>
+        <v>0.4</v>
       </c>
       <c r="H29" t="n">
-        <v>47.53</v>
-      </c>
-      <c r="I29" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.92</v>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>1.052</v>
+        <v>0.371</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0.959</v>
+        <v>0.369</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="7" t="inlineStr"/>
@@ -1789,39 +1789,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>2.6</v>
+        <v>0.525</v>
       </c>
       <c r="E30" s="8" t="n">
-        <v>-0.0226</v>
+        <v>-0.0187</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>1752600</v>
+        <v>2921100</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.1</v>
+        <v>1.18</v>
       </c>
       <c r="H30" t="n">
-        <v>48.48</v>
-      </c>
-      <c r="I30" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.53</v>
+      </c>
+      <c r="I30" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>2.645</v>
+        <v>0.544</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>2.554</v>
+        <v>0.572</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="7" t="inlineStr"/>
@@ -1834,39 +1834,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E31" s="8" t="n">
-        <v>-0.007900000000000001</v>
+        <v>3.87</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>0.0403</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>1700000</v>
+        <v>2863300</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.76</v>
+        <v>0.3</v>
       </c>
       <c r="H31" t="n">
-        <v>47.67</v>
-      </c>
-      <c r="I31" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>59.43</v>
+      </c>
+      <c r="I31" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.637</v>
+        <v>3.655</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0.622</v>
+        <v>3.009</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="7" t="inlineStr"/>
@@ -1879,39 +1879,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="E32" s="3" t="n">
-        <v>0.0269</v>
+        <v>1.01</v>
+      </c>
+      <c r="E32" s="8" t="n">
+        <v>-0.06480000000000001</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>1687500</v>
+        <v>2829400</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.18</v>
+        <v>0.71</v>
       </c>
       <c r="H32" t="n">
-        <v>58.32</v>
-      </c>
-      <c r="I32" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.41</v>
+      </c>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>3.65</v>
+        <v>0.842</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>3.008</v>
+        <v>0.573</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="7" t="inlineStr"/>
@@ -1924,39 +1924,39 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>6.61</v>
+        <v>0.41</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>0.0169</v>
+        <v>0.0123</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>1667700</v>
+        <v>2700200</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.17</v>
+        <v>1.39</v>
       </c>
       <c r="H33" t="n">
-        <v>25.41</v>
-      </c>
-      <c r="I33" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>41.24</v>
+      </c>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>7.202</v>
+        <v>0.416</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>7.605</v>
+        <v>0.434</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="7" t="inlineStr"/>
@@ -1969,39 +1969,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E34" s="10" t="n">
-        <v>0</v>
+        <v>0.995</v>
+      </c>
+      <c r="E34" s="8" t="n">
+        <v>-0.0149</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>1614900</v>
+        <v>2640100</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.15</v>
+        <v>0.33</v>
       </c>
       <c r="H34" t="n">
-        <v>56.82</v>
-      </c>
-      <c r="I34" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.16</v>
+      </c>
+      <c r="I34" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.617</v>
+        <v>1.049</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0.615</v>
+        <v>0.959</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="7" t="inlineStr"/>
@@ -2014,28 +2014,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>0.835</v>
+        <v>2</v>
       </c>
       <c r="E35" s="8" t="n">
-        <v>-0.0457</v>
+        <v>-0.0148</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>1607900</v>
+        <v>2593400</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.52</v>
+        <v>0.2</v>
       </c>
       <c r="H35" t="n">
-        <v>28.22</v>
+        <v>31.84</v>
       </c>
       <c r="I35" s="9" t="inlineStr">
         <is>
@@ -2043,10 +2043,10 @@
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.897</v>
+        <v>2.146</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0.953</v>
+        <v>2.233</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="7" t="inlineStr"/>
@@ -2059,28 +2059,28 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>VELESTO</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="E36" s="3" t="n">
-        <v>0.0345</v>
+        <v>0.26</v>
+      </c>
+      <c r="E36" s="8" t="n">
+        <v>-0.0189</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>1412500</v>
+        <v>2439800</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.06</v>
+        <v>0.34</v>
       </c>
       <c r="H36" t="n">
-        <v>42.77</v>
+        <v>42.45</v>
       </c>
       <c r="I36" s="9" t="inlineStr">
         <is>
@@ -2088,10 +2088,10 @@
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.218</v>
+        <v>0.273</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0.235</v>
+        <v>0.294</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="7" t="inlineStr"/>
@@ -2104,39 +2104,39 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="E37" s="8" t="n">
-        <v>-0.0238</v>
+        <v>1.28</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>0.007900000000000001</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>1382800</v>
+        <v>2356600</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.14</v>
+        <v>0.38</v>
       </c>
       <c r="H37" t="n">
-        <v>42.4</v>
-      </c>
-      <c r="I37" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.51</v>
+      </c>
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.438</v>
+        <v>1.198</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0.434</v>
+        <v>1.188</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="7" t="inlineStr"/>
@@ -2149,28 +2149,28 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>0.745</v>
-      </c>
-      <c r="E38" s="3" t="n">
-        <v>0.0136</v>
+        <v>5.11</v>
+      </c>
+      <c r="E38" s="8" t="n">
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>1359900</v>
+        <v>2350200</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="H38" t="n">
-        <v>42.4</v>
+        <v>34.12</v>
       </c>
       <c r="I38" s="9" t="inlineStr">
         <is>
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.769</v>
+        <v>5.494</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0.771</v>
+        <v>5.448</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="7" t="inlineStr"/>
@@ -2194,39 +2194,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="E39" s="10" t="n">
-        <v>0</v>
+        <v>1.19</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>0.008500000000000001</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>1317700</v>
+        <v>2274700</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.23</v>
+        <v>0.32</v>
       </c>
       <c r="H39" t="n">
-        <v>65.06</v>
-      </c>
-      <c r="I39" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.56</v>
+      </c>
+      <c r="I39" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.924</v>
+        <v>1.171</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0.877</v>
+        <v>1.137</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="7" t="inlineStr"/>
@@ -2239,28 +2239,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>0.575</v>
-      </c>
-      <c r="E40" s="8" t="n">
-        <v>-0.0336</v>
+        <v>6.65</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>0.0231</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>1295300</v>
+        <v>2183300</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.14</v>
+        <v>0.23</v>
       </c>
       <c r="H40" t="n">
-        <v>37.01</v>
+        <v>27.34</v>
       </c>
       <c r="I40" s="9" t="inlineStr">
         <is>
@@ -2268,10 +2268,10 @@
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.648</v>
+        <v>7.206</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0.62</v>
+        <v>7.606</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="7" t="inlineStr"/>
@@ -2284,28 +2284,28 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>5.07</v>
+        <v>1.43</v>
       </c>
       <c r="E41" s="8" t="n">
-        <v>-0.0155</v>
+        <v>-0.0138</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>1276000</v>
+        <v>2172400</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.09</v>
+        <v>0.19</v>
       </c>
       <c r="H41" t="n">
-        <v>33.09</v>
+        <v>21.76</v>
       </c>
       <c r="I41" s="9" t="inlineStr">
         <is>
@@ -2313,10 +2313,10 @@
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>5.49</v>
+        <v>1.692</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>5.447</v>
+        <v>1.945</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="7" t="inlineStr"/>
@@ -2329,39 +2329,39 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>0.445</v>
+        <v>1.65</v>
       </c>
       <c r="E42" s="8" t="n">
-        <v>-0.022</v>
+        <v>-0.012</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>1267800</v>
+        <v>2120700</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.05</v>
+        <v>0.31</v>
       </c>
       <c r="H42" t="n">
-        <v>26.49</v>
-      </c>
-      <c r="I42" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.49</v>
+      </c>
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.506</v>
+        <v>1.627</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0.677</v>
+        <v>1.695</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="7" t="inlineStr"/>
@@ -2374,28 +2374,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>0.455</v>
+        <v>0.84</v>
       </c>
       <c r="E43" s="8" t="n">
-        <v>-0.0215</v>
+        <v>-0.04</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>1264500</v>
+        <v>2092400</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.17</v>
+        <v>0.68</v>
       </c>
       <c r="H43" t="n">
-        <v>28.78</v>
+        <v>29.06</v>
       </c>
       <c r="I43" s="9" t="inlineStr">
         <is>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.498</v>
+        <v>0.897</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0.556</v>
+        <v>0.953</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="7" t="inlineStr"/>
@@ -2419,28 +2419,28 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>0.26</v>
+        <v>1.61</v>
       </c>
       <c r="E44" s="8" t="n">
-        <v>-0.0189</v>
+        <v>-0.0359</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>1250200</v>
+        <v>1981000</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.17</v>
+        <v>0.41</v>
       </c>
       <c r="H44" t="n">
-        <v>42.45</v>
+        <v>33.56</v>
       </c>
       <c r="I44" s="9" t="inlineStr">
         <is>
@@ -2448,10 +2448,10 @@
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.273</v>
+        <v>1.722</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0.294</v>
+        <v>1.767</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="7" t="inlineStr"/>
@@ -2464,28 +2464,28 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>5932</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>BPURI</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>0.21</v>
+        <v>0.575</v>
       </c>
       <c r="E45" s="8" t="n">
-        <v>-0.0233</v>
+        <v>-0.0336</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>1233100</v>
+        <v>1977600</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>1.8</v>
+        <v>0.22</v>
       </c>
       <c r="H45" t="n">
-        <v>38.22</v>
+        <v>37.01</v>
       </c>
       <c r="I45" s="9" t="inlineStr">
         <is>
@@ -2493,10 +2493,10 @@
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.223</v>
+        <v>0.648</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0.232</v>
+        <v>0.62</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="7" t="inlineStr"/>
@@ -2509,28 +2509,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>1.44</v>
+        <v>7.15</v>
       </c>
       <c r="E46" s="8" t="n">
         <v>-0.0069</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>1174600</v>
+        <v>1964900</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="H46" t="n">
-        <v>22.12</v>
+        <v>32.9</v>
       </c>
       <c r="I46" s="9" t="inlineStr">
         <is>
@@ -2538,10 +2538,10 @@
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>1.693</v>
+        <v>7.505</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>1.945</v>
+        <v>7.684</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="7" t="inlineStr"/>
@@ -2554,28 +2554,28 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0469</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>GTA</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>0.245</v>
+        <v>0.455</v>
       </c>
       <c r="E47" s="8" t="n">
-        <v>-0.02</v>
+        <v>-0.0215</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>1120300</v>
+        <v>1952500</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.31</v>
+        <v>0.26</v>
       </c>
       <c r="H47" t="n">
-        <v>16.72</v>
+        <v>28.78</v>
       </c>
       <c r="I47" s="9" t="inlineStr">
         <is>
@@ -2583,9 +2583,11 @@
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.272</v>
-      </c>
-      <c r="K47" s="2" t="n"/>
+        <v>0.498</v>
+      </c>
+      <c r="K47" s="2" t="n">
+        <v>0.556</v>
+      </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="7" t="inlineStr"/>
     </row>
@@ -2597,28 +2599,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>0.415</v>
+        <v>0.545</v>
       </c>
       <c r="E48" s="8" t="n">
-        <v>-0.0235</v>
+        <v>-0.04389999999999999</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>1114900</v>
+        <v>1928900</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.14</v>
+        <v>0.37</v>
       </c>
       <c r="H48" t="n">
-        <v>23.04</v>
+        <v>48.83</v>
       </c>
       <c r="I48" s="9" t="inlineStr">
         <is>
@@ -2626,10 +2628,10 @@
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.527</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0.614</v>
+        <v>0.516</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="7" t="inlineStr"/>
@@ -2642,28 +2644,28 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>0.515</v>
+        <v>0.445</v>
       </c>
       <c r="E49" s="8" t="n">
-        <v>-0.019</v>
+        <v>-0.022</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>1070600</v>
+        <v>1720000</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H49" t="n">
-        <v>51.37</v>
+        <v>26.49</v>
       </c>
       <c r="I49" s="9" t="inlineStr">
         <is>
@@ -2671,10 +2673,10 @@
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.52</v>
+        <v>0.506</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0.461</v>
+        <v>0.677</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="7" t="inlineStr"/>
@@ -2696,19 +2698,19 @@
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>0.355</v>
+        <v>0.36</v>
       </c>
       <c r="E50" s="8" t="n">
-        <v>-0.0274</v>
+        <v>-0.0137</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>1065900</v>
+        <v>1711900</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.18</v>
+        <v>0.3</v>
       </c>
       <c r="H50" t="n">
-        <v>60.83</v>
+        <v>62.55</v>
       </c>
       <c r="I50" s="6" t="inlineStr">
         <is>
@@ -2716,7 +2718,7 @@
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.318</v>
+        <v>0.319</v>
       </c>
       <c r="K50" s="2" t="n"/>
       <c r="L50" t="inlineStr"/>
@@ -2730,39 +2732,39 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>0.55</v>
+        <v>0.63</v>
       </c>
       <c r="E51" s="8" t="n">
-        <v>-0.0351</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>1046200</v>
+        <v>1705700</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.2</v>
+        <v>0.76</v>
       </c>
       <c r="H51" t="n">
-        <v>49.98</v>
-      </c>
-      <c r="I51" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.67</v>
+      </c>
+      <c r="I51" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.637</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0.516</v>
+        <v>0.622</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="7" t="inlineStr"/>
@@ -2775,28 +2777,28 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0450</t>
+          <t>0395</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>MFGROUP</t>
+          <t>OGX</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="E52" s="8" t="n">
-        <v>-0.0175</v>
+        <v>0.47</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>0.033</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>1006700</v>
+        <v>1667900</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>1.06</v>
+        <v>0.64</v>
       </c>
       <c r="H52" t="n">
-        <v>55.75</v>
+        <v>57.98</v>
       </c>
       <c r="I52" s="6" t="inlineStr">
         <is>
@@ -2804,10 +2806,10 @@
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.276</v>
+        <v>0.447</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0.267</v>
+        <v>0.45</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="7" t="inlineStr"/>
@@ -2820,28 +2822,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>1.29</v>
+        <v>4.72</v>
       </c>
       <c r="E53" s="8" t="n">
-        <v>-0.0301</v>
+        <v>-0.0167</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>998800</v>
+        <v>1664500</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.42</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H53" t="n">
-        <v>55.19</v>
+        <v>42.05</v>
       </c>
       <c r="I53" s="9" t="inlineStr">
         <is>
@@ -2849,10 +2851,10 @@
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>1.259</v>
+        <v>4.891</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>1.173</v>
+        <v>4.727</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="7" t="inlineStr"/>
@@ -2865,39 +2867,39 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E54" s="10" t="n">
-        <v>0</v>
+        <v>2.64</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>0.0038</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>992500</v>
+        <v>1640400</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.06</v>
+        <v>0.13</v>
       </c>
       <c r="H54" t="n">
-        <v>57.16</v>
-      </c>
-      <c r="I54" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.49</v>
+      </c>
+      <c r="I54" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.8139999999999999</v>
+        <v>2.758</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0.8110000000000001</v>
+        <v>2.738</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="7" t="inlineStr"/>
@@ -2910,39 +2912,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>0.585</v>
-      </c>
-      <c r="E55" s="10" t="n">
-        <v>0</v>
+        <v>0.41</v>
+      </c>
+      <c r="E55" s="8" t="n">
+        <v>-0.0238</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>875800</v>
+        <v>1598600</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.21</v>
+        <v>0.17</v>
       </c>
       <c r="H55" t="n">
-        <v>68.69</v>
-      </c>
-      <c r="I55" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.4</v>
+      </c>
+      <c r="I55" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.509</v>
+        <v>0.438</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0.468</v>
+        <v>0.434</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="7" t="inlineStr"/>
@@ -2955,39 +2957,39 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="E56" s="10" t="n">
-        <v>0</v>
+        <v>0.89</v>
+      </c>
+      <c r="E56" s="8" t="n">
+        <v>-0.0326</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>822000</v>
+        <v>1594600</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.27</v>
+        <v>0.96</v>
       </c>
       <c r="H56" t="n">
-        <v>82.09</v>
-      </c>
-      <c r="I56" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.65</v>
+      </c>
+      <c r="I56" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>2.827</v>
+        <v>0.913</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>2.43</v>
+        <v>0.874</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="7" t="inlineStr"/>
@@ -3000,28 +3002,28 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>0.735</v>
+        <v>0.515</v>
       </c>
       <c r="E57" s="8" t="n">
-        <v>-0.0329</v>
+        <v>-0.019</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>807300</v>
+        <v>1546400</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
       <c r="H57" t="n">
-        <v>48.09</v>
+        <v>51.37</v>
       </c>
       <c r="I57" s="9" t="inlineStr">
         <is>
@@ -3029,10 +3031,10 @@
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.761</v>
+        <v>0.52</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.461</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="7" t="inlineStr"/>
@@ -3045,28 +3047,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E58" s="8" t="n">
-        <v>-0.0155</v>
+        <v>0.74</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>0.0068</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>755200</v>
+        <v>1545900</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.08</v>
+        <v>0.19</v>
       </c>
       <c r="H58" t="n">
-        <v>40.95</v>
+        <v>40.73</v>
       </c>
       <c r="I58" s="9" t="inlineStr">
         <is>
@@ -3074,10 +3076,10 @@
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.678</v>
+        <v>0.769</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.771</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="7" t="inlineStr"/>
@@ -3090,28 +3092,28 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="E59" s="8" t="n">
-        <v>-0.0236</v>
+        <v>0.205</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>0.009899999999999999</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>741100</v>
+        <v>1543100</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.18</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H59" t="n">
-        <v>24.69</v>
+        <v>39.23</v>
       </c>
       <c r="I59" s="9" t="inlineStr">
         <is>
@@ -3119,10 +3121,10 @@
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>1.394</v>
+        <v>0.218</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>1.561</v>
+        <v>0.235</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="7" t="inlineStr"/>
@@ -3135,28 +3137,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>1.08</v>
+        <v>0.4</v>
       </c>
       <c r="E60" s="8" t="n">
-        <v>-0.027</v>
+        <v>-0.0123</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>724400</v>
+        <v>1477800</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.17</v>
+        <v>0.12</v>
       </c>
       <c r="H60" t="n">
-        <v>55.63</v>
+        <v>53.56</v>
       </c>
       <c r="I60" s="9" t="inlineStr">
         <is>
@@ -3164,10 +3166,10 @@
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>1.052</v>
+        <v>0.391</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>0.913</v>
+        <v>0.378</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="7" t="inlineStr"/>
@@ -3180,39 +3182,39 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>1.16</v>
+        <v>0.96</v>
       </c>
       <c r="E61" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>720100</v>
+        <v>1416200</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.17</v>
+        <v>0.25</v>
       </c>
       <c r="H61" t="n">
-        <v>52.61</v>
-      </c>
-      <c r="I61" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.06</v>
+      </c>
+      <c r="I61" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>1.16</v>
+        <v>0.924</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>1.1</v>
+        <v>0.877</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="7" t="inlineStr"/>
@@ -3225,28 +3227,28 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>2.6</v>
+        <v>1.29</v>
       </c>
       <c r="E62" s="8" t="n">
-        <v>-0.0114</v>
+        <v>-0.0301</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>683200</v>
+        <v>1366800</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.05</v>
+        <v>0.57</v>
       </c>
       <c r="H62" t="n">
-        <v>37.72</v>
+        <v>55.19</v>
       </c>
       <c r="I62" s="9" t="inlineStr">
         <is>
@@ -3254,10 +3256,10 @@
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>2.754</v>
+        <v>1.259</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>2.737</v>
+        <v>1.173</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="7" t="inlineStr"/>
@@ -3270,39 +3272,39 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>5932</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>BPURI</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>0.67</v>
+        <v>0.21</v>
       </c>
       <c r="E63" s="8" t="n">
-        <v>-0.0219</v>
+        <v>-0.0233</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>679800</v>
+        <v>1297400</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.25</v>
+        <v>1.89</v>
       </c>
       <c r="H63" t="n">
-        <v>59.56</v>
-      </c>
-      <c r="I63" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.22</v>
+      </c>
+      <c r="I63" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.647</v>
+        <v>0.223</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.232</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="7" t="inlineStr"/>
@@ -3315,39 +3317,39 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>0.88</v>
+        <v>0.86</v>
       </c>
       <c r="E64" s="8" t="n">
-        <v>-0.0168</v>
+        <v>-0.0058</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>679100</v>
+        <v>1260700</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="H64" t="n">
-        <v>44.55</v>
-      </c>
-      <c r="I64" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>40.62</v>
+      </c>
+      <c r="I64" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.929</v>
+        <v>0.868</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>0.847</v>
+        <v>0.869</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="7" t="inlineStr"/>
@@ -3360,28 +3362,28 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>8524</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>TALIWRK</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="E65" s="8" t="n">
-        <v>-0.0104</v>
+        <v>0.23</v>
+      </c>
+      <c r="E65" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>673400</v>
+        <v>1235600</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0.03</v>
+        <v>0.62</v>
       </c>
       <c r="H65" t="n">
-        <v>43.41</v>
+        <v>37.06</v>
       </c>
       <c r="I65" s="9" t="inlineStr">
         <is>
@@ -3389,10 +3391,10 @@
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>4.894</v>
+        <v>0.244</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>4.727</v>
+        <v>0.256</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="7" t="inlineStr"/>
@@ -3405,28 +3407,28 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="E66" s="3" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.335</v>
+      </c>
+      <c r="E66" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>613200</v>
+        <v>1217900</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>0.1</v>
+        <v>0.26</v>
       </c>
       <c r="H66" t="n">
-        <v>62.51</v>
+        <v>47.09</v>
       </c>
       <c r="I66" s="6" t="inlineStr">
         <is>
@@ -3434,10 +3436,10 @@
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>1.198</v>
+        <v>0.335</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>1.188</v>
+        <v>0.343</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="7" t="inlineStr"/>
@@ -3450,28 +3452,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>0469</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>GTA</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>7.21</v>
-      </c>
-      <c r="E67" s="3" t="n">
-        <v>0.0014</v>
+        <v>0.245</v>
+      </c>
+      <c r="E67" s="8" t="n">
+        <v>-0.02</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>611100</v>
+        <v>1216100</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>0.04</v>
+        <v>0.34</v>
       </c>
       <c r="H67" t="n">
-        <v>34.8</v>
+        <v>16.72</v>
       </c>
       <c r="I67" s="9" t="inlineStr">
         <is>
@@ -3479,11 +3481,9 @@
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>7.51</v>
-      </c>
-      <c r="K67" s="2" t="n">
-        <v>7.685</v>
-      </c>
+        <v>0.272</v>
+      </c>
+      <c r="K67" s="2" t="n"/>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="7" t="inlineStr"/>
     </row>
@@ -3495,28 +3495,28 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="E68" s="10" t="n">
-        <v>0</v>
+        <v>0.415</v>
+      </c>
+      <c r="E68" s="8" t="n">
+        <v>-0.0235</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>610200</v>
+        <v>1191300</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="H68" t="n">
-        <v>49.06</v>
+        <v>23.04</v>
       </c>
       <c r="I68" s="9" t="inlineStr">
         <is>
@@ -3524,10 +3524,10 @@
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.598</v>
+        <v>0.527</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0.586</v>
+        <v>0.614</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="7" t="inlineStr"/>
@@ -3540,39 +3540,39 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>0.845</v>
-      </c>
-      <c r="E69" s="8" t="n">
-        <v>-0.0059</v>
+        <v>0.82</v>
+      </c>
+      <c r="E69" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>604700</v>
+        <v>1162500</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>0.17</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H69" t="n">
-        <v>55.12</v>
-      </c>
-      <c r="I69" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.16</v>
+      </c>
+      <c r="I69" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.828</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0.782</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="7" t="inlineStr"/>
@@ -3585,28 +3585,28 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="E70" s="8" t="n">
-        <v>-0.0095</v>
+        <v>3.09</v>
+      </c>
+      <c r="E70" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>507500</v>
+        <v>1141700</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>0.03</v>
+        <v>0.37</v>
       </c>
       <c r="H70" t="n">
-        <v>45.7</v>
+        <v>82.09</v>
       </c>
       <c r="I70" s="6" t="inlineStr">
         <is>
@@ -3614,16 +3614,1366 @@
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>2.107</v>
+        <v>2.827</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>2.101</v>
+        <v>2.43</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="7" t="inlineStr"/>
     </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>0368</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>OXB</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="E71" s="8" t="n">
+        <v>-0.008500000000000001</v>
+      </c>
+      <c r="F71" s="4" t="n">
+        <v>1119800</v>
+      </c>
+      <c r="G71" s="5" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H71" t="n">
+        <v>67.36</v>
+      </c>
+      <c r="I71" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="n">
+        <v>0.509</v>
+      </c>
+      <c r="K71" s="2" t="n">
+        <v>0.468</v>
+      </c>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" s="7" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>5271</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>PECCA</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="E72" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" s="4" t="n">
+        <v>1113100</v>
+      </c>
+      <c r="G72" s="5" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H72" t="n">
+        <v>43.62</v>
+      </c>
+      <c r="I72" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="n">
+        <v>1.367</v>
+      </c>
+      <c r="K72" s="2" t="n">
+        <v>1.343</v>
+      </c>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" s="7" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>5249</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>IOIPG</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="F73" s="4" t="n">
+        <v>1108700</v>
+      </c>
+      <c r="G73" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H73" t="n">
+        <v>39.03</v>
+      </c>
+      <c r="I73" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="n">
+        <v>3.373</v>
+      </c>
+      <c r="K73" s="2" t="n">
+        <v>3.604</v>
+      </c>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" s="7" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>0459</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>SUM</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="n">
+        <v>0.735</v>
+      </c>
+      <c r="E74" s="8" t="n">
+        <v>-0.0329</v>
+      </c>
+      <c r="F74" s="4" t="n">
+        <v>1072600</v>
+      </c>
+      <c r="G74" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H74" t="n">
+        <v>48.09</v>
+      </c>
+      <c r="I74" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="n">
+        <v>0.761</v>
+      </c>
+      <c r="K74" s="2" t="n">
+        <v>0.6850000000000001</v>
+      </c>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" s="7" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>0275</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>OPPSTAR</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="E75" s="8" t="n">
+        <v>-0.0155</v>
+      </c>
+      <c r="F75" s="4" t="n">
+        <v>1012300</v>
+      </c>
+      <c r="G75" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H75" t="n">
+        <v>40.95</v>
+      </c>
+      <c r="I75" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="n">
+        <v>0.678</v>
+      </c>
+      <c r="K75" s="2" t="n">
+        <v>0.6889999999999999</v>
+      </c>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" s="7" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>0450</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>MFGROUP</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="E76" s="8" t="n">
+        <v>-0.0175</v>
+      </c>
+      <c r="F76" s="4" t="n">
+        <v>1006700</v>
+      </c>
+      <c r="G76" s="5" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="H76" t="n">
+        <v>55.75</v>
+      </c>
+      <c r="I76" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="n">
+        <v>0.276</v>
+      </c>
+      <c r="K76" s="2" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" s="7" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>0246</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>CNERGEN</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="E77" s="8" t="n">
+        <v>-0.027</v>
+      </c>
+      <c r="F77" s="4" t="n">
+        <v>969000</v>
+      </c>
+      <c r="G77" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H77" t="n">
+        <v>55.63</v>
+      </c>
+      <c r="I77" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="n">
+        <v>1.052</v>
+      </c>
+      <c r="K77" s="2" t="n">
+        <v>0.913</v>
+      </c>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" s="7" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>5285</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>SDG</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>0.0105</v>
+      </c>
+      <c r="F78" s="4" t="n">
+        <v>967900</v>
+      </c>
+      <c r="G78" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H78" t="n">
+        <v>31.42</v>
+      </c>
+      <c r="I78" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="n">
+        <v>6.024</v>
+      </c>
+      <c r="K78" s="2" t="n">
+        <v>6.309</v>
+      </c>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" s="7" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>0453</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>EIPOWER</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="E79" s="8" t="n">
+        <v>-0.0223</v>
+      </c>
+      <c r="F79" s="4" t="n">
+        <v>967500</v>
+      </c>
+      <c r="G79" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H79" t="n">
+        <v>43.95</v>
+      </c>
+      <c r="I79" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="n">
+        <v>0.928</v>
+      </c>
+      <c r="K79" s="2" t="n">
+        <v>0.847</v>
+      </c>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" s="7" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>0120</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>VIS</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="E80" s="8" t="n">
+        <v>-0.05690000000000001</v>
+      </c>
+      <c r="F80" s="4" t="n">
+        <v>957900</v>
+      </c>
+      <c r="G80" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H80" t="n">
+        <v>55.18</v>
+      </c>
+      <c r="I80" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="n">
+        <v>0.5679999999999999</v>
+      </c>
+      <c r="K80" s="2" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" s="7" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>0208</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>GREATEC</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="E81" s="8" t="n">
+        <v>-0.0273</v>
+      </c>
+      <c r="F81" s="4" t="n">
+        <v>952000</v>
+      </c>
+      <c r="G81" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H81" t="n">
+        <v>41.03</v>
+      </c>
+      <c r="I81" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="n">
+        <v>2.603</v>
+      </c>
+      <c r="K81" s="2" t="n">
+        <v>2.607</v>
+      </c>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" s="7" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>5555</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>SUNMED</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E82" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" s="4" t="n">
+        <v>950400</v>
+      </c>
+      <c r="G82" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H82" t="n">
+        <v>48.93</v>
+      </c>
+      <c r="I82" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="n">
+        <v>2.109</v>
+      </c>
+      <c r="K82" s="2" t="n">
+        <v>2.102</v>
+      </c>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" s="7" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>5183</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>PCHEM</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>0.0278</v>
+      </c>
+      <c r="F83" s="4" t="n">
+        <v>947400</v>
+      </c>
+      <c r="G83" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H83" t="n">
+        <v>52.29</v>
+      </c>
+      <c r="I83" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="K83" s="2" t="n">
+        <v>4.431</v>
+      </c>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" s="7" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>7579</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>AWC</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="E84" s="8" t="n">
+        <v>-0.0219</v>
+      </c>
+      <c r="F84" s="4" t="n">
+        <v>935000</v>
+      </c>
+      <c r="G84" s="5" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H84" t="n">
+        <v>59.56</v>
+      </c>
+      <c r="I84" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="n">
+        <v>0.647</v>
+      </c>
+      <c r="K84" s="2" t="n">
+        <v>0.5570000000000001</v>
+      </c>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" s="7" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>4715</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>GENM</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="E85" s="8" t="n">
+        <v>-0.0236</v>
+      </c>
+      <c r="F85" s="4" t="n">
+        <v>933300</v>
+      </c>
+      <c r="G85" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H85" t="n">
+        <v>24.69</v>
+      </c>
+      <c r="I85" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="n">
+        <v>1.394</v>
+      </c>
+      <c r="K85" s="2" t="n">
+        <v>1.561</v>
+      </c>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" s="7" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>0196</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>QES</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="E86" s="3" t="n">
+        <v>0.008500000000000001</v>
+      </c>
+      <c r="F86" s="4" t="n">
+        <v>895800</v>
+      </c>
+      <c r="G86" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H86" t="n">
+        <v>50.22</v>
+      </c>
+      <c r="I86" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="n">
+        <v>0.598</v>
+      </c>
+      <c r="K86" s="2" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" s="7" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>0146</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>JFTECH</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E87" s="8" t="n">
+        <v>-0.0323</v>
+      </c>
+      <c r="F87" s="4" t="n">
+        <v>852200</v>
+      </c>
+      <c r="G87" s="5" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H87" t="n">
+        <v>53.86</v>
+      </c>
+      <c r="I87" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="n">
+        <v>0.734</v>
+      </c>
+      <c r="K87" s="2" t="n">
+        <v>0.704</v>
+      </c>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" s="7" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>5102</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>GCB</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="E88" s="8" t="n">
+        <v>-0.016</v>
+      </c>
+      <c r="F88" s="4" t="n">
+        <v>831700</v>
+      </c>
+      <c r="G88" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H88" t="n">
+        <v>38.86</v>
+      </c>
+      <c r="I88" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="n">
+        <v>1.296</v>
+      </c>
+      <c r="K88" s="2" t="n">
+        <v>1.314</v>
+      </c>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" s="7" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>0321</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>SDCG</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="n">
+        <v>0.805</v>
+      </c>
+      <c r="E89" s="3" t="n">
+        <v>0.0126</v>
+      </c>
+      <c r="F89" s="4" t="n">
+        <v>820800</v>
+      </c>
+      <c r="G89" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H89" t="n">
+        <v>60.98</v>
+      </c>
+      <c r="I89" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="n">
+        <v>0.792</v>
+      </c>
+      <c r="K89" s="2" t="n">
+        <v>0.771</v>
+      </c>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" s="7" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>0390</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>ISF</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="n">
+        <v>0.835</v>
+      </c>
+      <c r="E90" s="8" t="n">
+        <v>-0.0176</v>
+      </c>
+      <c r="F90" s="4" t="n">
+        <v>751000</v>
+      </c>
+      <c r="G90" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H90" t="n">
+        <v>53.24</v>
+      </c>
+      <c r="I90" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="n">
+        <v>0.827</v>
+      </c>
+      <c r="K90" s="2" t="n">
+        <v>0.781</v>
+      </c>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" s="7" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>0217</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>PWRWELL</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="E91" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" s="4" t="n">
+        <v>727100</v>
+      </c>
+      <c r="G91" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H91" t="n">
+        <v>52.61</v>
+      </c>
+      <c r="I91" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="K91" s="2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" s="7" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>0045</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>SSB8</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="E92" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" s="4" t="n">
+        <v>664700</v>
+      </c>
+      <c r="G92" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H92" t="n">
+        <v>50.64</v>
+      </c>
+      <c r="I92" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="n">
+        <v>0.639</v>
+      </c>
+      <c r="K92" s="2" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" s="7" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>5248</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>BAUTO</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="E93" s="3" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="F93" s="4" t="n">
+        <v>661400</v>
+      </c>
+      <c r="G93" s="5" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="H93" t="n">
+        <v>49.48</v>
+      </c>
+      <c r="I93" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="n">
+        <v>0.892</v>
+      </c>
+      <c r="K93" s="2" t="n">
+        <v>0.908</v>
+      </c>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" s="7" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>5356</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>STRATUS</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E94" s="8" t="n">
+        <v>-0.0234</v>
+      </c>
+      <c r="F94" s="4" t="n">
+        <v>640000</v>
+      </c>
+      <c r="G94" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H94" t="n">
+        <v>32.79</v>
+      </c>
+      <c r="I94" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="n">
+        <v>2.808</v>
+      </c>
+      <c r="K94" s="2" t="n">
+        <v>2.877</v>
+      </c>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" s="7" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>1155</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>MAYBANK</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="n">
+        <v>9.949999999999999</v>
+      </c>
+      <c r="E95" s="8" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="F95" s="4" t="n">
+        <v>605100</v>
+      </c>
+      <c r="G95" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H95" t="n">
+        <v>44.09</v>
+      </c>
+      <c r="I95" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="n">
+        <v>10.006</v>
+      </c>
+      <c r="K95" s="2" t="n">
+        <v>10.149</v>
+      </c>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" s="7" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2852</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>CMSB</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E96" s="3" t="n">
+        <v>0.0059</v>
+      </c>
+      <c r="F96" s="4" t="n">
+        <v>602400</v>
+      </c>
+      <c r="G96" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H96" t="n">
+        <v>20.04</v>
+      </c>
+      <c r="I96" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="n">
+        <v>0.916</v>
+      </c>
+      <c r="K96" s="2" t="n">
+        <v>0.973</v>
+      </c>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" s="7" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>5292</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>UWC</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="n">
+        <v>7.16</v>
+      </c>
+      <c r="E97" s="8" t="n">
+        <v>-0.0192</v>
+      </c>
+      <c r="F97" s="4" t="n">
+        <v>596000</v>
+      </c>
+      <c r="G97" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H97" t="n">
+        <v>48.38</v>
+      </c>
+      <c r="I97" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="n">
+        <v>7.338</v>
+      </c>
+      <c r="K97" s="2" t="n">
+        <v>6.895</v>
+      </c>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" s="7" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>5357</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>SKYECHIP</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="E98" s="8" t="n">
+        <v>-0.0107</v>
+      </c>
+      <c r="F98" s="4" t="n">
+        <v>592600</v>
+      </c>
+      <c r="G98" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H98" t="n">
+        <v>39.95</v>
+      </c>
+      <c r="I98" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="n">
+        <v>2.896</v>
+      </c>
+      <c r="K98" s="2" t="n">
+        <v>3.013</v>
+      </c>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" s="7" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>5317</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>CPETECH</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="E99" s="8" t="n">
+        <v>-0.0227</v>
+      </c>
+      <c r="F99" s="4" t="n">
+        <v>524600</v>
+      </c>
+      <c r="G99" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H99" t="n">
+        <v>51.29</v>
+      </c>
+      <c r="I99" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="n">
+        <v>1.289</v>
+      </c>
+      <c r="K99" s="2" t="n">
+        <v>1.226</v>
+      </c>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" s="7" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>7277</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>DIALOG</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="E100" s="3" t="n">
+        <v>0.0321</v>
+      </c>
+      <c r="F100" s="4" t="n">
+        <v>512800</v>
+      </c>
+      <c r="G100" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H100" t="n">
+        <v>50</v>
+      </c>
+      <c r="I100" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="n">
+        <v>1.923</v>
+      </c>
+      <c r="K100" s="2" t="n">
+        <v>1.951</v>
+      </c>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M70"/>
+  <autoFilter ref="A1:M100"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-19/bursa-report-2026-10-19.xlsx
+++ b/docs/downloads/2026-10-19/bursa-report-2026-10-19.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-19" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-19'!$A$1:$M$100</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-19'!$A$1:$M$123</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M100"/>
+  <dimension ref="A1:M123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -552,19 +552,19 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.915</v>
+        <v>0.905</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0.0167</v>
+        <v>0.005600000000000001</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>31591100</v>
+        <v>35545600</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.47</v>
+        <v>0.52</v>
       </c>
       <c r="H2" t="n">
-        <v>67.87</v>
+        <v>66.83</v>
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.83</v>
+        <v>0.829</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0.737</v>
+        <v>0.736</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" s="7" t="inlineStr"/>
@@ -603,10 +603,10 @@
         <v>-0.0441</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>27017700</v>
+        <v>34723300</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
       <c r="H3" t="n">
         <v>61.81</v>
@@ -633,28 +633,28 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>0138</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>ZETRIX</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.13</v>
+        <v>0.05</v>
       </c>
       <c r="E4" s="8" t="n">
-        <v>-0.1034</v>
+        <v>-0.09089999999999999</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>24671900</v>
+        <v>34002400</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.36</v>
+        <v>0.09</v>
       </c>
       <c r="H4" t="n">
-        <v>38.6</v>
+        <v>22.63</v>
       </c>
       <c r="I4" s="9" t="inlineStr">
         <is>
@@ -662,10 +662,10 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.158</v>
+        <v>0.123</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.139</v>
+        <v>0.322</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" s="7" t="inlineStr"/>
@@ -678,28 +678,28 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0138</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ZETRIX</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.05</v>
+        <v>0.135</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>-0.09089999999999999</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>15008400</v>
+        <v>25869200</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.04</v>
+        <v>0.38</v>
       </c>
       <c r="H5" t="n">
-        <v>22.63</v>
+        <v>40.3</v>
       </c>
       <c r="I5" s="9" t="inlineStr">
         <is>
@@ -707,10 +707,10 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.123</v>
+        <v>0.158</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.322</v>
+        <v>0.139</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="7" t="inlineStr"/>
@@ -723,28 +723,28 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="E6" s="10" t="n">
-        <v>0</v>
+        <v>0.675</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0.0075</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>11693500</v>
+        <v>15596600</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.34</v>
+        <v>0.62</v>
       </c>
       <c r="H6" t="n">
-        <v>74.48999999999999</v>
+        <v>75.98999999999999</v>
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
@@ -752,10 +752,10 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.382</v>
+        <v>0.616</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.277</v>
+        <v>0.531</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="7" t="inlineStr"/>
@@ -768,28 +768,28 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.67</v>
+        <v>0.42</v>
       </c>
       <c r="E7" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>11249400</v>
+        <v>12115800</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.45</v>
+        <v>0.35</v>
       </c>
       <c r="H7" t="n">
-        <v>75.19</v>
+        <v>74.48999999999999</v>
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
@@ -797,10 +797,10 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.616</v>
+        <v>0.382</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.531</v>
+        <v>0.277</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="7" t="inlineStr"/>
@@ -828,10 +828,10 @@
         <v>-0.0806</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>10467300</v>
+        <v>11131200</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="H8" t="n">
         <v>45.31</v>
@@ -858,28 +858,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4251</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>IBHD</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0.205</v>
+        <v>4.74</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>-0.0682</v>
+        <v>-0.0186</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>9266700</v>
+        <v>10634100</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>31.82</v>
+        <v>0.57</v>
       </c>
       <c r="H9" t="n">
-        <v>42.78</v>
+        <v>49.11</v>
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
@@ -887,10 +887,10 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.211</v>
+        <v>4.731</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.217</v>
+        <v>4.848</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="7" t="inlineStr"/>
@@ -903,28 +903,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>4251</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>IBHD</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>4.75</v>
+        <v>0.21</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>-0.0166</v>
+        <v>-0.0455</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>9029700</v>
+        <v>9400000</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.48</v>
+        <v>32.28</v>
       </c>
       <c r="H10" t="n">
-        <v>49.91</v>
+        <v>47.37</v>
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>4.732</v>
+        <v>0.211</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>4.848</v>
+        <v>0.217</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="7" t="inlineStr"/>
@@ -948,28 +948,28 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0081</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>REKATECH</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="E11" s="8" t="n">
-        <v>-0.2222</v>
+        <v>0.445</v>
+      </c>
+      <c r="E11" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>7785200</v>
+        <v>8047300</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>21.05</v>
+        <v>0.4</v>
       </c>
       <c r="H11" t="n">
-        <v>62.28</v>
+        <v>59.08</v>
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
@@ -977,10 +977,10 @@
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.026</v>
+        <v>0.424</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0.023</v>
+        <v>0.368</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="7" t="inlineStr"/>
@@ -993,39 +993,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>0081</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>REKATECH</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0.44</v>
+        <v>0.035</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>-0.0222</v>
+        <v>-0.2222</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>7550600</v>
+        <v>7785200</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.21</v>
+        <v>21.05</v>
       </c>
       <c r="H12" t="n">
-        <v>37.57</v>
-      </c>
-      <c r="I12" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.28</v>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.478</v>
+        <v>0.026</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0.482</v>
+        <v>0.023</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="7" t="inlineStr"/>
@@ -1038,33 +1038,40 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SLG</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0.245</v>
+        <v>0.44</v>
       </c>
       <c r="E13" s="8" t="n">
-        <v>-0.02</v>
+        <v>-0.0222</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>6774700</v>
+        <v>7697300</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.27</v>
+        <v>0.21</v>
+      </c>
+      <c r="H13" t="n">
+        <v>37.57</v>
       </c>
       <c r="I13" s="9" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J13" s="2" t="n"/>
-      <c r="K13" s="2" t="n"/>
+      <c r="J13" s="2" t="n">
+        <v>0.478</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>0.482</v>
+      </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="7" t="inlineStr"/>
     </row>
@@ -1076,40 +1083,33 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>SLG</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>0.0112</v>
+        <v>0.25</v>
+      </c>
+      <c r="E14" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>6299100</v>
+        <v>6874700</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="H14" t="n">
-        <v>60.13</v>
-      </c>
-      <c r="I14" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="n">
-        <v>0.424</v>
-      </c>
-      <c r="K14" s="2" t="n">
-        <v>0.368</v>
-      </c>
+        <v>0.28</v>
+      </c>
+      <c r="I14" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="n"/>
+      <c r="K14" s="2" t="n"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="7" t="inlineStr"/>
     </row>
@@ -1121,39 +1121,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E15" s="10" t="n">
-        <v>0</v>
+        <v>1.95</v>
+      </c>
+      <c r="E15" s="8" t="n">
+        <v>-0.0347</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>6072500</v>
+        <v>6086600</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>1.95</v>
+        <v>0.21</v>
       </c>
       <c r="H15" t="n">
-        <v>49.08</v>
-      </c>
-      <c r="I15" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.64</v>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.295</v>
+        <v>1.923</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0.295</v>
+        <v>1.739</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="7" t="inlineStr"/>
@@ -1166,28 +1166,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>3891</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MUIIND</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0.04</v>
+        <v>0.295</v>
       </c>
       <c r="E16" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>5900400</v>
+        <v>6072500</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>3.48</v>
+        <v>1.95</v>
       </c>
       <c r="H16" t="n">
-        <v>46.69</v>
+        <v>49.08</v>
       </c>
       <c r="I16" s="9" t="inlineStr">
         <is>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.041</v>
+        <v>0.295</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0.042</v>
+        <v>0.295</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="7" t="inlineStr"/>
@@ -1211,39 +1211,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>3891</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>MUIIND</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="E17" s="8" t="n">
-        <v>-0.0396</v>
+        <v>0.04</v>
+      </c>
+      <c r="E17" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>4846100</v>
+        <v>6000400</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.17</v>
+        <v>3.54</v>
       </c>
       <c r="H17" t="n">
-        <v>54.02</v>
-      </c>
-      <c r="I17" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.69</v>
+      </c>
+      <c r="I17" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1.922</v>
+        <v>0.041</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>1.739</v>
+        <v>0.042</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="7" t="inlineStr"/>
@@ -1256,28 +1256,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>5156</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>XDL</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>1.1</v>
+        <v>0.005</v>
       </c>
       <c r="E18" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>4105400</v>
+        <v>5850000</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.43</v>
+        <v>2.38</v>
       </c>
       <c r="H18" t="n">
-        <v>54.23</v>
+        <v>44.81</v>
       </c>
       <c r="I18" s="9" t="inlineStr">
         <is>
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>1.079</v>
+        <v>0.007</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>1.045</v>
+        <v>0.007</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="7" t="inlineStr"/>
@@ -1301,39 +1301,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v>0.0238</v>
+        <v>0.31</v>
+      </c>
+      <c r="E19" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>3922900</v>
+        <v>5380400</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.58</v>
+        <v>0.28</v>
       </c>
       <c r="H19" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="I19" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.55</v>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.424</v>
+        <v>0.309</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0.416</v>
+        <v>0.3</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="7" t="inlineStr"/>
@@ -1346,39 +1346,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="E20" s="10" t="n">
-        <v>0</v>
+        <v>1.09</v>
+      </c>
+      <c r="E20" s="8" t="n">
+        <v>-0.0091</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>3688400</v>
+        <v>5087000</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.19</v>
+        <v>0.53</v>
       </c>
       <c r="H20" t="n">
-        <v>54.55</v>
-      </c>
-      <c r="I20" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.65</v>
+      </c>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.309</v>
+        <v>1.078</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0.3</v>
+        <v>1.045</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="7" t="inlineStr"/>
@@ -1391,28 +1391,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>2.56</v>
+        <v>0.775</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>-0.03759999999999999</v>
+        <v>-0.0064</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>3592300</v>
+        <v>4587900</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="H21" t="n">
-        <v>46.31</v>
+        <v>49.91</v>
       </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
@@ -1420,10 +1420,10 @@
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>2.641</v>
+        <v>0.775</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>2.553</v>
+        <v>0.776</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="7" t="inlineStr"/>
@@ -1436,39 +1436,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>0.535</v>
+        <v>2.56</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>-0.036</v>
+        <v>-0.03759999999999999</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>3520400</v>
+        <v>4513100</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.17</v>
+        <v>0.25</v>
       </c>
       <c r="H22" t="n">
-        <v>44.62</v>
-      </c>
-      <c r="I22" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.31</v>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.572</v>
+        <v>2.641</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0.541</v>
+        <v>2.553</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="7" t="inlineStr"/>
@@ -1481,39 +1481,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>2.37</v>
+        <v>0.43</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.0349</v>
+        <v>0.0238</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>3481300</v>
+        <v>4218900</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.98</v>
+        <v>0.62</v>
       </c>
       <c r="H23" t="n">
-        <v>62.65</v>
-      </c>
-      <c r="I23" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.5</v>
+      </c>
+      <c r="I23" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>2.229</v>
+        <v>0.424</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>2.167</v>
+        <v>0.416</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="7" t="inlineStr"/>
@@ -1526,28 +1526,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>0.335</v>
+        <v>0.99</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>-0.0147</v>
+        <v>-0.0198</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>3327400</v>
+        <v>4194700</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.35</v>
+        <v>0.53</v>
       </c>
       <c r="H24" t="n">
-        <v>47.31</v>
+        <v>43.57</v>
       </c>
       <c r="I24" s="9" t="inlineStr">
         <is>
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.346</v>
+        <v>1.049</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0.334</v>
+        <v>0.959</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="7" t="inlineStr"/>
@@ -1571,33 +1571,40 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0477</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ECOSYS</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E25" s="8" t="n">
-        <v>-0.0127</v>
+        <v>0.625</v>
+      </c>
+      <c r="E25" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>3171100</v>
+        <v>4156600</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.04</v>
+        <v>0.38</v>
+      </c>
+      <c r="H25" t="n">
+        <v>56.82</v>
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J25" s="2" t="n"/>
-      <c r="K25" s="2" t="n"/>
+      <c r="J25" s="2" t="n">
+        <v>0.617</v>
+      </c>
+      <c r="K25" s="2" t="n">
+        <v>0.615</v>
+      </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="7" t="inlineStr"/>
     </row>
@@ -1609,39 +1616,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>1.19</v>
+        <v>1.64</v>
       </c>
       <c r="E26" s="8" t="n">
-        <v>-0.0325</v>
+        <v>-0.018</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>3162100</v>
+        <v>4095800</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.42</v>
+        <v>0.86</v>
       </c>
       <c r="H26" t="n">
-        <v>38.78</v>
-      </c>
-      <c r="I26" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.28</v>
+      </c>
+      <c r="I26" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>1.235</v>
+        <v>1.725</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>1.323</v>
+        <v>1.768</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="7" t="inlineStr"/>
@@ -1654,28 +1661,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E27" s="10" t="n">
-        <v>0</v>
+        <v>1.2</v>
+      </c>
+      <c r="E27" s="8" t="n">
+        <v>-0.0244</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>3081600</v>
+        <v>3912300</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.28</v>
+        <v>0.52</v>
       </c>
       <c r="H27" t="n">
-        <v>56.82</v>
+        <v>40.08</v>
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
@@ -1683,10 +1690,10 @@
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.617</v>
+        <v>1.236</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0.615</v>
+        <v>1.323</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="7" t="inlineStr"/>
@@ -1699,28 +1706,28 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="E28" s="8" t="n">
-        <v>-0.0128</v>
+        <v>2.35</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>0.0262</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>3059900</v>
+        <v>3848100</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.2</v>
+        <v>1.08</v>
       </c>
       <c r="H28" t="n">
-        <v>46.74</v>
+        <v>61.48</v>
       </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
@@ -1728,10 +1735,10 @@
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.775</v>
+        <v>2.227</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0.776</v>
+        <v>2.167</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="7" t="inlineStr"/>
@@ -1744,39 +1751,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="E29" s="10" t="n">
-        <v>0</v>
+        <v>0.54</v>
+      </c>
+      <c r="E29" s="8" t="n">
+        <v>-0.027</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>2974600</v>
+        <v>3847600</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.4</v>
+        <v>0.19</v>
       </c>
       <c r="H29" t="n">
-        <v>55.92</v>
-      </c>
-      <c r="I29" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.4</v>
+      </c>
+      <c r="I29" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.371</v>
+        <v>0.572</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0.369</v>
+        <v>0.541</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="7" t="inlineStr"/>
@@ -1789,39 +1796,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>0.525</v>
-      </c>
-      <c r="E30" s="8" t="n">
-        <v>-0.0187</v>
+        <v>0.375</v>
+      </c>
+      <c r="E30" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>2921100</v>
+        <v>3597900</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>1.18</v>
+        <v>0.49</v>
       </c>
       <c r="H30" t="n">
-        <v>36.53</v>
-      </c>
-      <c r="I30" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.92</v>
+      </c>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.544</v>
+        <v>0.371</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0.572</v>
+        <v>0.369</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="7" t="inlineStr"/>
@@ -1834,28 +1841,28 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>3.87</v>
-      </c>
-      <c r="E31" s="3" t="n">
-        <v>0.0403</v>
+        <v>0.335</v>
+      </c>
+      <c r="E31" s="8" t="n">
+        <v>-0.0147</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>2863300</v>
+        <v>3554700</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.3</v>
+        <v>0.37</v>
       </c>
       <c r="H31" t="n">
-        <v>59.43</v>
+        <v>47.31</v>
       </c>
       <c r="I31" s="9" t="inlineStr">
         <is>
@@ -1863,10 +1870,10 @@
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>3.655</v>
+        <v>0.346</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>3.009</v>
+        <v>0.334</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="7" t="inlineStr"/>
@@ -1879,40 +1886,33 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>0477</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>ECOSYS</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>1.01</v>
+        <v>0.775</v>
       </c>
       <c r="E32" s="8" t="n">
-        <v>-0.06480000000000001</v>
+        <v>-0.0127</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>2829400</v>
+        <v>3343200</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="H32" t="n">
-        <v>66.41</v>
+        <v>0.04</v>
       </c>
       <c r="I32" s="6" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J32" s="2" t="n">
-        <v>0.842</v>
-      </c>
-      <c r="K32" s="2" t="n">
-        <v>0.573</v>
-      </c>
+      <c r="J32" s="2" t="n"/>
+      <c r="K32" s="2" t="n"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="7" t="inlineStr"/>
     </row>
@@ -1924,39 +1924,39 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>0.41</v>
+        <v>3.87</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>0.0123</v>
+        <v>0.0403</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>2700200</v>
+        <v>3330600</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>1.39</v>
+        <v>0.35</v>
       </c>
       <c r="H33" t="n">
-        <v>41.24</v>
-      </c>
-      <c r="I33" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>59.43</v>
+      </c>
+      <c r="I33" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.416</v>
+        <v>3.655</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0.434</v>
+        <v>3.009</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="7" t="inlineStr"/>
@@ -1969,28 +1969,28 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>0.995</v>
-      </c>
-      <c r="E34" s="8" t="n">
-        <v>-0.0149</v>
+        <v>2.66</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>0.0114</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>2640100</v>
+        <v>3293200</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.33</v>
+        <v>0.26</v>
       </c>
       <c r="H34" t="n">
-        <v>44.16</v>
+        <v>42.31</v>
       </c>
       <c r="I34" s="9" t="inlineStr">
         <is>
@@ -1998,10 +1998,10 @@
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>1.049</v>
+        <v>2.759</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0.959</v>
+        <v>2.738</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="7" t="inlineStr"/>
@@ -2014,28 +2014,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>2</v>
+        <v>0.52</v>
       </c>
       <c r="E35" s="8" t="n">
-        <v>-0.0148</v>
+        <v>-0.028</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>2593400</v>
+        <v>3234000</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.2</v>
+        <v>1.31</v>
       </c>
       <c r="H35" t="n">
-        <v>31.84</v>
+        <v>34.76</v>
       </c>
       <c r="I35" s="9" t="inlineStr">
         <is>
@@ -2043,10 +2043,10 @@
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>2.146</v>
+        <v>0.543</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>2.233</v>
+        <v>0.572</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="7" t="inlineStr"/>
@@ -2059,39 +2059,39 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E36" s="8" t="n">
-        <v>-0.0189</v>
+        <v>1.29</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>0.0157</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>2439800</v>
+        <v>3213400</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.34</v>
+        <v>0.52</v>
       </c>
       <c r="H36" t="n">
-        <v>42.45</v>
-      </c>
-      <c r="I36" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.45</v>
+      </c>
+      <c r="I36" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.273</v>
+        <v>1.199</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0.294</v>
+        <v>1.188</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="7" t="inlineStr"/>
@@ -2104,39 +2104,39 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="E37" s="3" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.84</v>
+      </c>
+      <c r="E37" s="8" t="n">
+        <v>-0.04</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>2356600</v>
+        <v>3057400</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.38</v>
+        <v>1</v>
       </c>
       <c r="H37" t="n">
-        <v>62.51</v>
-      </c>
-      <c r="I37" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>29.06</v>
+      </c>
+      <c r="I37" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>1.198</v>
+        <v>0.897</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>1.188</v>
+        <v>0.953</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="7" t="inlineStr"/>
@@ -2149,28 +2149,28 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>5.11</v>
-      </c>
-      <c r="E38" s="8" t="n">
-        <v>-0.007800000000000001</v>
+        <v>6.67</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>0.0262</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>2350200</v>
+        <v>3028200</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.17</v>
+        <v>0.31</v>
       </c>
       <c r="H38" t="n">
-        <v>34.12</v>
+        <v>28.27</v>
       </c>
       <c r="I38" s="9" t="inlineStr">
         <is>
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>5.494</v>
+        <v>7.208</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>5.448</v>
+        <v>7.606</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="7" t="inlineStr"/>
@@ -2194,28 +2194,28 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="E39" s="3" t="n">
-        <v>0.008500000000000001</v>
+        <v>2</v>
+      </c>
+      <c r="E39" s="8" t="n">
+        <v>-0.0148</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>2274700</v>
+        <v>2996000</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.32</v>
+        <v>0.23</v>
       </c>
       <c r="H39" t="n">
-        <v>53.56</v>
+        <v>31.84</v>
       </c>
       <c r="I39" s="9" t="inlineStr">
         <is>
@@ -2223,10 +2223,10 @@
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>1.171</v>
+        <v>2.146</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>1.137</v>
+        <v>2.233</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="7" t="inlineStr"/>
@@ -2239,28 +2239,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>6.65</v>
+        <v>5.17</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0.0231</v>
+        <v>0.0039</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>2183300</v>
+        <v>2873900</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.23</v>
+        <v>0.2</v>
       </c>
       <c r="H40" t="n">
-        <v>27.34</v>
+        <v>36.22</v>
       </c>
       <c r="I40" s="9" t="inlineStr">
         <is>
@@ -2268,10 +2268,10 @@
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>7.206</v>
+        <v>5.5</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>7.606</v>
+        <v>5.449</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="7" t="inlineStr"/>
@@ -2299,10 +2299,10 @@
         <v>-0.0138</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>2172400</v>
+        <v>2870000</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.19</v>
+        <v>0.26</v>
       </c>
       <c r="H41" t="n">
         <v>21.76</v>
@@ -2329,28 +2329,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>1.65</v>
+        <v>1.01</v>
       </c>
       <c r="E42" s="8" t="n">
-        <v>-0.012</v>
+        <v>-0.06480000000000001</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>2120700</v>
+        <v>2864200</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.31</v>
+        <v>0.72</v>
       </c>
       <c r="H42" t="n">
-        <v>51.49</v>
+        <v>66.41</v>
       </c>
       <c r="I42" s="6" t="inlineStr">
         <is>
@@ -2358,10 +2358,10 @@
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>1.627</v>
+        <v>0.842</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>1.695</v>
+        <v>0.573</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="7" t="inlineStr"/>
@@ -2374,28 +2374,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>0.84</v>
+        <v>0.46</v>
       </c>
       <c r="E43" s="8" t="n">
-        <v>-0.04</v>
+        <v>-0.0108</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>2092400</v>
+        <v>2775400</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.68</v>
+        <v>0.37</v>
       </c>
       <c r="H43" t="n">
-        <v>29.06</v>
+        <v>29.85</v>
       </c>
       <c r="I43" s="9" t="inlineStr">
         <is>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.897</v>
+        <v>0.498</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0.953</v>
+        <v>0.556</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="7" t="inlineStr"/>
@@ -2419,28 +2419,28 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>1.61</v>
+        <v>0.505</v>
       </c>
       <c r="E44" s="8" t="n">
-        <v>-0.0359</v>
+        <v>-0.0381</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>1981000</v>
+        <v>2763200</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.41</v>
+        <v>0.23</v>
       </c>
       <c r="H44" t="n">
-        <v>33.56</v>
+        <v>49.41</v>
       </c>
       <c r="I44" s="9" t="inlineStr">
         <is>
@@ -2448,10 +2448,10 @@
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>1.722</v>
+        <v>0.519</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>1.767</v>
+        <v>0.46</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="7" t="inlineStr"/>
@@ -2464,39 +2464,39 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>0.575</v>
-      </c>
-      <c r="E45" s="8" t="n">
-        <v>-0.0336</v>
+        <v>0.415</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>0.0247</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>1977600</v>
+        <v>2705900</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.22</v>
+        <v>1.39</v>
       </c>
       <c r="H45" t="n">
-        <v>37.01</v>
-      </c>
-      <c r="I45" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>45.72</v>
+      </c>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.648</v>
+        <v>0.416</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0.62</v>
+        <v>0.434</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="7" t="inlineStr"/>
@@ -2509,28 +2509,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>7.15</v>
-      </c>
-      <c r="E46" s="8" t="n">
-        <v>-0.0069</v>
+        <v>1.18</v>
+      </c>
+      <c r="E46" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>1964900</v>
+        <v>2683800</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.12</v>
+        <v>0.37</v>
       </c>
       <c r="H46" t="n">
-        <v>32.9</v>
+        <v>52.34</v>
       </c>
       <c r="I46" s="9" t="inlineStr">
         <is>
@@ -2538,10 +2538,10 @@
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>7.505</v>
+        <v>1.17</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>7.684</v>
+        <v>1.136</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="7" t="inlineStr"/>
@@ -2554,28 +2554,28 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>0.455</v>
+        <v>0.26</v>
       </c>
       <c r="E47" s="8" t="n">
-        <v>-0.0215</v>
+        <v>-0.0189</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>1952500</v>
+        <v>2543600</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.26</v>
+        <v>0.35</v>
       </c>
       <c r="H47" t="n">
-        <v>28.78</v>
+        <v>42.45</v>
       </c>
       <c r="I47" s="9" t="inlineStr">
         <is>
@@ -2583,10 +2583,10 @@
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.498</v>
+        <v>0.273</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0.556</v>
+        <v>0.294</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="7" t="inlineStr"/>
@@ -2599,28 +2599,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>0.545</v>
+        <v>7.15</v>
       </c>
       <c r="E48" s="8" t="n">
-        <v>-0.04389999999999999</v>
+        <v>-0.0069</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>1928900</v>
+        <v>2538700</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.37</v>
+        <v>0.16</v>
       </c>
       <c r="H48" t="n">
-        <v>48.83</v>
+        <v>32.9</v>
       </c>
       <c r="I48" s="9" t="inlineStr">
         <is>
@@ -2628,10 +2628,10 @@
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>7.505</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0.516</v>
+        <v>7.684</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="7" t="inlineStr"/>
@@ -2659,10 +2659,10 @@
         <v>-0.022</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>1720000</v>
+        <v>2483900</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="H49" t="n">
         <v>26.49</v>
@@ -2689,38 +2689,40 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>0.36</v>
+        <v>4.72</v>
       </c>
       <c r="E50" s="8" t="n">
-        <v>-0.0137</v>
+        <v>-0.0167</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>1711900</v>
+        <v>2468700</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="H50" t="n">
-        <v>62.55</v>
-      </c>
-      <c r="I50" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.05</v>
+      </c>
+      <c r="I50" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.319</v>
-      </c>
-      <c r="K50" s="2" t="n"/>
+        <v>4.891</v>
+      </c>
+      <c r="K50" s="2" t="n">
+        <v>4.727</v>
+      </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="7" t="inlineStr"/>
     </row>
@@ -2732,28 +2734,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>0.63</v>
+        <v>1.65</v>
       </c>
       <c r="E51" s="8" t="n">
-        <v>-0.007900000000000001</v>
+        <v>-0.012</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>1705700</v>
+        <v>2425400</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.76</v>
+        <v>0.36</v>
       </c>
       <c r="H51" t="n">
-        <v>47.67</v>
+        <v>51.49</v>
       </c>
       <c r="I51" s="6" t="inlineStr">
         <is>
@@ -2761,10 +2763,10 @@
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.637</v>
+        <v>1.627</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0.622</v>
+        <v>1.695</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="7" t="inlineStr"/>
@@ -2777,39 +2779,39 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0395</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>OGX</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="E52" s="3" t="n">
-        <v>0.033</v>
+        <v>0.545</v>
+      </c>
+      <c r="E52" s="8" t="n">
+        <v>-0.04389999999999999</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>1667900</v>
+        <v>2354300</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.64</v>
+        <v>0.45</v>
       </c>
       <c r="H52" t="n">
-        <v>57.98</v>
-      </c>
-      <c r="I52" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.83</v>
+      </c>
+      <c r="I52" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.447</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0.45</v>
+        <v>0.516</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="7" t="inlineStr"/>
@@ -2822,39 +2824,39 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>4.72</v>
-      </c>
-      <c r="E53" s="8" t="n">
-        <v>-0.0167</v>
+        <v>0.82</v>
+      </c>
+      <c r="E53" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>1664500</v>
+        <v>2341300</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="H53" t="n">
-        <v>42.05</v>
-      </c>
-      <c r="I53" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.16</v>
+      </c>
+      <c r="I53" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>4.891</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>4.727</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="7" t="inlineStr"/>
@@ -2867,28 +2869,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="E54" s="3" t="n">
-        <v>0.0038</v>
+        <v>0.405</v>
+      </c>
+      <c r="E54" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>1640400</v>
+        <v>2267700</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.13</v>
+        <v>0.18</v>
       </c>
       <c r="H54" t="n">
-        <v>40.49</v>
+        <v>55.08</v>
       </c>
       <c r="I54" s="9" t="inlineStr">
         <is>
@@ -2896,10 +2898,10 @@
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>2.758</v>
+        <v>0.391</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>2.738</v>
+        <v>0.378</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="7" t="inlineStr"/>
@@ -2912,28 +2914,28 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="E55" s="8" t="n">
-        <v>-0.0238</v>
+        <v>0.92</v>
+      </c>
+      <c r="E55" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>1598600</v>
+        <v>2261500</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.17</v>
+        <v>1.36</v>
       </c>
       <c r="H55" t="n">
-        <v>42.4</v>
+        <v>52</v>
       </c>
       <c r="I55" s="9" t="inlineStr">
         <is>
@@ -2941,10 +2943,10 @@
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.438</v>
+        <v>0.916</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0.434</v>
+        <v>0.874</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="7" t="inlineStr"/>
@@ -2957,39 +2959,39 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>0395</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>OGX</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="E56" s="8" t="n">
-        <v>-0.0326</v>
+        <v>0.47</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>0.033</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>1594600</v>
+        <v>2241600</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.96</v>
+        <v>0.86</v>
       </c>
       <c r="H56" t="n">
-        <v>47.65</v>
-      </c>
-      <c r="I56" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.98</v>
+      </c>
+      <c r="I56" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.913</v>
+        <v>0.447</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0.874</v>
+        <v>0.45</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="7" t="inlineStr"/>
@@ -3002,28 +3004,28 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>0.515</v>
+        <v>0.415</v>
       </c>
       <c r="E57" s="8" t="n">
-        <v>-0.019</v>
+        <v>-0.0119</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>1546400</v>
+        <v>2212700</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.13</v>
+        <v>0.23</v>
       </c>
       <c r="H57" t="n">
-        <v>51.37</v>
+        <v>43.52</v>
       </c>
       <c r="I57" s="9" t="inlineStr">
         <is>
@@ -3031,10 +3033,10 @@
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.52</v>
+        <v>0.438</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0.461</v>
+        <v>0.434</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="7" t="inlineStr"/>
@@ -3047,39 +3049,39 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="E58" s="3" t="n">
-        <v>0.0068</v>
+        <v>3.09</v>
+      </c>
+      <c r="E58" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>1545900</v>
+        <v>2130500</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.19</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H58" t="n">
-        <v>40.73</v>
-      </c>
-      <c r="I58" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>82.09</v>
+      </c>
+      <c r="I58" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.769</v>
+        <v>2.827</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0.771</v>
+        <v>2.43</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="7" t="inlineStr"/>
@@ -3092,39 +3094,39 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>VELESTO</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>0.205</v>
-      </c>
-      <c r="E59" s="3" t="n">
-        <v>0.009899999999999999</v>
+        <v>0.865</v>
+      </c>
+      <c r="E59" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>1543100</v>
+        <v>2099600</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="H59" t="n">
-        <v>39.23</v>
-      </c>
-      <c r="I59" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>45.57</v>
+      </c>
+      <c r="I59" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.218</v>
+        <v>0.868</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0.235</v>
+        <v>0.869</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="7" t="inlineStr"/>
@@ -3137,28 +3139,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>0.4</v>
+        <v>0.57</v>
       </c>
       <c r="E60" s="8" t="n">
-        <v>-0.0123</v>
+        <v>-0.042</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>1477800</v>
+        <v>2082600</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.12</v>
+        <v>0.23</v>
       </c>
       <c r="H60" t="n">
-        <v>53.56</v>
+        <v>36.38</v>
       </c>
       <c r="I60" s="9" t="inlineStr">
         <is>
@@ -3166,10 +3168,10 @@
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.391</v>
+        <v>0.647</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>0.378</v>
+        <v>0.62</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="7" t="inlineStr"/>
@@ -3182,39 +3184,39 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="E61" s="10" t="n">
-        <v>0</v>
+        <v>0.74</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>0.0068</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>1416200</v>
+        <v>1995900</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="H61" t="n">
-        <v>65.06</v>
-      </c>
-      <c r="I61" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.73</v>
+      </c>
+      <c r="I61" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.924</v>
+        <v>0.769</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0.877</v>
+        <v>0.771</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="7" t="inlineStr"/>
@@ -3227,28 +3229,28 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>0469</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>GTA</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>1.29</v>
+        <v>0.24</v>
       </c>
       <c r="E62" s="8" t="n">
-        <v>-0.0301</v>
+        <v>-0.04</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>1366800</v>
+        <v>1905400</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="H62" t="n">
-        <v>55.19</v>
+        <v>16.11</v>
       </c>
       <c r="I62" s="9" t="inlineStr">
         <is>
@@ -3256,11 +3258,9 @@
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>1.259</v>
-      </c>
-      <c r="K62" s="2" t="n">
-        <v>1.173</v>
-      </c>
+        <v>0.272</v>
+      </c>
+      <c r="K62" s="2" t="n"/>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="7" t="inlineStr"/>
     </row>
@@ -3272,39 +3272,39 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>5932</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>BPURI</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>0.21</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="E63" s="8" t="n">
-        <v>-0.0233</v>
+        <v>-0.004</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>1297400</v>
+        <v>1901000</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>1.89</v>
+        <v>0.14</v>
       </c>
       <c r="H63" t="n">
-        <v>38.22</v>
-      </c>
-      <c r="I63" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>44.09</v>
+      </c>
+      <c r="I63" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.223</v>
+        <v>10.006</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0.232</v>
+        <v>10.149</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="7" t="inlineStr"/>
@@ -3317,28 +3317,28 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>0.86</v>
+        <v>0.36</v>
       </c>
       <c r="E64" s="8" t="n">
-        <v>-0.0058</v>
+        <v>-0.0137</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>1260700</v>
+        <v>1870300</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.06</v>
+        <v>0.32</v>
       </c>
       <c r="H64" t="n">
-        <v>40.62</v>
+        <v>62.55</v>
       </c>
       <c r="I64" s="6" t="inlineStr">
         <is>
@@ -3346,11 +3346,9 @@
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.868</v>
-      </c>
-      <c r="K64" s="2" t="n">
-        <v>0.869</v>
-      </c>
+        <v>0.319</v>
+      </c>
+      <c r="K64" s="2" t="n"/>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="7" t="inlineStr"/>
     </row>
@@ -3362,28 +3360,28 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>8524</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>TALIWRK</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="E65" s="10" t="n">
-        <v>0</v>
+        <v>0.41</v>
+      </c>
+      <c r="E65" s="8" t="n">
+        <v>-0.0353</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>1235600</v>
+        <v>1757100</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0.62</v>
+        <v>0.22</v>
       </c>
       <c r="H65" t="n">
-        <v>37.06</v>
+        <v>22.61</v>
       </c>
       <c r="I65" s="9" t="inlineStr">
         <is>
@@ -3391,10 +3389,10 @@
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.244</v>
+        <v>0.526</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>0.256</v>
+        <v>0.614</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="7" t="inlineStr"/>
@@ -3407,28 +3405,28 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>0.335</v>
-      </c>
-      <c r="E66" s="10" t="n">
-        <v>0</v>
+        <v>0.63</v>
+      </c>
+      <c r="E66" s="8" t="n">
+        <v>-0.007900000000000001</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>1217900</v>
+        <v>1705700</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>0.26</v>
+        <v>0.76</v>
       </c>
       <c r="H66" t="n">
-        <v>47.09</v>
+        <v>47.67</v>
       </c>
       <c r="I66" s="6" t="inlineStr">
         <is>
@@ -3436,10 +3434,10 @@
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.335</v>
+        <v>0.637</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0.343</v>
+        <v>0.622</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="7" t="inlineStr"/>
@@ -3452,28 +3450,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0469</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>GTA</t>
+          <t>PECCA</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>0.245</v>
-      </c>
-      <c r="E67" s="8" t="n">
-        <v>-0.02</v>
+        <v>1.35</v>
+      </c>
+      <c r="E67" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>1216100</v>
+        <v>1681500</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>0.34</v>
+        <v>0.86</v>
       </c>
       <c r="H67" t="n">
-        <v>16.72</v>
+        <v>43.62</v>
       </c>
       <c r="I67" s="9" t="inlineStr">
         <is>
@@ -3481,9 +3479,11 @@
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.272</v>
-      </c>
-      <c r="K67" s="2" t="n"/>
+        <v>1.367</v>
+      </c>
+      <c r="K67" s="2" t="n">
+        <v>1.343</v>
+      </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="7" t="inlineStr"/>
     </row>
@@ -3495,28 +3495,28 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>0.415</v>
+        <v>1.29</v>
       </c>
       <c r="E68" s="8" t="n">
-        <v>-0.0235</v>
+        <v>-0.0301</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>1191300</v>
+        <v>1639600</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>0.15</v>
+        <v>0.68</v>
       </c>
       <c r="H68" t="n">
-        <v>23.04</v>
+        <v>55.19</v>
       </c>
       <c r="I68" s="9" t="inlineStr">
         <is>
@@ -3524,10 +3524,10 @@
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.527</v>
+        <v>1.259</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0.614</v>
+        <v>1.173</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="7" t="inlineStr"/>
@@ -3540,39 +3540,39 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E69" s="10" t="n">
-        <v>0</v>
+        <v>0.205</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>0.009899999999999999</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>1162500</v>
+        <v>1574500</v>
       </c>
       <c r="G69" s="5" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="H69" t="n">
-        <v>57.16</v>
-      </c>
-      <c r="I69" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.23</v>
+      </c>
+      <c r="I69" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.218</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.235</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="7" t="inlineStr"/>
@@ -3585,28 +3585,28 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>3.09</v>
+        <v>0.335</v>
       </c>
       <c r="E70" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>1141700</v>
+        <v>1524400</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>0.37</v>
+        <v>0.32</v>
       </c>
       <c r="H70" t="n">
-        <v>82.09</v>
+        <v>47.09</v>
       </c>
       <c r="I70" s="6" t="inlineStr">
         <is>
@@ -3614,10 +3614,10 @@
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>2.827</v>
+        <v>0.335</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>2.43</v>
+        <v>0.343</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="7" t="inlineStr"/>
@@ -3630,39 +3630,39 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>0192</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>INTA</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>0.58</v>
+        <v>0.38</v>
       </c>
       <c r="E71" s="8" t="n">
-        <v>-0.008500000000000001</v>
+        <v>-0.013</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>1119800</v>
+        <v>1514500</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>0.27</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H71" t="n">
-        <v>67.36</v>
-      </c>
-      <c r="I71" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.3</v>
+      </c>
+      <c r="I71" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.509</v>
+        <v>0.394</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>0.468</v>
+        <v>0.389</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="7" t="inlineStr"/>
@@ -3675,39 +3675,39 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>5271</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>PECCA</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>1.35</v>
+        <v>0.96</v>
       </c>
       <c r="E72" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>1113100</v>
+        <v>1461200</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>0.57</v>
+        <v>0.25</v>
       </c>
       <c r="H72" t="n">
-        <v>43.62</v>
-      </c>
-      <c r="I72" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.06</v>
+      </c>
+      <c r="I72" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>1.367</v>
+        <v>0.924</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>1.343</v>
+        <v>0.877</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="7" t="inlineStr"/>
@@ -3720,39 +3720,39 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>IOIPG</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="E73" s="3" t="n">
-        <v>0.038</v>
+        <v>0.58</v>
+      </c>
+      <c r="E73" s="8" t="n">
+        <v>-0.008500000000000001</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>1108700</v>
+        <v>1437100</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>0.19</v>
+        <v>0.34</v>
       </c>
       <c r="H73" t="n">
-        <v>39.03</v>
-      </c>
-      <c r="I73" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>67.36</v>
+      </c>
+      <c r="I73" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>3.373</v>
+        <v>0.509</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>3.604</v>
+        <v>0.468</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="7" t="inlineStr"/>
@@ -3765,28 +3765,28 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>0.735</v>
+        <v>0.28</v>
       </c>
       <c r="E74" s="8" t="n">
-        <v>-0.0329</v>
+        <v>-0.0175</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>1072600</v>
+        <v>1433800</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
       <c r="H74" t="n">
-        <v>48.09</v>
+        <v>21.33</v>
       </c>
       <c r="I74" s="9" t="inlineStr">
         <is>
@@ -3794,10 +3794,10 @@
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.761</v>
+        <v>0.333</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.372</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="7" t="inlineStr"/>
@@ -3810,28 +3810,28 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>8524</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>TALIWRK</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>0.635</v>
+        <v>0.225</v>
       </c>
       <c r="E75" s="8" t="n">
-        <v>-0.0155</v>
+        <v>-0.0217</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>1012300</v>
+        <v>1361700</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>0.11</v>
+        <v>0.68</v>
       </c>
       <c r="H75" t="n">
-        <v>40.95</v>
+        <v>34.68</v>
       </c>
       <c r="I75" s="9" t="inlineStr">
         <is>
@@ -3839,10 +3839,10 @@
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.678</v>
+        <v>0.243</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.256</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="7" t="inlineStr"/>
@@ -3855,39 +3855,39 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0450</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>MFGROUP</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>0.28</v>
+        <v>0.585</v>
       </c>
       <c r="E76" s="8" t="n">
-        <v>-0.0175</v>
+        <v>-0.0488</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>1006700</v>
+        <v>1303100</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>1.06</v>
+        <v>0.23</v>
       </c>
       <c r="H76" t="n">
-        <v>55.75</v>
-      </c>
-      <c r="I76" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>55.93</v>
+      </c>
+      <c r="I76" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.276</v>
+        <v>0.569</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>0.267</v>
+        <v>0.47</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="7" t="inlineStr"/>
@@ -3900,28 +3900,28 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>1.08</v>
+        <v>0.725</v>
       </c>
       <c r="E77" s="8" t="n">
-        <v>-0.027</v>
+        <v>-0.0461</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>969000</v>
+        <v>1302600</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>0.22</v>
+        <v>0.24</v>
       </c>
       <c r="H77" t="n">
-        <v>55.63</v>
+        <v>46.5</v>
       </c>
       <c r="I77" s="9" t="inlineStr">
         <is>
@@ -3929,10 +3929,10 @@
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>1.052</v>
+        <v>0.76</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>0.913</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="7" t="inlineStr"/>
@@ -3945,28 +3945,28 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>5932</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>BPURI</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="E78" s="3" t="n">
-        <v>0.0105</v>
+        <v>0.21</v>
+      </c>
+      <c r="E78" s="8" t="n">
+        <v>-0.0233</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>967900</v>
+        <v>1297400</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>0.13</v>
+        <v>1.89</v>
       </c>
       <c r="H78" t="n">
-        <v>31.42</v>
+        <v>38.22</v>
       </c>
       <c r="I78" s="9" t="inlineStr">
         <is>
@@ -3974,10 +3974,10 @@
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>6.024</v>
+        <v>0.223</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>6.309</v>
+        <v>0.232</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="7" t="inlineStr"/>
@@ -3990,28 +3990,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>IOIPG</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="E79" s="8" t="n">
-        <v>-0.0223</v>
+        <v>3.28</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>0.038</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>967500</v>
+        <v>1272700</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>0.12</v>
+        <v>0.21</v>
       </c>
       <c r="H79" t="n">
-        <v>43.95</v>
+        <v>39.03</v>
       </c>
       <c r="I79" s="9" t="inlineStr">
         <is>
@@ -4019,10 +4019,10 @@
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.928</v>
+        <v>3.373</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>0.847</v>
+        <v>3.604</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="7" t="inlineStr"/>
@@ -4035,28 +4035,28 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>0.58</v>
+        <v>0.875</v>
       </c>
       <c r="E80" s="8" t="n">
-        <v>-0.05690000000000001</v>
+        <v>-0.0223</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>957900</v>
+        <v>1272200</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="H80" t="n">
-        <v>55.18</v>
+        <v>43.95</v>
       </c>
       <c r="I80" s="9" t="inlineStr">
         <is>
@@ -4064,10 +4064,10 @@
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.928</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0.469</v>
+        <v>0.847</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="7" t="inlineStr"/>
@@ -4080,39 +4080,39 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>2.49</v>
+        <v>2.09</v>
       </c>
       <c r="E81" s="8" t="n">
-        <v>-0.0273</v>
+        <v>-0.0048</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>952000</v>
+        <v>1260300</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>0.16</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H81" t="n">
-        <v>41.03</v>
-      </c>
-      <c r="I81" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.26</v>
+      </c>
+      <c r="I81" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>2.603</v>
+        <v>2.108</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>2.607</v>
+        <v>2.101</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="7" t="inlineStr"/>
@@ -4125,39 +4125,39 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="E82" s="10" t="n">
-        <v>0</v>
+        <v>0.635</v>
+      </c>
+      <c r="E82" s="8" t="n">
+        <v>-0.0155</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>950400</v>
+        <v>1241300</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>0.06</v>
+        <v>0.14</v>
       </c>
       <c r="H82" t="n">
-        <v>48.93</v>
-      </c>
-      <c r="I82" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.95</v>
+      </c>
+      <c r="I82" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>2.109</v>
+        <v>0.678</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>2.102</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="7" t="inlineStr"/>
@@ -4170,39 +4170,39 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>4.44</v>
-      </c>
-      <c r="E83" s="3" t="n">
-        <v>0.0278</v>
+        <v>2.49</v>
+      </c>
+      <c r="E83" s="8" t="n">
+        <v>-0.0273</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>947400</v>
+        <v>1199500</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="H83" t="n">
-        <v>52.29</v>
-      </c>
-      <c r="I83" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.03</v>
+      </c>
+      <c r="I83" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>4.36</v>
+        <v>2.603</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>4.431</v>
+        <v>2.607</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="7" t="inlineStr"/>
@@ -4215,39 +4215,39 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>0.67</v>
+        <v>1.18</v>
       </c>
       <c r="E84" s="8" t="n">
-        <v>-0.0219</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>935000</v>
+        <v>1190500</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="H84" t="n">
-        <v>59.56</v>
-      </c>
-      <c r="I84" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.42</v>
+      </c>
+      <c r="I84" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.647</v>
+        <v>1.238</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>0.5570000000000001</v>
+        <v>1.067</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="7" t="inlineStr"/>
@@ -4269,19 +4269,19 @@
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="E85" s="8" t="n">
-        <v>-0.0236</v>
+        <v>-0.0315</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>933300</v>
+        <v>1176900</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>0.22</v>
+        <v>0.28</v>
       </c>
       <c r="H85" t="n">
-        <v>24.69</v>
+        <v>24.1</v>
       </c>
       <c r="I85" s="9" t="inlineStr">
         <is>
@@ -4305,39 +4305,39 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>0.595</v>
+        <v>4.41</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.0208</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>895800</v>
+        <v>1131000</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="H86" t="n">
-        <v>50.22</v>
-      </c>
-      <c r="I86" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.22</v>
+      </c>
+      <c r="I86" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.598</v>
+        <v>4.357</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>0.586</v>
+        <v>4.431</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="7" t="inlineStr"/>
@@ -4350,28 +4350,28 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>0.75</v>
+        <v>1.09</v>
       </c>
       <c r="E87" s="8" t="n">
-        <v>-0.0323</v>
+        <v>-0.018</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>852200</v>
+        <v>1130900</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>0.35</v>
+        <v>0.26</v>
       </c>
       <c r="H87" t="n">
-        <v>53.86</v>
+        <v>56.65</v>
       </c>
       <c r="I87" s="9" t="inlineStr">
         <is>
@@ -4379,10 +4379,10 @@
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.734</v>
+        <v>1.053</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>0.704</v>
+        <v>0.913</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="7" t="inlineStr"/>
@@ -4395,28 +4395,28 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="E88" s="8" t="n">
-        <v>-0.016</v>
+        <v>5.75</v>
+      </c>
+      <c r="E88" s="3" t="n">
+        <v>0.0105</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>831700</v>
+        <v>1125900</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>0.09</v>
+        <v>0.15</v>
       </c>
       <c r="H88" t="n">
-        <v>38.86</v>
+        <v>31.42</v>
       </c>
       <c r="I88" s="9" t="inlineStr">
         <is>
@@ -4424,10 +4424,10 @@
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>1.296</v>
+        <v>6.024</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>1.314</v>
+        <v>6.309</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="7" t="inlineStr"/>
@@ -4440,28 +4440,28 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>DATASONIC</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>0.805</v>
-      </c>
-      <c r="E89" s="3" t="n">
-        <v>0.0126</v>
+        <v>0.28</v>
+      </c>
+      <c r="E89" s="8" t="n">
+        <v>-0.0175</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>820800</v>
+        <v>1100900</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>0.15</v>
+        <v>0.09</v>
       </c>
       <c r="H89" t="n">
-        <v>60.98</v>
+        <v>46.28</v>
       </c>
       <c r="I89" s="9" t="inlineStr">
         <is>
@@ -4469,10 +4469,10 @@
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.792</v>
+        <v>0.291</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>0.771</v>
+        <v>0.283</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="7" t="inlineStr"/>
@@ -4485,28 +4485,28 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>0.835</v>
-      </c>
-      <c r="E90" s="8" t="n">
-        <v>-0.0176</v>
+        <v>1.25</v>
+      </c>
+      <c r="E90" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>751000</v>
+        <v>1097400</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>0.21</v>
+        <v>0.12</v>
       </c>
       <c r="H90" t="n">
-        <v>53.24</v>
+        <v>41.23</v>
       </c>
       <c r="I90" s="9" t="inlineStr">
         <is>
@@ -4514,10 +4514,10 @@
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.827</v>
+        <v>1.298</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>0.781</v>
+        <v>1.314</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="7" t="inlineStr"/>
@@ -4530,28 +4530,28 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="E91" s="10" t="n">
-        <v>0</v>
+        <v>0.47</v>
+      </c>
+      <c r="E91" s="8" t="n">
+        <v>-0.0105</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>727100</v>
+        <v>1057600</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>0.17</v>
+        <v>0.12</v>
       </c>
       <c r="H91" t="n">
-        <v>52.61</v>
+        <v>35.57</v>
       </c>
       <c r="I91" s="9" t="inlineStr">
         <is>
@@ -4559,10 +4559,10 @@
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>1.16</v>
+        <v>0.506</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>1.1</v>
+        <v>0.524</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="7" t="inlineStr"/>
@@ -4575,28 +4575,28 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0045</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>SSB8</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E92" s="10" t="n">
-        <v>0</v>
+        <v>0.75</v>
+      </c>
+      <c r="E92" s="8" t="n">
+        <v>-0.0323</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>664700</v>
+        <v>1056900</v>
       </c>
       <c r="G92" s="5" t="n">
-        <v>0.18</v>
+        <v>0.43</v>
       </c>
       <c r="H92" t="n">
-        <v>50.64</v>
+        <v>53.86</v>
       </c>
       <c r="I92" s="9" t="inlineStr">
         <is>
@@ -4604,10 +4604,10 @@
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.639</v>
+        <v>0.734</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>0.615</v>
+        <v>0.704</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="7" t="inlineStr"/>
@@ -4620,28 +4620,28 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>5248</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>BAUTO</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>0.895</v>
-      </c>
-      <c r="E93" s="3" t="n">
-        <v>0.017</v>
+        <v>0.625</v>
+      </c>
+      <c r="E93" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>661400</v>
+        <v>1054300</v>
       </c>
       <c r="G93" s="5" t="n">
-        <v>0.41</v>
+        <v>0.31</v>
       </c>
       <c r="H93" t="n">
-        <v>49.48</v>
+        <v>70.16</v>
       </c>
       <c r="I93" s="6" t="inlineStr">
         <is>
@@ -4649,10 +4649,10 @@
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.892</v>
+        <v>0.617</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>0.908</v>
+        <v>0.605</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="7" t="inlineStr"/>
@@ -4665,39 +4665,39 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>0278</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>EDELTEQ</t>
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>2.5</v>
+        <v>0.415</v>
       </c>
       <c r="E94" s="8" t="n">
-        <v>-0.0234</v>
+        <v>-0.0349</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>640000</v>
+        <v>1023300</v>
       </c>
       <c r="G94" s="5" t="n">
-        <v>0.12</v>
+        <v>0.18</v>
       </c>
       <c r="H94" t="n">
-        <v>32.79</v>
-      </c>
-      <c r="I94" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.05</v>
+      </c>
+      <c r="I94" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>2.808</v>
+        <v>0.39</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>2.877</v>
+        <v>0.36</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="7" t="inlineStr"/>
@@ -4710,28 +4710,28 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>0450</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>MFGROUP</t>
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>9.949999999999999</v>
+        <v>0.28</v>
       </c>
       <c r="E95" s="8" t="n">
-        <v>-0.004</v>
+        <v>-0.0175</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>605100</v>
+        <v>1006700</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>0.05</v>
+        <v>1.06</v>
       </c>
       <c r="H95" t="n">
-        <v>44.09</v>
+        <v>55.75</v>
       </c>
       <c r="I95" s="6" t="inlineStr">
         <is>
@@ -4739,10 +4739,10 @@
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>10.006</v>
+        <v>0.276</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>10.149</v>
+        <v>0.267</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="7" t="inlineStr"/>
@@ -4755,39 +4755,39 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>5248</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>BAUTO</t>
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="E96" s="3" t="n">
-        <v>0.0059</v>
+        <v>0.0227</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>602400</v>
+        <v>999300</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>0.2</v>
+        <v>0.61</v>
       </c>
       <c r="H96" t="n">
-        <v>20.04</v>
-      </c>
-      <c r="I96" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.19</v>
+      </c>
+      <c r="I96" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.916</v>
+        <v>0.893</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>0.973</v>
+        <v>0.908</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="7" t="inlineStr"/>
@@ -4800,28 +4800,28 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>UWC</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>7.16</v>
-      </c>
-      <c r="E97" s="8" t="n">
-        <v>-0.0192</v>
+        <v>0.59</v>
+      </c>
+      <c r="E97" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>596000</v>
+        <v>998300</v>
       </c>
       <c r="G97" s="5" t="n">
-        <v>0.14</v>
+        <v>0.23</v>
       </c>
       <c r="H97" t="n">
-        <v>48.38</v>
+        <v>49.06</v>
       </c>
       <c r="I97" s="9" t="inlineStr">
         <is>
@@ -4829,10 +4829,10 @@
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>7.338</v>
+        <v>0.598</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>6.895</v>
+        <v>0.586</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="7" t="inlineStr"/>
@@ -4845,39 +4845,39 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>AWC</t>
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>2.77</v>
+        <v>0.67</v>
       </c>
       <c r="E98" s="8" t="n">
-        <v>-0.0107</v>
+        <v>-0.0219</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>592600</v>
+        <v>986900</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>0.16</v>
+        <v>0.37</v>
       </c>
       <c r="H98" t="n">
-        <v>39.95</v>
-      </c>
-      <c r="I98" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.56</v>
+      </c>
+      <c r="I98" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>2.896</v>
+        <v>0.647</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>3.013</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="7" t="inlineStr"/>
@@ -4890,28 +4890,28 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D99" s="2" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="E99" s="8" t="n">
-        <v>-0.0227</v>
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="E99" s="3" t="n">
+        <v>0.0252</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v>524600</v>
+        <v>966400</v>
       </c>
       <c r="G99" s="5" t="n">
         <v>0.17</v>
       </c>
       <c r="H99" t="n">
-        <v>51.29</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="I99" s="9" t="inlineStr">
         <is>
@@ -4919,10 +4919,10 @@
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>1.289</v>
+        <v>0.793</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>1.226</v>
+        <v>0.771</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="7" t="inlineStr"/>
@@ -4935,28 +4935,28 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>0325</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="D100" s="2" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="E100" s="3" t="n">
-        <v>0.0321</v>
+        <v>1.1</v>
+      </c>
+      <c r="E100" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>512800</v>
+        <v>957000</v>
       </c>
       <c r="G100" s="5" t="n">
-        <v>0.09</v>
+        <v>0.49</v>
       </c>
       <c r="H100" t="n">
-        <v>50</v>
+        <v>51.14</v>
       </c>
       <c r="I100" s="6" t="inlineStr">
         <is>
@@ -4964,16 +4964,1051 @@
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>1.923</v>
+        <v>1.091</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>1.951</v>
+        <v>1.097</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="7" t="inlineStr"/>
     </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>5317</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>CPETECH</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="E101" s="8" t="n">
+        <v>-0.0455</v>
+      </c>
+      <c r="F101" s="4" t="n">
+        <v>856500</v>
+      </c>
+      <c r="G101" s="5" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H101" t="n">
+        <v>48.93</v>
+      </c>
+      <c r="I101" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="n">
+        <v>1.286</v>
+      </c>
+      <c r="K101" s="2" t="n">
+        <v>1.225</v>
+      </c>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" s="7" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>7081</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>PHARMA</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="E102" s="8" t="n">
+        <v>-0.0252</v>
+      </c>
+      <c r="F102" s="4" t="n">
+        <v>855900</v>
+      </c>
+      <c r="G102" s="5" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="H102" t="n">
+        <v>15.02</v>
+      </c>
+      <c r="I102" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="n">
+        <v>0.9370000000000001</v>
+      </c>
+      <c r="K102" s="2" t="n">
+        <v>1.077</v>
+      </c>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" s="7" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>5292</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>UWC</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="n">
+        <v>7.18</v>
+      </c>
+      <c r="E103" s="8" t="n">
+        <v>-0.0164</v>
+      </c>
+      <c r="F103" s="4" t="n">
+        <v>846800</v>
+      </c>
+      <c r="G103" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H103" t="n">
+        <v>48.79</v>
+      </c>
+      <c r="I103" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="n">
+        <v>7.34</v>
+      </c>
+      <c r="K103" s="2" t="n">
+        <v>6.895</v>
+      </c>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" s="7" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2852</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>CMSB</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="n">
+        <v>0.845</v>
+      </c>
+      <c r="E104" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F104" s="4" t="n">
+        <v>834000</v>
+      </c>
+      <c r="G104" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H104" t="n">
+        <v>17.21</v>
+      </c>
+      <c r="I104" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="n">
+        <v>0.916</v>
+      </c>
+      <c r="K104" s="2" t="n">
+        <v>0.973</v>
+      </c>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" s="7" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>0390</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>ISF</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="n">
+        <v>0.835</v>
+      </c>
+      <c r="E105" s="8" t="n">
+        <v>-0.0176</v>
+      </c>
+      <c r="F105" s="4" t="n">
+        <v>807200</v>
+      </c>
+      <c r="G105" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H105" t="n">
+        <v>53.24</v>
+      </c>
+      <c r="I105" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="n">
+        <v>0.827</v>
+      </c>
+      <c r="K105" s="2" t="n">
+        <v>0.781</v>
+      </c>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" s="7" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>0245</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>MNHLDG</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="E106" s="8" t="n">
+        <v>-0.0235</v>
+      </c>
+      <c r="F106" s="4" t="n">
+        <v>784600</v>
+      </c>
+      <c r="G106" s="5" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H106" t="n">
+        <v>46.79</v>
+      </c>
+      <c r="I106" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="K106" s="2" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" s="7" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>0045</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>SSB8</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="E107" s="8" t="n">
+        <v>-0.007900000000000001</v>
+      </c>
+      <c r="F107" s="4" t="n">
+        <v>758800</v>
+      </c>
+      <c r="G107" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H107" t="n">
+        <v>48.81</v>
+      </c>
+      <c r="I107" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="n">
+        <v>0.638</v>
+      </c>
+      <c r="K107" s="2" t="n">
+        <v>0.614</v>
+      </c>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" s="7" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>5356</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>STRATUS</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="E108" s="8" t="n">
+        <v>-0.0273</v>
+      </c>
+      <c r="F108" s="4" t="n">
+        <v>756500</v>
+      </c>
+      <c r="G108" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H108" t="n">
+        <v>32.47</v>
+      </c>
+      <c r="I108" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="n">
+        <v>2.807</v>
+      </c>
+      <c r="K108" s="2" t="n">
+        <v>2.877</v>
+      </c>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" s="7" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>0217</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>PWRWELL</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="E109" s="8" t="n">
+        <v>-0.0086</v>
+      </c>
+      <c r="F109" s="4" t="n">
+        <v>742300</v>
+      </c>
+      <c r="G109" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H109" t="n">
+        <v>50.8</v>
+      </c>
+      <c r="I109" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="n">
+        <v>1.159</v>
+      </c>
+      <c r="K109" s="2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" s="7" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>5357</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>SKYECHIP</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="E110" s="8" t="n">
+        <v>-0.0107</v>
+      </c>
+      <c r="F110" s="4" t="n">
+        <v>727100</v>
+      </c>
+      <c r="G110" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H110" t="n">
+        <v>39.95</v>
+      </c>
+      <c r="I110" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="n">
+        <v>2.896</v>
+      </c>
+      <c r="K110" s="2" t="n">
+        <v>3.013</v>
+      </c>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" s="7" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>5162</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>VSTECS</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E111" s="8" t="n">
+        <v>-0.0323</v>
+      </c>
+      <c r="F111" s="4" t="n">
+        <v>626500</v>
+      </c>
+      <c r="G111" s="5" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="H111" t="n">
+        <v>35.96</v>
+      </c>
+      <c r="I111" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="n">
+        <v>1.621</v>
+      </c>
+      <c r="K111" s="2" t="n">
+        <v>1.664</v>
+      </c>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" s="7" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>0099</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>SCICOM</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E112" s="3" t="n">
+        <v>0.0048</v>
+      </c>
+      <c r="F112" s="4" t="n">
+        <v>624500</v>
+      </c>
+      <c r="G112" s="5" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="H112" t="n">
+        <v>40.78</v>
+      </c>
+      <c r="I112" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="n">
+        <v>2.197</v>
+      </c>
+      <c r="K112" s="2" t="n">
+        <v>2.235</v>
+      </c>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" s="7" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>0151</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>KGB</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="n">
+        <v>8.109999999999999</v>
+      </c>
+      <c r="E113" s="8" t="n">
+        <v>-0.0287</v>
+      </c>
+      <c r="F113" s="4" t="n">
+        <v>622900</v>
+      </c>
+      <c r="G113" s="5" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H113" t="n">
+        <v>37.82</v>
+      </c>
+      <c r="I113" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="n">
+        <v>8.605</v>
+      </c>
+      <c r="K113" s="2" t="n">
+        <v>8.69</v>
+      </c>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" s="7" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>0271</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>WELLS</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="n">
+        <v>0.555</v>
+      </c>
+      <c r="E114" s="3" t="n">
+        <v>0.0091</v>
+      </c>
+      <c r="F114" s="4" t="n">
+        <v>622500</v>
+      </c>
+      <c r="G114" s="5" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="H114" t="n">
+        <v>42.07</v>
+      </c>
+      <c r="I114" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="n">
+        <v>0.5679999999999999</v>
+      </c>
+      <c r="K114" s="2" t="n">
+        <v>0.611</v>
+      </c>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" s="7" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>0225</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>SCGBHD</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="E115" s="8" t="n">
+        <v>-0.0142</v>
+      </c>
+      <c r="F115" s="4" t="n">
+        <v>620900</v>
+      </c>
+      <c r="G115" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H115" t="n">
+        <v>50.61</v>
+      </c>
+      <c r="I115" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="n">
+        <v>2.789</v>
+      </c>
+      <c r="K115" s="2" t="n">
+        <v>2.663</v>
+      </c>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" s="7" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>0168</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>BMGREEN</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="E116" s="8" t="n">
+        <v>-0.0408</v>
+      </c>
+      <c r="F116" s="4" t="n">
+        <v>619300</v>
+      </c>
+      <c r="G116" s="5" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="H116" t="n">
+        <v>30.82</v>
+      </c>
+      <c r="I116" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="n">
+        <v>1.555</v>
+      </c>
+      <c r="K116" s="2" t="n">
+        <v>1.648</v>
+      </c>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" s="7" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>5302</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>ATECH</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="n">
+        <v>0.755</v>
+      </c>
+      <c r="E117" s="8" t="n">
+        <v>-0.0382</v>
+      </c>
+      <c r="F117" s="4" t="n">
+        <v>595400</v>
+      </c>
+      <c r="G117" s="5" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H117" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="I117" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="K117" s="2" t="n">
+        <v>0.769</v>
+      </c>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" s="7" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>7277</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>DIALOG</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="E118" s="3" t="n">
+        <v>0.0214</v>
+      </c>
+      <c r="F118" s="4" t="n">
+        <v>576600</v>
+      </c>
+      <c r="G118" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H118" t="n">
+        <v>47.22</v>
+      </c>
+      <c r="I118" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J118" s="2" t="n">
+        <v>1.921</v>
+      </c>
+      <c r="K118" s="2" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" s="7" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>6971</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>KOBAY</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="E119" s="8" t="n">
+        <v>-0.0143</v>
+      </c>
+      <c r="F119" s="4" t="n">
+        <v>562600</v>
+      </c>
+      <c r="G119" s="5" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="H119" t="n">
+        <v>43.56</v>
+      </c>
+      <c r="I119" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J119" s="2" t="n">
+        <v>2.125</v>
+      </c>
+      <c r="K119" s="2" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" s="7" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>5286</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="n">
+        <v>6.38</v>
+      </c>
+      <c r="E120" s="8" t="n">
+        <v>-0.0185</v>
+      </c>
+      <c r="F120" s="4" t="n">
+        <v>556000</v>
+      </c>
+      <c r="G120" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H120" t="n">
+        <v>55.01</v>
+      </c>
+      <c r="I120" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J120" s="2" t="n">
+        <v>6.161</v>
+      </c>
+      <c r="K120" s="2" t="n">
+        <v>5.909</v>
+      </c>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" s="7" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>1619</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>DRBHCOM</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E121" s="8" t="n">
+        <v>-0.0184</v>
+      </c>
+      <c r="F121" s="4" t="n">
+        <v>539200</v>
+      </c>
+      <c r="G121" s="5" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="H121" t="n">
+        <v>15.65</v>
+      </c>
+      <c r="I121" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J121" s="2" t="n">
+        <v>0.884</v>
+      </c>
+      <c r="K121" s="2" t="n">
+        <v>0.9379999999999999</v>
+      </c>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" s="7" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>0233</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>PEKAT</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="E122" s="8" t="n">
+        <v>-0.0036</v>
+      </c>
+      <c r="F122" s="4" t="n">
+        <v>523500</v>
+      </c>
+      <c r="G122" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H122" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="I122" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="n">
+        <v>2.675</v>
+      </c>
+      <c r="K122" s="2" t="n">
+        <v>2.261</v>
+      </c>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" s="7" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>7233</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>DUFU</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="E123" s="8" t="n">
+        <v>-0.0195</v>
+      </c>
+      <c r="F123" s="4" t="n">
+        <v>506700</v>
+      </c>
+      <c r="G123" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H123" t="n">
+        <v>51.22</v>
+      </c>
+      <c r="I123" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J123" s="2" t="n">
+        <v>3.027</v>
+      </c>
+      <c r="K123" s="2" t="n">
+        <v>2.856</v>
+      </c>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M100"/>
+  <autoFilter ref="A1:M123"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-19/bursa-report-2026-10-19.xlsx
+++ b/docs/downloads/2026-10-19/bursa-report-2026-10-19.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-19" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-19'!$A$1:$M$123</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-19'!$A$1:$M$141</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -35,10 +35,10 @@
       <color rgb="00FFFFFF"/>
     </font>
     <font>
-      <color rgb="000CA30C"/>
+      <color rgb="00D03B3B"/>
     </font>
     <font>
-      <color rgb="00D03B3B"/>
+      <color rgb="000CA30C"/>
     </font>
     <font>
       <color rgb="00898781"/>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M123"/>
+  <dimension ref="A1:M141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -543,39 +543,39 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>0138</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>ZETRIX</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.905</v>
+        <v>0.05</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0.005600000000000001</v>
+        <v>-0.09089999999999999</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>35545600</v>
+        <v>48618800</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.52</v>
+        <v>0.12</v>
       </c>
       <c r="H2" t="n">
-        <v>66.83</v>
+        <v>22.63</v>
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.829</v>
+        <v>0.123</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0.736</v>
+        <v>0.322</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" s="7" t="inlineStr"/>
@@ -599,19 +599,19 @@
       <c r="D3" s="2" t="n">
         <v>0.325</v>
       </c>
-      <c r="E3" s="8" t="n">
+      <c r="E3" s="3" t="n">
         <v>-0.0441</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>34723300</v>
+        <v>43579300</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.45</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H3" t="n">
         <v>61.81</v>
       </c>
-      <c r="I3" s="9" t="inlineStr">
+      <c r="I3" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -633,39 +633,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0138</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ZETRIX</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.05</v>
+        <v>0.905</v>
       </c>
       <c r="E4" s="8" t="n">
-        <v>-0.09089999999999999</v>
+        <v>0.005600000000000001</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>34002400</v>
+        <v>36686000</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.09</v>
+        <v>0.54</v>
       </c>
       <c r="H4" t="n">
-        <v>22.63</v>
+        <v>66.83</v>
       </c>
       <c r="I4" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.123</v>
+        <v>0.829</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.322</v>
+        <v>0.736</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" s="7" t="inlineStr"/>
@@ -689,19 +689,19 @@
       <c r="D5" s="2" t="n">
         <v>0.135</v>
       </c>
-      <c r="E5" s="8" t="n">
+      <c r="E5" s="3" t="n">
         <v>-0.06900000000000001</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>25869200</v>
+        <v>26937300</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.38</v>
+        <v>0.4</v>
       </c>
       <c r="H5" t="n">
         <v>40.3</v>
       </c>
-      <c r="I5" s="9" t="inlineStr">
+      <c r="I5" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -732,27 +732,27 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.675</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>0.0075</v>
+        <v>0.6850000000000001</v>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>0.0224</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>15596600</v>
+        <v>18593600</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.62</v>
+        <v>0.74</v>
       </c>
       <c r="H6" t="n">
-        <v>75.98999999999999</v>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
+        <v>77.45</v>
+      </c>
+      <c r="I6" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.616</v>
+        <v>0.617</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>0.531</v>
@@ -783,15 +783,15 @@
         <v>0</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>12115800</v>
+        <v>14291000</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.35</v>
+        <v>0.41</v>
       </c>
       <c r="H7" t="n">
         <v>74.48999999999999</v>
       </c>
-      <c r="I7" s="6" t="inlineStr">
+      <c r="I7" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -813,39 +813,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.285</v>
-      </c>
-      <c r="E8" s="8" t="n">
-        <v>-0.0806</v>
+        <v>4.71</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>-0.0248</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>11131200</v>
+        <v>13608800</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>1.28</v>
+        <v>0.73</v>
       </c>
       <c r="H8" t="n">
-        <v>45.31</v>
+        <v>46.84</v>
       </c>
       <c r="I8" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.299</v>
+        <v>4.728</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.28</v>
+        <v>4.848</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="7" t="inlineStr"/>
@@ -858,39 +858,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>4.74</v>
-      </c>
-      <c r="E9" s="8" t="n">
-        <v>-0.0186</v>
+        <v>0.285</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>-0.0806</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>10634100</v>
+        <v>11265600</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.57</v>
+        <v>1.29</v>
       </c>
       <c r="H9" t="n">
-        <v>49.11</v>
+        <v>45.31</v>
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>4.731</v>
+        <v>0.299</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>4.848</v>
+        <v>0.28</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="7" t="inlineStr"/>
@@ -912,27 +912,27 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="E10" s="8" t="n">
-        <v>-0.0455</v>
+        <v>0.215</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>-0.0227</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>9400000</v>
+        <v>9430100</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>32.28</v>
+        <v>32.38</v>
       </c>
       <c r="H10" t="n">
-        <v>47.37</v>
-      </c>
-      <c r="I10" s="6" t="inlineStr">
+        <v>53.06</v>
+      </c>
+      <c r="I10" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.211</v>
+        <v>0.212</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>0.217</v>
@@ -963,15 +963,15 @@
         <v>0</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>8047300</v>
+        <v>8411800</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.4</v>
+        <v>0.42</v>
       </c>
       <c r="H11" t="n">
         <v>59.08</v>
       </c>
-      <c r="I11" s="6" t="inlineStr">
+      <c r="I11" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -1002,21 +1002,21 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="E12" s="8" t="n">
-        <v>-0.2222</v>
+        <v>0.04</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>-0.1111</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>7785200</v>
+        <v>7878500</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>21.05</v>
+        <v>21.3</v>
       </c>
       <c r="H12" t="n">
-        <v>62.28</v>
-      </c>
-      <c r="I12" s="6" t="inlineStr">
+        <v>70.23999999999999</v>
+      </c>
+      <c r="I12" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -1025,7 +1025,7 @@
         <v>0.026</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0.023</v>
+        <v>0.024</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="7" t="inlineStr"/>
@@ -1038,39 +1038,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="E13" s="8" t="n">
-        <v>-0.0222</v>
+        <v>0.31</v>
+      </c>
+      <c r="E13" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>7697300</v>
+        <v>7865500</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.21</v>
+        <v>0.41</v>
       </c>
       <c r="H13" t="n">
-        <v>37.57</v>
+        <v>54.55</v>
       </c>
       <c r="I13" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.478</v>
+        <v>0.309</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0.482</v>
+        <v>0.3</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="7" t="inlineStr"/>
@@ -1083,33 +1083,40 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SLG</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E14" s="10" t="n">
-        <v>0</v>
+        <v>0.435</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>-0.0333</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>6874700</v>
+        <v>7864700</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="I14" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="n"/>
-      <c r="K14" s="2" t="n"/>
+        <v>0.22</v>
+      </c>
+      <c r="H14" t="n">
+        <v>36.45</v>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>0.477</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>0.482</v>
+      </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="7" t="inlineStr"/>
     </row>
@@ -1121,40 +1128,33 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>SLG</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="E15" s="8" t="n">
-        <v>-0.0347</v>
+        <v>0.25</v>
+      </c>
+      <c r="E15" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>6086600</v>
+        <v>6874700</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="H15" t="n">
-        <v>54.64</v>
+        <v>0.28</v>
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="n">
-        <v>1.923</v>
-      </c>
-      <c r="K15" s="2" t="n">
-        <v>1.739</v>
-      </c>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="n"/>
+      <c r="K15" s="2" t="n"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="7" t="inlineStr"/>
     </row>
@@ -1166,39 +1166,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E16" s="10" t="n">
-        <v>0</v>
+        <v>1.97</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>-0.0248</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>6072500</v>
+        <v>6815300</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>1.95</v>
+        <v>0.23</v>
       </c>
       <c r="H16" t="n">
-        <v>49.08</v>
+        <v>55.91</v>
       </c>
       <c r="I16" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.295</v>
+        <v>1.925</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0.295</v>
+        <v>1.739</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="7" t="inlineStr"/>
@@ -1211,39 +1211,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>3891</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MUIIND</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="E17" s="10" t="n">
-        <v>0</v>
+        <v>2.56</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>-0.03759999999999999</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>6000400</v>
+        <v>6155400</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>3.54</v>
+        <v>0.34</v>
       </c>
       <c r="H17" t="n">
-        <v>46.69</v>
-      </c>
-      <c r="I17" s="9" t="inlineStr">
+        <v>46.31</v>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.041</v>
+        <v>2.641</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0.042</v>
+        <v>2.553</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="7" t="inlineStr"/>
@@ -1256,39 +1256,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>5156</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>XDL</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>0.005</v>
+        <v>0.295</v>
       </c>
       <c r="E18" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>5850000</v>
+        <v>6072500</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>2.38</v>
+        <v>1.95</v>
       </c>
       <c r="H18" t="n">
-        <v>44.81</v>
-      </c>
-      <c r="I18" s="9" t="inlineStr">
+        <v>49.08</v>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.007</v>
+        <v>0.295</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0.007</v>
+        <v>0.295</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="7" t="inlineStr"/>
@@ -1301,39 +1301,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>3891</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>MUIIND</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>0.31</v>
+        <v>0.04</v>
       </c>
       <c r="E19" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>5380400</v>
+        <v>6000400</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.28</v>
+        <v>3.54</v>
       </c>
       <c r="H19" t="n">
-        <v>54.55</v>
+        <v>46.69</v>
       </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.309</v>
+        <v>0.041</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0.3</v>
+        <v>0.042</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="7" t="inlineStr"/>
@@ -1346,39 +1346,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>5156</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>XDL</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="E20" s="8" t="n">
-        <v>-0.0091</v>
+        <v>0.005</v>
+      </c>
+      <c r="E20" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>5087000</v>
+        <v>5950100</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.53</v>
+        <v>2.42</v>
       </c>
       <c r="H20" t="n">
-        <v>52.65</v>
-      </c>
-      <c r="I20" s="9" t="inlineStr">
+        <v>44.81</v>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1.078</v>
+        <v>0.007</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>1.045</v>
+        <v>0.007</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="7" t="inlineStr"/>
@@ -1391,39 +1391,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E21" s="8" t="n">
-        <v>-0.0064</v>
+        <v>1.08</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>-0.0182</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>4587900</v>
+        <v>5323700</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="H21" t="n">
-        <v>49.91</v>
+        <v>51.15</v>
       </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.775</v>
+        <v>1.077</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0.776</v>
+        <v>1.045</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="7" t="inlineStr"/>
@@ -1436,39 +1436,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="E22" s="8" t="n">
-        <v>-0.03759999999999999</v>
+        <v>0.98</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>-0.0297</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>4513100</v>
+        <v>5260600</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.25</v>
+        <v>0.66</v>
       </c>
       <c r="H22" t="n">
-        <v>46.31</v>
+        <v>42.43</v>
       </c>
       <c r="I22" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>2.641</v>
+        <v>1.048</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>2.553</v>
+        <v>0.959</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="7" t="inlineStr"/>
@@ -1481,39 +1481,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="E23" s="3" t="n">
-        <v>0.0238</v>
+        <v>0.625</v>
+      </c>
+      <c r="E23" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>4218900</v>
+        <v>5092300</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.62</v>
+        <v>0.47</v>
       </c>
       <c r="H23" t="n">
-        <v>52.5</v>
+        <v>56.82</v>
       </c>
       <c r="I23" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.424</v>
+        <v>0.617</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0.416</v>
+        <v>0.615</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="7" t="inlineStr"/>
@@ -1526,39 +1526,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="E24" s="8" t="n">
-        <v>-0.0198</v>
+        <v>0.775</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>-0.0064</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>4194700</v>
+        <v>4857900</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.53</v>
+        <v>0.32</v>
       </c>
       <c r="H24" t="n">
-        <v>43.57</v>
+        <v>49.91</v>
       </c>
       <c r="I24" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>1.049</v>
+        <v>0.775</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0.959</v>
+        <v>0.776</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="7" t="inlineStr"/>
@@ -1571,39 +1571,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E25" s="10" t="n">
-        <v>0</v>
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>-0.0061</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>4156600</v>
+        <v>4823300</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.38</v>
+        <v>0.3</v>
       </c>
       <c r="H25" t="n">
-        <v>56.82</v>
-      </c>
-      <c r="I25" s="6" t="inlineStr">
+        <v>51.98</v>
+      </c>
+      <c r="I25" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.617</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0.615</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="7" t="inlineStr"/>
@@ -1616,39 +1616,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="E26" s="8" t="n">
-        <v>-0.018</v>
+        <v>0.865</v>
+      </c>
+      <c r="E26" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>4095800</v>
+        <v>4730900</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.86</v>
+        <v>0.24</v>
       </c>
       <c r="H26" t="n">
-        <v>36.28</v>
+        <v>45.57</v>
       </c>
       <c r="I26" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>1.725</v>
+        <v>0.868</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>1.768</v>
+        <v>0.869</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="7" t="inlineStr"/>
@@ -1661,39 +1661,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>1.2</v>
+        <v>0.435</v>
       </c>
       <c r="E27" s="8" t="n">
-        <v>-0.0244</v>
+        <v>0.0357</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>3912300</v>
+        <v>4645800</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.52</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H27" t="n">
-        <v>40.08</v>
+        <v>53.65</v>
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>1.236</v>
+        <v>0.425</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>1.323</v>
+        <v>0.416</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="7" t="inlineStr"/>
@@ -1706,40 +1706,33 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>0477</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>ECOSYS</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>2.35</v>
+        <v>0.775</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0.0262</v>
+        <v>-0.0127</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>3848100</v>
+        <v>4420100</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="H28" t="n">
-        <v>61.48</v>
-      </c>
-      <c r="I28" s="6" t="inlineStr">
+        <v>0.06</v>
+      </c>
+      <c r="I28" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J28" s="2" t="n">
-        <v>2.227</v>
-      </c>
-      <c r="K28" s="2" t="n">
-        <v>2.167</v>
-      </c>
+      <c r="J28" s="2" t="n"/>
+      <c r="K28" s="2" t="n"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="7" t="inlineStr"/>
     </row>
@@ -1751,39 +1744,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>0.54</v>
+        <v>6.67</v>
       </c>
       <c r="E29" s="8" t="n">
-        <v>-0.027</v>
+        <v>0.0262</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>3847600</v>
+        <v>4352800</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.19</v>
+        <v>0.45</v>
       </c>
       <c r="H29" t="n">
-        <v>45.4</v>
-      </c>
-      <c r="I29" s="9" t="inlineStr">
+        <v>28.27</v>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.572</v>
+        <v>7.208</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0.541</v>
+        <v>7.606</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="7" t="inlineStr"/>
@@ -1796,39 +1789,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="E30" s="10" t="n">
-        <v>0</v>
+        <v>1.62</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>-0.0299</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>3597900</v>
+        <v>4343100</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.49</v>
+        <v>0.91</v>
       </c>
       <c r="H30" t="n">
-        <v>55.92</v>
+        <v>34.42</v>
       </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.371</v>
+        <v>1.723</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0.369</v>
+        <v>1.767</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="7" t="inlineStr"/>
@@ -1841,39 +1834,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>0.335</v>
-      </c>
-      <c r="E31" s="8" t="n">
-        <v>-0.0147</v>
+        <v>0.375</v>
+      </c>
+      <c r="E31" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>3554700</v>
+        <v>4205400</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.37</v>
+        <v>0.57</v>
       </c>
       <c r="H31" t="n">
-        <v>47.31</v>
+        <v>55.92</v>
       </c>
       <c r="I31" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.346</v>
+        <v>0.371</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0.334</v>
+        <v>0.369</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="7" t="inlineStr"/>
@@ -1886,33 +1879,40 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0477</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ECOSYS</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E32" s="8" t="n">
-        <v>-0.0127</v>
+        <v>1.2</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>-0.0244</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>3343200</v>
+        <v>4155600</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="I32" s="6" t="inlineStr">
+        <v>0.55</v>
+      </c>
+      <c r="H32" t="n">
+        <v>40.08</v>
+      </c>
+      <c r="I32" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J32" s="2" t="n"/>
-      <c r="K32" s="2" t="n"/>
+      <c r="J32" s="2" t="n">
+        <v>1.236</v>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>1.323</v>
+      </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="7" t="inlineStr"/>
     </row>
@@ -1924,39 +1924,39 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>3.87</v>
+        <v>0.54</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>0.0403</v>
+        <v>-0.027</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>3330600</v>
+        <v>4149400</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.35</v>
+        <v>0.2</v>
       </c>
       <c r="H33" t="n">
-        <v>59.43</v>
-      </c>
-      <c r="I33" s="9" t="inlineStr">
+        <v>45.4</v>
+      </c>
+      <c r="I33" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>3.655</v>
+        <v>0.572</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>3.009</v>
+        <v>0.541</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="7" t="inlineStr"/>
@@ -1969,39 +1969,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="E34" s="3" t="n">
-        <v>0.0114</v>
+        <v>2.35</v>
+      </c>
+      <c r="E34" s="8" t="n">
+        <v>0.0262</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>3293200</v>
+        <v>4142500</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.26</v>
+        <v>1.16</v>
       </c>
       <c r="H34" t="n">
-        <v>42.31</v>
+        <v>61.48</v>
       </c>
       <c r="I34" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>2.759</v>
+        <v>2.227</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>2.738</v>
+        <v>2.167</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="7" t="inlineStr"/>
@@ -2014,39 +2014,39 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="E35" s="8" t="n">
-        <v>-0.028</v>
+        <v>4.72</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>-0.0167</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>3234000</v>
+        <v>3931700</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>1.31</v>
+        <v>0.15</v>
       </c>
       <c r="H35" t="n">
-        <v>34.76</v>
-      </c>
-      <c r="I35" s="9" t="inlineStr">
+        <v>42.05</v>
+      </c>
+      <c r="I35" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.543</v>
+        <v>4.891</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0.572</v>
+        <v>4.727</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="7" t="inlineStr"/>
@@ -2059,39 +2059,39 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.0157</v>
+        <v>-0.0207</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>3213400</v>
+        <v>3895000</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.52</v>
+        <v>0.35</v>
       </c>
       <c r="H36" t="n">
-        <v>63.45</v>
+        <v>21.41</v>
       </c>
       <c r="I36" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>1.199</v>
+        <v>1.691</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>1.188</v>
+        <v>1.944</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="7" t="inlineStr"/>
@@ -2104,39 +2104,39 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="E37" s="8" t="n">
-        <v>-0.04</v>
+        <v>1.26</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>-0.007900000000000001</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>3057400</v>
+        <v>3805600</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>1</v>
+        <v>0.62</v>
       </c>
       <c r="H37" t="n">
-        <v>29.06</v>
+        <v>59.95</v>
       </c>
       <c r="I37" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.897</v>
+        <v>1.196</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0.953</v>
+        <v>1.187</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="7" t="inlineStr"/>
@@ -2149,39 +2149,39 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>6.67</v>
+        <v>2</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>0.0262</v>
+        <v>-0.0148</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>3028200</v>
+        <v>3796400</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="H38" t="n">
-        <v>28.27</v>
-      </c>
-      <c r="I38" s="9" t="inlineStr">
+        <v>31.84</v>
+      </c>
+      <c r="I38" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>7.208</v>
+        <v>2.146</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>7.606</v>
+        <v>2.233</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="7" t="inlineStr"/>
@@ -2194,39 +2194,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>2</v>
+        <v>3.85</v>
       </c>
       <c r="E39" s="8" t="n">
-        <v>-0.0148</v>
+        <v>0.0349</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>2996000</v>
+        <v>3700100</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.23</v>
+        <v>0.39</v>
       </c>
       <c r="H39" t="n">
-        <v>31.84</v>
-      </c>
-      <c r="I39" s="9" t="inlineStr">
+        <v>58.99</v>
+      </c>
+      <c r="I39" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>2.146</v>
+        <v>3.653</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>2.233</v>
+        <v>3.008</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="7" t="inlineStr"/>
@@ -2239,39 +2239,39 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>5.17</v>
+        <v>0.33</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0.0039</v>
+        <v>-0.0294</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>2873900</v>
+        <v>3669700</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.2</v>
+        <v>0.39</v>
       </c>
       <c r="H40" t="n">
-        <v>36.22</v>
-      </c>
-      <c r="I40" s="9" t="inlineStr">
+        <v>45.62</v>
+      </c>
+      <c r="I40" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>5.5</v>
+        <v>0.345</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>5.449</v>
+        <v>0.333</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="7" t="inlineStr"/>
@@ -2284,39 +2284,39 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>1.43</v>
+        <v>2.66</v>
       </c>
       <c r="E41" s="8" t="n">
-        <v>-0.0138</v>
+        <v>0.0114</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>2870000</v>
+        <v>3514700</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.26</v>
+        <v>0.28</v>
       </c>
       <c r="H41" t="n">
-        <v>21.76</v>
-      </c>
-      <c r="I41" s="9" t="inlineStr">
+        <v>42.31</v>
+      </c>
+      <c r="I41" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>1.692</v>
+        <v>2.759</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>1.945</v>
+        <v>2.738</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="7" t="inlineStr"/>
@@ -2329,39 +2329,39 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="E42" s="8" t="n">
-        <v>-0.06480000000000001</v>
+        <v>9.880000000000001</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>-0.011</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>2864200</v>
+        <v>3475500</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.72</v>
+        <v>0.26</v>
       </c>
       <c r="H42" t="n">
-        <v>66.41</v>
-      </c>
-      <c r="I42" s="6" t="inlineStr">
+        <v>40.55</v>
+      </c>
+      <c r="I42" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.842</v>
+        <v>9.999000000000001</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0.573</v>
+        <v>10.147</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="7" t="inlineStr"/>
@@ -2374,39 +2374,39 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="E43" s="8" t="n">
-        <v>-0.0108</v>
+        <v>0.52</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>-0.028</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>2775400</v>
+        <v>3437300</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.37</v>
+        <v>1.39</v>
       </c>
       <c r="H43" t="n">
-        <v>29.85</v>
-      </c>
-      <c r="I43" s="9" t="inlineStr">
+        <v>34.76</v>
+      </c>
+      <c r="I43" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.498</v>
+        <v>0.543</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0.556</v>
+        <v>0.572</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="7" t="inlineStr"/>
@@ -2419,39 +2419,39 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="E44" s="8" t="n">
-        <v>-0.0381</v>
+        <v>0.835</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>-0.0457</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>2763200</v>
+        <v>3422500</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.23</v>
+        <v>1.12</v>
       </c>
       <c r="H44" t="n">
-        <v>49.41</v>
-      </c>
-      <c r="I44" s="9" t="inlineStr">
+        <v>28.22</v>
+      </c>
+      <c r="I44" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.519</v>
+        <v>0.897</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0.46</v>
+        <v>0.953</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="7" t="inlineStr"/>
@@ -2464,39 +2464,39 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>0.415</v>
+        <v>0.985</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>0.0247</v>
+        <v>-0.08800000000000001</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>2705900</v>
+        <v>3273100</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>1.39</v>
+        <v>0.83</v>
       </c>
       <c r="H45" t="n">
-        <v>45.72</v>
-      </c>
-      <c r="I45" s="6" t="inlineStr">
+        <v>64.31999999999999</v>
+      </c>
+      <c r="I45" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.416</v>
+        <v>0.84</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0.434</v>
+        <v>0.572</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="7" t="inlineStr"/>
@@ -2509,39 +2509,39 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="E46" s="10" t="n">
-        <v>0</v>
+        <v>5.18</v>
+      </c>
+      <c r="E46" s="8" t="n">
+        <v>0.0058</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>2683800</v>
+        <v>3189800</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.37</v>
+        <v>0.23</v>
       </c>
       <c r="H46" t="n">
-        <v>52.34</v>
-      </c>
-      <c r="I46" s="9" t="inlineStr">
+        <v>36.72</v>
+      </c>
+      <c r="I46" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>1.17</v>
+        <v>5.501</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>1.136</v>
+        <v>5.449</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="7" t="inlineStr"/>
@@ -2554,39 +2554,39 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="E47" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="4" t="n">
+        <v>3187000</v>
+      </c>
+      <c r="G47" s="5" t="n">
         <v>0.26</v>
       </c>
-      <c r="E47" s="8" t="n">
-        <v>-0.0189</v>
-      </c>
-      <c r="F47" s="4" t="n">
-        <v>2543600</v>
-      </c>
-      <c r="G47" s="5" t="n">
-        <v>0.35</v>
-      </c>
       <c r="H47" t="n">
-        <v>42.45</v>
-      </c>
-      <c r="I47" s="9" t="inlineStr">
+        <v>55.08</v>
+      </c>
+      <c r="I47" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.273</v>
+        <v>0.391</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0.294</v>
+        <v>0.378</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="7" t="inlineStr"/>
@@ -2599,39 +2599,39 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>7.15</v>
-      </c>
-      <c r="E48" s="8" t="n">
-        <v>-0.0069</v>
+        <v>0.51</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>-0.0286</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>2538700</v>
+        <v>3145200</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.16</v>
+        <v>0.26</v>
       </c>
       <c r="H48" t="n">
-        <v>32.9</v>
-      </c>
-      <c r="I48" s="9" t="inlineStr">
+        <v>50.37</v>
+      </c>
+      <c r="I48" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>7.505</v>
+        <v>0.519</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>7.684</v>
+        <v>0.461</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="7" t="inlineStr"/>
@@ -2644,39 +2644,39 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>0.445</v>
-      </c>
-      <c r="E49" s="8" t="n">
-        <v>-0.022</v>
+        <v>1.66</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>-0.006</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>2483900</v>
+        <v>3126500</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.1</v>
+        <v>0.46</v>
       </c>
       <c r="H49" t="n">
-        <v>26.49</v>
+        <v>52.91</v>
       </c>
       <c r="I49" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.506</v>
+        <v>1.628</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0.677</v>
+        <v>1.695</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="7" t="inlineStr"/>
@@ -2689,39 +2689,39 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>4.72</v>
-      </c>
-      <c r="E50" s="8" t="n">
-        <v>-0.0167</v>
+        <v>7.16</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>-0.005600000000000001</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>2468700</v>
+        <v>3108300</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.1</v>
+        <v>0.19</v>
       </c>
       <c r="H50" t="n">
-        <v>42.05</v>
-      </c>
-      <c r="I50" s="9" t="inlineStr">
+        <v>33.16</v>
+      </c>
+      <c r="I50" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>4.891</v>
+        <v>7.505</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>4.727</v>
+        <v>7.684</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="7" t="inlineStr"/>
@@ -2734,39 +2734,39 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="E51" s="8" t="n">
-        <v>-0.012</v>
+        <v>0.46</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>-0.0108</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>2425400</v>
+        <v>3095800</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="H51" t="n">
-        <v>51.49</v>
+        <v>29.85</v>
       </c>
       <c r="I51" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>1.627</v>
+        <v>0.498</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>1.695</v>
+        <v>0.556</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="7" t="inlineStr"/>
@@ -2779,39 +2779,39 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="E52" s="8" t="n">
-        <v>-0.04389999999999999</v>
+        <v>0.45</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>-0.011</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>2354300</v>
+        <v>3082100</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.45</v>
+        <v>0.12</v>
       </c>
       <c r="H52" t="n">
-        <v>48.83</v>
-      </c>
-      <c r="I52" s="9" t="inlineStr">
+        <v>27.11</v>
+      </c>
+      <c r="I52" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.507</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0.516</v>
+        <v>0.677</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="7" t="inlineStr"/>
@@ -2824,39 +2824,39 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E53" s="10" t="n">
-        <v>0</v>
+        <v>1.19</v>
+      </c>
+      <c r="E53" s="8" t="n">
+        <v>0.008500000000000001</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>2341300</v>
+        <v>2916000</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.14</v>
+        <v>0.4</v>
       </c>
       <c r="H53" t="n">
-        <v>57.16</v>
+        <v>53.56</v>
       </c>
       <c r="I53" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.8139999999999999</v>
+        <v>1.171</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0.8110000000000001</v>
+        <v>1.137</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="7" t="inlineStr"/>
@@ -2869,39 +2869,39 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>0.405</v>
-      </c>
-      <c r="E54" s="10" t="n">
-        <v>0</v>
+        <v>0.41</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>-0.0353</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>2267700</v>
+        <v>2810800</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.18</v>
+        <v>0.36</v>
       </c>
       <c r="H54" t="n">
-        <v>55.08</v>
-      </c>
-      <c r="I54" s="9" t="inlineStr">
+        <v>22.61</v>
+      </c>
+      <c r="I54" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.391</v>
+        <v>0.526</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0.378</v>
+        <v>0.614</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="7" t="inlineStr"/>
@@ -2914,39 +2914,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="E55" s="10" t="n">
-        <v>0</v>
+        <v>0.41</v>
+      </c>
+      <c r="E55" s="8" t="n">
+        <v>0.0123</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>2261500</v>
+        <v>2792200</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="H55" t="n">
-        <v>52</v>
+        <v>41.24</v>
       </c>
       <c r="I55" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.916</v>
+        <v>0.416</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0.874</v>
+        <v>0.434</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="7" t="inlineStr"/>
@@ -2959,39 +2959,39 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0395</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>OGX</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>0.47</v>
+        <v>0.89</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>0.033</v>
+        <v>-0.0326</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>2241600</v>
+        <v>2727600</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.86</v>
+        <v>1.64</v>
       </c>
       <c r="H56" t="n">
-        <v>57.98</v>
+        <v>47.65</v>
       </c>
       <c r="I56" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.447</v>
+        <v>0.913</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0.45</v>
+        <v>0.874</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="7" t="inlineStr"/>
@@ -3004,39 +3004,39 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>0.415</v>
-      </c>
-      <c r="E57" s="8" t="n">
-        <v>-0.0119</v>
+        <v>0.26</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>-0.0189</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>2212700</v>
+        <v>2717700</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.23</v>
+        <v>0.38</v>
       </c>
       <c r="H57" t="n">
-        <v>43.52</v>
-      </c>
-      <c r="I57" s="9" t="inlineStr">
+        <v>42.45</v>
+      </c>
+      <c r="I57" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.438</v>
+        <v>0.273</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0.434</v>
+        <v>0.294</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="7" t="inlineStr"/>
@@ -3049,39 +3049,39 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>5041</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>PBA</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="E58" s="10" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>-0.0196</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>2130500</v>
+        <v>2636500</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.6899999999999999</v>
+        <v>8.08</v>
       </c>
       <c r="H58" t="n">
-        <v>82.09</v>
+        <v>32</v>
       </c>
       <c r="I58" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>2.827</v>
+        <v>2.091</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>2.43</v>
+        <v>2.156</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="7" t="inlineStr"/>
@@ -3094,39 +3094,39 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E59" s="10" t="n">
-        <v>0</v>
+        <v>0.545</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>-0.04389999999999999</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>2099600</v>
+        <v>2570000</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.11</v>
+        <v>0.5</v>
       </c>
       <c r="H59" t="n">
-        <v>45.57</v>
+        <v>48.83</v>
       </c>
       <c r="I59" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.868</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0.869</v>
+        <v>0.516</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="7" t="inlineStr"/>
@@ -3139,40 +3139,38 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>0469</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>GTA</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="E60" s="8" t="n">
-        <v>-0.042</v>
+        <v>0.24</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>-0.04</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>2082600</v>
+        <v>2411900</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.23</v>
+        <v>0.68</v>
       </c>
       <c r="H60" t="n">
-        <v>36.38</v>
-      </c>
-      <c r="I60" s="9" t="inlineStr">
+        <v>16.11</v>
+      </c>
+      <c r="I60" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.647</v>
-      </c>
-      <c r="K60" s="2" t="n">
-        <v>0.62</v>
-      </c>
+        <v>0.272</v>
+      </c>
+      <c r="K60" s="2" t="n"/>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="7" t="inlineStr"/>
     </row>
@@ -3184,39 +3182,39 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="E61" s="3" t="n">
-        <v>0.0068</v>
+        <v>0.205</v>
+      </c>
+      <c r="E61" s="8" t="n">
+        <v>0.009899999999999999</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>1995900</v>
+        <v>2311200</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.24</v>
+        <v>0.1</v>
       </c>
       <c r="H61" t="n">
-        <v>40.73</v>
-      </c>
-      <c r="I61" s="9" t="inlineStr">
+        <v>39.23</v>
+      </c>
+      <c r="I61" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.769</v>
+        <v>0.218</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0.771</v>
+        <v>0.235</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="7" t="inlineStr"/>
@@ -3229,38 +3227,40 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0469</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>GTA</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="E62" s="8" t="n">
-        <v>-0.04</v>
+        <v>0.575</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>-0.0336</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>1905400</v>
+        <v>2295700</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.54</v>
+        <v>0.25</v>
       </c>
       <c r="H62" t="n">
-        <v>16.11</v>
-      </c>
-      <c r="I62" s="9" t="inlineStr">
+        <v>37.01</v>
+      </c>
+      <c r="I62" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.272</v>
-      </c>
-      <c r="K62" s="2" t="n"/>
+        <v>0.648</v>
+      </c>
+      <c r="K62" s="2" t="n">
+        <v>0.62</v>
+      </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="7" t="inlineStr"/>
     </row>
@@ -3272,39 +3272,39 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>9.949999999999999</v>
-      </c>
-      <c r="E63" s="8" t="n">
-        <v>-0.004</v>
+        <v>0.415</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>-0.0119</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>1901000</v>
+        <v>2291000</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.14</v>
+        <v>0.24</v>
       </c>
       <c r="H63" t="n">
-        <v>44.09</v>
+        <v>43.52</v>
       </c>
       <c r="I63" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>10.006</v>
+        <v>0.438</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>10.149</v>
+        <v>0.434</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="7" t="inlineStr"/>
@@ -3317,38 +3317,40 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="E64" s="8" t="n">
-        <v>-0.0137</v>
+        <v>3.08</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>-0.0032</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>1870300</v>
+        <v>2279600</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.32</v>
+        <v>0.74</v>
       </c>
       <c r="H64" t="n">
-        <v>62.55</v>
-      </c>
-      <c r="I64" s="6" t="inlineStr">
+        <v>80.70999999999999</v>
+      </c>
+      <c r="I64" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.319</v>
-      </c>
-      <c r="K64" s="2" t="n"/>
+        <v>2.827</v>
+      </c>
+      <c r="K64" s="2" t="n">
+        <v>2.429</v>
+      </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="7" t="inlineStr"/>
     </row>
@@ -3360,39 +3362,39 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>0395</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>OGX</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>0.41</v>
+        <v>0.465</v>
       </c>
       <c r="E65" s="8" t="n">
-        <v>-0.0353</v>
+        <v>0.022</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>1757100</v>
+        <v>2257600</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0.22</v>
+        <v>0.86</v>
       </c>
       <c r="H65" t="n">
-        <v>22.61</v>
+        <v>56.6</v>
       </c>
       <c r="I65" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.526</v>
+        <v>0.447</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>0.614</v>
+        <v>0.449</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="7" t="inlineStr"/>
@@ -3405,39 +3407,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>0.63</v>
+        <v>0.745</v>
       </c>
       <c r="E66" s="8" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.0136</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>1705700</v>
+        <v>2222000</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>0.76</v>
+        <v>0.27</v>
       </c>
       <c r="H66" t="n">
-        <v>47.67</v>
+        <v>42.4</v>
       </c>
       <c r="I66" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.637</v>
+        <v>0.769</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0.622</v>
+        <v>0.771</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="7" t="inlineStr"/>
@@ -3450,39 +3452,39 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>5271</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>PECCA</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="E67" s="10" t="n">
-        <v>0</v>
+        <v>1.22</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>-0.0394</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>1681500</v>
+        <v>1925600</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>0.86</v>
+        <v>0.46</v>
       </c>
       <c r="H67" t="n">
-        <v>43.62</v>
-      </c>
-      <c r="I67" s="9" t="inlineStr">
+        <v>23.54</v>
+      </c>
+      <c r="I67" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>1.367</v>
+        <v>1.393</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>1.343</v>
+        <v>1.561</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="7" t="inlineStr"/>
@@ -3495,40 +3497,38 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="E68" s="8" t="n">
-        <v>-0.0301</v>
+        <v>0.36</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>-0.0137</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>1639600</v>
+        <v>1922000</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>0.68</v>
+        <v>0.33</v>
       </c>
       <c r="H68" t="n">
-        <v>55.19</v>
+        <v>62.55</v>
       </c>
       <c r="I68" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>1.259</v>
-      </c>
-      <c r="K68" s="2" t="n">
-        <v>1.173</v>
-      </c>
+        <v>0.319</v>
+      </c>
+      <c r="K68" s="2" t="n"/>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="7" t="inlineStr"/>
     </row>
@@ -3540,39 +3540,39 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>VELESTO</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>0.205</v>
-      </c>
-      <c r="E69" s="3" t="n">
-        <v>0.009899999999999999</v>
+        <v>0.965</v>
+      </c>
+      <c r="E69" s="8" t="n">
+        <v>0.0052</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>1574500</v>
+        <v>1868000</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.32</v>
       </c>
       <c r="H69" t="n">
-        <v>39.23</v>
+        <v>66.12</v>
       </c>
       <c r="I69" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.218</v>
+        <v>0.925</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0.235</v>
+        <v>0.877</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="7" t="inlineStr"/>
@@ -3585,39 +3585,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>0.335</v>
+        <v>0.625</v>
       </c>
       <c r="E70" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>1524400</v>
+        <v>1794400</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>0.32</v>
+        <v>0.53</v>
       </c>
       <c r="H70" t="n">
-        <v>47.09</v>
-      </c>
-      <c r="I70" s="6" t="inlineStr">
+        <v>70.16</v>
+      </c>
+      <c r="I70" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.335</v>
+        <v>0.617</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>0.343</v>
+        <v>0.605</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="7" t="inlineStr"/>
@@ -3630,39 +3630,39 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0192</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>INTA</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E71" s="8" t="n">
-        <v>-0.013</v>
+        <v>2.08</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>-0.0095</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>1514500</v>
+        <v>1778100</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="H71" t="n">
-        <v>41.3</v>
+        <v>45.7</v>
       </c>
       <c r="I71" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.394</v>
+        <v>2.107</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>0.389</v>
+        <v>2.101</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="7" t="inlineStr"/>
@@ -3675,39 +3675,39 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="E72" s="10" t="n">
-        <v>0</v>
+        <v>1.3</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>-0.0226</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>1461200</v>
+        <v>1769500</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>0.25</v>
+        <v>0.74</v>
       </c>
       <c r="H72" t="n">
-        <v>65.06</v>
+        <v>56.17</v>
       </c>
       <c r="I72" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.924</v>
+        <v>1.26</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0.877</v>
+        <v>1.173</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="7" t="inlineStr"/>
@@ -3720,39 +3720,39 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>PECCA</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="E73" s="8" t="n">
-        <v>-0.008500000000000001</v>
+        <v>1.35</v>
+      </c>
+      <c r="E73" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>1437100</v>
+        <v>1728800</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>0.34</v>
+        <v>0.89</v>
       </c>
       <c r="H73" t="n">
-        <v>67.36</v>
+        <v>43.62</v>
       </c>
       <c r="I73" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.509</v>
+        <v>1.367</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>0.468</v>
+        <v>1.343</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="7" t="inlineStr"/>
@@ -3765,39 +3765,39 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="E74" s="8" t="n">
-        <v>-0.0175</v>
+        <v>0.635</v>
+      </c>
+      <c r="E74" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>1433800</v>
+        <v>1715400</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>0.24</v>
+        <v>0.77</v>
       </c>
       <c r="H74" t="n">
-        <v>21.33</v>
+        <v>50.9</v>
       </c>
       <c r="I74" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.333</v>
+        <v>0.637</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0.372</v>
+        <v>0.622</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="7" t="inlineStr"/>
@@ -3810,39 +3810,39 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>8524</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>TALIWRK</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>0.225</v>
+        <v>4.48</v>
       </c>
       <c r="E75" s="8" t="n">
-        <v>-0.0217</v>
+        <v>0.03700000000000001</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>1361700</v>
+        <v>1702800</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>0.68</v>
+        <v>0.32</v>
       </c>
       <c r="H75" t="n">
-        <v>34.68</v>
+        <v>53.65</v>
       </c>
       <c r="I75" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.243</v>
+        <v>4.364</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>0.256</v>
+        <v>4.432</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="7" t="inlineStr"/>
@@ -3855,39 +3855,39 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>DATASONIC</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>0.585</v>
-      </c>
-      <c r="E76" s="8" t="n">
-        <v>-0.0488</v>
+        <v>0.28</v>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>-0.0175</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>1303100</v>
+        <v>1695500</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>0.23</v>
+        <v>0.14</v>
       </c>
       <c r="H76" t="n">
-        <v>55.93</v>
-      </c>
-      <c r="I76" s="9" t="inlineStr">
+        <v>46.28</v>
+      </c>
+      <c r="I76" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.569</v>
+        <v>0.291</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>0.47</v>
+        <v>0.283</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="7" t="inlineStr"/>
@@ -3900,39 +3900,39 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>0.725</v>
-      </c>
-      <c r="E77" s="8" t="n">
-        <v>-0.0461</v>
+        <v>0.585</v>
+      </c>
+      <c r="E77" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>1302600</v>
+        <v>1659100</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>0.24</v>
+        <v>0.4</v>
       </c>
       <c r="H77" t="n">
-        <v>46.5</v>
+        <v>68.69</v>
       </c>
       <c r="I77" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.76</v>
+        <v>0.509</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.468</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="7" t="inlineStr"/>
@@ -3945,39 +3945,39 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>5932</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>BPURI</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="E78" s="8" t="n">
-        <v>-0.0233</v>
+        <v>0.255</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>-0.0192</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>1297400</v>
+        <v>1650400</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>1.89</v>
+        <v>0.19</v>
       </c>
       <c r="H78" t="n">
-        <v>38.22</v>
-      </c>
-      <c r="I78" s="9" t="inlineStr">
+        <v>27.74</v>
+      </c>
+      <c r="I78" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.223</v>
+        <v>0.276</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>0.232</v>
+        <v>0.301</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="7" t="inlineStr"/>
@@ -3990,39 +3990,39 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>IOIPG</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="E79" s="3" t="n">
-        <v>0.038</v>
+        <v>0.335</v>
+      </c>
+      <c r="E79" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>1272700</v>
+        <v>1641100</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>0.21</v>
+        <v>0.35</v>
       </c>
       <c r="H79" t="n">
-        <v>39.03</v>
+        <v>47.09</v>
       </c>
       <c r="I79" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>3.373</v>
+        <v>0.335</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>3.604</v>
+        <v>0.343</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="7" t="inlineStr"/>
@@ -4035,39 +4035,39 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>IOIPG</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>0.875</v>
+        <v>3.28</v>
       </c>
       <c r="E80" s="8" t="n">
-        <v>-0.0223</v>
+        <v>0.038</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>1272200</v>
+        <v>1632100</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>0.16</v>
+        <v>0.27</v>
       </c>
       <c r="H80" t="n">
-        <v>43.95</v>
-      </c>
-      <c r="I80" s="9" t="inlineStr">
+        <v>39.03</v>
+      </c>
+      <c r="I80" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.928</v>
+        <v>3.373</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0.847</v>
+        <v>3.604</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="7" t="inlineStr"/>
@@ -4080,39 +4080,39 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="E81" s="8" t="n">
-        <v>-0.0048</v>
+        <v>0.725</v>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>-0.0461</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>1260300</v>
+        <v>1602700</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="H81" t="n">
-        <v>47.26</v>
+        <v>46.5</v>
       </c>
       <c r="I81" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>2.108</v>
+        <v>0.76</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>2.101</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="7" t="inlineStr"/>
@@ -4125,39 +4125,39 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E82" s="8" t="n">
-        <v>-0.0155</v>
+        <v>0.87</v>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>-0.0279</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>1241300</v>
+        <v>1595300</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>0.14</v>
+        <v>0.21</v>
       </c>
       <c r="H82" t="n">
-        <v>40.95</v>
-      </c>
-      <c r="I82" s="9" t="inlineStr">
+        <v>43.36</v>
+      </c>
+      <c r="I82" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.678</v>
+        <v>0.928</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.847</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="7" t="inlineStr"/>
@@ -4170,39 +4170,39 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>0372</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>CHEEDING</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="E83" s="8" t="n">
-        <v>-0.0273</v>
+        <v>0.485</v>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>-0.0583</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>1199500</v>
+        <v>1553000</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>0.2</v>
+        <v>0.36</v>
       </c>
       <c r="H83" t="n">
-        <v>41.03</v>
-      </c>
-      <c r="I83" s="9" t="inlineStr">
+        <v>28.14</v>
+      </c>
+      <c r="I83" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>2.603</v>
+        <v>0.58</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>2.607</v>
+        <v>0.599</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="7" t="inlineStr"/>
@@ -4215,39 +4215,39 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>0192</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>INTA</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="E84" s="8" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0.38</v>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>-0.013</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>1190500</v>
+        <v>1538400</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>0.34</v>
+        <v>0.57</v>
       </c>
       <c r="H84" t="n">
-        <v>47.42</v>
-      </c>
-      <c r="I84" s="9" t="inlineStr">
+        <v>41.3</v>
+      </c>
+      <c r="I84" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>1.238</v>
+        <v>0.394</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>1.067</v>
+        <v>0.389</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="7" t="inlineStr"/>
@@ -4260,39 +4260,39 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>1.23</v>
+        <v>5.73</v>
       </c>
       <c r="E85" s="8" t="n">
-        <v>-0.0315</v>
+        <v>0.006999999999999999</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>1176900</v>
+        <v>1488100</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>0.28</v>
+        <v>0.2</v>
       </c>
       <c r="H85" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="I85" s="9" t="inlineStr">
+        <v>29.97</v>
+      </c>
+      <c r="I85" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>1.394</v>
+        <v>6.022</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>1.561</v>
+        <v>6.308</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="7" t="inlineStr"/>
@@ -4305,39 +4305,39 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>4.41</v>
+        <v>0.595</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>0.0208</v>
+        <v>-0.0325</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>1131000</v>
+        <v>1482500</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>0.21</v>
+        <v>0.26</v>
       </c>
       <c r="H86" t="n">
-        <v>51.22</v>
+        <v>57.47</v>
       </c>
       <c r="I86" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>4.357</v>
+        <v>0.57</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>4.431</v>
+        <v>0.47</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="7" t="inlineStr"/>
@@ -4350,39 +4350,39 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="E87" s="8" t="n">
-        <v>-0.018</v>
+        <v>0.285</v>
+      </c>
+      <c r="E87" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>1130900</v>
+        <v>1466300</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="H87" t="n">
-        <v>56.65</v>
-      </c>
-      <c r="I87" s="9" t="inlineStr">
+        <v>22.28</v>
+      </c>
+      <c r="I87" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>1.053</v>
+        <v>0.333</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>0.913</v>
+        <v>0.372</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="7" t="inlineStr"/>
@@ -4395,39 +4395,39 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>8524</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>TALIWRK</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>5.75</v>
+        <v>0.225</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>0.0105</v>
+        <v>-0.0217</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>1125900</v>
+        <v>1404000</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>0.15</v>
+        <v>0.7</v>
       </c>
       <c r="H88" t="n">
-        <v>31.42</v>
-      </c>
-      <c r="I88" s="9" t="inlineStr">
+        <v>34.68</v>
+      </c>
+      <c r="I88" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>6.024</v>
+        <v>0.243</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>6.309</v>
+        <v>0.256</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="7" t="inlineStr"/>
@@ -4440,39 +4440,39 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>DATASONIC</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="E89" s="8" t="n">
-        <v>-0.0175</v>
+        <v>1.19</v>
+      </c>
+      <c r="E89" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>1100900</v>
+        <v>1391200</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>0.09</v>
+        <v>0.4</v>
       </c>
       <c r="H89" t="n">
-        <v>46.28</v>
-      </c>
-      <c r="I89" s="9" t="inlineStr">
+        <v>48.4</v>
+      </c>
+      <c r="I89" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.291</v>
+        <v>1.239</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>0.283</v>
+        <v>1.068</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="7" t="inlineStr"/>
@@ -4485,39 +4485,39 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="E90" s="10" t="n">
-        <v>0</v>
+        <v>1.9</v>
+      </c>
+      <c r="E90" s="8" t="n">
+        <v>0.016</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>1097400</v>
+        <v>1379200</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>0.12</v>
+        <v>0.24</v>
       </c>
       <c r="H90" t="n">
-        <v>41.23</v>
+        <v>45.71</v>
       </c>
       <c r="I90" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>1.298</v>
+        <v>1.92</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>1.314</v>
+        <v>1.95</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="7" t="inlineStr"/>
@@ -4530,39 +4530,39 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>0261</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>COSMOS</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>0.47</v>
+        <v>0.42</v>
       </c>
       <c r="E91" s="8" t="n">
-        <v>-0.0105</v>
+        <v>0.05</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>1057600</v>
+        <v>1376500</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>0.12</v>
+        <v>4.13</v>
       </c>
       <c r="H91" t="n">
-        <v>35.57</v>
+        <v>70.20999999999999</v>
       </c>
       <c r="I91" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.506</v>
+        <v>0.382</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>0.524</v>
+        <v>0.363</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="7" t="inlineStr"/>
@@ -4575,39 +4575,39 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="E92" s="8" t="n">
-        <v>-0.0323</v>
+        <v>2.49</v>
+      </c>
+      <c r="E92" s="3" t="n">
+        <v>-0.0273</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>1056900</v>
+        <v>1367400</v>
       </c>
       <c r="G92" s="5" t="n">
-        <v>0.43</v>
+        <v>0.23</v>
       </c>
       <c r="H92" t="n">
-        <v>53.86</v>
-      </c>
-      <c r="I92" s="9" t="inlineStr">
+        <v>41.03</v>
+      </c>
+      <c r="I92" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.734</v>
+        <v>2.603</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>0.704</v>
+        <v>2.607</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="7" t="inlineStr"/>
@@ -4620,39 +4620,39 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0388</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>SEMICO</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E93" s="10" t="n">
-        <v>0</v>
+        <v>0.635</v>
+      </c>
+      <c r="E93" s="3" t="n">
+        <v>-0.0155</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>1054300</v>
+        <v>1329700</v>
       </c>
       <c r="G93" s="5" t="n">
-        <v>0.31</v>
+        <v>0.15</v>
       </c>
       <c r="H93" t="n">
-        <v>70.16</v>
+        <v>40.95</v>
       </c>
       <c r="I93" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.617</v>
+        <v>0.678</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>0.605</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="7" t="inlineStr"/>
@@ -4665,39 +4665,39 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0278</t>
+          <t>5932</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>EDELTEQ</t>
+          <t>BPURI</t>
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>0.415</v>
-      </c>
-      <c r="E94" s="8" t="n">
-        <v>-0.0349</v>
+        <v>0.21</v>
+      </c>
+      <c r="E94" s="3" t="n">
+        <v>-0.0233</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>1023300</v>
+        <v>1297400</v>
       </c>
       <c r="G94" s="5" t="n">
-        <v>0.18</v>
+        <v>1.89</v>
       </c>
       <c r="H94" t="n">
-        <v>57.05</v>
+        <v>38.22</v>
       </c>
       <c r="I94" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.39</v>
+        <v>0.223</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>0.36</v>
+        <v>0.232</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="7" t="inlineStr"/>
@@ -4710,39 +4710,39 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0450</t>
+          <t>0298</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>MFGROUP</t>
+          <t>WENTEL</t>
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="E95" s="8" t="n">
-        <v>-0.0175</v>
+        <v>0.235</v>
+      </c>
+      <c r="E95" s="3" t="n">
+        <v>-0.0408</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>1006700</v>
+        <v>1295300</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>1.06</v>
+        <v>0.76</v>
       </c>
       <c r="H95" t="n">
-        <v>55.75</v>
+        <v>36.24</v>
       </c>
       <c r="I95" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.276</v>
+        <v>0.254</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>0.267</v>
+        <v>0.274</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="7" t="inlineStr"/>
@@ -4755,39 +4755,39 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>5248</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>BAUTO</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E96" s="3" t="n">
-        <v>0.0227</v>
+        <v>1.11</v>
+      </c>
+      <c r="E96" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>999300</v>
+        <v>1294300</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>0.61</v>
+        <v>0.29</v>
       </c>
       <c r="H96" t="n">
-        <v>51.19</v>
+        <v>58.81</v>
       </c>
       <c r="I96" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.893</v>
+        <v>1.055</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>0.908</v>
+        <v>0.914</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="7" t="inlineStr"/>
@@ -4800,39 +4800,39 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="E97" s="10" t="n">
-        <v>0</v>
+        <v>1.24</v>
+      </c>
+      <c r="E97" s="3" t="n">
+        <v>-0.008</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>998300</v>
+        <v>1243100</v>
       </c>
       <c r="G97" s="5" t="n">
-        <v>0.23</v>
+        <v>0.13</v>
       </c>
       <c r="H97" t="n">
-        <v>49.06</v>
-      </c>
-      <c r="I97" s="9" t="inlineStr">
+        <v>40.01</v>
+      </c>
+      <c r="I97" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.598</v>
+        <v>1.297</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>0.586</v>
+        <v>1.314</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="7" t="inlineStr"/>
@@ -4845,39 +4845,39 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>5248</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>BAUTO</t>
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>0.67</v>
+        <v>0.905</v>
       </c>
       <c r="E98" s="8" t="n">
-        <v>-0.0219</v>
+        <v>0.0284</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>986900</v>
+        <v>1233400</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>0.37</v>
+        <v>0.76</v>
       </c>
       <c r="H98" t="n">
-        <v>59.56</v>
-      </c>
-      <c r="I98" s="6" t="inlineStr">
+        <v>52.78</v>
+      </c>
+      <c r="I98" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.647</v>
+        <v>0.893</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.908</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="7" t="inlineStr"/>
@@ -4890,39 +4890,39 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>0245</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>MNHLDG</t>
         </is>
       </c>
       <c r="D99" s="2" t="n">
-        <v>0.8149999999999999</v>
+        <v>3.77</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>0.0252</v>
+        <v>-0.0157</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v>966400</v>
+        <v>1230100</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>0.17</v>
+        <v>0.42</v>
       </c>
       <c r="H99" t="n">
-        <v>64.98999999999999</v>
-      </c>
-      <c r="I99" s="9" t="inlineStr">
+        <v>48.07</v>
+      </c>
+      <c r="I99" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.793</v>
+        <v>3.843</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>0.771</v>
+        <v>3.681</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="7" t="inlineStr"/>
@@ -4935,39 +4935,39 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0325</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D100" s="2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="E100" s="10" t="n">
-        <v>0</v>
+        <v>0.925</v>
+      </c>
+      <c r="E100" s="3" t="n">
+        <v>-0.0054</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>957000</v>
+        <v>1209300</v>
       </c>
       <c r="G100" s="5" t="n">
-        <v>0.49</v>
+        <v>0.31</v>
       </c>
       <c r="H100" t="n">
-        <v>51.14</v>
+        <v>25.84</v>
       </c>
       <c r="I100" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>1.091</v>
+        <v>0.97</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>1.097</v>
+        <v>1.053</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="7" t="inlineStr"/>
@@ -4980,39 +4980,39 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>0278</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>EDELTEQ</t>
         </is>
       </c>
       <c r="D101" s="2" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="E101" s="8" t="n">
-        <v>-0.0455</v>
+        <v>0.415</v>
+      </c>
+      <c r="E101" s="3" t="n">
+        <v>-0.0349</v>
       </c>
       <c r="F101" s="4" t="n">
-        <v>856500</v>
+        <v>1204900</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>0.27</v>
+        <v>0.21</v>
       </c>
       <c r="H101" t="n">
-        <v>48.93</v>
+        <v>57.05</v>
       </c>
       <c r="I101" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>1.286</v>
+        <v>0.39</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>1.225</v>
+        <v>0.36</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="7" t="inlineStr"/>
@@ -5025,39 +5025,39 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>AWC</t>
         </is>
       </c>
       <c r="D102" s="2" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E102" s="8" t="n">
-        <v>-0.0252</v>
+        <v>0.665</v>
+      </c>
+      <c r="E102" s="3" t="n">
+        <v>-0.0292</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>855900</v>
+        <v>1195300</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>0.39</v>
+        <v>0.44</v>
       </c>
       <c r="H102" t="n">
-        <v>15.02</v>
+        <v>58.27</v>
       </c>
       <c r="I102" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.647</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>1.077</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="7" t="inlineStr"/>
@@ -5070,39 +5070,39 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>UWC</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D103" s="2" t="n">
-        <v>7.18</v>
-      </c>
-      <c r="E103" s="8" t="n">
-        <v>-0.0164</v>
+        <v>0.585</v>
+      </c>
+      <c r="E103" s="3" t="n">
+        <v>-0.008500000000000001</v>
       </c>
       <c r="F103" s="4" t="n">
-        <v>846800</v>
+        <v>1190600</v>
       </c>
       <c r="G103" s="5" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="H103" t="n">
-        <v>48.79</v>
-      </c>
-      <c r="I103" s="9" t="inlineStr">
+        <v>47.94</v>
+      </c>
+      <c r="I103" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J103" s="2" t="n">
-        <v>7.34</v>
+        <v>0.597</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>6.895</v>
+        <v>0.586</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="7" t="inlineStr"/>
@@ -5115,39 +5115,39 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D104" s="2" t="n">
-        <v>0.845</v>
-      </c>
-      <c r="E104" s="10" t="n">
-        <v>0</v>
+        <v>0.82</v>
+      </c>
+      <c r="E104" s="8" t="n">
+        <v>0.0314</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v>834000</v>
+        <v>1186300</v>
       </c>
       <c r="G104" s="5" t="n">
-        <v>0.28</v>
+        <v>0.21</v>
       </c>
       <c r="H104" t="n">
-        <v>17.21</v>
+        <v>66.7</v>
       </c>
       <c r="I104" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.916</v>
+        <v>0.794</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>0.973</v>
+        <v>0.772</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="7" t="inlineStr"/>
@@ -5160,39 +5160,39 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>0325</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="D105" s="2" t="n">
-        <v>0.835</v>
-      </c>
-      <c r="E105" s="8" t="n">
-        <v>-0.0176</v>
+        <v>1.1</v>
+      </c>
+      <c r="E105" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F105" s="4" t="n">
-        <v>807200</v>
+        <v>1126100</v>
       </c>
       <c r="G105" s="5" t="n">
-        <v>0.23</v>
+        <v>0.57</v>
       </c>
       <c r="H105" t="n">
-        <v>53.24</v>
+        <v>51.14</v>
       </c>
       <c r="I105" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.827</v>
+        <v>1.091</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>0.781</v>
+        <v>1.097</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="7" t="inlineStr"/>
@@ -5205,39 +5205,39 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D106" s="2" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="E106" s="8" t="n">
-        <v>-0.0235</v>
+        <v>0.785</v>
+      </c>
+      <c r="E106" s="3" t="n">
+        <v>-0.0126</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v>784600</v>
+        <v>1119000</v>
       </c>
       <c r="G106" s="5" t="n">
-        <v>0.27</v>
+        <v>0.51</v>
       </c>
       <c r="H106" t="n">
-        <v>46.79</v>
-      </c>
-      <c r="I106" s="9" t="inlineStr">
+        <v>15.53</v>
+      </c>
+      <c r="I106" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J106" s="2" t="n">
-        <v>3.84</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>3.68</v>
+        <v>1.078</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="7" t="inlineStr"/>
@@ -5250,39 +5250,39 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>0045</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>SSB8</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E107" s="8" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.75</v>
+      </c>
+      <c r="E107" s="3" t="n">
+        <v>-0.0323</v>
       </c>
       <c r="F107" s="4" t="n">
-        <v>758800</v>
+        <v>1107500</v>
       </c>
       <c r="G107" s="5" t="n">
-        <v>0.2</v>
+        <v>0.45</v>
       </c>
       <c r="H107" t="n">
-        <v>48.81</v>
-      </c>
-      <c r="I107" s="9" t="inlineStr">
+        <v>53.86</v>
+      </c>
+      <c r="I107" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.638</v>
+        <v>0.734</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>0.614</v>
+        <v>0.704</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="7" t="inlineStr"/>
@@ -5295,39 +5295,39 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>UWC</t>
         </is>
       </c>
       <c r="D108" s="2" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="E108" s="8" t="n">
-        <v>-0.0273</v>
+        <v>7.18</v>
+      </c>
+      <c r="E108" s="3" t="n">
+        <v>-0.0164</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>756500</v>
+        <v>1082200</v>
       </c>
       <c r="G108" s="5" t="n">
-        <v>0.15</v>
+        <v>0.25</v>
       </c>
       <c r="H108" t="n">
-        <v>32.47</v>
-      </c>
-      <c r="I108" s="9" t="inlineStr">
+        <v>48.79</v>
+      </c>
+      <c r="I108" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J108" s="2" t="n">
-        <v>2.807</v>
+        <v>7.34</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>2.877</v>
+        <v>6.895</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="7" t="inlineStr"/>
@@ -5340,39 +5340,39 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D109" s="2" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="E109" s="8" t="n">
-        <v>-0.0086</v>
+        <v>0.47</v>
+      </c>
+      <c r="E109" s="3" t="n">
+        <v>-0.0105</v>
       </c>
       <c r="F109" s="4" t="n">
-        <v>742300</v>
+        <v>1057600</v>
       </c>
       <c r="G109" s="5" t="n">
-        <v>0.18</v>
+        <v>0.12</v>
       </c>
       <c r="H109" t="n">
-        <v>50.8</v>
-      </c>
-      <c r="I109" s="9" t="inlineStr">
+        <v>35.57</v>
+      </c>
+      <c r="I109" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J109" s="2" t="n">
-        <v>1.159</v>
+        <v>0.506</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>1.1</v>
+        <v>0.524</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="7" t="inlineStr"/>
@@ -5385,39 +5385,39 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>0217</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>PWRWELL</t>
         </is>
       </c>
       <c r="D110" s="2" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="E110" s="8" t="n">
-        <v>-0.0107</v>
+        <v>1.14</v>
+      </c>
+      <c r="E110" s="3" t="n">
+        <v>-0.0172</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>727100</v>
+        <v>1028600</v>
       </c>
       <c r="G110" s="5" t="n">
-        <v>0.19</v>
+        <v>0.24</v>
       </c>
       <c r="H110" t="n">
-        <v>39.95</v>
-      </c>
-      <c r="I110" s="9" t="inlineStr">
+        <v>49.11</v>
+      </c>
+      <c r="I110" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J110" s="2" t="n">
-        <v>2.896</v>
+        <v>1.159</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>3.013</v>
+        <v>1.1</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="7" t="inlineStr"/>
@@ -5430,39 +5430,39 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>5162</t>
+          <t>0450</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>VSTECS</t>
+          <t>MFGROUP</t>
         </is>
       </c>
       <c r="D111" s="2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="E111" s="8" t="n">
-        <v>-0.0323</v>
+        <v>0.28</v>
+      </c>
+      <c r="E111" s="3" t="n">
+        <v>-0.0175</v>
       </c>
       <c r="F111" s="4" t="n">
-        <v>626500</v>
+        <v>1006700</v>
       </c>
       <c r="G111" s="5" t="n">
-        <v>0.36</v>
+        <v>1.06</v>
       </c>
       <c r="H111" t="n">
-        <v>35.96</v>
+        <v>55.75</v>
       </c>
       <c r="I111" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J111" s="2" t="n">
-        <v>1.621</v>
+        <v>0.276</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>1.664</v>
+        <v>0.267</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="7" t="inlineStr"/>
@@ -5475,39 +5475,39 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>0099</t>
+          <t>5162</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>SCICOM</t>
+          <t>VSTECS</t>
         </is>
       </c>
       <c r="D112" s="2" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0.0048</v>
+        <v>-0.0323</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>624500</v>
+        <v>986000</v>
       </c>
       <c r="G112" s="5" t="n">
-        <v>0.84</v>
+        <v>0.57</v>
       </c>
       <c r="H112" t="n">
-        <v>40.78</v>
-      </c>
-      <c r="I112" s="9" t="inlineStr">
+        <v>35.96</v>
+      </c>
+      <c r="I112" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J112" s="2" t="n">
-        <v>2.197</v>
+        <v>1.621</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>2.235</v>
+        <v>1.664</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="7" t="inlineStr"/>
@@ -5520,39 +5520,39 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>0151</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>KGB</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D113" s="2" t="n">
-        <v>8.109999999999999</v>
-      </c>
-      <c r="E113" s="8" t="n">
-        <v>-0.0287</v>
+        <v>2.5</v>
+      </c>
+      <c r="E113" s="3" t="n">
+        <v>-0.0234</v>
       </c>
       <c r="F113" s="4" t="n">
-        <v>622900</v>
+        <v>948400</v>
       </c>
       <c r="G113" s="5" t="n">
-        <v>0.27</v>
+        <v>0.18</v>
       </c>
       <c r="H113" t="n">
-        <v>37.82</v>
-      </c>
-      <c r="I113" s="9" t="inlineStr">
+        <v>32.79</v>
+      </c>
+      <c r="I113" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J113" s="2" t="n">
-        <v>8.605</v>
+        <v>2.808</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>8.69</v>
+        <v>2.877</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="7" t="inlineStr"/>
@@ -5565,39 +5565,39 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>0271</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>WELLS</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D114" s="2" t="n">
-        <v>0.555</v>
-      </c>
-      <c r="E114" s="3" t="n">
-        <v>0.0091</v>
+        <v>0.845</v>
+      </c>
+      <c r="E114" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F114" s="4" t="n">
-        <v>622500</v>
+        <v>922000</v>
       </c>
       <c r="G114" s="5" t="n">
-        <v>0.54</v>
+        <v>0.31</v>
       </c>
       <c r="H114" t="n">
-        <v>42.07</v>
+        <v>17.21</v>
       </c>
       <c r="I114" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.916</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>0.611</v>
+        <v>0.973</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="7" t="inlineStr"/>
@@ -5610,39 +5610,39 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D115" s="2" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="E115" s="8" t="n">
-        <v>-0.0142</v>
+        <v>2.76</v>
+      </c>
+      <c r="E115" s="3" t="n">
+        <v>-0.0143</v>
       </c>
       <c r="F115" s="4" t="n">
-        <v>620900</v>
+        <v>916100</v>
       </c>
       <c r="G115" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.24</v>
       </c>
       <c r="H115" t="n">
-        <v>50.61</v>
-      </c>
-      <c r="I115" s="9" t="inlineStr">
+        <v>39.45</v>
+      </c>
+      <c r="I115" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J115" s="2" t="n">
-        <v>2.789</v>
+        <v>2.895</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>2.663</v>
+        <v>3.012</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="7" t="inlineStr"/>
@@ -5655,39 +5655,39 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>0168</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>BMGREEN</t>
+          <t>CPETECH</t>
         </is>
       </c>
       <c r="D116" s="2" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="E116" s="8" t="n">
-        <v>-0.0408</v>
+        <v>1.27</v>
+      </c>
+      <c r="E116" s="3" t="n">
+        <v>-0.0379</v>
       </c>
       <c r="F116" s="4" t="n">
-        <v>619300</v>
+        <v>901800</v>
       </c>
       <c r="G116" s="5" t="n">
-        <v>0.65</v>
+        <v>0.29</v>
       </c>
       <c r="H116" t="n">
-        <v>30.82</v>
-      </c>
-      <c r="I116" s="9" t="inlineStr">
+        <v>49.69</v>
+      </c>
+      <c r="I116" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J116" s="2" t="n">
-        <v>1.555</v>
+        <v>1.287</v>
       </c>
       <c r="K116" s="2" t="n">
-        <v>1.648</v>
+        <v>1.225</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="7" t="inlineStr"/>
@@ -5700,39 +5700,39 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>7498</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>ATECH</t>
+          <t>RALCO</t>
         </is>
       </c>
       <c r="D117" s="2" t="n">
-        <v>0.755</v>
-      </c>
-      <c r="E117" s="8" t="n">
-        <v>-0.0382</v>
+        <v>1.02</v>
+      </c>
+      <c r="E117" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F117" s="4" t="n">
-        <v>595400</v>
+        <v>878700</v>
       </c>
       <c r="G117" s="5" t="n">
-        <v>0.26</v>
+        <v>1.28</v>
       </c>
       <c r="H117" t="n">
-        <v>46.3</v>
+        <v>59.46</v>
       </c>
       <c r="I117" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.775</v>
+        <v>1.004</v>
       </c>
       <c r="K117" s="2" t="n">
-        <v>0.769</v>
+        <v>0.984</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="7" t="inlineStr"/>
@@ -5745,39 +5745,39 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D118" s="2" t="n">
-        <v>1.91</v>
+        <v>2.79</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0.0214</v>
+        <v>-0.0071</v>
       </c>
       <c r="F118" s="4" t="n">
-        <v>576600</v>
+        <v>875300</v>
       </c>
       <c r="G118" s="5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="H118" t="n">
-        <v>47.22</v>
+        <v>51.82</v>
       </c>
       <c r="I118" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J118" s="2" t="n">
-        <v>1.921</v>
+        <v>2.791</v>
       </c>
       <c r="K118" s="2" t="n">
-        <v>1.95</v>
+        <v>2.664</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="7" t="inlineStr"/>
@@ -5790,39 +5790,39 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>6971</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>KOBAY</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D119" s="2" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="E119" s="8" t="n">
-        <v>-0.0143</v>
+        <v>0.83</v>
+      </c>
+      <c r="E119" s="3" t="n">
+        <v>-0.0235</v>
       </c>
       <c r="F119" s="4" t="n">
-        <v>562600</v>
+        <v>857300</v>
       </c>
       <c r="G119" s="5" t="n">
-        <v>0.46</v>
+        <v>0.24</v>
       </c>
       <c r="H119" t="n">
-        <v>43.56</v>
-      </c>
-      <c r="I119" s="9" t="inlineStr">
+        <v>52.34</v>
+      </c>
+      <c r="I119" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J119" s="2" t="n">
-        <v>2.125</v>
+        <v>0.827</v>
       </c>
       <c r="K119" s="2" t="n">
-        <v>2.28</v>
+        <v>0.781</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="7" t="inlineStr"/>
@@ -5835,39 +5835,39 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>ATECH</t>
         </is>
       </c>
       <c r="D120" s="2" t="n">
-        <v>6.38</v>
-      </c>
-      <c r="E120" s="8" t="n">
-        <v>-0.0185</v>
+        <v>0.76</v>
+      </c>
+      <c r="E120" s="3" t="n">
+        <v>-0.0318</v>
       </c>
       <c r="F120" s="4" t="n">
-        <v>556000</v>
+        <v>837200</v>
       </c>
       <c r="G120" s="5" t="n">
-        <v>0.1</v>
+        <v>0.36</v>
       </c>
       <c r="H120" t="n">
-        <v>55.01</v>
+        <v>47.23</v>
       </c>
       <c r="I120" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J120" s="2" t="n">
-        <v>6.161</v>
+        <v>0.775</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>5.909</v>
+        <v>0.769</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="7" t="inlineStr"/>
@@ -5880,39 +5880,39 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>1619</t>
+          <t>0045</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>DRBHCOM</t>
+          <t>SSB8</t>
         </is>
       </c>
       <c r="D121" s="2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E121" s="8" t="n">
-        <v>-0.0184</v>
+        <v>0.63</v>
+      </c>
+      <c r="E121" s="3" t="n">
+        <v>-0.007900000000000001</v>
       </c>
       <c r="F121" s="4" t="n">
-        <v>539200</v>
+        <v>826800</v>
       </c>
       <c r="G121" s="5" t="n">
-        <v>1.09</v>
+        <v>0.22</v>
       </c>
       <c r="H121" t="n">
-        <v>15.65</v>
-      </c>
-      <c r="I121" s="9" t="inlineStr">
+        <v>48.81</v>
+      </c>
+      <c r="I121" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.884</v>
+        <v>0.638</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.614</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="7" t="inlineStr"/>
@@ -5936,19 +5936,19 @@
       <c r="D122" s="2" t="n">
         <v>2.75</v>
       </c>
-      <c r="E122" s="8" t="n">
+      <c r="E122" s="3" t="n">
         <v>-0.0036</v>
       </c>
       <c r="F122" s="4" t="n">
-        <v>523500</v>
+        <v>824200</v>
       </c>
       <c r="G122" s="5" t="n">
-        <v>0.14</v>
+        <v>0.23</v>
       </c>
       <c r="H122" t="n">
         <v>57.1</v>
       </c>
-      <c r="I122" s="9" t="inlineStr">
+      <c r="I122" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -5970,45 +5970,855 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>0151</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>DUFU</t>
+          <t>KGB</t>
         </is>
       </c>
       <c r="D123" s="2" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="E123" s="8" t="n">
-        <v>-0.0195</v>
+        <v>8.23</v>
+      </c>
+      <c r="E123" s="3" t="n">
+        <v>-0.0144</v>
       </c>
       <c r="F123" s="4" t="n">
-        <v>506700</v>
+        <v>783800</v>
       </c>
       <c r="G123" s="5" t="n">
-        <v>0.16</v>
+        <v>0.34</v>
       </c>
       <c r="H123" t="n">
-        <v>51.22</v>
-      </c>
-      <c r="I123" s="9" t="inlineStr">
+        <v>39.96</v>
+      </c>
+      <c r="I123" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J123" s="2" t="n">
-        <v>3.027</v>
+        <v>8.616</v>
       </c>
       <c r="K123" s="2" t="n">
-        <v>2.856</v>
+        <v>8.692</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="7" t="inlineStr"/>
     </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>1619</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>DRBHCOM</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="E124" s="3" t="n">
+        <v>-0.0307</v>
+      </c>
+      <c r="F124" s="4" t="n">
+        <v>779900</v>
+      </c>
+      <c r="G124" s="5" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="H124" t="n">
+        <v>14.69</v>
+      </c>
+      <c r="I124" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J124" s="2" t="n">
+        <v>0.883</v>
+      </c>
+      <c r="K124" s="2" t="n">
+        <v>0.9379999999999999</v>
+      </c>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" s="7" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>0099</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>SCICOM</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="E125" s="8" t="n">
+        <v>0.009599999999999999</v>
+      </c>
+      <c r="F125" s="4" t="n">
+        <v>777100</v>
+      </c>
+      <c r="G125" s="5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="H125" t="n">
+        <v>41.72</v>
+      </c>
+      <c r="I125" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J125" s="2" t="n">
+        <v>2.198</v>
+      </c>
+      <c r="K125" s="2" t="n">
+        <v>2.235</v>
+      </c>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" s="7" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>RHBBANK</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="E126" s="3" t="n">
+        <v>-0.0164</v>
+      </c>
+      <c r="F126" s="4" t="n">
+        <v>761300</v>
+      </c>
+      <c r="G126" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H126" t="n">
+        <v>31.05</v>
+      </c>
+      <c r="I126" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J126" s="2" t="n">
+        <v>7.454</v>
+      </c>
+      <c r="K126" s="2" t="n">
+        <v>7.948</v>
+      </c>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" s="7" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>6971</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>KOBAY</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="E127" s="3" t="n">
+        <v>-0.019</v>
+      </c>
+      <c r="F127" s="4" t="n">
+        <v>754100</v>
+      </c>
+      <c r="G127" s="5" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="H127" t="n">
+        <v>42.97</v>
+      </c>
+      <c r="I127" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="n">
+        <v>2.124</v>
+      </c>
+      <c r="K127" s="2" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" s="7" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>0168</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>BMGREEN</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="E128" s="3" t="n">
+        <v>-0.0408</v>
+      </c>
+      <c r="F128" s="4" t="n">
+        <v>744800</v>
+      </c>
+      <c r="G128" s="5" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="H128" t="n">
+        <v>30.82</v>
+      </c>
+      <c r="I128" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J128" s="2" t="n">
+        <v>1.555</v>
+      </c>
+      <c r="K128" s="2" t="n">
+        <v>1.648</v>
+      </c>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" s="7" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>5286</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="n">
+        <v>6.39</v>
+      </c>
+      <c r="E129" s="3" t="n">
+        <v>-0.0169</v>
+      </c>
+      <c r="F129" s="4" t="n">
+        <v>696400</v>
+      </c>
+      <c r="G129" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H129" t="n">
+        <v>55.18</v>
+      </c>
+      <c r="I129" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J129" s="2" t="n">
+        <v>6.162</v>
+      </c>
+      <c r="K129" s="2" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" s="7" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>7160</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>PENTA</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="E130" s="3" t="n">
+        <v>-0.0268</v>
+      </c>
+      <c r="F130" s="4" t="n">
+        <v>690600</v>
+      </c>
+      <c r="G130" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H130" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="I130" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J130" s="2" t="n">
+        <v>5.508</v>
+      </c>
+      <c r="K130" s="2" t="n">
+        <v>5.393</v>
+      </c>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" s="7" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>0271</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>WELLS</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="n">
+        <v>0.555</v>
+      </c>
+      <c r="E131" s="8" t="n">
+        <v>0.0091</v>
+      </c>
+      <c r="F131" s="4" t="n">
+        <v>622500</v>
+      </c>
+      <c r="G131" s="5" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="H131" t="n">
+        <v>42.07</v>
+      </c>
+      <c r="I131" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J131" s="2" t="n">
+        <v>0.5679999999999999</v>
+      </c>
+      <c r="K131" s="2" t="n">
+        <v>0.611</v>
+      </c>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" s="7" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>0310</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>UUE</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="n">
+        <v>0.735</v>
+      </c>
+      <c r="E132" s="3" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="F132" s="4" t="n">
+        <v>605900</v>
+      </c>
+      <c r="G132" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H132" t="n">
+        <v>51.27</v>
+      </c>
+      <c r="I132" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="n">
+        <v>0.741</v>
+      </c>
+      <c r="K132" s="2" t="n">
+        <v>0.676</v>
+      </c>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" s="7" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>5053</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>OSK</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="E133" s="3" t="n">
+        <v>-0.0182</v>
+      </c>
+      <c r="F133" s="4" t="n">
+        <v>588000</v>
+      </c>
+      <c r="G133" s="5" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="H133" t="n">
+        <v>29.39</v>
+      </c>
+      <c r="I133" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J133" s="2" t="n">
+        <v>1.727</v>
+      </c>
+      <c r="K133" s="2" t="n">
+        <v>1.884</v>
+      </c>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" s="7" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>4197</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>SIME</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="E134" s="8" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="F134" s="4" t="n">
+        <v>576500</v>
+      </c>
+      <c r="G134" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H134" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="I134" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J134" s="2" t="n">
+        <v>2.441</v>
+      </c>
+      <c r="K134" s="2" t="n">
+        <v>2.384</v>
+      </c>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" s="7" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>3417</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>E&amp;O</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="n">
+        <v>0.745</v>
+      </c>
+      <c r="E135" s="3" t="n">
+        <v>-0.0067</v>
+      </c>
+      <c r="F135" s="4" t="n">
+        <v>565200</v>
+      </c>
+      <c r="G135" s="5" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="H135" t="n">
+        <v>40.03</v>
+      </c>
+      <c r="I135" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="n">
+        <v>0.764</v>
+      </c>
+      <c r="K135" s="2" t="n">
+        <v>0.769</v>
+      </c>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" s="7" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>7233</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>DUFU</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="E136" s="3" t="n">
+        <v>-0.0195</v>
+      </c>
+      <c r="F136" s="4" t="n">
+        <v>562100</v>
+      </c>
+      <c r="G136" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H136" t="n">
+        <v>51.22</v>
+      </c>
+      <c r="I136" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="n">
+        <v>3.027</v>
+      </c>
+      <c r="K136" s="2" t="n">
+        <v>2.856</v>
+      </c>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" s="7" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>5211</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>SUNWAY</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="E137" s="8" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="F137" s="4" t="n">
+        <v>544400</v>
+      </c>
+      <c r="G137" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H137" t="n">
+        <v>35.84</v>
+      </c>
+      <c r="I137" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J137" s="2" t="n">
+        <v>4.412</v>
+      </c>
+      <c r="K137" s="2" t="n">
+        <v>4.719</v>
+      </c>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" s="7" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>9792</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>SEG</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E138" s="3" t="n">
+        <v>-0.007900000000000001</v>
+      </c>
+      <c r="F138" s="4" t="n">
+        <v>538500</v>
+      </c>
+      <c r="G138" s="5" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="H138" t="n">
+        <v>34.58</v>
+      </c>
+      <c r="I138" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J138" s="2" t="n">
+        <v>0.631</v>
+      </c>
+      <c r="K138" s="2" t="n">
+        <v>0.631</v>
+      </c>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" s="7" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>5184</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>CYPARK</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="n">
+        <v>0.6850000000000001</v>
+      </c>
+      <c r="E139" s="3" t="n">
+        <v>-0.0072</v>
+      </c>
+      <c r="F139" s="4" t="n">
+        <v>518500</v>
+      </c>
+      <c r="G139" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H139" t="n">
+        <v>40.04</v>
+      </c>
+      <c r="I139" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J139" s="2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="K139" s="2" t="n">
+        <v>0.723</v>
+      </c>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" s="7" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>0296</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>HEGROUP</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="E140" s="3" t="n">
+        <v>-0.0098</v>
+      </c>
+      <c r="F140" s="4" t="n">
+        <v>506400</v>
+      </c>
+      <c r="G140" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H140" t="n">
+        <v>47.81</v>
+      </c>
+      <c r="I140" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J140" s="2" t="n">
+        <v>1.044</v>
+      </c>
+      <c r="K140" s="2" t="n">
+        <v>0.9419999999999999</v>
+      </c>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" s="7" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>6947</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>CDB</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="E141" s="3" t="n">
+        <v>-0.0235</v>
+      </c>
+      <c r="F141" s="4" t="n">
+        <v>503100</v>
+      </c>
+      <c r="G141" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H141" t="n">
+        <v>38.18</v>
+      </c>
+      <c r="I141" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J141" s="2" t="n">
+        <v>2.558</v>
+      </c>
+      <c r="K141" s="2" t="n">
+        <v>2.685</v>
+      </c>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M123"/>
+  <autoFilter ref="A1:M141"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-19/bursa-report-2026-10-19.xlsx
+++ b/docs/downloads/2026-10-19/bursa-report-2026-10-19.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-19" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-19'!$A$1:$M$141</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-19'!$A$1:$M$162</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -82,8 +82,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M141"/>
+  <dimension ref="A1:M162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -558,10 +558,10 @@
         <v>-0.09089999999999999</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>48618800</v>
+        <v>56805100</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="H2" t="n">
         <v>22.63</v>
@@ -597,19 +597,19 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.325</v>
+        <v>0.32</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>-0.0441</v>
+        <v>-0.0588</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>43579300</v>
+        <v>44809000</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="H3" t="n">
-        <v>61.81</v>
+        <v>59.82</v>
       </c>
       <c r="I3" s="6" t="inlineStr">
         <is>
@@ -642,27 +642,27 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.905</v>
-      </c>
-      <c r="E4" s="8" t="n">
-        <v>0.005600000000000001</v>
+        <v>0.895</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>-0.005600000000000001</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>36686000</v>
+        <v>42106200</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.54</v>
+        <v>0.62</v>
       </c>
       <c r="H4" t="n">
-        <v>66.83</v>
-      </c>
-      <c r="I4" s="9" t="inlineStr">
+        <v>65.20999999999999</v>
+      </c>
+      <c r="I4" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.829</v>
+        <v>0.828</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>0.736</v>
@@ -693,7 +693,7 @@
         <v>-0.06900000000000001</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>26937300</v>
+        <v>27276100</v>
       </c>
       <c r="G5" s="5" t="n">
         <v>0.4</v>
@@ -732,21 +732,21 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.6850000000000001</v>
-      </c>
-      <c r="E6" s="8" t="n">
-        <v>0.0224</v>
+        <v>0.68</v>
+      </c>
+      <c r="E6" s="9" t="n">
+        <v>0.0149</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>18593600</v>
+        <v>20252800</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.74</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>77.45</v>
-      </c>
-      <c r="I6" s="9" t="inlineStr">
+        <v>76.73999999999999</v>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -768,39 +768,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="E7" s="10" t="n">
-        <v>0</v>
+        <v>4.7</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>-0.0269</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>14291000</v>
+        <v>15108700</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.41</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>74.48999999999999</v>
-      </c>
-      <c r="I7" s="9" t="inlineStr">
+        <v>46.13</v>
+      </c>
+      <c r="I7" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.382</v>
+        <v>4.727</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.277</v>
+        <v>4.847</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="7" t="inlineStr"/>
@@ -813,39 +813,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>4.71</v>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>-0.0248</v>
+        <v>0.42</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>13608800</v>
+        <v>14556700</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.73</v>
+        <v>0.42</v>
       </c>
       <c r="H8" t="n">
-        <v>46.84</v>
-      </c>
-      <c r="I8" s="9" t="inlineStr">
+        <v>74.48999999999999</v>
+      </c>
+      <c r="I8" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>4.728</v>
+        <v>0.382</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>4.848</v>
+        <v>0.277</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="7" t="inlineStr"/>
@@ -867,19 +867,19 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0.285</v>
+        <v>0.28</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>-0.0806</v>
+        <v>-0.0968</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>11265600</v>
+        <v>12186100</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="H9" t="n">
-        <v>45.31</v>
+        <v>43.38</v>
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.299</v>
+        <v>0.298</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>0.28</v>
@@ -903,39 +903,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>4251</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>IBHD</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0.215</v>
+        <v>0.44</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>-0.0227</v>
+        <v>-0.0112</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>9430100</v>
+        <v>10286100</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>32.38</v>
+        <v>0.51</v>
       </c>
       <c r="H10" t="n">
-        <v>53.06</v>
-      </c>
-      <c r="I10" s="9" t="inlineStr">
+        <v>57.56</v>
+      </c>
+      <c r="I10" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.212</v>
+        <v>0.423</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0.217</v>
+        <v>0.367</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="7" t="inlineStr"/>
@@ -948,39 +948,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>4251</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>IBHD</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0.445</v>
-      </c>
-      <c r="E11" s="10" t="n">
-        <v>0</v>
+        <v>0.215</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>-0.0227</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>8411800</v>
+        <v>9430100</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.42</v>
+        <v>32.38</v>
       </c>
       <c r="H11" t="n">
-        <v>59.08</v>
-      </c>
-      <c r="I11" s="9" t="inlineStr">
+        <v>53.06</v>
+      </c>
+      <c r="I11" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.424</v>
+        <v>0.212</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0.368</v>
+        <v>0.217</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="7" t="inlineStr"/>
@@ -993,39 +993,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0081</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>REKATECH</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>-0.1111</v>
+        <v>0.31</v>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>7878500</v>
+        <v>9161500</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>21.3</v>
+        <v>0.47</v>
       </c>
       <c r="H12" t="n">
-        <v>70.23999999999999</v>
-      </c>
-      <c r="I12" s="9" t="inlineStr">
+        <v>54.55</v>
+      </c>
+      <c r="I12" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.026</v>
+        <v>0.309</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0.024</v>
+        <v>0.3</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="7" t="inlineStr"/>
@@ -1038,39 +1038,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="E13" s="10" t="n">
-        <v>0</v>
+        <v>0.435</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>-0.0333</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>7865500</v>
+        <v>7949400</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.41</v>
+        <v>0.22</v>
       </c>
       <c r="H13" t="n">
-        <v>54.55</v>
-      </c>
-      <c r="I13" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.45</v>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.309</v>
+        <v>0.477</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0.3</v>
+        <v>0.482</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="7" t="inlineStr"/>
@@ -1083,39 +1083,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>0081</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>REKATECH</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0.435</v>
+        <v>0.04</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>-0.0333</v>
+        <v>-0.1111</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>7864700</v>
+        <v>7943500</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.22</v>
+        <v>21.48</v>
       </c>
       <c r="H14" t="n">
-        <v>36.45</v>
-      </c>
-      <c r="I14" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>70.23999999999999</v>
+      </c>
+      <c r="I14" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.477</v>
+        <v>0.026</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0.482</v>
+        <v>0.024</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="7" t="inlineStr"/>
@@ -1128,33 +1128,40 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>0095</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SLG</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0.25</v>
+        <v>0.155</v>
       </c>
       <c r="E15" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>6874700</v>
+        <v>7414800</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.28</v>
+        <v>0.21</v>
+      </c>
+      <c r="H15" t="n">
+        <v>48.61</v>
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J15" s="2" t="n"/>
-      <c r="K15" s="2" t="n"/>
+      <c r="J15" s="2" t="n">
+        <v>0.155</v>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>0.156</v>
+      </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="7" t="inlineStr"/>
     </row>
@@ -1175,27 +1182,27 @@
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>-0.0248</v>
+        <v>-0.0297</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>6815300</v>
+        <v>7301400</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.23</v>
+        <v>0.25</v>
       </c>
       <c r="H16" t="n">
-        <v>55.91</v>
-      </c>
-      <c r="I16" s="9" t="inlineStr">
+        <v>55.27</v>
+      </c>
+      <c r="I16" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.925</v>
+        <v>1.924</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>1.739</v>
@@ -1211,40 +1218,33 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>SLG</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="E17" s="3" t="n">
-        <v>-0.03759999999999999</v>
+        <v>0.25</v>
+      </c>
+      <c r="E17" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>6155400</v>
+        <v>6874700</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="H17" t="n">
-        <v>46.31</v>
+        <v>0.28</v>
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J17" s="2" t="n">
-        <v>2.641</v>
-      </c>
-      <c r="K17" s="2" t="n">
-        <v>2.553</v>
-      </c>
+      <c r="J17" s="2" t="n"/>
+      <c r="K17" s="2" t="n"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="7" t="inlineStr"/>
     </row>
@@ -1256,28 +1256,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E18" s="10" t="n">
-        <v>0</v>
+        <v>2.56</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>-0.03759999999999999</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>6072500</v>
+        <v>6617200</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>1.95</v>
+        <v>0.37</v>
       </c>
       <c r="H18" t="n">
-        <v>49.08</v>
+        <v>46.31</v>
       </c>
       <c r="I18" s="6" t="inlineStr">
         <is>
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.295</v>
+        <v>2.641</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0.295</v>
+        <v>2.553</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="7" t="inlineStr"/>
@@ -1316,10 +1316,10 @@
         <v>0</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>6000400</v>
+        <v>6500400</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>3.54</v>
+        <v>3.83</v>
       </c>
       <c r="H19" t="n">
         <v>46.69</v>
@@ -1346,39 +1346,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>5156</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>XDL</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="E20" s="10" t="n">
-        <v>0</v>
+        <v>0.86</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>-0.0058</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>5950100</v>
+        <v>6281000</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>2.42</v>
+        <v>0.32</v>
       </c>
       <c r="H20" t="n">
-        <v>44.81</v>
-      </c>
-      <c r="I20" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>40.62</v>
+      </c>
+      <c r="I20" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.007</v>
+        <v>0.868</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0.007</v>
+        <v>0.869</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="7" t="inlineStr"/>
@@ -1391,40 +1391,33 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>0477</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>ECOSYS</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>1.08</v>
+        <v>0.755</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>-0.0182</v>
+        <v>-0.0382</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>5323700</v>
+        <v>6235600</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="H21" t="n">
-        <v>51.15</v>
-      </c>
-      <c r="I21" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="n">
-        <v>1.077</v>
-      </c>
-      <c r="K21" s="2" t="n">
-        <v>1.045</v>
-      </c>
+        <v>0.08</v>
+      </c>
+      <c r="I21" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="n"/>
+      <c r="K21" s="2" t="n"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="7" t="inlineStr"/>
     </row>
@@ -1436,28 +1429,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="E22" s="3" t="n">
-        <v>-0.0297</v>
+        <v>0.295</v>
+      </c>
+      <c r="E22" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>5260600</v>
+        <v>6072500</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.66</v>
+        <v>1.95</v>
       </c>
       <c r="H22" t="n">
-        <v>42.43</v>
+        <v>49.08</v>
       </c>
       <c r="I22" s="6" t="inlineStr">
         <is>
@@ -1465,10 +1458,10 @@
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>1.048</v>
+        <v>0.295</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0.959</v>
+        <v>0.295</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="7" t="inlineStr"/>
@@ -1481,39 +1474,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E23" s="10" t="n">
-        <v>0</v>
+        <v>0.775</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>-0.0064</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>5092300</v>
+        <v>6053100</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.47</v>
+        <v>0.39</v>
       </c>
       <c r="H23" t="n">
-        <v>56.82</v>
-      </c>
-      <c r="I23" s="9" t="inlineStr">
+        <v>49.91</v>
+      </c>
+      <c r="I23" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.617</v>
+        <v>0.775</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0.615</v>
+        <v>0.776</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="7" t="inlineStr"/>
@@ -1526,39 +1519,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>5156</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>XDL</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E24" s="3" t="n">
-        <v>-0.0064</v>
+        <v>0.005</v>
+      </c>
+      <c r="E24" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>4857900</v>
+        <v>5950100</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.32</v>
+        <v>2.42</v>
       </c>
       <c r="H24" t="n">
-        <v>49.91</v>
-      </c>
-      <c r="I24" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.81</v>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.775</v>
+        <v>0.007</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0.776</v>
+        <v>0.007</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="7" t="inlineStr"/>
@@ -1571,39 +1564,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>0.8149999999999999</v>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>-0.0061</v>
+        <v>0.625</v>
+      </c>
+      <c r="E25" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>4823300</v>
+        <v>5874600</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.3</v>
+        <v>0.54</v>
       </c>
       <c r="H25" t="n">
-        <v>51.98</v>
-      </c>
-      <c r="I25" s="9" t="inlineStr">
+        <v>56.82</v>
+      </c>
+      <c r="I25" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.617</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.615</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="7" t="inlineStr"/>
@@ -1616,39 +1609,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>0.865</v>
+        <v>0.82</v>
       </c>
       <c r="E26" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>4730900</v>
+        <v>5812300</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.24</v>
+        <v>0.36</v>
       </c>
       <c r="H26" t="n">
-        <v>45.57</v>
-      </c>
-      <c r="I26" s="9" t="inlineStr">
+        <v>57.16</v>
+      </c>
+      <c r="I26" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.868</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0.869</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="7" t="inlineStr"/>
@@ -1661,28 +1654,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>0.435</v>
-      </c>
-      <c r="E27" s="8" t="n">
-        <v>0.0357</v>
+        <v>1.08</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>-0.0182</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>4645800</v>
+        <v>5472300</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.57</v>
       </c>
       <c r="H27" t="n">
-        <v>53.65</v>
+        <v>51.15</v>
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
@@ -1690,10 +1683,10 @@
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.425</v>
+        <v>1.077</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0.416</v>
+        <v>1.045</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="7" t="inlineStr"/>
@@ -1706,33 +1699,40 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0477</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ECOSYS</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>0.775</v>
+        <v>0.98</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>-0.0127</v>
+        <v>-0.0297</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>4420100</v>
+        <v>5465400</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="I28" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="n"/>
-      <c r="K28" s="2" t="n"/>
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="H28" t="n">
+        <v>42.43</v>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="n">
+        <v>1.048</v>
+      </c>
+      <c r="K28" s="2" t="n">
+        <v>0.959</v>
+      </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="7" t="inlineStr"/>
     </row>
@@ -1744,28 +1744,28 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>6.67</v>
-      </c>
-      <c r="E29" s="8" t="n">
-        <v>0.0262</v>
+        <v>4.76</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>-0.0083</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>4352800</v>
+        <v>5262900</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.45</v>
+        <v>0.21</v>
       </c>
       <c r="H29" t="n">
-        <v>28.27</v>
+        <v>43.88</v>
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
@@ -1773,10 +1773,10 @@
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>7.208</v>
+        <v>4.895</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>7.606</v>
+        <v>4.728</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="7" t="inlineStr"/>
@@ -1789,28 +1789,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>1.62</v>
+        <v>0.535</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-0.0299</v>
+        <v>-0.036</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>4343100</v>
+        <v>5188500</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.91</v>
+        <v>0.25</v>
       </c>
       <c r="H30" t="n">
-        <v>34.42</v>
+        <v>44.62</v>
       </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
@@ -1818,10 +1818,10 @@
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>1.723</v>
+        <v>0.572</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>1.767</v>
+        <v>0.541</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="7" t="inlineStr"/>
@@ -1834,39 +1834,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="E31" s="10" t="n">
-        <v>0</v>
+        <v>6.67</v>
+      </c>
+      <c r="E31" s="9" t="n">
+        <v>0.0262</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>4205400</v>
+        <v>5055100</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.57</v>
+        <v>0.52</v>
       </c>
       <c r="H31" t="n">
-        <v>55.92</v>
-      </c>
-      <c r="I31" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>28.27</v>
+      </c>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.371</v>
+        <v>7.208</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0.369</v>
+        <v>7.606</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="7" t="inlineStr"/>
@@ -1879,39 +1879,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="E32" s="3" t="n">
-        <v>-0.0244</v>
+        <v>0.435</v>
+      </c>
+      <c r="E32" s="9" t="n">
+        <v>0.0357</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>4155600</v>
+        <v>4880300</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.55</v>
+        <v>0.72</v>
       </c>
       <c r="H32" t="n">
-        <v>40.08</v>
-      </c>
-      <c r="I32" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.65</v>
+      </c>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>1.236</v>
+        <v>0.425</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>1.323</v>
+        <v>0.416</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="7" t="inlineStr"/>
@@ -1924,28 +1924,28 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>0.54</v>
+        <v>1.42</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>-0.027</v>
+        <v>-0.0207</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>4149400</v>
+        <v>4856700</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.2</v>
+        <v>0.43</v>
       </c>
       <c r="H33" t="n">
-        <v>45.4</v>
+        <v>21.41</v>
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
@@ -1953,10 +1953,10 @@
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.572</v>
+        <v>1.691</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0.541</v>
+        <v>1.944</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="7" t="inlineStr"/>
@@ -1969,40 +1969,33 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>0472</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>ECOGRP</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="E34" s="8" t="n">
-        <v>0.0262</v>
+        <v>0.12</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>-0.1111</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>4142500</v>
+        <v>4840700</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="H34" t="n">
-        <v>61.48</v>
-      </c>
-      <c r="I34" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="n">
-        <v>2.227</v>
-      </c>
-      <c r="K34" s="2" t="n">
-        <v>2.167</v>
-      </c>
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="n"/>
+      <c r="K34" s="2" t="n"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="7" t="inlineStr"/>
     </row>
@@ -2014,39 +2007,39 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>4.72</v>
+        <v>1.19</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>-0.0167</v>
+        <v>-0.0325</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>3931700</v>
+        <v>4716400</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.15</v>
+        <v>0.62</v>
       </c>
       <c r="H35" t="n">
-        <v>42.05</v>
-      </c>
-      <c r="I35" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>38.78</v>
+      </c>
+      <c r="I35" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>4.891</v>
+        <v>1.235</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>4.727</v>
+        <v>1.323</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="7" t="inlineStr"/>
@@ -2059,28 +2052,28 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>1.42</v>
+        <v>1.62</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>-0.0207</v>
+        <v>-0.0299</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>3895000</v>
+        <v>4676100</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.35</v>
+        <v>0.98</v>
       </c>
       <c r="H36" t="n">
-        <v>21.41</v>
+        <v>34.42</v>
       </c>
       <c r="I36" s="6" t="inlineStr">
         <is>
@@ -2088,10 +2081,10 @@
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>1.691</v>
+        <v>1.723</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>1.944</v>
+        <v>1.767</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="7" t="inlineStr"/>
@@ -2104,39 +2097,39 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="E37" s="3" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.405</v>
+      </c>
+      <c r="E37" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>3805600</v>
+        <v>4597200</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.62</v>
+        <v>0.37</v>
       </c>
       <c r="H37" t="n">
-        <v>59.95</v>
-      </c>
-      <c r="I37" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>55.08</v>
+      </c>
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>1.196</v>
+        <v>0.391</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>1.187</v>
+        <v>0.378</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="7" t="inlineStr"/>
@@ -2149,39 +2142,39 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E38" s="3" t="n">
-        <v>-0.0148</v>
+        <v>2.34</v>
+      </c>
+      <c r="E38" s="9" t="n">
+        <v>0.0218</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>3796400</v>
+        <v>4421600</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.29</v>
+        <v>1.24</v>
       </c>
       <c r="H38" t="n">
-        <v>31.84</v>
-      </c>
-      <c r="I38" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.87</v>
+      </c>
+      <c r="I38" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>2.146</v>
+        <v>2.226</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>2.233</v>
+        <v>2.167</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="7" t="inlineStr"/>
@@ -2194,39 +2187,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>6203</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>KHEESAN</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="E39" s="8" t="n">
-        <v>0.0349</v>
+        <v>0.105</v>
+      </c>
+      <c r="E39" s="9" t="n">
+        <v>0.1053</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>3700100</v>
+        <v>4392300</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.39</v>
+        <v>2.56</v>
       </c>
       <c r="H39" t="n">
-        <v>58.99</v>
-      </c>
-      <c r="I39" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.33</v>
+      </c>
+      <c r="I39" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>3.653</v>
+        <v>0.091</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>3.008</v>
+        <v>0.095</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="7" t="inlineStr"/>
@@ -2239,39 +2232,39 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
+        <v>9.869999999999999</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>-0.012</v>
+      </c>
+      <c r="F40" s="4" t="n">
+        <v>4384300</v>
+      </c>
+      <c r="G40" s="5" t="n">
         <v>0.33</v>
       </c>
-      <c r="E40" s="3" t="n">
-        <v>-0.0294</v>
-      </c>
-      <c r="F40" s="4" t="n">
-        <v>3669700</v>
-      </c>
-      <c r="G40" s="5" t="n">
-        <v>0.39</v>
-      </c>
       <c r="H40" t="n">
-        <v>45.62</v>
-      </c>
-      <c r="I40" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>40.09</v>
+      </c>
+      <c r="I40" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.345</v>
+        <v>9.997999999999999</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0.333</v>
+        <v>10.147</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="7" t="inlineStr"/>
@@ -2284,39 +2277,39 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="E41" s="8" t="n">
-        <v>0.0114</v>
+        <v>1.26</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>-0.007900000000000001</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>3514700</v>
+        <v>4383000</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.28</v>
+        <v>0.71</v>
       </c>
       <c r="H41" t="n">
-        <v>42.31</v>
-      </c>
-      <c r="I41" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.95</v>
+      </c>
+      <c r="I41" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>2.759</v>
+        <v>1.196</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>2.738</v>
+        <v>1.187</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="7" t="inlineStr"/>
@@ -2329,39 +2322,39 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>9.880000000000001</v>
-      </c>
-      <c r="E42" s="3" t="n">
-        <v>-0.011</v>
+        <v>0.375</v>
+      </c>
+      <c r="E42" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>3475500</v>
+        <v>4365300</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.26</v>
+        <v>0.59</v>
       </c>
       <c r="H42" t="n">
-        <v>40.55</v>
-      </c>
-      <c r="I42" s="9" t="inlineStr">
+        <v>55.92</v>
+      </c>
+      <c r="I42" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>9.999000000000001</v>
+        <v>0.371</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>10.147</v>
+        <v>0.369</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="7" t="inlineStr"/>
@@ -2374,28 +2367,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>6769</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>JKGLAND</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="E43" s="3" t="n">
-        <v>-0.028</v>
+        <v>0.1</v>
+      </c>
+      <c r="E43" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>3437300</v>
+        <v>4361300</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>1.39</v>
+        <v>17.57</v>
       </c>
       <c r="H43" t="n">
-        <v>34.76</v>
+        <v>39.48</v>
       </c>
       <c r="I43" s="6" t="inlineStr">
         <is>
@@ -2403,10 +2396,10 @@
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.543</v>
+        <v>0.103</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0.572</v>
+        <v>0.107</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="7" t="inlineStr"/>
@@ -2419,28 +2412,28 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>0.835</v>
+        <v>0.525</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>-0.0457</v>
+        <v>-0.0187</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>3422500</v>
+        <v>4203500</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>1.12</v>
+        <v>1.7</v>
       </c>
       <c r="H44" t="n">
-        <v>28.22</v>
+        <v>36.53</v>
       </c>
       <c r="I44" s="6" t="inlineStr">
         <is>
@@ -2448,10 +2441,10 @@
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.897</v>
+        <v>0.544</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0.953</v>
+        <v>0.572</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="7" t="inlineStr"/>
@@ -2464,39 +2457,39 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>0.985</v>
+        <v>2</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>-0.08800000000000001</v>
+        <v>-0.0148</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>3273100</v>
+        <v>4108700</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.83</v>
+        <v>0.32</v>
       </c>
       <c r="H45" t="n">
-        <v>64.31999999999999</v>
-      </c>
-      <c r="I45" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31.84</v>
+      </c>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.84</v>
+        <v>2.146</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0.572</v>
+        <v>2.233</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="7" t="inlineStr"/>
@@ -2509,28 +2502,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>5.18</v>
-      </c>
-      <c r="E46" s="8" t="n">
-        <v>0.0058</v>
+        <v>3.87</v>
+      </c>
+      <c r="E46" s="9" t="n">
+        <v>0.0403</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>3189800</v>
+        <v>4039400</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.23</v>
+        <v>0.43</v>
       </c>
       <c r="H46" t="n">
-        <v>36.72</v>
+        <v>59.43</v>
       </c>
       <c r="I46" s="6" t="inlineStr">
         <is>
@@ -2538,10 +2531,10 @@
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>5.501</v>
+        <v>3.655</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>5.449</v>
+        <v>3.009</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="7" t="inlineStr"/>
@@ -2554,28 +2547,28 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>0.405</v>
-      </c>
-      <c r="E47" s="10" t="n">
-        <v>0</v>
+        <v>0.45</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>-0.011</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>3187000</v>
+        <v>3936900</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.26</v>
+        <v>0.16</v>
       </c>
       <c r="H47" t="n">
-        <v>55.08</v>
+        <v>27.11</v>
       </c>
       <c r="I47" s="6" t="inlineStr">
         <is>
@@ -2583,10 +2576,10 @@
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.391</v>
+        <v>0.507</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0.378</v>
+        <v>0.677</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="7" t="inlineStr"/>
@@ -2599,28 +2592,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="E48" s="3" t="n">
-        <v>-0.0286</v>
+        <v>2.67</v>
+      </c>
+      <c r="E48" s="9" t="n">
+        <v>0.0152</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>3145200</v>
+        <v>3810700</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.26</v>
+        <v>0.3</v>
       </c>
       <c r="H48" t="n">
-        <v>50.37</v>
+        <v>43.18</v>
       </c>
       <c r="I48" s="6" t="inlineStr">
         <is>
@@ -2628,10 +2621,10 @@
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.519</v>
+        <v>2.76</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0.461</v>
+        <v>2.738</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="7" t="inlineStr"/>
@@ -2644,39 +2637,39 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>1.66</v>
+        <v>0.415</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>-0.006</v>
+        <v>-0.0235</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>3126500</v>
+        <v>3797000</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.46</v>
+        <v>0.49</v>
       </c>
       <c r="H49" t="n">
-        <v>52.91</v>
-      </c>
-      <c r="I49" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>23.04</v>
+      </c>
+      <c r="I49" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>1.628</v>
+        <v>0.527</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>1.695</v>
+        <v>0.614</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="7" t="inlineStr"/>
@@ -2689,28 +2682,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>7.16</v>
+        <v>0.33</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>-0.005600000000000001</v>
+        <v>-0.0294</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>3108300</v>
+        <v>3751700</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.19</v>
+        <v>0.4</v>
       </c>
       <c r="H50" t="n">
-        <v>33.16</v>
+        <v>45.62</v>
       </c>
       <c r="I50" s="6" t="inlineStr">
         <is>
@@ -2718,10 +2711,10 @@
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>7.505</v>
+        <v>0.345</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>7.684</v>
+        <v>0.333</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="7" t="inlineStr"/>
@@ -2734,28 +2727,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>0.46</v>
+        <v>7.16</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>-0.0108</v>
+        <v>-0.005600000000000001</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>3095800</v>
+        <v>3681300</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.42</v>
+        <v>0.23</v>
       </c>
       <c r="H51" t="n">
-        <v>29.85</v>
+        <v>33.16</v>
       </c>
       <c r="I51" s="6" t="inlineStr">
         <is>
@@ -2763,10 +2756,10 @@
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.498</v>
+        <v>7.505</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0.556</v>
+        <v>7.684</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="7" t="inlineStr"/>
@@ -2779,39 +2772,39 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>0.45</v>
+        <v>0.99</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>-0.011</v>
+        <v>-0.0833</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>3082100</v>
+        <v>3635100</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.12</v>
+        <v>0.92</v>
       </c>
       <c r="H52" t="n">
-        <v>27.11</v>
-      </c>
-      <c r="I52" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.73</v>
+      </c>
+      <c r="I52" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.507</v>
+        <v>0.84</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0.677</v>
+        <v>0.572</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="7" t="inlineStr"/>
@@ -2824,39 +2817,39 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="E53" s="8" t="n">
-        <v>0.008500000000000001</v>
+        <v>1.66</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>-0.006</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>2916000</v>
+        <v>3591700</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.4</v>
+        <v>0.53</v>
       </c>
       <c r="H53" t="n">
-        <v>53.56</v>
-      </c>
-      <c r="I53" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.91</v>
+      </c>
+      <c r="I53" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>1.171</v>
+        <v>1.628</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>1.137</v>
+        <v>1.695</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="7" t="inlineStr"/>
@@ -2869,28 +2862,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>0.41</v>
+        <v>0.835</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>-0.0353</v>
+        <v>-0.0457</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>2810800</v>
+        <v>3586100</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.36</v>
+        <v>1.17</v>
       </c>
       <c r="H54" t="n">
-        <v>22.61</v>
+        <v>28.22</v>
       </c>
       <c r="I54" s="6" t="inlineStr">
         <is>
@@ -2898,10 +2891,10 @@
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.526</v>
+        <v>0.897</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0.614</v>
+        <v>0.953</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="7" t="inlineStr"/>
@@ -2914,39 +2907,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="E55" s="8" t="n">
-        <v>0.0123</v>
+        <v>1.18</v>
+      </c>
+      <c r="E55" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>2792200</v>
+        <v>3466200</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>1.44</v>
+        <v>0.48</v>
       </c>
       <c r="H55" t="n">
-        <v>41.24</v>
-      </c>
-      <c r="I55" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.34</v>
+      </c>
+      <c r="I55" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.416</v>
+        <v>1.17</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0.434</v>
+        <v>1.136</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="7" t="inlineStr"/>
@@ -2959,28 +2952,28 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>0.89</v>
+        <v>0.51</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>-0.0326</v>
+        <v>-0.0286</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>2727600</v>
+        <v>3339300</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>1.64</v>
+        <v>0.28</v>
       </c>
       <c r="H56" t="n">
-        <v>47.65</v>
+        <v>50.37</v>
       </c>
       <c r="I56" s="6" t="inlineStr">
         <is>
@@ -2988,10 +2981,10 @@
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.913</v>
+        <v>0.519</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0.874</v>
+        <v>0.461</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="7" t="inlineStr"/>
@@ -3004,28 +2997,28 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>0.26</v>
+        <v>0.45</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>-0.0189</v>
+        <v>-0.0323</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>2717700</v>
+        <v>3336600</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.38</v>
+        <v>0.45</v>
       </c>
       <c r="H57" t="n">
-        <v>42.45</v>
+        <v>27.78</v>
       </c>
       <c r="I57" s="6" t="inlineStr">
         <is>
@@ -3033,10 +3026,10 @@
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.273</v>
+        <v>0.497</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0.294</v>
+        <v>0.556</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="7" t="inlineStr"/>
@@ -3049,28 +3042,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>5041</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>PBA</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E58" s="3" t="n">
-        <v>-0.0196</v>
+        <v>5.18</v>
+      </c>
+      <c r="E58" s="9" t="n">
+        <v>0.0058</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>2636500</v>
+        <v>3320100</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>8.08</v>
+        <v>0.24</v>
       </c>
       <c r="H58" t="n">
-        <v>32</v>
+        <v>36.72</v>
       </c>
       <c r="I58" s="6" t="inlineStr">
         <is>
@@ -3078,10 +3071,10 @@
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>2.091</v>
+        <v>5.501</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>2.156</v>
+        <v>5.449</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="7" t="inlineStr"/>
@@ -3094,28 +3087,28 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="E59" s="3" t="n">
-        <v>-0.04389999999999999</v>
+        <v>0.18</v>
+      </c>
+      <c r="E59" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>2570000</v>
+        <v>3269500</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.5</v>
+        <v>0.14</v>
       </c>
       <c r="H59" t="n">
-        <v>48.83</v>
+        <v>42.99</v>
       </c>
       <c r="I59" s="6" t="inlineStr">
         <is>
@@ -3123,10 +3116,10 @@
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.19</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0.516</v>
+        <v>0.186</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="7" t="inlineStr"/>
@@ -3139,28 +3132,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0469</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>GTA</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>0.24</v>
+        <v>0.57</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>-0.04</v>
+        <v>-0.042</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>2411900</v>
+        <v>3115900</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.68</v>
+        <v>0.35</v>
       </c>
       <c r="H60" t="n">
-        <v>16.11</v>
+        <v>36.38</v>
       </c>
       <c r="I60" s="6" t="inlineStr">
         <is>
@@ -3168,9 +3161,11 @@
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.272</v>
-      </c>
-      <c r="K60" s="2" t="n"/>
+        <v>0.647</v>
+      </c>
+      <c r="K60" s="2" t="n">
+        <v>0.62</v>
+      </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="7" t="inlineStr"/>
     </row>
@@ -3182,39 +3177,39 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>VELESTO</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>0.205</v>
-      </c>
-      <c r="E61" s="8" t="n">
-        <v>0.009899999999999999</v>
+        <v>2.08</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>-0.0095</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>2311200</v>
+        <v>2984500</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="H61" t="n">
-        <v>39.23</v>
-      </c>
-      <c r="I61" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>45.7</v>
+      </c>
+      <c r="I61" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.218</v>
+        <v>2.107</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0.235</v>
+        <v>2.101</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="7" t="inlineStr"/>
@@ -3227,39 +3222,39 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>0.575</v>
-      </c>
-      <c r="E62" s="3" t="n">
-        <v>-0.0336</v>
+        <v>0.41</v>
+      </c>
+      <c r="E62" s="9" t="n">
+        <v>0.0123</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>2295700</v>
+        <v>2792500</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.25</v>
+        <v>1.44</v>
       </c>
       <c r="H62" t="n">
-        <v>37.01</v>
-      </c>
-      <c r="I62" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>41.24</v>
+      </c>
+      <c r="I62" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.648</v>
+        <v>0.416</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>0.62</v>
+        <v>0.434</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="7" t="inlineStr"/>
@@ -3272,28 +3267,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>0.415</v>
+        <v>0.26</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>-0.0119</v>
+        <v>-0.0189</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>2291000</v>
+        <v>2774200</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.24</v>
+        <v>0.38</v>
       </c>
       <c r="H63" t="n">
-        <v>43.52</v>
+        <v>42.45</v>
       </c>
       <c r="I63" s="6" t="inlineStr">
         <is>
@@ -3301,10 +3296,10 @@
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.438</v>
+        <v>0.273</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0.434</v>
+        <v>0.294</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="7" t="inlineStr"/>
@@ -3317,39 +3312,39 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>3.08</v>
+        <v>0.54</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>-0.0032</v>
+        <v>-0.0526</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>2279600</v>
+        <v>2760400</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.74</v>
+        <v>0.53</v>
       </c>
       <c r="H64" t="n">
-        <v>80.70999999999999</v>
-      </c>
-      <c r="I64" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.73</v>
+      </c>
+      <c r="I64" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>2.827</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>2.429</v>
+        <v>0.516</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="7" t="inlineStr"/>
@@ -3362,39 +3357,39 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0395</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>OGX</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>0.465</v>
-      </c>
-      <c r="E65" s="8" t="n">
-        <v>0.022</v>
+        <v>0.89</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>-0.0326</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>2257600</v>
+        <v>2742000</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0.86</v>
+        <v>1.65</v>
       </c>
       <c r="H65" t="n">
-        <v>56.6</v>
-      </c>
-      <c r="I65" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.65</v>
+      </c>
+      <c r="I65" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.447</v>
+        <v>0.913</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>0.449</v>
+        <v>0.874</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="7" t="inlineStr"/>
@@ -3407,28 +3402,28 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>5041</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>PBA</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>0.745</v>
-      </c>
-      <c r="E66" s="8" t="n">
-        <v>0.0136</v>
+        <v>2</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>-0.0196</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>2222000</v>
+        <v>2637000</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>0.27</v>
+        <v>8.08</v>
       </c>
       <c r="H66" t="n">
-        <v>42.4</v>
+        <v>32</v>
       </c>
       <c r="I66" s="6" t="inlineStr">
         <is>
@@ -3436,10 +3431,10 @@
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.769</v>
+        <v>2.091</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0.771</v>
+        <v>2.156</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="7" t="inlineStr"/>
@@ -3452,39 +3447,39 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="E67" s="3" t="n">
-        <v>-0.0394</v>
+        <v>0.625</v>
+      </c>
+      <c r="E67" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>1925600</v>
+        <v>2632800</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>0.46</v>
+        <v>0.78</v>
       </c>
       <c r="H67" t="n">
-        <v>23.54</v>
-      </c>
-      <c r="I67" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>70.16</v>
+      </c>
+      <c r="I67" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>1.393</v>
+        <v>0.617</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>1.561</v>
+        <v>0.605</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="7" t="inlineStr"/>
@@ -3497,38 +3492,40 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="E68" s="3" t="n">
-        <v>-0.0137</v>
+        <v>0.75</v>
+      </c>
+      <c r="E68" s="9" t="n">
+        <v>0.0204</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>1922000</v>
+        <v>2556900</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="H68" t="n">
-        <v>62.55</v>
-      </c>
-      <c r="I68" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.98</v>
+      </c>
+      <c r="I68" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.319</v>
-      </c>
-      <c r="K68" s="2" t="n"/>
+        <v>0.77</v>
+      </c>
+      <c r="K68" s="2" t="n">
+        <v>0.771</v>
+      </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="7" t="inlineStr"/>
     </row>
@@ -3540,39 +3537,39 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>0.965</v>
-      </c>
-      <c r="E69" s="8" t="n">
-        <v>0.0052</v>
+        <v>3.09</v>
+      </c>
+      <c r="E69" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>1868000</v>
+        <v>2495000</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>0.32</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H69" t="n">
-        <v>66.12</v>
-      </c>
-      <c r="I69" s="9" t="inlineStr">
+        <v>82.09</v>
+      </c>
+      <c r="I69" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.925</v>
+        <v>2.827</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0.877</v>
+        <v>2.43</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="7" t="inlineStr"/>
@@ -3585,40 +3582,38 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0388</t>
+          <t>0469</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>SEMICO</t>
+          <t>GTA</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E70" s="10" t="n">
-        <v>0</v>
+        <v>0.24</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>-0.04</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>1794400</v>
+        <v>2480400</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>0.53</v>
+        <v>0.7</v>
       </c>
       <c r="H70" t="n">
-        <v>70.16</v>
-      </c>
-      <c r="I70" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>16.11</v>
+      </c>
+      <c r="I70" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.617</v>
-      </c>
-      <c r="K70" s="2" t="n">
-        <v>0.605</v>
-      </c>
+        <v>0.272</v>
+      </c>
+      <c r="K70" s="2" t="n"/>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="7" t="inlineStr"/>
     </row>
@@ -3630,39 +3625,39 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>2.08</v>
+        <v>1.22</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>-0.0095</v>
+        <v>-0.0394</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>1778100</v>
+        <v>2403700</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>0.1</v>
+        <v>0.57</v>
       </c>
       <c r="H71" t="n">
-        <v>45.7</v>
-      </c>
-      <c r="I71" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>23.54</v>
+      </c>
+      <c r="I71" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>2.107</v>
+        <v>1.393</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>2.101</v>
+        <v>1.561</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="7" t="inlineStr"/>
@@ -3675,28 +3670,28 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="E72" s="3" t="n">
-        <v>-0.0226</v>
+        <v>0.205</v>
+      </c>
+      <c r="E72" s="9" t="n">
+        <v>0.009899999999999999</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>1769500</v>
+        <v>2386700</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>0.74</v>
+        <v>0.11</v>
       </c>
       <c r="H72" t="n">
-        <v>56.17</v>
+        <v>39.23</v>
       </c>
       <c r="I72" s="6" t="inlineStr">
         <is>
@@ -3704,10 +3699,10 @@
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>1.26</v>
+        <v>0.218</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>1.173</v>
+        <v>0.235</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="7" t="inlineStr"/>
@@ -3720,28 +3715,28 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>5271</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>PECCA</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="E73" s="10" t="n">
-        <v>0</v>
+        <v>0.405</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>-0.0357</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>1728800</v>
+        <v>2317200</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>0.89</v>
+        <v>0.24</v>
       </c>
       <c r="H73" t="n">
-        <v>43.62</v>
+        <v>41.34</v>
       </c>
       <c r="I73" s="6" t="inlineStr">
         <is>
@@ -3749,10 +3744,10 @@
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>1.367</v>
+        <v>0.437</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>1.343</v>
+        <v>0.434</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="7" t="inlineStr"/>
@@ -3765,39 +3760,39 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E74" s="10" t="n">
-        <v>0</v>
+        <v>1.9</v>
+      </c>
+      <c r="E74" s="9" t="n">
+        <v>0.016</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>1715400</v>
+        <v>2304200</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>0.77</v>
+        <v>0.4</v>
       </c>
       <c r="H74" t="n">
-        <v>50.9</v>
-      </c>
-      <c r="I74" s="9" t="inlineStr">
+        <v>45.71</v>
+      </c>
+      <c r="I74" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.637</v>
+        <v>1.92</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0.622</v>
+        <v>1.95</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="7" t="inlineStr"/>
@@ -3810,39 +3805,39 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>0395</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>OGX</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>4.48</v>
-      </c>
-      <c r="E75" s="8" t="n">
-        <v>0.03700000000000001</v>
+        <v>0.465</v>
+      </c>
+      <c r="E75" s="9" t="n">
+        <v>0.022</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>1702800</v>
+        <v>2267600</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>0.32</v>
+        <v>0.87</v>
       </c>
       <c r="H75" t="n">
-        <v>53.65</v>
-      </c>
-      <c r="I75" s="9" t="inlineStr">
+        <v>56.6</v>
+      </c>
+      <c r="I75" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>4.364</v>
+        <v>0.447</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>4.432</v>
+        <v>0.449</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="7" t="inlineStr"/>
@@ -3855,28 +3850,28 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>DATASONIC</t>
+          <t>IOIPG</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="E76" s="3" t="n">
-        <v>-0.0175</v>
+        <v>3.25</v>
+      </c>
+      <c r="E76" s="9" t="n">
+        <v>0.0285</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>1695500</v>
+        <v>2085600</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>0.14</v>
+        <v>0.35</v>
       </c>
       <c r="H76" t="n">
-        <v>46.28</v>
+        <v>36.23</v>
       </c>
       <c r="I76" s="6" t="inlineStr">
         <is>
@@ -3884,10 +3879,10 @@
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.291</v>
+        <v>3.37</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>0.283</v>
+        <v>3.604</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="7" t="inlineStr"/>
@@ -3900,40 +3895,38 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>0.585</v>
-      </c>
-      <c r="E77" s="10" t="n">
-        <v>0</v>
+        <v>0.355</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>-0.0274</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>1659100</v>
+        <v>2007000</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="H77" t="n">
-        <v>68.69</v>
-      </c>
-      <c r="I77" s="9" t="inlineStr">
+        <v>60.83</v>
+      </c>
+      <c r="I77" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.509</v>
-      </c>
-      <c r="K77" s="2" t="n">
-        <v>0.468</v>
-      </c>
+        <v>0.318</v>
+      </c>
+      <c r="K77" s="2" t="n"/>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="7" t="inlineStr"/>
     </row>
@@ -3945,28 +3938,28 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>MRCB</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>0.255</v>
+        <v>0.86</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>-0.0192</v>
+        <v>-0.0391</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>1650400</v>
+        <v>1993400</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>0.19</v>
+        <v>0.26</v>
       </c>
       <c r="H78" t="n">
-        <v>27.74</v>
+        <v>42.22</v>
       </c>
       <c r="I78" s="6" t="inlineStr">
         <is>
@@ -3974,10 +3967,10 @@
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.276</v>
+        <v>0.927</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>0.301</v>
+        <v>0.847</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="7" t="inlineStr"/>
@@ -3990,39 +3983,39 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>0.335</v>
-      </c>
-      <c r="E79" s="10" t="n">
-        <v>0</v>
+        <v>0.965</v>
+      </c>
+      <c r="E79" s="9" t="n">
+        <v>0.0052</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>1641100</v>
+        <v>1971800</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="H79" t="n">
-        <v>47.09</v>
-      </c>
-      <c r="I79" s="9" t="inlineStr">
+        <v>66.12</v>
+      </c>
+      <c r="I79" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.335</v>
+        <v>0.925</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>0.343</v>
+        <v>0.877</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="7" t="inlineStr"/>
@@ -4035,39 +4028,39 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>IOIPG</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="E80" s="8" t="n">
-        <v>0.038</v>
+        <v>4.43</v>
+      </c>
+      <c r="E80" s="9" t="n">
+        <v>0.0255</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>1632100</v>
+        <v>1927000</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>0.27</v>
+        <v>0.36</v>
       </c>
       <c r="H80" t="n">
-        <v>39.03</v>
-      </c>
-      <c r="I80" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.94</v>
+      </c>
+      <c r="I80" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>3.373</v>
+        <v>4.359</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>3.604</v>
+        <v>4.431</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="7" t="inlineStr"/>
@@ -4080,39 +4073,39 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>0261</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>COSMOS</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>0.725</v>
-      </c>
-      <c r="E81" s="3" t="n">
-        <v>-0.0461</v>
+        <v>0.415</v>
+      </c>
+      <c r="E81" s="9" t="n">
+        <v>0.0375</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>1602700</v>
+        <v>1923300</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>0.3</v>
+        <v>5.77</v>
       </c>
       <c r="H81" t="n">
-        <v>46.5</v>
-      </c>
-      <c r="I81" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.86</v>
+      </c>
+      <c r="I81" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.76</v>
+        <v>0.382</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.363</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="7" t="inlineStr"/>
@@ -4125,28 +4118,28 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="E82" s="3" t="n">
-        <v>-0.0279</v>
+        <v>5.74</v>
+      </c>
+      <c r="E82" s="9" t="n">
+        <v>0.008800000000000001</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>1595300</v>
+        <v>1907000</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="H82" t="n">
-        <v>43.36</v>
+        <v>30.7</v>
       </c>
       <c r="I82" s="6" t="inlineStr">
         <is>
@@ -4154,10 +4147,10 @@
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.928</v>
+        <v>6.023</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>0.847</v>
+        <v>6.309</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="7" t="inlineStr"/>
@@ -4170,28 +4163,28 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0372</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>CHEEDING</t>
+          <t>DATASONIC</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>0.485</v>
+        <v>0.28</v>
       </c>
       <c r="E83" s="3" t="n">
-        <v>-0.0583</v>
+        <v>-0.0175</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>1553000</v>
+        <v>1871700</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>0.36</v>
+        <v>0.16</v>
       </c>
       <c r="H83" t="n">
-        <v>28.14</v>
+        <v>46.28</v>
       </c>
       <c r="I83" s="6" t="inlineStr">
         <is>
@@ -4199,10 +4192,10 @@
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.58</v>
+        <v>0.291</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>0.599</v>
+        <v>0.283</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="7" t="inlineStr"/>
@@ -4215,28 +4208,28 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0192</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>INTA</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>0.38</v>
+        <v>1.3</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>-0.013</v>
+        <v>-0.0226</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>1538400</v>
+        <v>1864000</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>0.57</v>
+        <v>0.78</v>
       </c>
       <c r="H84" t="n">
-        <v>41.3</v>
+        <v>56.17</v>
       </c>
       <c r="I84" s="6" t="inlineStr">
         <is>
@@ -4244,10 +4237,10 @@
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.394</v>
+        <v>1.26</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>0.389</v>
+        <v>1.173</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="7" t="inlineStr"/>
@@ -4260,39 +4253,39 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>5.73</v>
-      </c>
-      <c r="E85" s="8" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.58</v>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>-0.008500000000000001</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>1488100</v>
+        <v>1833300</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>0.2</v>
+        <v>0.44</v>
       </c>
       <c r="H85" t="n">
-        <v>29.97</v>
-      </c>
-      <c r="I85" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>67.36</v>
+      </c>
+      <c r="I85" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>6.022</v>
+        <v>0.509</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>6.308</v>
+        <v>0.468</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="7" t="inlineStr"/>
@@ -4305,28 +4298,28 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>0372</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>CHEEDING</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>0.595</v>
+        <v>0.49</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>-0.0325</v>
+        <v>-0.04849999999999999</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>1482500</v>
+        <v>1827300</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>0.26</v>
+        <v>0.42</v>
       </c>
       <c r="H86" t="n">
-        <v>57.47</v>
+        <v>28.71</v>
       </c>
       <c r="I86" s="6" t="inlineStr">
         <is>
@@ -4334,10 +4327,10 @@
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>0.47</v>
+        <v>0.599</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="7" t="inlineStr"/>
@@ -4350,39 +4343,39 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>0.285</v>
-      </c>
-      <c r="E87" s="10" t="n">
-        <v>0</v>
+        <v>0.34</v>
+      </c>
+      <c r="E87" s="9" t="n">
+        <v>0.0149</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>1466300</v>
+        <v>1755600</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>0.24</v>
+        <v>0.37</v>
       </c>
       <c r="H87" t="n">
-        <v>22.28</v>
-      </c>
-      <c r="I87" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.08</v>
+      </c>
+      <c r="I87" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.333</v>
+        <v>0.336</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>0.372</v>
+        <v>0.343</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="7" t="inlineStr"/>
@@ -4395,28 +4388,28 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>8524</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>TALIWRK</t>
+          <t>PECCA</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="E88" s="3" t="n">
-        <v>-0.0217</v>
+        <v>1.35</v>
+      </c>
+      <c r="E88" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>1404000</v>
+        <v>1728800</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>0.7</v>
+        <v>0.89</v>
       </c>
       <c r="H88" t="n">
-        <v>34.68</v>
+        <v>43.62</v>
       </c>
       <c r="I88" s="6" t="inlineStr">
         <is>
@@ -4424,10 +4417,10 @@
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.243</v>
+        <v>1.367</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>0.256</v>
+        <v>1.343</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="7" t="inlineStr"/>
@@ -4440,39 +4433,39 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>1.19</v>
+        <v>0.635</v>
       </c>
       <c r="E89" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>1391200</v>
+        <v>1715400</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>0.4</v>
+        <v>0.77</v>
       </c>
       <c r="H89" t="n">
-        <v>48.4</v>
-      </c>
-      <c r="I89" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.9</v>
+      </c>
+      <c r="I89" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>1.239</v>
+        <v>0.637</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>1.068</v>
+        <v>0.622</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="7" t="inlineStr"/>
@@ -4485,39 +4478,39 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="E90" s="8" t="n">
-        <v>0.016</v>
+        <v>0.26</v>
+      </c>
+      <c r="E90" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>1379200</v>
+        <v>1704300</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>0.24</v>
+        <v>0.2</v>
       </c>
       <c r="H90" t="n">
-        <v>45.71</v>
-      </c>
-      <c r="I90" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>30.11</v>
+      </c>
+      <c r="I90" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>1.92</v>
+        <v>0.277</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>1.95</v>
+        <v>0.301</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="7" t="inlineStr"/>
@@ -4530,39 +4523,39 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0261</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>COSMOS</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="E91" s="8" t="n">
-        <v>0.05</v>
+        <v>0.73</v>
+      </c>
+      <c r="E91" s="3" t="n">
+        <v>-0.0395</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>1376500</v>
+        <v>1680800</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>4.13</v>
+        <v>0.32</v>
       </c>
       <c r="H91" t="n">
-        <v>70.20999999999999</v>
-      </c>
-      <c r="I91" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.28</v>
+      </c>
+      <c r="I91" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.382</v>
+        <v>0.761</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>0.363</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="7" t="inlineStr"/>
@@ -4575,28 +4568,28 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="E92" s="3" t="n">
-        <v>-0.0273</v>
+        <v>0.285</v>
+      </c>
+      <c r="E92" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>1367400</v>
+        <v>1594500</v>
       </c>
       <c r="G92" s="5" t="n">
-        <v>0.23</v>
+        <v>0.26</v>
       </c>
       <c r="H92" t="n">
-        <v>41.03</v>
+        <v>22.28</v>
       </c>
       <c r="I92" s="6" t="inlineStr">
         <is>
@@ -4604,10 +4597,10 @@
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>2.603</v>
+        <v>0.333</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>2.607</v>
+        <v>0.372</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="7" t="inlineStr"/>
@@ -4620,28 +4613,28 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>0192</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>INTA</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>0.635</v>
+        <v>0.38</v>
       </c>
       <c r="E93" s="3" t="n">
-        <v>-0.0155</v>
+        <v>-0.013</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>1329700</v>
+        <v>1588400</v>
       </c>
       <c r="G93" s="5" t="n">
-        <v>0.15</v>
+        <v>0.59</v>
       </c>
       <c r="H93" t="n">
-        <v>40.95</v>
+        <v>41.3</v>
       </c>
       <c r="I93" s="6" t="inlineStr">
         <is>
@@ -4649,10 +4642,10 @@
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.678</v>
+        <v>0.394</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.389</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="7" t="inlineStr"/>
@@ -4665,28 +4658,28 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>5932</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>BPURI</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>0.21</v>
+        <v>1.17</v>
       </c>
       <c r="E94" s="3" t="n">
-        <v>-0.0233</v>
+        <v>-0.0168</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>1297400</v>
+        <v>1555600</v>
       </c>
       <c r="G94" s="5" t="n">
-        <v>1.89</v>
+        <v>0.44</v>
       </c>
       <c r="H94" t="n">
-        <v>38.22</v>
+        <v>46.47</v>
       </c>
       <c r="I94" s="6" t="inlineStr">
         <is>
@@ -4694,10 +4687,10 @@
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.223</v>
+        <v>1.237</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>0.232</v>
+        <v>1.067</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="7" t="inlineStr"/>
@@ -4710,28 +4703,28 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0298</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>WENTEL</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>0.235</v>
+        <v>0.635</v>
       </c>
       <c r="E95" s="3" t="n">
-        <v>-0.0408</v>
+        <v>-0.0155</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>1295300</v>
+        <v>1511200</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>0.76</v>
+        <v>0.17</v>
       </c>
       <c r="H95" t="n">
-        <v>36.24</v>
+        <v>40.95</v>
       </c>
       <c r="I95" s="6" t="inlineStr">
         <is>
@@ -4739,10 +4732,10 @@
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.254</v>
+        <v>0.678</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>0.274</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="7" t="inlineStr"/>
@@ -4755,28 +4748,28 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="E96" s="10" t="n">
-        <v>0</v>
+        <v>0.59</v>
+      </c>
+      <c r="E96" s="3" t="n">
+        <v>-0.0407</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>1294300</v>
+        <v>1508000</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="H96" t="n">
-        <v>58.81</v>
+        <v>56.69</v>
       </c>
       <c r="I96" s="6" t="inlineStr">
         <is>
@@ -4784,10 +4777,10 @@
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>1.055</v>
+        <v>0.569</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>0.914</v>
+        <v>0.47</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="7" t="inlineStr"/>
@@ -4800,28 +4793,28 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>1.24</v>
+        <v>0.925</v>
       </c>
       <c r="E97" s="3" t="n">
-        <v>-0.008</v>
+        <v>-0.0054</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>1243100</v>
+        <v>1497400</v>
       </c>
       <c r="G97" s="5" t="n">
-        <v>0.13</v>
+        <v>0.38</v>
       </c>
       <c r="H97" t="n">
-        <v>40.01</v>
+        <v>25.84</v>
       </c>
       <c r="I97" s="6" t="inlineStr">
         <is>
@@ -4829,10 +4822,10 @@
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>1.297</v>
+        <v>0.97</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>1.314</v>
+        <v>1.053</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="7" t="inlineStr"/>
@@ -4845,39 +4838,39 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>5248</t>
+          <t>5053</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>BAUTO</t>
+          <t>OSK</t>
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>0.905</v>
-      </c>
-      <c r="E98" s="8" t="n">
-        <v>0.0284</v>
+        <v>1.62</v>
+      </c>
+      <c r="E98" s="3" t="n">
+        <v>-0.0182</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>1233400</v>
+        <v>1470500</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>0.76</v>
+        <v>1.03</v>
       </c>
       <c r="H98" t="n">
-        <v>52.78</v>
-      </c>
-      <c r="I98" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>29.39</v>
+      </c>
+      <c r="I98" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.893</v>
+        <v>1.727</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>0.908</v>
+        <v>1.884</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="7" t="inlineStr"/>
@@ -4890,28 +4883,28 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D99" s="2" t="n">
-        <v>3.77</v>
+        <v>2.49</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>-0.0157</v>
+        <v>-0.0273</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v>1230100</v>
+        <v>1448900</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>0.42</v>
+        <v>0.24</v>
       </c>
       <c r="H99" t="n">
-        <v>48.07</v>
+        <v>41.03</v>
       </c>
       <c r="I99" s="6" t="inlineStr">
         <is>
@@ -4919,10 +4912,10 @@
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>3.843</v>
+        <v>2.603</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>3.681</v>
+        <v>2.607</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="7" t="inlineStr"/>
@@ -4935,28 +4928,28 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>8524</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>TALIWRK</t>
         </is>
       </c>
       <c r="D100" s="2" t="n">
-        <v>0.925</v>
+        <v>0.225</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>-0.0054</v>
+        <v>-0.0217</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>1209300</v>
+        <v>1422000</v>
       </c>
       <c r="G100" s="5" t="n">
-        <v>0.31</v>
+        <v>0.71</v>
       </c>
       <c r="H100" t="n">
-        <v>25.84</v>
+        <v>34.68</v>
       </c>
       <c r="I100" s="6" t="inlineStr">
         <is>
@@ -4964,10 +4957,10 @@
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.97</v>
+        <v>0.243</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>1.053</v>
+        <v>0.256</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="7" t="inlineStr"/>
@@ -4980,39 +4973,39 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0278</t>
+          <t>0325</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>EDELTEQ</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="D101" s="2" t="n">
-        <v>0.415</v>
-      </c>
-      <c r="E101" s="3" t="n">
-        <v>-0.0349</v>
+        <v>1.1</v>
+      </c>
+      <c r="E101" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F101" s="4" t="n">
-        <v>1204900</v>
+        <v>1400700</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>0.21</v>
+        <v>0.71</v>
       </c>
       <c r="H101" t="n">
-        <v>57.05</v>
-      </c>
-      <c r="I101" s="9" t="inlineStr">
+        <v>51.14</v>
+      </c>
+      <c r="I101" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.39</v>
+        <v>1.091</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>0.36</v>
+        <v>1.097</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="7" t="inlineStr"/>
@@ -5025,39 +5018,39 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D102" s="2" t="n">
-        <v>0.665</v>
-      </c>
-      <c r="E102" s="3" t="n">
-        <v>-0.0292</v>
+        <v>1.12</v>
+      </c>
+      <c r="E102" s="9" t="n">
+        <v>0.009000000000000001</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>1195300</v>
+        <v>1385100</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>0.44</v>
+        <v>0.32</v>
       </c>
       <c r="H102" t="n">
-        <v>58.27</v>
-      </c>
-      <c r="I102" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>59.59</v>
+      </c>
+      <c r="I102" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.647</v>
+        <v>1.056</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.914</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="7" t="inlineStr"/>
@@ -5085,10 +5078,10 @@
         <v>-0.008500000000000001</v>
       </c>
       <c r="F103" s="4" t="n">
-        <v>1190600</v>
+        <v>1375900</v>
       </c>
       <c r="G103" s="5" t="n">
-        <v>0.27</v>
+        <v>0.31</v>
       </c>
       <c r="H103" t="n">
         <v>47.94</v>
@@ -5115,39 +5108,39 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>5248</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>BAUTO</t>
         </is>
       </c>
       <c r="D104" s="2" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E104" s="8" t="n">
-        <v>0.0314</v>
+        <v>0.9</v>
+      </c>
+      <c r="E104" s="9" t="n">
+        <v>0.0227</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v>1186300</v>
+        <v>1367600</v>
       </c>
       <c r="G104" s="5" t="n">
-        <v>0.21</v>
+        <v>0.84</v>
       </c>
       <c r="H104" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="I104" s="9" t="inlineStr">
+        <v>51.19</v>
+      </c>
+      <c r="I104" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.794</v>
+        <v>0.893</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>0.772</v>
+        <v>0.908</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="7" t="inlineStr"/>
@@ -5160,39 +5153,39 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>0325</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D105" s="2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="E105" s="10" t="n">
-        <v>0</v>
+        <v>0.785</v>
+      </c>
+      <c r="E105" s="3" t="n">
+        <v>-0.0126</v>
       </c>
       <c r="F105" s="4" t="n">
-        <v>1126100</v>
+        <v>1364700</v>
       </c>
       <c r="G105" s="5" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="H105" t="n">
-        <v>51.14</v>
-      </c>
-      <c r="I105" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>15.53</v>
+      </c>
+      <c r="I105" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J105" s="2" t="n">
-        <v>1.091</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>1.097</v>
+        <v>1.078</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="7" t="inlineStr"/>
@@ -5205,39 +5198,39 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>0056</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>NCT</t>
         </is>
       </c>
       <c r="D106" s="2" t="n">
-        <v>0.785</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>-0.0126</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v>1119000</v>
+        <v>1360000</v>
       </c>
       <c r="G106" s="5" t="n">
-        <v>0.51</v>
+        <v>0.65</v>
       </c>
       <c r="H106" t="n">
-        <v>15.53</v>
-      </c>
-      <c r="I106" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.02</v>
+      </c>
+      <c r="I106" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>1.078</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="7" t="inlineStr"/>
@@ -5250,28 +5243,28 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>0245</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>MNHLDG</t>
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>0.75</v>
+        <v>3.75</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>-0.0323</v>
+        <v>-0.0209</v>
       </c>
       <c r="F107" s="4" t="n">
-        <v>1107500</v>
+        <v>1308700</v>
       </c>
       <c r="G107" s="5" t="n">
         <v>0.45</v>
       </c>
       <c r="H107" t="n">
-        <v>53.86</v>
+        <v>47.21</v>
       </c>
       <c r="I107" s="6" t="inlineStr">
         <is>
@@ -5279,10 +5272,10 @@
         </is>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.734</v>
+        <v>3.841</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>0.704</v>
+        <v>3.68</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="7" t="inlineStr"/>
@@ -5295,28 +5288,28 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>UWC</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D108" s="2" t="n">
-        <v>7.18</v>
-      </c>
-      <c r="E108" s="3" t="n">
-        <v>-0.0164</v>
+        <v>1.25</v>
+      </c>
+      <c r="E108" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>1082200</v>
+        <v>1308600</v>
       </c>
       <c r="G108" s="5" t="n">
-        <v>0.25</v>
+        <v>0.14</v>
       </c>
       <c r="H108" t="n">
-        <v>48.79</v>
+        <v>41.23</v>
       </c>
       <c r="I108" s="6" t="inlineStr">
         <is>
@@ -5324,10 +5317,10 @@
         </is>
       </c>
       <c r="J108" s="2" t="n">
-        <v>7.34</v>
+        <v>1.298</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>6.895</v>
+        <v>1.314</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="7" t="inlineStr"/>
@@ -5340,28 +5333,28 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D109" s="2" t="n">
-        <v>0.47</v>
+        <v>0.82</v>
       </c>
       <c r="E109" s="3" t="n">
-        <v>-0.0105</v>
+        <v>-0.0353</v>
       </c>
       <c r="F109" s="4" t="n">
-        <v>1057600</v>
+        <v>1305300</v>
       </c>
       <c r="G109" s="5" t="n">
-        <v>0.12</v>
+        <v>0.37</v>
       </c>
       <c r="H109" t="n">
-        <v>35.57</v>
+        <v>50.64</v>
       </c>
       <c r="I109" s="6" t="inlineStr">
         <is>
@@ -5369,10 +5362,10 @@
         </is>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.506</v>
+        <v>0.826</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>0.524</v>
+        <v>0.781</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="7" t="inlineStr"/>
@@ -5385,39 +5378,39 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>AWC</t>
         </is>
       </c>
       <c r="D110" s="2" t="n">
-        <v>1.14</v>
+        <v>0.665</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>-0.0172</v>
+        <v>-0.0292</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>1028600</v>
+        <v>1303300</v>
       </c>
       <c r="G110" s="5" t="n">
-        <v>0.24</v>
+        <v>0.48</v>
       </c>
       <c r="H110" t="n">
-        <v>49.11</v>
-      </c>
-      <c r="I110" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.27</v>
+      </c>
+      <c r="I110" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J110" s="2" t="n">
-        <v>1.159</v>
+        <v>0.647</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>1.1</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="7" t="inlineStr"/>
@@ -5430,39 +5423,39 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>0450</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>MFGROUP</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D111" s="2" t="n">
-        <v>0.28</v>
+        <v>2.76</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>-0.0175</v>
+        <v>-0.0143</v>
       </c>
       <c r="F111" s="4" t="n">
-        <v>1006700</v>
+        <v>1299100</v>
       </c>
       <c r="G111" s="5" t="n">
-        <v>1.06</v>
+        <v>0.35</v>
       </c>
       <c r="H111" t="n">
-        <v>55.75</v>
-      </c>
-      <c r="I111" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.45</v>
+      </c>
+      <c r="I111" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.276</v>
+        <v>2.895</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>0.267</v>
+        <v>3.012</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="7" t="inlineStr"/>
@@ -5475,28 +5468,28 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>5162</t>
+          <t>5932</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>VSTECS</t>
+          <t>BPURI</t>
         </is>
       </c>
       <c r="D112" s="2" t="n">
-        <v>1.5</v>
+        <v>0.21</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>-0.0323</v>
+        <v>-0.0233</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>986000</v>
+        <v>1297400</v>
       </c>
       <c r="G112" s="5" t="n">
-        <v>0.57</v>
+        <v>1.89</v>
       </c>
       <c r="H112" t="n">
-        <v>35.96</v>
+        <v>38.22</v>
       </c>
       <c r="I112" s="6" t="inlineStr">
         <is>
@@ -5504,10 +5497,10 @@
         </is>
       </c>
       <c r="J112" s="2" t="n">
-        <v>1.621</v>
+        <v>0.223</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>1.664</v>
+        <v>0.232</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="7" t="inlineStr"/>
@@ -5520,28 +5513,28 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>0298</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>WENTEL</t>
         </is>
       </c>
       <c r="D113" s="2" t="n">
-        <v>2.5</v>
+        <v>0.235</v>
       </c>
       <c r="E113" s="3" t="n">
-        <v>-0.0234</v>
+        <v>-0.0408</v>
       </c>
       <c r="F113" s="4" t="n">
-        <v>948400</v>
+        <v>1295300</v>
       </c>
       <c r="G113" s="5" t="n">
-        <v>0.18</v>
+        <v>0.76</v>
       </c>
       <c r="H113" t="n">
-        <v>32.79</v>
+        <v>36.24</v>
       </c>
       <c r="I113" s="6" t="inlineStr">
         <is>
@@ -5549,10 +5542,10 @@
         </is>
       </c>
       <c r="J113" s="2" t="n">
-        <v>2.808</v>
+        <v>0.254</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>2.877</v>
+        <v>0.274</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="7" t="inlineStr"/>
@@ -5565,28 +5558,28 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>5162</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>VSTECS</t>
         </is>
       </c>
       <c r="D114" s="2" t="n">
-        <v>0.845</v>
-      </c>
-      <c r="E114" s="10" t="n">
-        <v>0</v>
+        <v>1.51</v>
+      </c>
+      <c r="E114" s="3" t="n">
+        <v>-0.0258</v>
       </c>
       <c r="F114" s="4" t="n">
-        <v>922000</v>
+        <v>1266100</v>
       </c>
       <c r="G114" s="5" t="n">
-        <v>0.31</v>
+        <v>0.73</v>
       </c>
       <c r="H114" t="n">
-        <v>17.21</v>
+        <v>36.69</v>
       </c>
       <c r="I114" s="6" t="inlineStr">
         <is>
@@ -5594,10 +5587,10 @@
         </is>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.916</v>
+        <v>1.622</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>0.973</v>
+        <v>1.665</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="7" t="inlineStr"/>
@@ -5610,28 +5603,28 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>UWC</t>
         </is>
       </c>
       <c r="D115" s="2" t="n">
-        <v>2.76</v>
+        <v>7.22</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>-0.0143</v>
+        <v>-0.011</v>
       </c>
       <c r="F115" s="4" t="n">
-        <v>916100</v>
+        <v>1261100</v>
       </c>
       <c r="G115" s="5" t="n">
-        <v>0.24</v>
+        <v>0.29</v>
       </c>
       <c r="H115" t="n">
-        <v>39.45</v>
+        <v>49.64</v>
       </c>
       <c r="I115" s="6" t="inlineStr">
         <is>
@@ -5639,10 +5632,10 @@
         </is>
       </c>
       <c r="J115" s="2" t="n">
-        <v>2.895</v>
+        <v>7.344</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>3.012</v>
+        <v>6.896</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="7" t="inlineStr"/>
@@ -5655,28 +5648,28 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D116" s="2" t="n">
-        <v>1.27</v>
+        <v>0.465</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>-0.0379</v>
+        <v>-0.0211</v>
       </c>
       <c r="F116" s="4" t="n">
-        <v>901800</v>
+        <v>1228200</v>
       </c>
       <c r="G116" s="5" t="n">
-        <v>0.29</v>
+        <v>0.14</v>
       </c>
       <c r="H116" t="n">
-        <v>49.69</v>
+        <v>34.4</v>
       </c>
       <c r="I116" s="6" t="inlineStr">
         <is>
@@ -5684,10 +5677,10 @@
         </is>
       </c>
       <c r="J116" s="2" t="n">
-        <v>1.287</v>
+        <v>0.505</v>
       </c>
       <c r="K116" s="2" t="n">
-        <v>1.225</v>
+        <v>0.524</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="7" t="inlineStr"/>
@@ -5700,39 +5693,39 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>7498</t>
+          <t>0278</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>RALCO</t>
+          <t>EDELTEQ</t>
         </is>
       </c>
       <c r="D117" s="2" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="E117" s="10" t="n">
-        <v>0</v>
+        <v>0.415</v>
+      </c>
+      <c r="E117" s="3" t="n">
+        <v>-0.0349</v>
       </c>
       <c r="F117" s="4" t="n">
-        <v>878700</v>
+        <v>1215900</v>
       </c>
       <c r="G117" s="5" t="n">
-        <v>1.28</v>
+        <v>0.22</v>
       </c>
       <c r="H117" t="n">
-        <v>59.46</v>
-      </c>
-      <c r="I117" s="9" t="inlineStr">
+        <v>57.05</v>
+      </c>
+      <c r="I117" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J117" s="2" t="n">
-        <v>1.004</v>
+        <v>0.39</v>
       </c>
       <c r="K117" s="2" t="n">
-        <v>0.984</v>
+        <v>0.36</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="7" t="inlineStr"/>
@@ -5745,28 +5738,28 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>5329</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>AZAMJAYA</t>
         </is>
       </c>
       <c r="D118" s="2" t="n">
-        <v>2.79</v>
+        <v>0.96</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>-0.0071</v>
+        <v>-0.0352</v>
       </c>
       <c r="F118" s="4" t="n">
-        <v>875300</v>
+        <v>1202200</v>
       </c>
       <c r="G118" s="5" t="n">
-        <v>0.09</v>
+        <v>7.36</v>
       </c>
       <c r="H118" t="n">
-        <v>51.82</v>
+        <v>47.43</v>
       </c>
       <c r="I118" s="6" t="inlineStr">
         <is>
@@ -5774,10 +5767,10 @@
         </is>
       </c>
       <c r="J118" s="2" t="n">
-        <v>2.791</v>
+        <v>0.97</v>
       </c>
       <c r="K118" s="2" t="n">
-        <v>2.664</v>
+        <v>0.977</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="7" t="inlineStr"/>
@@ -5790,39 +5783,39 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D119" s="2" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="E119" s="3" t="n">
-        <v>-0.0235</v>
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="E119" s="9" t="n">
+        <v>0.0252</v>
       </c>
       <c r="F119" s="4" t="n">
-        <v>857300</v>
+        <v>1198800</v>
       </c>
       <c r="G119" s="5" t="n">
-        <v>0.24</v>
+        <v>0.21</v>
       </c>
       <c r="H119" t="n">
-        <v>52.34</v>
-      </c>
-      <c r="I119" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.98999999999999</v>
+      </c>
+      <c r="I119" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.827</v>
+        <v>0.793</v>
       </c>
       <c r="K119" s="2" t="n">
-        <v>0.781</v>
+        <v>0.771</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="7" t="inlineStr"/>
@@ -5835,28 +5828,28 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>0470</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>ATECH</t>
+          <t>BFIELD</t>
         </is>
       </c>
       <c r="D120" s="2" t="n">
-        <v>0.76</v>
+        <v>0.42</v>
       </c>
       <c r="E120" s="3" t="n">
-        <v>-0.0318</v>
+        <v>-0.0118</v>
       </c>
       <c r="F120" s="4" t="n">
-        <v>837200</v>
+        <v>1185200</v>
       </c>
       <c r="G120" s="5" t="n">
-        <v>0.36</v>
+        <v>0.21</v>
       </c>
       <c r="H120" t="n">
-        <v>47.23</v>
+        <v>17.86</v>
       </c>
       <c r="I120" s="6" t="inlineStr">
         <is>
@@ -5864,11 +5857,9 @@
         </is>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="K120" s="2" t="n">
-        <v>0.769</v>
-      </c>
+        <v>0.46</v>
+      </c>
+      <c r="K120" s="2" t="n"/>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="7" t="inlineStr"/>
     </row>
@@ -5880,28 +5871,28 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>0045</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>SSB8</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D121" s="2" t="n">
-        <v>0.63</v>
+        <v>0.68</v>
       </c>
       <c r="E121" s="3" t="n">
-        <v>-0.007900000000000001</v>
+        <v>-0.0145</v>
       </c>
       <c r="F121" s="4" t="n">
-        <v>826800</v>
+        <v>1182400</v>
       </c>
       <c r="G121" s="5" t="n">
-        <v>0.22</v>
+        <v>0.08</v>
       </c>
       <c r="H121" t="n">
-        <v>48.81</v>
+        <v>39.44</v>
       </c>
       <c r="I121" s="6" t="inlineStr">
         <is>
@@ -5909,10 +5900,10 @@
         </is>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.638</v>
+        <v>0.75</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>0.614</v>
+        <v>0.723</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="7" t="inlineStr"/>
@@ -5925,39 +5916,39 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>0233</t>
+          <t>8494</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>PEKAT</t>
+          <t>LBICAP</t>
         </is>
       </c>
       <c r="D122" s="2" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="E122" s="3" t="n">
-        <v>-0.0036</v>
+        <v>0.505</v>
+      </c>
+      <c r="E122" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F122" s="4" t="n">
-        <v>824200</v>
+        <v>1141000</v>
       </c>
       <c r="G122" s="5" t="n">
-        <v>0.23</v>
+        <v>6.51</v>
       </c>
       <c r="H122" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="I122" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>79.44</v>
+      </c>
+      <c r="I122" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J122" s="2" t="n">
-        <v>2.675</v>
+        <v>0.463</v>
       </c>
       <c r="K122" s="2" t="n">
-        <v>2.261</v>
+        <v>0.405</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="7" t="inlineStr"/>
@@ -5970,28 +5961,28 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>0151</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>KGB</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D123" s="2" t="n">
-        <v>8.23</v>
+        <v>0.75</v>
       </c>
       <c r="E123" s="3" t="n">
-        <v>-0.0144</v>
+        <v>-0.0323</v>
       </c>
       <c r="F123" s="4" t="n">
-        <v>783800</v>
+        <v>1107500</v>
       </c>
       <c r="G123" s="5" t="n">
-        <v>0.34</v>
+        <v>0.45</v>
       </c>
       <c r="H123" t="n">
-        <v>39.96</v>
+        <v>53.86</v>
       </c>
       <c r="I123" s="6" t="inlineStr">
         <is>
@@ -5999,10 +5990,10 @@
         </is>
       </c>
       <c r="J123" s="2" t="n">
-        <v>8.616</v>
+        <v>0.734</v>
       </c>
       <c r="K123" s="2" t="n">
-        <v>8.692</v>
+        <v>0.704</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="7" t="inlineStr"/>
@@ -6015,28 +6006,28 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>1619</t>
+          <t>0217</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>DRBHCOM</t>
+          <t>PWRWELL</t>
         </is>
       </c>
       <c r="D124" s="2" t="n">
-        <v>0.79</v>
+        <v>1.14</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>-0.0307</v>
+        <v>-0.0172</v>
       </c>
       <c r="F124" s="4" t="n">
-        <v>779900</v>
+        <v>1104200</v>
       </c>
       <c r="G124" s="5" t="n">
-        <v>1.58</v>
+        <v>0.26</v>
       </c>
       <c r="H124" t="n">
-        <v>14.69</v>
+        <v>49.11</v>
       </c>
       <c r="I124" s="6" t="inlineStr">
         <is>
@@ -6044,10 +6035,10 @@
         </is>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.883</v>
+        <v>1.159</v>
       </c>
       <c r="K124" s="2" t="n">
-        <v>0.9379999999999999</v>
+        <v>1.1</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="7" t="inlineStr"/>
@@ -6060,28 +6051,28 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>0099</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>SCICOM</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D125" s="2" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="E125" s="8" t="n">
-        <v>0.009599999999999999</v>
+        <v>2.49</v>
+      </c>
+      <c r="E125" s="3" t="n">
+        <v>-0.0273</v>
       </c>
       <c r="F125" s="4" t="n">
-        <v>777100</v>
+        <v>1095900</v>
       </c>
       <c r="G125" s="5" t="n">
-        <v>1.05</v>
+        <v>0.21</v>
       </c>
       <c r="H125" t="n">
-        <v>41.72</v>
+        <v>32.47</v>
       </c>
       <c r="I125" s="6" t="inlineStr">
         <is>
@@ -6089,10 +6080,10 @@
         </is>
       </c>
       <c r="J125" s="2" t="n">
-        <v>2.198</v>
+        <v>2.807</v>
       </c>
       <c r="K125" s="2" t="n">
-        <v>2.235</v>
+        <v>2.877</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="7" t="inlineStr"/>
@@ -6105,39 +6096,39 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>0045</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>SSB8</t>
         </is>
       </c>
       <c r="D126" s="2" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="E126" s="3" t="n">
-        <v>-0.0164</v>
+        <v>0.635</v>
+      </c>
+      <c r="E126" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F126" s="4" t="n">
-        <v>761300</v>
+        <v>1024300</v>
       </c>
       <c r="G126" s="5" t="n">
-        <v>0.08</v>
+        <v>0.27</v>
       </c>
       <c r="H126" t="n">
-        <v>31.05</v>
-      </c>
-      <c r="I126" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.64</v>
+      </c>
+      <c r="I126" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J126" s="2" t="n">
-        <v>7.454</v>
+        <v>0.639</v>
       </c>
       <c r="K126" s="2" t="n">
-        <v>7.948</v>
+        <v>0.615</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="7" t="inlineStr"/>
@@ -6150,39 +6141,39 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>6971</t>
+          <t>0450</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>KOBAY</t>
+          <t>MFGROUP</t>
         </is>
       </c>
       <c r="D127" s="2" t="n">
-        <v>2.06</v>
+        <v>0.28</v>
       </c>
       <c r="E127" s="3" t="n">
-        <v>-0.019</v>
+        <v>-0.0175</v>
       </c>
       <c r="F127" s="4" t="n">
-        <v>754100</v>
+        <v>1006700</v>
       </c>
       <c r="G127" s="5" t="n">
-        <v>0.62</v>
+        <v>1.06</v>
       </c>
       <c r="H127" t="n">
-        <v>42.97</v>
-      </c>
-      <c r="I127" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.75</v>
+      </c>
+      <c r="I127" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J127" s="2" t="n">
-        <v>2.124</v>
+        <v>0.276</v>
       </c>
       <c r="K127" s="2" t="n">
-        <v>2.28</v>
+        <v>0.267</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="7" t="inlineStr"/>
@@ -6195,28 +6186,28 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>0168</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>BMGREEN</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D128" s="2" t="n">
-        <v>1.41</v>
+        <v>0.84</v>
       </c>
       <c r="E128" s="3" t="n">
-        <v>-0.0408</v>
+        <v>-0.0059</v>
       </c>
       <c r="F128" s="4" t="n">
-        <v>744800</v>
+        <v>1004700</v>
       </c>
       <c r="G128" s="5" t="n">
-        <v>0.78</v>
+        <v>0.34</v>
       </c>
       <c r="H128" t="n">
-        <v>30.82</v>
+        <v>16.62</v>
       </c>
       <c r="I128" s="6" t="inlineStr">
         <is>
@@ -6224,10 +6215,10 @@
         </is>
       </c>
       <c r="J128" s="2" t="n">
-        <v>1.555</v>
+        <v>0.915</v>
       </c>
       <c r="K128" s="2" t="n">
-        <v>1.648</v>
+        <v>0.973</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="7" t="inlineStr"/>
@@ -6240,39 +6231,39 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>0151</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>KGB</t>
         </is>
       </c>
       <c r="D129" s="2" t="n">
-        <v>6.39</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E129" s="3" t="n">
-        <v>-0.0169</v>
+        <v>-0.006</v>
       </c>
       <c r="F129" s="4" t="n">
-        <v>696400</v>
+        <v>992000</v>
       </c>
       <c r="G129" s="5" t="n">
-        <v>0.12</v>
+        <v>0.44</v>
       </c>
       <c r="H129" t="n">
-        <v>55.18</v>
-      </c>
-      <c r="I129" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.33</v>
+      </c>
+      <c r="I129" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J129" s="2" t="n">
-        <v>6.162</v>
+        <v>8.622999999999999</v>
       </c>
       <c r="K129" s="2" t="n">
-        <v>5.91</v>
+        <v>8.694000000000001</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="7" t="inlineStr"/>
@@ -6285,39 +6276,39 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>PENTA</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D130" s="2" t="n">
-        <v>5.45</v>
+        <v>2.8</v>
       </c>
       <c r="E130" s="3" t="n">
-        <v>-0.0268</v>
+        <v>-0.0036</v>
       </c>
       <c r="F130" s="4" t="n">
-        <v>690600</v>
+        <v>990400</v>
       </c>
       <c r="G130" s="5" t="n">
-        <v>0.18</v>
+        <v>0.11</v>
       </c>
       <c r="H130" t="n">
-        <v>49.5</v>
-      </c>
-      <c r="I130" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.45</v>
+      </c>
+      <c r="I130" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J130" s="2" t="n">
-        <v>5.508</v>
+        <v>2.792</v>
       </c>
       <c r="K130" s="2" t="n">
-        <v>5.393</v>
+        <v>2.664</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="7" t="inlineStr"/>
@@ -6330,39 +6321,39 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>0271</t>
+          <t>0233</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>WELLS</t>
+          <t>PEKAT</t>
         </is>
       </c>
       <c r="D131" s="2" t="n">
-        <v>0.555</v>
-      </c>
-      <c r="E131" s="8" t="n">
-        <v>0.0091</v>
+        <v>2.79</v>
+      </c>
+      <c r="E131" s="9" t="n">
+        <v>0.0109</v>
       </c>
       <c r="F131" s="4" t="n">
-        <v>622500</v>
+        <v>967100</v>
       </c>
       <c r="G131" s="5" t="n">
-        <v>0.54</v>
+        <v>0.27</v>
       </c>
       <c r="H131" t="n">
-        <v>42.07</v>
-      </c>
-      <c r="I131" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>58.67</v>
+      </c>
+      <c r="I131" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J131" s="2" t="n">
-        <v>0.5679999999999999</v>
+        <v>2.678</v>
       </c>
       <c r="K131" s="2" t="n">
-        <v>0.611</v>
+        <v>2.261</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="7" t="inlineStr"/>
@@ -6375,28 +6366,28 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>1619</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>DRBHCOM</t>
         </is>
       </c>
       <c r="D132" s="2" t="n">
-        <v>0.735</v>
+        <v>0.795</v>
       </c>
       <c r="E132" s="3" t="n">
-        <v>-0.02</v>
+        <v>-0.0245</v>
       </c>
       <c r="F132" s="4" t="n">
-        <v>605900</v>
+        <v>915100</v>
       </c>
       <c r="G132" s="5" t="n">
-        <v>0.09</v>
+        <v>1.86</v>
       </c>
       <c r="H132" t="n">
-        <v>51.27</v>
+        <v>15.15</v>
       </c>
       <c r="I132" s="6" t="inlineStr">
         <is>
@@ -6404,10 +6395,10 @@
         </is>
       </c>
       <c r="J132" s="2" t="n">
-        <v>0.741</v>
+        <v>0.884</v>
       </c>
       <c r="K132" s="2" t="n">
-        <v>0.676</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="7" t="inlineStr"/>
@@ -6420,28 +6411,28 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>5053</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>OSK</t>
+          <t>CPETECH</t>
         </is>
       </c>
       <c r="D133" s="2" t="n">
-        <v>1.62</v>
+        <v>1.27</v>
       </c>
       <c r="E133" s="3" t="n">
-        <v>-0.0182</v>
+        <v>-0.0379</v>
       </c>
       <c r="F133" s="4" t="n">
-        <v>588000</v>
+        <v>908400</v>
       </c>
       <c r="G133" s="5" t="n">
-        <v>0.41</v>
+        <v>0.29</v>
       </c>
       <c r="H133" t="n">
-        <v>29.39</v>
+        <v>49.69</v>
       </c>
       <c r="I133" s="6" t="inlineStr">
         <is>
@@ -6449,10 +6440,10 @@
         </is>
       </c>
       <c r="J133" s="2" t="n">
-        <v>1.727</v>
+        <v>1.287</v>
       </c>
       <c r="K133" s="2" t="n">
-        <v>1.884</v>
+        <v>1.225</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="7" t="inlineStr"/>
@@ -6465,28 +6456,28 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>0168</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>BMGREEN</t>
         </is>
       </c>
       <c r="D134" s="2" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="E134" s="8" t="n">
-        <v>0.0042</v>
+        <v>1.39</v>
+      </c>
+      <c r="E134" s="3" t="n">
+        <v>-0.0544</v>
       </c>
       <c r="F134" s="4" t="n">
-        <v>576500</v>
+        <v>890200</v>
       </c>
       <c r="G134" s="5" t="n">
-        <v>0.05</v>
+        <v>0.93</v>
       </c>
       <c r="H134" t="n">
-        <v>43.4</v>
+        <v>29.55</v>
       </c>
       <c r="I134" s="6" t="inlineStr">
         <is>
@@ -6494,10 +6485,10 @@
         </is>
       </c>
       <c r="J134" s="2" t="n">
-        <v>2.441</v>
+        <v>1.553</v>
       </c>
       <c r="K134" s="2" t="n">
-        <v>2.384</v>
+        <v>1.648</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="7" t="inlineStr"/>
@@ -6510,28 +6501,28 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>3417</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>E&amp;O</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D135" s="2" t="n">
-        <v>0.745</v>
-      </c>
-      <c r="E135" s="3" t="n">
-        <v>-0.0067</v>
+        <v>2.41</v>
+      </c>
+      <c r="E135" s="9" t="n">
+        <v>0.0126</v>
       </c>
       <c r="F135" s="4" t="n">
-        <v>565200</v>
+        <v>882500</v>
       </c>
       <c r="G135" s="5" t="n">
-        <v>0.42</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H135" t="n">
-        <v>40.03</v>
+        <v>46.52</v>
       </c>
       <c r="I135" s="6" t="inlineStr">
         <is>
@@ -6539,10 +6530,10 @@
         </is>
       </c>
       <c r="J135" s="2" t="n">
-        <v>0.764</v>
+        <v>2.443</v>
       </c>
       <c r="K135" s="2" t="n">
-        <v>0.769</v>
+        <v>2.384</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="7" t="inlineStr"/>
@@ -6555,39 +6546,39 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>DUFU</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D136" s="2" t="n">
-        <v>3.01</v>
+        <v>6.39</v>
       </c>
       <c r="E136" s="3" t="n">
-        <v>-0.0195</v>
+        <v>-0.0169</v>
       </c>
       <c r="F136" s="4" t="n">
-        <v>562100</v>
+        <v>878800</v>
       </c>
       <c r="G136" s="5" t="n">
-        <v>0.18</v>
+        <v>0.15</v>
       </c>
       <c r="H136" t="n">
-        <v>51.22</v>
-      </c>
-      <c r="I136" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.18</v>
+      </c>
+      <c r="I136" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J136" s="2" t="n">
-        <v>3.027</v>
+        <v>6.162</v>
       </c>
       <c r="K136" s="2" t="n">
-        <v>2.856</v>
+        <v>5.91</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="7" t="inlineStr"/>
@@ -6600,39 +6591,39 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>5211</t>
+          <t>7498</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>SUNWAY</t>
+          <t>RALCO</t>
         </is>
       </c>
       <c r="D137" s="2" t="n">
-        <v>4.23</v>
-      </c>
-      <c r="E137" s="8" t="n">
-        <v>0.012</v>
+        <v>1.02</v>
+      </c>
+      <c r="E137" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F137" s="4" t="n">
-        <v>544400</v>
+        <v>878700</v>
       </c>
       <c r="G137" s="5" t="n">
-        <v>0.11</v>
+        <v>1.28</v>
       </c>
       <c r="H137" t="n">
-        <v>35.84</v>
-      </c>
-      <c r="I137" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.46</v>
+      </c>
+      <c r="I137" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J137" s="2" t="n">
-        <v>4.412</v>
+        <v>1.004</v>
       </c>
       <c r="K137" s="2" t="n">
-        <v>4.719</v>
+        <v>0.984</v>
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" s="7" t="inlineStr"/>
@@ -6645,28 +6636,28 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>SEG</t>
+          <t>ATECH</t>
         </is>
       </c>
       <c r="D138" s="2" t="n">
-        <v>0.625</v>
+        <v>0.76</v>
       </c>
       <c r="E138" s="3" t="n">
-        <v>-0.007900000000000001</v>
+        <v>-0.0318</v>
       </c>
       <c r="F138" s="4" t="n">
-        <v>538500</v>
+        <v>857700</v>
       </c>
       <c r="G138" s="5" t="n">
-        <v>0.47</v>
+        <v>0.37</v>
       </c>
       <c r="H138" t="n">
-        <v>34.58</v>
+        <v>47.23</v>
       </c>
       <c r="I138" s="6" t="inlineStr">
         <is>
@@ -6674,10 +6665,10 @@
         </is>
       </c>
       <c r="J138" s="2" t="n">
-        <v>0.631</v>
+        <v>0.775</v>
       </c>
       <c r="K138" s="2" t="n">
-        <v>0.631</v>
+        <v>0.769</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" s="7" t="inlineStr"/>
@@ -6690,39 +6681,39 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D139" s="2" t="n">
-        <v>0.6850000000000001</v>
+        <v>7.19</v>
       </c>
       <c r="E139" s="3" t="n">
-        <v>-0.0072</v>
+        <v>-0.0178</v>
       </c>
       <c r="F139" s="4" t="n">
-        <v>518500</v>
+        <v>831200</v>
       </c>
       <c r="G139" s="5" t="n">
-        <v>0.03</v>
+        <v>0.08</v>
       </c>
       <c r="H139" t="n">
-        <v>40.04</v>
-      </c>
-      <c r="I139" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>30.74</v>
+      </c>
+      <c r="I139" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J139" s="2" t="n">
-        <v>0.75</v>
+        <v>7.453</v>
       </c>
       <c r="K139" s="2" t="n">
-        <v>0.723</v>
+        <v>7.948</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" s="7" t="inlineStr"/>
@@ -6735,28 +6726,28 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>6971</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>KOBAY</t>
         </is>
       </c>
       <c r="D140" s="2" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="E140" s="3" t="n">
-        <v>-0.0098</v>
+        <v>-0.019</v>
       </c>
       <c r="F140" s="4" t="n">
-        <v>506400</v>
+        <v>812100</v>
       </c>
       <c r="G140" s="5" t="n">
-        <v>0.12</v>
+        <v>0.66</v>
       </c>
       <c r="H140" t="n">
-        <v>47.81</v>
+        <v>42.97</v>
       </c>
       <c r="I140" s="6" t="inlineStr">
         <is>
@@ -6764,10 +6755,10 @@
         </is>
       </c>
       <c r="J140" s="2" t="n">
-        <v>1.044</v>
+        <v>2.124</v>
       </c>
       <c r="K140" s="2" t="n">
-        <v>0.9419999999999999</v>
+        <v>2.28</v>
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" s="7" t="inlineStr"/>
@@ -6780,45 +6771,990 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>6947</t>
+          <t>7160</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>PENTA</t>
         </is>
       </c>
       <c r="D141" s="2" t="n">
-        <v>2.49</v>
+        <v>5.47</v>
       </c>
       <c r="E141" s="3" t="n">
-        <v>-0.0235</v>
+        <v>-0.0232</v>
       </c>
       <c r="F141" s="4" t="n">
-        <v>503100</v>
+        <v>811800</v>
       </c>
       <c r="G141" s="5" t="n">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="H141" t="n">
-        <v>38.18</v>
-      </c>
-      <c r="I141" s="9" t="inlineStr">
+        <v>49.98</v>
+      </c>
+      <c r="I141" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J141" s="2" t="n">
-        <v>2.558</v>
+        <v>5.51</v>
       </c>
       <c r="K141" s="2" t="n">
-        <v>2.685</v>
+        <v>5.393</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" s="7" t="inlineStr"/>
     </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>5272</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>RANHILL</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="E142" s="3" t="n">
+        <v>-0.0064</v>
+      </c>
+      <c r="F142" s="4" t="n">
+        <v>802200</v>
+      </c>
+      <c r="G142" s="5" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="H142" t="n">
+        <v>50.69</v>
+      </c>
+      <c r="I142" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J142" s="2" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="K142" s="2" t="n">
+        <v>2.876</v>
+      </c>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" s="7" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>0215</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>SLVEST</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="E143" s="9" t="n">
+        <v>0.0026</v>
+      </c>
+      <c r="F143" s="4" t="n">
+        <v>800800</v>
+      </c>
+      <c r="G143" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H143" t="n">
+        <v>51.6</v>
+      </c>
+      <c r="I143" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J143" s="2" t="n">
+        <v>3.957</v>
+      </c>
+      <c r="K143" s="2" t="n">
+        <v>3.555</v>
+      </c>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" s="7" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>0099</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>SCICOM</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="E144" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F144" s="4" t="n">
+        <v>791600</v>
+      </c>
+      <c r="G144" s="5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="H144" t="n">
+        <v>39.81</v>
+      </c>
+      <c r="I144" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J144" s="2" t="n">
+        <v>2.196</v>
+      </c>
+      <c r="K144" s="2" t="n">
+        <v>2.235</v>
+      </c>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" s="7" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>5347</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>TENAGA</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="n">
+        <v>12.82</v>
+      </c>
+      <c r="E145" s="3" t="n">
+        <v>-0.0138</v>
+      </c>
+      <c r="F145" s="4" t="n">
+        <v>776700</v>
+      </c>
+      <c r="G145" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H145" t="n">
+        <v>37.85</v>
+      </c>
+      <c r="I145" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J145" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="K145" s="2" t="n">
+        <v>13.412</v>
+      </c>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" s="7" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>0310</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>UUE</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="n">
+        <v>0.735</v>
+      </c>
+      <c r="E146" s="3" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="F146" s="4" t="n">
+        <v>766100</v>
+      </c>
+      <c r="G146" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H146" t="n">
+        <v>51.27</v>
+      </c>
+      <c r="I146" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J146" s="2" t="n">
+        <v>0.741</v>
+      </c>
+      <c r="K146" s="2" t="n">
+        <v>0.676</v>
+      </c>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" s="7" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>5141</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>DAYANG</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="E147" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F147" s="4" t="n">
+        <v>723500</v>
+      </c>
+      <c r="G147" s="5" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="H147" t="n">
+        <v>27.74</v>
+      </c>
+      <c r="I147" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J147" s="2" t="n">
+        <v>1.404</v>
+      </c>
+      <c r="K147" s="2" t="n">
+        <v>1.466</v>
+      </c>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" s="7" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>0223</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>SAMAIDEN</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="E148" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F148" s="4" t="n">
+        <v>723400</v>
+      </c>
+      <c r="G148" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H148" t="n">
+        <v>58.22</v>
+      </c>
+      <c r="I148" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J148" s="2" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="K148" s="2" t="n">
+        <v>2.212</v>
+      </c>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" s="7" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>5211</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>SUNWAY</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="E149" s="9" t="n">
+        <v>0.009599999999999999</v>
+      </c>
+      <c r="F149" s="4" t="n">
+        <v>702600</v>
+      </c>
+      <c r="G149" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H149" t="n">
+        <v>35.14</v>
+      </c>
+      <c r="I149" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J149" s="2" t="n">
+        <v>4.411</v>
+      </c>
+      <c r="K149" s="2" t="n">
+        <v>4.719</v>
+      </c>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" s="7" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>5299</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>IGBCR</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="E150" s="9" t="n">
+        <v>0.008199999999999999</v>
+      </c>
+      <c r="F150" s="4" t="n">
+        <v>639200</v>
+      </c>
+      <c r="G150" s="5" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="H150" t="n">
+        <v>51.11</v>
+      </c>
+      <c r="I150" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J150" s="2" t="n">
+        <v>0.614</v>
+      </c>
+      <c r="K150" s="2" t="n">
+        <v>0.613</v>
+      </c>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" s="7" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>0296</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>HEGROUP</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="E151" s="3" t="n">
+        <v>-0.0098</v>
+      </c>
+      <c r="F151" s="4" t="n">
+        <v>638100</v>
+      </c>
+      <c r="G151" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H151" t="n">
+        <v>47.81</v>
+      </c>
+      <c r="I151" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J151" s="2" t="n">
+        <v>1.044</v>
+      </c>
+      <c r="K151" s="2" t="n">
+        <v>0.9419999999999999</v>
+      </c>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" s="7" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>5258</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>BIMB</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E152" s="3" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="F152" s="4" t="n">
+        <v>625300</v>
+      </c>
+      <c r="G152" s="5" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="H152" t="n">
+        <v>34.83</v>
+      </c>
+      <c r="I152" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J152" s="2" t="n">
+        <v>2.037</v>
+      </c>
+      <c r="K152" s="2" t="n">
+        <v>2.081</v>
+      </c>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" s="7" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>0271</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>WELLS</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="n">
+        <v>0.555</v>
+      </c>
+      <c r="E153" s="9" t="n">
+        <v>0.0091</v>
+      </c>
+      <c r="F153" s="4" t="n">
+        <v>622500</v>
+      </c>
+      <c r="G153" s="5" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="H153" t="n">
+        <v>42.07</v>
+      </c>
+      <c r="I153" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J153" s="2" t="n">
+        <v>0.5679999999999999</v>
+      </c>
+      <c r="K153" s="2" t="n">
+        <v>0.611</v>
+      </c>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" s="7" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>3417</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>E&amp;O</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="n">
+        <v>0.745</v>
+      </c>
+      <c r="E154" s="3" t="n">
+        <v>-0.0067</v>
+      </c>
+      <c r="F154" s="4" t="n">
+        <v>607700</v>
+      </c>
+      <c r="G154" s="5" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H154" t="n">
+        <v>40.03</v>
+      </c>
+      <c r="I154" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J154" s="2" t="n">
+        <v>0.764</v>
+      </c>
+      <c r="K154" s="2" t="n">
+        <v>0.769</v>
+      </c>
+      <c r="L154" t="inlineStr"/>
+      <c r="M154" s="7" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>6947</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>CDB</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E155" s="3" t="n">
+        <v>-0.0196</v>
+      </c>
+      <c r="F155" s="4" t="n">
+        <v>594500</v>
+      </c>
+      <c r="G155" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H155" t="n">
+        <v>39.11</v>
+      </c>
+      <c r="I155" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J155" s="2" t="n">
+        <v>2.559</v>
+      </c>
+      <c r="K155" s="2" t="n">
+        <v>2.685</v>
+      </c>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" s="7" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>0167</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>MCLEAN</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E156" s="3" t="n">
+        <v>-0.0299</v>
+      </c>
+      <c r="F156" s="4" t="n">
+        <v>594100</v>
+      </c>
+      <c r="G156" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H156" t="n">
+        <v>33.63</v>
+      </c>
+      <c r="I156" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J156" s="2" t="n">
+        <v>0.723</v>
+      </c>
+      <c r="K156" s="2" t="n">
+        <v>0.744</v>
+      </c>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" s="7" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>5323</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>JPG</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="E157" s="9" t="n">
+        <v>0.0117</v>
+      </c>
+      <c r="F157" s="4" t="n">
+        <v>576800</v>
+      </c>
+      <c r="G157" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H157" t="n">
+        <v>39.28</v>
+      </c>
+      <c r="I157" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J157" s="2" t="n">
+        <v>1.775</v>
+      </c>
+      <c r="K157" s="2" t="n">
+        <v>1.888</v>
+      </c>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" s="7" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>7233</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>DUFU</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="E158" s="3" t="n">
+        <v>-0.0195</v>
+      </c>
+      <c r="F158" s="4" t="n">
+        <v>573800</v>
+      </c>
+      <c r="G158" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H158" t="n">
+        <v>51.22</v>
+      </c>
+      <c r="I158" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J158" s="2" t="n">
+        <v>3.027</v>
+      </c>
+      <c r="K158" s="2" t="n">
+        <v>2.856</v>
+      </c>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" s="7" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>4383</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>JTIASA</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="E159" s="9" t="n">
+        <v>0.005500000000000001</v>
+      </c>
+      <c r="F159" s="4" t="n">
+        <v>557200</v>
+      </c>
+      <c r="G159" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H159" t="n">
+        <v>33.51</v>
+      </c>
+      <c r="I159" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J159" s="2" t="n">
+        <v>0.945</v>
+      </c>
+      <c r="K159" s="2" t="n">
+        <v>1.002</v>
+      </c>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" s="7" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>5212</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>PAVREIT</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="E160" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F160" s="4" t="n">
+        <v>547100</v>
+      </c>
+      <c r="G160" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H160" t="n">
+        <v>47.18</v>
+      </c>
+      <c r="I160" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J160" s="2" t="n">
+        <v>1.568</v>
+      </c>
+      <c r="K160" s="2" t="n">
+        <v>1.601</v>
+      </c>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" s="7" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>9792</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>SEG</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E161" s="3" t="n">
+        <v>-0.007900000000000001</v>
+      </c>
+      <c r="F161" s="4" t="n">
+        <v>538500</v>
+      </c>
+      <c r="G161" s="5" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="H161" t="n">
+        <v>34.58</v>
+      </c>
+      <c r="I161" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J161" s="2" t="n">
+        <v>0.631</v>
+      </c>
+      <c r="K161" s="2" t="n">
+        <v>0.631</v>
+      </c>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" s="7" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>5176</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>SUNREIT</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="E162" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F162" s="4" t="n">
+        <v>515800</v>
+      </c>
+      <c r="G162" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H162" t="n">
+        <v>44.02</v>
+      </c>
+      <c r="I162" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J162" s="2" t="n">
+        <v>2.044</v>
+      </c>
+      <c r="K162" s="2" t="n">
+        <v>2.071</v>
+      </c>
+      <c r="L162" t="inlineStr"/>
+      <c r="M162" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M141"/>
+  <autoFilter ref="A1:M162"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-19/bursa-report-2026-10-19.xlsx
+++ b/docs/downloads/2026-10-19/bursa-report-2026-10-19.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-19" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-19'!$A$1:$M$162</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-19'!$A$1:$M$184</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -35,13 +35,13 @@
       <color rgb="00FFFFFF"/>
     </font>
     <font>
+      <color rgb="00898781"/>
+    </font>
+    <font>
       <color rgb="00D03B3B"/>
     </font>
     <font>
       <color rgb="000CA30C"/>
-    </font>
-    <font>
-      <color rgb="00898781"/>
     </font>
   </fonts>
   <fills count="3">
@@ -78,12 +78,12 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M162"/>
+  <dimension ref="A1:M184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -552,19 +552,19 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.05</v>
+        <v>0.055</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>-0.09089999999999999</v>
+        <v>0</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>56805100</v>
+        <v>62710900</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="H2" t="n">
-        <v>22.63</v>
+        <v>23.16</v>
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
@@ -599,14 +599,14 @@
       <c r="D3" s="2" t="n">
         <v>0.32</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" s="8" t="n">
         <v>-0.0588</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>44809000</v>
+        <v>47628600</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.58</v>
+        <v>0.61</v>
       </c>
       <c r="H3" t="n">
         <v>59.82</v>
@@ -642,21 +642,21 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.895</v>
+        <v>0.9</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>-0.005600000000000001</v>
+        <v>0</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>42106200</v>
+        <v>42961200</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="H4" t="n">
-        <v>65.20999999999999</v>
-      </c>
-      <c r="I4" s="8" t="inlineStr">
+        <v>66.28</v>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -689,14 +689,14 @@
       <c r="D5" s="2" t="n">
         <v>0.135</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="E5" s="8" t="n">
         <v>-0.06900000000000001</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>27276100</v>
+        <v>27879200</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="H5" t="n">
         <v>40.3</v>
@@ -732,27 +732,27 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="E6" s="9" t="n">
-        <v>0.0149</v>
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>0.0299</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>20252800</v>
+        <v>21902100</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.87</v>
       </c>
       <c r="H6" t="n">
-        <v>76.73999999999999</v>
-      </c>
-      <c r="I6" s="8" t="inlineStr">
+        <v>78.11</v>
+      </c>
+      <c r="I6" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.617</v>
+        <v>0.618</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>0.531</v>
@@ -768,39 +768,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>4.7</v>
+        <v>0.42</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>-0.0269</v>
+        <v>0</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>15108700</v>
+        <v>17494600</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="H7" t="n">
-        <v>46.13</v>
-      </c>
-      <c r="I7" s="8" t="inlineStr">
+        <v>74.48999999999999</v>
+      </c>
+      <c r="I7" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>4.727</v>
+        <v>0.382</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>4.847</v>
+        <v>0.277</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="7" t="inlineStr"/>
@@ -813,39 +813,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="E8" s="10" t="n">
-        <v>0</v>
+        <v>4.69</v>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>-0.029</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>14556700</v>
+        <v>15886300</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.42</v>
+        <v>0.85</v>
       </c>
       <c r="H8" t="n">
-        <v>74.48999999999999</v>
-      </c>
-      <c r="I8" s="8" t="inlineStr">
+        <v>45.45</v>
+      </c>
+      <c r="I8" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.382</v>
+        <v>4.726</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.277</v>
+        <v>4.847</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="7" t="inlineStr"/>
@@ -858,28 +858,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>7071</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>OCR</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>-0.0968</v>
+        <v>0.045</v>
+      </c>
+      <c r="E9" s="8" t="n">
+        <v>-0.1</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>12186100</v>
+        <v>14934300</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>1.4</v>
+        <v>13.41</v>
       </c>
       <c r="H9" t="n">
-        <v>43.38</v>
+        <v>29.14</v>
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
@@ -887,10 +887,10 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.298</v>
+        <v>0.049</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.28</v>
+        <v>0.05</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="7" t="inlineStr"/>
@@ -903,39 +903,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0.44</v>
+        <v>0.31</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>-0.0112</v>
+        <v>0</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>10286100</v>
+        <v>12273000</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.51</v>
+        <v>0.63</v>
       </c>
       <c r="H10" t="n">
-        <v>57.56</v>
-      </c>
-      <c r="I10" s="8" t="inlineStr">
+        <v>54.55</v>
+      </c>
+      <c r="I10" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.423</v>
+        <v>0.309</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0.367</v>
+        <v>0.3</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="7" t="inlineStr"/>
@@ -948,39 +948,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>4251</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>IBHD</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0.215</v>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>-0.0227</v>
+        <v>0.285</v>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>-0.0806</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>9430100</v>
+        <v>12201200</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>32.38</v>
+        <v>1.4</v>
       </c>
       <c r="H11" t="n">
-        <v>53.06</v>
-      </c>
-      <c r="I11" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.31</v>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.212</v>
+        <v>0.299</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0.217</v>
+        <v>0.28</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="7" t="inlineStr"/>
@@ -993,39 +993,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="E12" s="10" t="n">
-        <v>0</v>
+        <v>0.44</v>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>-0.0112</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>9161500</v>
+        <v>11959500</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.47</v>
+        <v>0.59</v>
       </c>
       <c r="H12" t="n">
-        <v>54.55</v>
-      </c>
-      <c r="I12" s="8" t="inlineStr">
+        <v>57.56</v>
+      </c>
+      <c r="I12" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.309</v>
+        <v>0.423</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0.3</v>
+        <v>0.367</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="7" t="inlineStr"/>
@@ -1038,28 +1038,28 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>0095</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0.435</v>
+        <v>0.155</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>-0.0333</v>
+        <v>0</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>7949400</v>
+        <v>11914800</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.22</v>
+        <v>0.34</v>
       </c>
       <c r="H13" t="n">
-        <v>36.45</v>
+        <v>48.61</v>
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
@@ -1067,10 +1067,10 @@
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.477</v>
+        <v>0.155</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0.482</v>
+        <v>0.156</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="7" t="inlineStr"/>
@@ -1083,39 +1083,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0081</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>REKATECH</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>-0.1111</v>
+        <v>0.44</v>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>-0.0222</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>7943500</v>
+        <v>9870500</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>21.48</v>
+        <v>0.27</v>
       </c>
       <c r="H14" t="n">
-        <v>70.23999999999999</v>
-      </c>
-      <c r="I14" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.57</v>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.026</v>
+        <v>0.478</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0.024</v>
+        <v>0.482</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="7" t="inlineStr"/>
@@ -1128,39 +1128,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0095</t>
+          <t>4251</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MAG</t>
+          <t>IBHD</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="E15" s="10" t="n">
-        <v>0</v>
+        <v>0.215</v>
+      </c>
+      <c r="E15" s="8" t="n">
+        <v>-0.0227</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>7414800</v>
+        <v>9440100</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.21</v>
+        <v>32.41</v>
       </c>
       <c r="H15" t="n">
-        <v>48.61</v>
-      </c>
-      <c r="I15" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.06</v>
+      </c>
+      <c r="I15" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.155</v>
+        <v>0.212</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0.156</v>
+        <v>0.217</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="7" t="inlineStr"/>
@@ -1173,39 +1173,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>1.96</v>
+        <v>0.865</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>-0.0297</v>
+        <v>0</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>7301400</v>
+        <v>8277900</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.25</v>
+        <v>0.42</v>
       </c>
       <c r="H16" t="n">
-        <v>55.27</v>
-      </c>
-      <c r="I16" s="8" t="inlineStr">
+        <v>45.57</v>
+      </c>
+      <c r="I16" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.924</v>
+        <v>0.868</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>1.739</v>
+        <v>0.869</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="7" t="inlineStr"/>
@@ -1218,33 +1218,40 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>0081</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SLG</t>
+          <t>REKATECH</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E17" s="10" t="n">
-        <v>0</v>
+        <v>0.04</v>
+      </c>
+      <c r="E17" s="8" t="n">
+        <v>-0.1111</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>6874700</v>
+        <v>7943500</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="I17" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="n"/>
-      <c r="K17" s="2" t="n"/>
+        <v>21.48</v>
+      </c>
+      <c r="H17" t="n">
+        <v>70.23999999999999</v>
+      </c>
+      <c r="I17" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="K17" s="2" t="n">
+        <v>0.024</v>
+      </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="7" t="inlineStr"/>
     </row>
@@ -1256,39 +1263,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="E18" s="3" t="n">
-        <v>-0.03759999999999999</v>
+        <v>1.98</v>
+      </c>
+      <c r="E18" s="8" t="n">
+        <v>-0.0198</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>6617200</v>
+        <v>7713600</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.37</v>
+        <v>0.26</v>
       </c>
       <c r="H18" t="n">
-        <v>46.31</v>
-      </c>
-      <c r="I18" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.58</v>
+      </c>
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>2.641</v>
+        <v>1.926</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>2.553</v>
+        <v>1.74</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="7" t="inlineStr"/>
@@ -1301,28 +1308,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>3891</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MUIIND</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="E19" s="10" t="n">
-        <v>0</v>
+        <v>2.56</v>
+      </c>
+      <c r="E19" s="8" t="n">
+        <v>-0.03759999999999999</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>6500400</v>
+        <v>7234700</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>3.83</v>
+        <v>0.4</v>
       </c>
       <c r="H19" t="n">
-        <v>46.69</v>
+        <v>46.31</v>
       </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
@@ -1330,10 +1337,10 @@
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.041</v>
+        <v>2.641</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0.042</v>
+        <v>2.553</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="7" t="inlineStr"/>
@@ -1346,39 +1353,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="E20" s="3" t="n">
-        <v>-0.0058</v>
+        <v>0.775</v>
+      </c>
+      <c r="E20" s="8" t="n">
+        <v>-0.0064</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>6281000</v>
+        <v>7034000</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.32</v>
+        <v>0.46</v>
       </c>
       <c r="H20" t="n">
-        <v>40.62</v>
-      </c>
-      <c r="I20" s="8" t="inlineStr">
+        <v>49.91</v>
+      </c>
+      <c r="I20" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.868</v>
+        <v>0.775</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0.869</v>
+        <v>0.776</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="7" t="inlineStr"/>
@@ -1391,29 +1398,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0477</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ECOSYS</t>
+          <t>SLG</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>0.755</v>
+        <v>0.25</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>-0.0382</v>
+        <v>0</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>6235600</v>
+        <v>6915700</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="I21" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>0.28</v>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J21" s="2" t="n"/>
@@ -1429,28 +1436,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E22" s="10" t="n">
-        <v>0</v>
+        <v>4.78</v>
+      </c>
+      <c r="E22" s="8" t="n">
+        <v>-0.0042</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>6072500</v>
+        <v>6899700</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>1.95</v>
+        <v>0.27</v>
       </c>
       <c r="H22" t="n">
-        <v>49.08</v>
+        <v>44.85</v>
       </c>
       <c r="I22" s="6" t="inlineStr">
         <is>
@@ -1458,10 +1465,10 @@
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.295</v>
+        <v>4.897</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0.295</v>
+        <v>4.728</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="7" t="inlineStr"/>
@@ -1474,40 +1481,33 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>0477</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>ECOSYS</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E23" s="3" t="n">
-        <v>-0.0064</v>
+        <v>0.755</v>
+      </c>
+      <c r="E23" s="8" t="n">
+        <v>-0.0382</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>6053100</v>
+        <v>6716300</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="H23" t="n">
-        <v>49.91</v>
-      </c>
-      <c r="I23" s="8" t="inlineStr">
+        <v>0.09</v>
+      </c>
+      <c r="I23" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J23" s="2" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="K23" s="2" t="n">
-        <v>0.776</v>
-      </c>
+      <c r="J23" s="2" t="n"/>
+      <c r="K23" s="2" t="n"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="7" t="inlineStr"/>
     </row>
@@ -1519,39 +1519,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>5156</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>XDL</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="E24" s="10" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="E24" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>5950100</v>
+        <v>6697200</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>2.42</v>
+        <v>0.41</v>
       </c>
       <c r="H24" t="n">
-        <v>44.81</v>
-      </c>
-      <c r="I24" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.16</v>
+      </c>
+      <c r="I24" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.007</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0.007</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="7" t="inlineStr"/>
@@ -1564,39 +1564,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E25" s="10" t="n">
-        <v>0</v>
+        <v>0.99</v>
+      </c>
+      <c r="E25" s="8" t="n">
+        <v>-0.0198</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>5874600</v>
+        <v>6651400</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.54</v>
+        <v>0.84</v>
       </c>
       <c r="H25" t="n">
-        <v>56.82</v>
-      </c>
-      <c r="I25" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.57</v>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.617</v>
+        <v>1.049</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0.615</v>
+        <v>0.959</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="7" t="inlineStr"/>
@@ -1609,39 +1609,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>3891</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>MUIIND</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E26" s="10" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E26" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>5812300</v>
+        <v>6510400</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.36</v>
+        <v>3.84</v>
       </c>
       <c r="H26" t="n">
-        <v>57.16</v>
-      </c>
-      <c r="I26" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.69</v>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.041</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.042</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="7" t="inlineStr"/>
@@ -1654,39 +1654,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>1.08</v>
+        <v>0.625</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.0182</v>
+        <v>0</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>5472300</v>
+        <v>6500600</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="H27" t="n">
-        <v>51.15</v>
-      </c>
-      <c r="I27" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.82</v>
+      </c>
+      <c r="I27" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>1.077</v>
+        <v>0.617</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>1.045</v>
+        <v>0.615</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="7" t="inlineStr"/>
@@ -1699,28 +1699,28 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>0.98</v>
+        <v>0.405</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>-0.0297</v>
+        <v>0</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>5465400</v>
+        <v>6303700</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.51</v>
       </c>
       <c r="H28" t="n">
-        <v>42.43</v>
+        <v>55.08</v>
       </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
@@ -1728,10 +1728,10 @@
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>1.048</v>
+        <v>0.391</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0.959</v>
+        <v>0.378</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="7" t="inlineStr"/>
@@ -1744,28 +1744,28 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>4.76</v>
-      </c>
-      <c r="E29" s="3" t="n">
-        <v>-0.0083</v>
+        <v>6.67</v>
+      </c>
+      <c r="E29" s="10" t="n">
+        <v>0.0262</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>5262900</v>
+        <v>6143200</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.21</v>
+        <v>0.63</v>
       </c>
       <c r="H29" t="n">
-        <v>43.88</v>
+        <v>28.27</v>
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
@@ -1773,10 +1773,10 @@
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>4.895</v>
+        <v>7.208</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>4.728</v>
+        <v>7.606</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="7" t="inlineStr"/>
@@ -1789,28 +1789,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>0.535</v>
+        <v>0.295</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-0.036</v>
+        <v>0</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>5188500</v>
+        <v>6072500</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.25</v>
+        <v>1.95</v>
       </c>
       <c r="H30" t="n">
-        <v>44.62</v>
+        <v>49.08</v>
       </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
@@ -1818,10 +1818,10 @@
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.572</v>
+        <v>0.295</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0.541</v>
+        <v>0.295</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="7" t="inlineStr"/>
@@ -1834,28 +1834,28 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>5156</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>XDL</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>6.67</v>
-      </c>
-      <c r="E31" s="9" t="n">
-        <v>0.0262</v>
+        <v>0.005</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>5055100</v>
+        <v>5950100</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.52</v>
+        <v>2.42</v>
       </c>
       <c r="H31" t="n">
-        <v>28.27</v>
+        <v>44.81</v>
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
@@ -1863,10 +1863,10 @@
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>7.208</v>
+        <v>0.007</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>7.606</v>
+        <v>0.007</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="7" t="inlineStr"/>
@@ -1879,28 +1879,28 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>0.435</v>
-      </c>
-      <c r="E32" s="9" t="n">
-        <v>0.0357</v>
+        <v>1.42</v>
+      </c>
+      <c r="E32" s="8" t="n">
+        <v>-0.0207</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>4880300</v>
+        <v>5807800</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.72</v>
+        <v>0.52</v>
       </c>
       <c r="H32" t="n">
-        <v>53.65</v>
+        <v>21.41</v>
       </c>
       <c r="I32" s="6" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.425</v>
+        <v>1.691</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0.416</v>
+        <v>1.944</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="7" t="inlineStr"/>
@@ -1924,28 +1924,28 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="E33" s="3" t="n">
-        <v>-0.0207</v>
+        <v>1.08</v>
+      </c>
+      <c r="E33" s="8" t="n">
+        <v>-0.0182</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>4856700</v>
+        <v>5682000</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.43</v>
+        <v>0.59</v>
       </c>
       <c r="H33" t="n">
-        <v>21.41</v>
+        <v>51.15</v>
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
@@ -1953,10 +1953,10 @@
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>1.691</v>
+        <v>1.077</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>1.944</v>
+        <v>1.045</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="7" t="inlineStr"/>
@@ -1969,33 +1969,40 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0472</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ECOGRP</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="E34" s="3" t="n">
-        <v>-0.1111</v>
+        <v>2.02</v>
+      </c>
+      <c r="E34" s="8" t="n">
+        <v>-0.0049</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>4840700</v>
+        <v>5371800</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.41</v>
+      </c>
+      <c r="H34" t="n">
+        <v>33.2</v>
       </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J34" s="2" t="n"/>
-      <c r="K34" s="2" t="n"/>
+      <c r="J34" s="2" t="n">
+        <v>2.148</v>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v>2.234</v>
+      </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="7" t="inlineStr"/>
     </row>
@@ -2007,39 +2014,39 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="E35" s="3" t="n">
-        <v>-0.0325</v>
+        <v>0.435</v>
+      </c>
+      <c r="E35" s="10" t="n">
+        <v>0.0357</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>4716400</v>
+        <v>5359700</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="H35" t="n">
-        <v>38.78</v>
-      </c>
-      <c r="I35" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.65</v>
+      </c>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>1.235</v>
+        <v>0.425</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>1.323</v>
+        <v>0.416</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="7" t="inlineStr"/>
@@ -2052,39 +2059,39 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="E36" s="3" t="n">
-        <v>-0.0299</v>
+        <v>0.98</v>
+      </c>
+      <c r="E36" s="10" t="n">
+        <v>0.0208</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>4676100</v>
+        <v>5348300</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.98</v>
+        <v>0.93</v>
       </c>
       <c r="H36" t="n">
-        <v>34.42</v>
-      </c>
-      <c r="I36" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.93000000000001</v>
+      </c>
+      <c r="I36" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>1.723</v>
+        <v>0.926</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>1.767</v>
+        <v>0.877</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="7" t="inlineStr"/>
@@ -2097,39 +2104,39 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>0.405</v>
-      </c>
-      <c r="E37" s="10" t="n">
-        <v>0</v>
+        <v>1.19</v>
+      </c>
+      <c r="E37" s="8" t="n">
+        <v>-0.0325</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>4597200</v>
+        <v>5221300</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.37</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H37" t="n">
-        <v>55.08</v>
-      </c>
-      <c r="I37" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>38.78</v>
+      </c>
+      <c r="I37" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.391</v>
+        <v>1.235</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0.378</v>
+        <v>1.323</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="7" t="inlineStr"/>
@@ -2142,39 +2149,39 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="E38" s="9" t="n">
-        <v>0.0218</v>
+        <v>0.54</v>
+      </c>
+      <c r="E38" s="8" t="n">
+        <v>-0.027</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>4421600</v>
+        <v>5209000</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>1.24</v>
+        <v>0.25</v>
       </c>
       <c r="H38" t="n">
-        <v>60.87</v>
-      </c>
-      <c r="I38" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.4</v>
+      </c>
+      <c r="I38" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>2.226</v>
+        <v>0.572</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>2.167</v>
+        <v>0.541</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="7" t="inlineStr"/>
@@ -2187,40 +2194,33 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>6203</t>
+          <t>0472</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>KHEESAN</t>
+          <t>ECOGRP</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>0.105</v>
-      </c>
-      <c r="E39" s="9" t="n">
-        <v>0.1053</v>
+        <v>0.12</v>
+      </c>
+      <c r="E39" s="8" t="n">
+        <v>-0.1111</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>4392300</v>
+        <v>5102500</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="H39" t="n">
-        <v>61.33</v>
-      </c>
-      <c r="I39" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="n">
-        <v>0.091</v>
-      </c>
-      <c r="K39" s="2" t="n">
-        <v>0.095</v>
-      </c>
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="n"/>
+      <c r="K39" s="2" t="n"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="7" t="inlineStr"/>
     </row>
@@ -2232,39 +2232,39 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>6203</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>KHEESAN</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>9.869999999999999</v>
-      </c>
-      <c r="E40" s="3" t="n">
-        <v>-0.012</v>
+        <v>0.1</v>
+      </c>
+      <c r="E40" s="10" t="n">
+        <v>0.0526</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>4384300</v>
+        <v>4951800</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.33</v>
+        <v>2.89</v>
       </c>
       <c r="H40" t="n">
-        <v>40.09</v>
-      </c>
-      <c r="I40" s="8" t="inlineStr">
+        <v>58.17</v>
+      </c>
+      <c r="I40" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>9.997999999999999</v>
+        <v>0.09</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>10.147</v>
+        <v>0.095</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="7" t="inlineStr"/>
@@ -2277,39 +2277,39 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v>-0.007900000000000001</v>
+        <v>3.9</v>
+      </c>
+      <c r="E41" s="10" t="n">
+        <v>0.0484</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>4383000</v>
+        <v>4928500</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.71</v>
+        <v>0.52</v>
       </c>
       <c r="H41" t="n">
-        <v>59.95</v>
-      </c>
-      <c r="I41" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>60.08</v>
+      </c>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>1.196</v>
+        <v>3.658</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>1.187</v>
+        <v>3.009</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="7" t="inlineStr"/>
@@ -2322,39 +2322,39 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="E42" s="10" t="n">
-        <v>0</v>
+        <v>9.869999999999999</v>
+      </c>
+      <c r="E42" s="8" t="n">
+        <v>-0.012</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>4365300</v>
+        <v>4900900</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.59</v>
+        <v>0.37</v>
       </c>
       <c r="H42" t="n">
-        <v>55.92</v>
-      </c>
-      <c r="I42" s="8" t="inlineStr">
+        <v>40.09</v>
+      </c>
+      <c r="I42" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.371</v>
+        <v>9.997999999999999</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0.369</v>
+        <v>10.147</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="7" t="inlineStr"/>
@@ -2378,14 +2378,14 @@
       <c r="D43" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="E43" s="10" t="n">
+      <c r="E43" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>4361300</v>
+        <v>4861300</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>17.57</v>
+        <v>19.59</v>
       </c>
       <c r="H43" t="n">
         <v>39.48</v>
@@ -2412,39 +2412,39 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>0.525</v>
+        <v>1.27</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>-0.0187</v>
+        <v>0</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>4203500</v>
+        <v>4813700</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>1.7</v>
+        <v>0.78</v>
       </c>
       <c r="H44" t="n">
-        <v>36.53</v>
-      </c>
-      <c r="I44" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.53</v>
+      </c>
+      <c r="I44" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.544</v>
+        <v>1.197</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0.572</v>
+        <v>1.188</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="7" t="inlineStr"/>
@@ -2457,28 +2457,28 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E45" s="3" t="n">
-        <v>-0.0148</v>
+        <v>1.62</v>
+      </c>
+      <c r="E45" s="8" t="n">
+        <v>-0.0299</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>4108700</v>
+        <v>4764500</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.32</v>
+        <v>1</v>
       </c>
       <c r="H45" t="n">
-        <v>31.84</v>
+        <v>34.42</v>
       </c>
       <c r="I45" s="6" t="inlineStr">
         <is>
@@ -2486,10 +2486,10 @@
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>2.146</v>
+        <v>1.723</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>2.233</v>
+        <v>1.767</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="7" t="inlineStr"/>
@@ -2502,39 +2502,39 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>3.87</v>
-      </c>
-      <c r="E46" s="9" t="n">
-        <v>0.0403</v>
+        <v>2.34</v>
+      </c>
+      <c r="E46" s="10" t="n">
+        <v>0.0218</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>4039400</v>
+        <v>4755800</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.43</v>
+        <v>1.34</v>
       </c>
       <c r="H46" t="n">
-        <v>59.43</v>
-      </c>
-      <c r="I46" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.87</v>
+      </c>
+      <c r="I46" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>3.655</v>
+        <v>2.226</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>3.009</v>
+        <v>2.167</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="7" t="inlineStr"/>
@@ -2547,39 +2547,39 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>0280</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>MBN</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>0.45</v>
+        <v>0.16</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>-0.011</v>
+        <v>0</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>3936900</v>
+        <v>4710200</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.16</v>
+        <v>1.95</v>
       </c>
       <c r="H47" t="n">
-        <v>27.11</v>
-      </c>
-      <c r="I47" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.48</v>
+      </c>
+      <c r="I47" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.507</v>
+        <v>0.155</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0.677</v>
+        <v>0.154</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="7" t="inlineStr"/>
@@ -2592,39 +2592,39 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="E48" s="9" t="n">
-        <v>0.0152</v>
+        <v>0.375</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>3810700</v>
+        <v>4587200</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.3</v>
+        <v>0.62</v>
       </c>
       <c r="H48" t="n">
-        <v>43.18</v>
-      </c>
-      <c r="I48" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.92</v>
+      </c>
+      <c r="I48" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>2.76</v>
+        <v>0.371</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>2.738</v>
+        <v>0.369</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="7" t="inlineStr"/>
@@ -2646,19 +2646,19 @@
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>0.415</v>
-      </c>
-      <c r="E49" s="3" t="n">
-        <v>-0.0235</v>
+        <v>0.41</v>
+      </c>
+      <c r="E49" s="8" t="n">
+        <v>-0.0353</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>3797000</v>
+        <v>4521800</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.49</v>
+        <v>0.58</v>
       </c>
       <c r="H49" t="n">
-        <v>23.04</v>
+        <v>22.61</v>
       </c>
       <c r="I49" s="6" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.527</v>
+        <v>0.526</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0.614</v>
@@ -2691,19 +2691,19 @@
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="E50" s="3" t="n">
-        <v>-0.0294</v>
+        <v>0.335</v>
+      </c>
+      <c r="E50" s="8" t="n">
+        <v>-0.0147</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>3751700</v>
+        <v>4456700</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.4</v>
+        <v>0.47</v>
       </c>
       <c r="H50" t="n">
-        <v>45.62</v>
+        <v>47.31</v>
       </c>
       <c r="I50" s="6" t="inlineStr">
         <is>
@@ -2711,10 +2711,10 @@
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.345</v>
+        <v>0.346</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0.333</v>
+        <v>0.334</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="7" t="inlineStr"/>
@@ -2727,28 +2727,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>7.16</v>
-      </c>
-      <c r="E51" s="3" t="n">
-        <v>-0.005600000000000001</v>
+        <v>0.555</v>
+      </c>
+      <c r="E51" s="8" t="n">
+        <v>-0.0672</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>3681300</v>
+        <v>4433800</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.23</v>
+        <v>0.49</v>
       </c>
       <c r="H51" t="n">
-        <v>33.16</v>
+        <v>34.6</v>
       </c>
       <c r="I51" s="6" t="inlineStr">
         <is>
@@ -2756,10 +2756,10 @@
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>7.505</v>
+        <v>0.646</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>7.684</v>
+        <v>0.619</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="7" t="inlineStr"/>
@@ -2772,39 +2772,39 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="E52" s="3" t="n">
-        <v>-0.0833</v>
+        <v>2.66</v>
+      </c>
+      <c r="E52" s="10" t="n">
+        <v>0.0114</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>3635100</v>
+        <v>4339900</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.92</v>
+        <v>0.34</v>
       </c>
       <c r="H52" t="n">
-        <v>64.73</v>
-      </c>
-      <c r="I52" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.31</v>
+      </c>
+      <c r="I52" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.84</v>
+        <v>2.759</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0.572</v>
+        <v>2.738</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="7" t="inlineStr"/>
@@ -2817,39 +2817,39 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="E53" s="3" t="n">
-        <v>-0.006</v>
+        <v>0.525</v>
+      </c>
+      <c r="E53" s="8" t="n">
+        <v>-0.0187</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>3591700</v>
+        <v>4228800</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.53</v>
+        <v>1.71</v>
       </c>
       <c r="H53" t="n">
-        <v>52.91</v>
-      </c>
-      <c r="I53" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.53</v>
+      </c>
+      <c r="I53" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>1.628</v>
+        <v>0.544</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>1.695</v>
+        <v>0.572</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="7" t="inlineStr"/>
@@ -2862,28 +2862,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>0.835</v>
-      </c>
-      <c r="E54" s="3" t="n">
-        <v>-0.0457</v>
+        <v>5.21</v>
+      </c>
+      <c r="E54" s="10" t="n">
+        <v>0.0117</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>3586100</v>
+        <v>4170000</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>1.17</v>
+        <v>0.3</v>
       </c>
       <c r="H54" t="n">
-        <v>28.22</v>
+        <v>38.17</v>
       </c>
       <c r="I54" s="6" t="inlineStr">
         <is>
@@ -2891,10 +2891,10 @@
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.897</v>
+        <v>5.504</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0.953</v>
+        <v>5.45</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="7" t="inlineStr"/>
@@ -2907,28 +2907,28 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="E55" s="10" t="n">
-        <v>0</v>
+        <v>7.15</v>
+      </c>
+      <c r="E55" s="8" t="n">
+        <v>-0.0069</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>3466200</v>
+        <v>4120800</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.48</v>
+        <v>0.25</v>
       </c>
       <c r="H55" t="n">
-        <v>52.34</v>
+        <v>32.9</v>
       </c>
       <c r="I55" s="6" t="inlineStr">
         <is>
@@ -2936,10 +2936,10 @@
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>1.17</v>
+        <v>7.505</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>1.136</v>
+        <v>7.684</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="7" t="inlineStr"/>
@@ -2952,39 +2952,39 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="E56" s="3" t="n">
-        <v>-0.0286</v>
+        <v>1.66</v>
+      </c>
+      <c r="E56" s="8" t="n">
+        <v>-0.006</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>3339300</v>
+        <v>4012200</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.28</v>
+        <v>0.59</v>
       </c>
       <c r="H56" t="n">
-        <v>50.37</v>
-      </c>
-      <c r="I56" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.91</v>
+      </c>
+      <c r="I56" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.519</v>
+        <v>1.628</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0.461</v>
+        <v>1.695</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="7" t="inlineStr"/>
@@ -2997,28 +2997,28 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>0175</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>HHRG</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="E57" s="3" t="n">
-        <v>-0.0323</v>
+        <v>0.12</v>
+      </c>
+      <c r="E57" s="8" t="n">
+        <v>-0.04</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>3336600</v>
+        <v>3984900</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.45</v>
+        <v>0.17</v>
       </c>
       <c r="H57" t="n">
-        <v>27.78</v>
+        <v>34.67</v>
       </c>
       <c r="I57" s="6" t="inlineStr">
         <is>
@@ -3026,10 +3026,10 @@
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.497</v>
+        <v>0.143</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0.556</v>
+        <v>0.148</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="7" t="inlineStr"/>
@@ -3042,28 +3042,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>5.18</v>
-      </c>
-      <c r="E58" s="9" t="n">
-        <v>0.0058</v>
+        <v>0.455</v>
+      </c>
+      <c r="E58" s="8" t="n">
+        <v>-0.0215</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>3320100</v>
+        <v>3964500</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.24</v>
+        <v>0.53</v>
       </c>
       <c r="H58" t="n">
-        <v>36.72</v>
+        <v>28.78</v>
       </c>
       <c r="I58" s="6" t="inlineStr">
         <is>
@@ -3071,10 +3071,10 @@
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>5.501</v>
+        <v>0.498</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>5.449</v>
+        <v>0.556</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="7" t="inlineStr"/>
@@ -3087,28 +3087,28 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="E59" s="10" t="n">
-        <v>0</v>
+        <v>0.45</v>
+      </c>
+      <c r="E59" s="8" t="n">
+        <v>-0.011</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>3269500</v>
+        <v>3945300</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
       <c r="H59" t="n">
-        <v>42.99</v>
+        <v>27.11</v>
       </c>
       <c r="I59" s="6" t="inlineStr">
         <is>
@@ -3116,10 +3116,10 @@
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.19</v>
+        <v>0.507</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0.186</v>
+        <v>0.677</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="7" t="inlineStr"/>
@@ -3132,28 +3132,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="E60" s="3" t="n">
-        <v>-0.042</v>
+        <v>0.83</v>
+      </c>
+      <c r="E60" s="8" t="n">
+        <v>-0.05139999999999999</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>3115900</v>
+        <v>3769700</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.35</v>
+        <v>1.23</v>
       </c>
       <c r="H60" t="n">
-        <v>36.38</v>
+        <v>27.43</v>
       </c>
       <c r="I60" s="6" t="inlineStr">
         <is>
@@ -3161,10 +3161,10 @@
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.647</v>
+        <v>0.896</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>0.62</v>
+        <v>0.953</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="7" t="inlineStr"/>
@@ -3177,39 +3177,39 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="E61" s="3" t="n">
-        <v>-0.0095</v>
+        <v>0.985</v>
+      </c>
+      <c r="E61" s="8" t="n">
+        <v>-0.08800000000000001</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>2984500</v>
+        <v>3680600</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.18</v>
+        <v>0.93</v>
       </c>
       <c r="H61" t="n">
-        <v>45.7</v>
-      </c>
-      <c r="I61" s="8" t="inlineStr">
+        <v>64.31999999999999</v>
+      </c>
+      <c r="I61" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>2.107</v>
+        <v>0.84</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>2.101</v>
+        <v>0.572</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="7" t="inlineStr"/>
@@ -3222,39 +3222,39 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="E62" s="9" t="n">
-        <v>0.0123</v>
+        <v>0.51</v>
+      </c>
+      <c r="E62" s="8" t="n">
+        <v>-0.0286</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>2792500</v>
+        <v>3617000</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>1.44</v>
+        <v>0.3</v>
       </c>
       <c r="H62" t="n">
-        <v>41.24</v>
-      </c>
-      <c r="I62" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.37</v>
+      </c>
+      <c r="I62" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.416</v>
+        <v>0.519</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>0.434</v>
+        <v>0.461</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="7" t="inlineStr"/>
@@ -3267,28 +3267,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E63" s="3" t="n">
-        <v>-0.0189</v>
+        <v>0.255</v>
+      </c>
+      <c r="E63" s="8" t="n">
+        <v>-0.0192</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>2774200</v>
+        <v>3550500</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.38</v>
+        <v>0.42</v>
       </c>
       <c r="H63" t="n">
-        <v>42.45</v>
+        <v>27.74</v>
       </c>
       <c r="I63" s="6" t="inlineStr">
         <is>
@@ -3296,10 +3296,10 @@
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.273</v>
+        <v>0.276</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0.294</v>
+        <v>0.301</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="7" t="inlineStr"/>
@@ -3312,28 +3312,28 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>0.54</v>
+        <v>1.18</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>-0.0526</v>
+        <v>0</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>2760400</v>
+        <v>3528000</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.53</v>
+        <v>0.49</v>
       </c>
       <c r="H64" t="n">
-        <v>47.73</v>
+        <v>52.34</v>
       </c>
       <c r="I64" s="6" t="inlineStr">
         <is>
@@ -3341,10 +3341,10 @@
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.5590000000000001</v>
+        <v>1.17</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>0.516</v>
+        <v>1.136</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="7" t="inlineStr"/>
@@ -3357,28 +3357,28 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>0.89</v>
+        <v>0.18</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>-0.0326</v>
+        <v>0</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>2742000</v>
+        <v>3269500</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>1.65</v>
+        <v>0.14</v>
       </c>
       <c r="H65" t="n">
-        <v>47.65</v>
+        <v>42.99</v>
       </c>
       <c r="I65" s="6" t="inlineStr">
         <is>
@@ -3386,10 +3386,10 @@
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.913</v>
+        <v>0.19</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>0.874</v>
+        <v>0.186</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="7" t="inlineStr"/>
@@ -3402,28 +3402,28 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>5041</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>PBA</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E66" s="3" t="n">
-        <v>-0.0196</v>
+        <v>0.26</v>
+      </c>
+      <c r="E66" s="8" t="n">
+        <v>-0.0189</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>2637000</v>
+        <v>3206600</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>8.08</v>
+        <v>0.44</v>
       </c>
       <c r="H66" t="n">
-        <v>32</v>
+        <v>42.45</v>
       </c>
       <c r="I66" s="6" t="inlineStr">
         <is>
@@ -3431,10 +3431,10 @@
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>2.091</v>
+        <v>0.273</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>2.156</v>
+        <v>0.294</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="7" t="inlineStr"/>
@@ -3447,39 +3447,39 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0388</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>SEMICO</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E67" s="10" t="n">
-        <v>0</v>
+        <v>2.08</v>
+      </c>
+      <c r="E67" s="8" t="n">
+        <v>-0.0095</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>2632800</v>
+        <v>3077400</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>0.78</v>
+        <v>0.18</v>
       </c>
       <c r="H67" t="n">
-        <v>70.16</v>
-      </c>
-      <c r="I67" s="8" t="inlineStr">
+        <v>45.7</v>
+      </c>
+      <c r="I67" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.617</v>
+        <v>2.107</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>0.605</v>
+        <v>2.101</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="7" t="inlineStr"/>
@@ -3503,14 +3503,14 @@
       <c r="D68" s="2" t="n">
         <v>0.75</v>
       </c>
-      <c r="E68" s="9" t="n">
+      <c r="E68" s="10" t="n">
         <v>0.0204</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>2556900</v>
+        <v>2969400</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="H68" t="n">
         <v>43.98</v>
@@ -3537,39 +3537,39 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="E69" s="10" t="n">
-        <v>0</v>
+        <v>0.405</v>
+      </c>
+      <c r="E69" s="8" t="n">
+        <v>-0.0357</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>2495000</v>
+        <v>2900800</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="H69" t="n">
-        <v>82.09</v>
-      </c>
-      <c r="I69" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.34</v>
+      </c>
+      <c r="I69" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>2.827</v>
+        <v>0.437</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>2.43</v>
+        <v>0.434</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="7" t="inlineStr"/>
@@ -3582,28 +3582,28 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0469</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>GTA</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="E70" s="3" t="n">
-        <v>-0.04</v>
+        <v>0.545</v>
+      </c>
+      <c r="E70" s="8" t="n">
+        <v>-0.04389999999999999</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>2480400</v>
+        <v>2819700</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>0.7</v>
+        <v>0.54</v>
       </c>
       <c r="H70" t="n">
-        <v>16.11</v>
+        <v>48.83</v>
       </c>
       <c r="I70" s="6" t="inlineStr">
         <is>
@@ -3611,9 +3611,11 @@
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.272</v>
-      </c>
-      <c r="K70" s="2" t="n"/>
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="K70" s="2" t="n">
+        <v>0.516</v>
+      </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="7" t="inlineStr"/>
     </row>
@@ -3625,28 +3627,28 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="E71" s="3" t="n">
-        <v>-0.0394</v>
+        <v>0.885</v>
+      </c>
+      <c r="E71" s="8" t="n">
+        <v>-0.038</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>2403700</v>
+        <v>2814700</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>0.57</v>
+        <v>1.69</v>
       </c>
       <c r="H71" t="n">
-        <v>23.54</v>
+        <v>46.99</v>
       </c>
       <c r="I71" s="6" t="inlineStr">
         <is>
@@ -3654,10 +3656,10 @@
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>1.393</v>
+        <v>0.913</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>1.561</v>
+        <v>0.874</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="7" t="inlineStr"/>
@@ -3670,39 +3672,39 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>VELESTO</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>0.205</v>
-      </c>
-      <c r="E72" s="9" t="n">
-        <v>0.009899999999999999</v>
+        <v>0.405</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>2386700</v>
+        <v>2797300</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>0.11</v>
+        <v>1.44</v>
       </c>
       <c r="H72" t="n">
-        <v>39.23</v>
-      </c>
-      <c r="I72" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>35.96</v>
+      </c>
+      <c r="I72" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.218</v>
+        <v>0.416</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0.235</v>
+        <v>0.433</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="7" t="inlineStr"/>
@@ -3715,39 +3717,39 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>0.405</v>
-      </c>
-      <c r="E73" s="3" t="n">
-        <v>-0.0357</v>
+        <v>3.12</v>
+      </c>
+      <c r="E73" s="10" t="n">
+        <v>0.0097</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>2317200</v>
+        <v>2708900</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>0.24</v>
+        <v>0.88</v>
       </c>
       <c r="H73" t="n">
-        <v>41.34</v>
-      </c>
-      <c r="I73" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>82.95999999999999</v>
+      </c>
+      <c r="I73" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.437</v>
+        <v>2.83</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>0.434</v>
+        <v>2.43</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="7" t="inlineStr"/>
@@ -3760,39 +3762,39 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>0395</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>OGX</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="E74" s="9" t="n">
-        <v>0.016</v>
+        <v>0.465</v>
+      </c>
+      <c r="E74" s="10" t="n">
+        <v>0.022</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>2304200</v>
+        <v>2642900</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>0.4</v>
+        <v>1.01</v>
       </c>
       <c r="H74" t="n">
-        <v>45.71</v>
-      </c>
-      <c r="I74" s="8" t="inlineStr">
+        <v>56.6</v>
+      </c>
+      <c r="I74" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>1.92</v>
+        <v>0.447</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>1.95</v>
+        <v>0.449</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="7" t="inlineStr"/>
@@ -3805,39 +3807,39 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0395</t>
+          <t>5041</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>OGX</t>
+          <t>PBA</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>0.465</v>
-      </c>
-      <c r="E75" s="9" t="n">
-        <v>0.022</v>
+        <v>2</v>
+      </c>
+      <c r="E75" s="8" t="n">
+        <v>-0.0196</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>2267600</v>
+        <v>2639000</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>0.87</v>
+        <v>8.08</v>
       </c>
       <c r="H75" t="n">
-        <v>56.6</v>
-      </c>
-      <c r="I75" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>32</v>
+      </c>
+      <c r="I75" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.447</v>
+        <v>2.091</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>0.449</v>
+        <v>2.156</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="7" t="inlineStr"/>
@@ -3850,39 +3852,39 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>IOIPG</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="E76" s="9" t="n">
-        <v>0.0285</v>
+        <v>0.625</v>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>2085600</v>
+        <v>2632800</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>0.35</v>
+        <v>0.78</v>
       </c>
       <c r="H76" t="n">
-        <v>36.23</v>
-      </c>
-      <c r="I76" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>70.16</v>
+      </c>
+      <c r="I76" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>3.37</v>
+        <v>0.617</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>3.604</v>
+        <v>0.605</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="7" t="inlineStr"/>
@@ -3895,38 +3897,40 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>0.355</v>
-      </c>
-      <c r="E77" s="3" t="n">
-        <v>-0.0274</v>
+        <v>1.22</v>
+      </c>
+      <c r="E77" s="8" t="n">
+        <v>-0.0394</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>2007000</v>
+        <v>2612200</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>0.35</v>
+        <v>0.62</v>
       </c>
       <c r="H77" t="n">
-        <v>60.83</v>
-      </c>
-      <c r="I77" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>23.54</v>
+      </c>
+      <c r="I77" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.318</v>
-      </c>
-      <c r="K77" s="2" t="n"/>
+        <v>1.393</v>
+      </c>
+      <c r="K77" s="2" t="n">
+        <v>1.561</v>
+      </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="7" t="inlineStr"/>
     </row>
@@ -3938,39 +3942,39 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="E78" s="3" t="n">
-        <v>-0.0391</v>
+        <v>1.91</v>
+      </c>
+      <c r="E78" s="10" t="n">
+        <v>0.0214</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>1993400</v>
+        <v>2607500</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>0.26</v>
+        <v>0.46</v>
       </c>
       <c r="H78" t="n">
-        <v>42.22</v>
-      </c>
-      <c r="I78" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.22</v>
+      </c>
+      <c r="I78" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.927</v>
+        <v>1.921</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>0.847</v>
+        <v>1.95</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="7" t="inlineStr"/>
@@ -3983,40 +3987,38 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>0469</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>GTA</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>0.965</v>
-      </c>
-      <c r="E79" s="9" t="n">
-        <v>0.0052</v>
+        <v>0.24</v>
+      </c>
+      <c r="E79" s="8" t="n">
+        <v>-0.04</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>1971800</v>
+        <v>2593100</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>0.34</v>
+        <v>0.73</v>
       </c>
       <c r="H79" t="n">
-        <v>66.12</v>
-      </c>
-      <c r="I79" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>16.11</v>
+      </c>
+      <c r="I79" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.925</v>
-      </c>
-      <c r="K79" s="2" t="n">
-        <v>0.877</v>
-      </c>
+        <v>0.272</v>
+      </c>
+      <c r="K79" s="2" t="n"/>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="7" t="inlineStr"/>
     </row>
@@ -4028,39 +4030,39 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>4.43</v>
-      </c>
-      <c r="E80" s="9" t="n">
-        <v>0.0255</v>
+        <v>0.205</v>
+      </c>
+      <c r="E80" s="10" t="n">
+        <v>0.009899999999999999</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>1927000</v>
+        <v>2521000</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>0.36</v>
+        <v>0.11</v>
       </c>
       <c r="H80" t="n">
-        <v>51.94</v>
-      </c>
-      <c r="I80" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.23</v>
+      </c>
+      <c r="I80" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>4.359</v>
+        <v>0.218</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>4.431</v>
+        <v>0.235</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="7" t="inlineStr"/>
@@ -4082,21 +4084,21 @@
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>0.415</v>
-      </c>
-      <c r="E81" s="9" t="n">
-        <v>0.0375</v>
+        <v>0.42</v>
+      </c>
+      <c r="E81" s="10" t="n">
+        <v>0.05</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>1923300</v>
+        <v>2300300</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>5.77</v>
+        <v>6.9</v>
       </c>
       <c r="H81" t="n">
-        <v>68.86</v>
-      </c>
-      <c r="I81" s="8" t="inlineStr">
+        <v>70.20999999999999</v>
+      </c>
+      <c r="I81" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -4118,28 +4120,28 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>IOIPG</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>5.74</v>
-      </c>
-      <c r="E82" s="9" t="n">
-        <v>0.008800000000000001</v>
+        <v>3.25</v>
+      </c>
+      <c r="E82" s="10" t="n">
+        <v>0.0285</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>1907000</v>
+        <v>2255800</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>0.25</v>
+        <v>0.38</v>
       </c>
       <c r="H82" t="n">
-        <v>30.7</v>
+        <v>36.23</v>
       </c>
       <c r="I82" s="6" t="inlineStr">
         <is>
@@ -4147,10 +4149,10 @@
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>6.023</v>
+        <v>3.37</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>6.309</v>
+        <v>3.604</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="7" t="inlineStr"/>
@@ -4163,39 +4165,39 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>DATASONIC</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="E83" s="3" t="n">
-        <v>-0.0175</v>
+        <v>4.47</v>
+      </c>
+      <c r="E83" s="10" t="n">
+        <v>0.0347</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>1871700</v>
+        <v>2229300</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>0.16</v>
+        <v>0.42</v>
       </c>
       <c r="H83" t="n">
-        <v>46.28</v>
-      </c>
-      <c r="I83" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.31</v>
+      </c>
+      <c r="I83" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.291</v>
+        <v>4.363</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>0.283</v>
+        <v>4.432</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="7" t="inlineStr"/>
@@ -4208,28 +4210,28 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="E84" s="3" t="n">
-        <v>-0.0226</v>
+        <v>5.74</v>
+      </c>
+      <c r="E84" s="10" t="n">
+        <v>0.008800000000000001</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>1864000</v>
+        <v>2227800</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>0.78</v>
+        <v>0.3</v>
       </c>
       <c r="H84" t="n">
-        <v>56.17</v>
+        <v>30.7</v>
       </c>
       <c r="I84" s="6" t="inlineStr">
         <is>
@@ -4237,10 +4239,10 @@
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>1.26</v>
+        <v>6.023</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>1.173</v>
+        <v>6.309</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="7" t="inlineStr"/>
@@ -4253,39 +4255,39 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="E85" s="3" t="n">
-        <v>-0.008500000000000001</v>
+        <v>0.875</v>
+      </c>
+      <c r="E85" s="8" t="n">
+        <v>-0.0223</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>1833300</v>
+        <v>2176600</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>0.44</v>
+        <v>0.28</v>
       </c>
       <c r="H85" t="n">
-        <v>67.36</v>
-      </c>
-      <c r="I85" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.95</v>
+      </c>
+      <c r="I85" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.509</v>
+        <v>0.928</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>0.468</v>
+        <v>0.847</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="7" t="inlineStr"/>
@@ -4298,28 +4300,28 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0372</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>CHEEDING</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="E86" s="3" t="n">
-        <v>-0.04849999999999999</v>
+        <v>1.31</v>
+      </c>
+      <c r="E86" s="8" t="n">
+        <v>-0.015</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>1827300</v>
+        <v>2055300</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>0.42</v>
+        <v>0.86</v>
       </c>
       <c r="H86" t="n">
-        <v>28.71</v>
+        <v>57.19</v>
       </c>
       <c r="I86" s="6" t="inlineStr">
         <is>
@@ -4327,10 +4329,10 @@
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.58</v>
+        <v>1.261</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>0.599</v>
+        <v>1.173</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="7" t="inlineStr"/>
@@ -4343,39 +4345,39 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="E87" s="9" t="n">
-        <v>0.0149</v>
+        <v>0.28</v>
+      </c>
+      <c r="E87" s="8" t="n">
+        <v>-0.0175</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>1755600</v>
+        <v>2013000</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>0.37</v>
+        <v>0.33</v>
       </c>
       <c r="H87" t="n">
-        <v>52.08</v>
-      </c>
-      <c r="I87" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>21.33</v>
+      </c>
+      <c r="I87" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.336</v>
+        <v>0.333</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>0.343</v>
+        <v>0.372</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="7" t="inlineStr"/>
@@ -4388,40 +4390,38 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>5271</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>PECCA</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="E88" s="10" t="n">
-        <v>0</v>
+        <v>0.355</v>
+      </c>
+      <c r="E88" s="8" t="n">
+        <v>-0.0274</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>1728800</v>
+        <v>2007000</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>0.89</v>
+        <v>0.35</v>
       </c>
       <c r="H88" t="n">
-        <v>43.62</v>
-      </c>
-      <c r="I88" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.83</v>
+      </c>
+      <c r="I88" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>1.367</v>
-      </c>
-      <c r="K88" s="2" t="n">
-        <v>1.343</v>
-      </c>
+        <v>0.318</v>
+      </c>
+      <c r="K88" s="2" t="n"/>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="7" t="inlineStr"/>
     </row>
@@ -4433,39 +4433,39 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E89" s="10" t="n">
-        <v>0</v>
+        <v>0.925</v>
+      </c>
+      <c r="E89" s="8" t="n">
+        <v>-0.0054</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>1715400</v>
+        <v>1996400</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>0.77</v>
+        <v>0.51</v>
       </c>
       <c r="H89" t="n">
-        <v>50.9</v>
-      </c>
-      <c r="I89" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>25.84</v>
+      </c>
+      <c r="I89" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.637</v>
+        <v>0.97</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>0.622</v>
+        <v>1.053</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="7" t="inlineStr"/>
@@ -4478,28 +4478,28 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>0372</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>MRCB</t>
+          <t>CHEEDING</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E90" s="10" t="n">
-        <v>0</v>
+        <v>0.5</v>
+      </c>
+      <c r="E90" s="8" t="n">
+        <v>-0.0291</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>1704300</v>
+        <v>1976300</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>0.2</v>
+        <v>0.45</v>
       </c>
       <c r="H90" t="n">
-        <v>30.11</v>
+        <v>29.93</v>
       </c>
       <c r="I90" s="6" t="inlineStr">
         <is>
@@ -4507,10 +4507,10 @@
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.277</v>
+        <v>0.581</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>0.301</v>
+        <v>0.599</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="7" t="inlineStr"/>
@@ -4523,39 +4523,39 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="E91" s="3" t="n">
-        <v>-0.0395</v>
+        <v>0.58</v>
+      </c>
+      <c r="E91" s="8" t="n">
+        <v>-0.008500000000000001</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>1680800</v>
+        <v>1972700</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>0.32</v>
+        <v>0.47</v>
       </c>
       <c r="H91" t="n">
-        <v>47.28</v>
-      </c>
-      <c r="I91" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>67.36</v>
+      </c>
+      <c r="I91" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.761</v>
+        <v>0.509</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.468</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="7" t="inlineStr"/>
@@ -4568,28 +4568,28 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>DATASONIC</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>0.285</v>
-      </c>
-      <c r="E92" s="10" t="n">
-        <v>0</v>
+        <v>0.28</v>
+      </c>
+      <c r="E92" s="8" t="n">
+        <v>-0.0175</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>1594500</v>
+        <v>1913700</v>
       </c>
       <c r="G92" s="5" t="n">
-        <v>0.26</v>
+        <v>0.16</v>
       </c>
       <c r="H92" t="n">
-        <v>22.28</v>
+        <v>46.28</v>
       </c>
       <c r="I92" s="6" t="inlineStr">
         <is>
@@ -4597,10 +4597,10 @@
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.333</v>
+        <v>0.291</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>0.372</v>
+        <v>0.283</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="7" t="inlineStr"/>
@@ -4613,28 +4613,28 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0192</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>INTA</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E93" s="3" t="n">
-        <v>-0.013</v>
+        <v>0.735</v>
+      </c>
+      <c r="E93" s="8" t="n">
+        <v>-0.0329</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>1588400</v>
+        <v>1860500</v>
       </c>
       <c r="G93" s="5" t="n">
-        <v>0.59</v>
+        <v>0.35</v>
       </c>
       <c r="H93" t="n">
-        <v>41.3</v>
+        <v>48.09</v>
       </c>
       <c r="I93" s="6" t="inlineStr">
         <is>
@@ -4642,10 +4642,10 @@
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.394</v>
+        <v>0.761</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>0.389</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="7" t="inlineStr"/>
@@ -4658,39 +4658,39 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>1.17</v>
+        <v>0.335</v>
       </c>
       <c r="E94" s="3" t="n">
-        <v>-0.0168</v>
+        <v>0</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>1555600</v>
+        <v>1806200</v>
       </c>
       <c r="G94" s="5" t="n">
-        <v>0.44</v>
+        <v>0.38</v>
       </c>
       <c r="H94" t="n">
-        <v>46.47</v>
-      </c>
-      <c r="I94" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.09</v>
+      </c>
+      <c r="I94" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>1.237</v>
+        <v>0.335</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>1.067</v>
+        <v>0.343</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="7" t="inlineStr"/>
@@ -4703,28 +4703,28 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>PECCA</t>
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>0.635</v>
+        <v>1.35</v>
       </c>
       <c r="E95" s="3" t="n">
-        <v>-0.0155</v>
+        <v>0</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>1511200</v>
+        <v>1795400</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>0.17</v>
+        <v>0.92</v>
       </c>
       <c r="H95" t="n">
-        <v>40.95</v>
+        <v>43.62</v>
       </c>
       <c r="I95" s="6" t="inlineStr">
         <is>
@@ -4732,10 +4732,10 @@
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.678</v>
+        <v>1.367</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>0.6889999999999999</v>
+        <v>1.343</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="7" t="inlineStr"/>
@@ -4748,28 +4748,28 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="E96" s="3" t="n">
-        <v>-0.0407</v>
+        <v>0.68</v>
+      </c>
+      <c r="E96" s="8" t="n">
+        <v>-0.0145</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>1508000</v>
+        <v>1750200</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>0.27</v>
+        <v>0.12</v>
       </c>
       <c r="H96" t="n">
-        <v>56.69</v>
+        <v>39.44</v>
       </c>
       <c r="I96" s="6" t="inlineStr">
         <is>
@@ -4777,10 +4777,10 @@
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.569</v>
+        <v>0.75</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>0.47</v>
+        <v>0.723</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="7" t="inlineStr"/>
@@ -4793,39 +4793,39 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>0.925</v>
+        <v>0.635</v>
       </c>
       <c r="E97" s="3" t="n">
-        <v>-0.0054</v>
+        <v>0</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>1497400</v>
+        <v>1715400</v>
       </c>
       <c r="G97" s="5" t="n">
-        <v>0.38</v>
+        <v>0.77</v>
       </c>
       <c r="H97" t="n">
-        <v>25.84</v>
-      </c>
-      <c r="I97" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.9</v>
+      </c>
+      <c r="I97" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.97</v>
+        <v>0.637</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>1.053</v>
+        <v>0.622</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="7" t="inlineStr"/>
@@ -4838,28 +4838,28 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>5053</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>OSK</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="E98" s="3" t="n">
-        <v>-0.0182</v>
+        <v>0.635</v>
+      </c>
+      <c r="E98" s="8" t="n">
+        <v>-0.0155</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>1470500</v>
+        <v>1685000</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>1.03</v>
+        <v>0.19</v>
       </c>
       <c r="H98" t="n">
-        <v>29.39</v>
+        <v>40.95</v>
       </c>
       <c r="I98" s="6" t="inlineStr">
         <is>
@@ -4867,10 +4867,10 @@
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>1.727</v>
+        <v>0.678</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>1.884</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="7" t="inlineStr"/>
@@ -4883,28 +4883,28 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D99" s="2" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="E99" s="3" t="n">
-        <v>-0.0273</v>
+        <v>1.18</v>
+      </c>
+      <c r="E99" s="8" t="n">
+        <v>-0.008399999999999999</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v>1448900</v>
+        <v>1685000</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>0.24</v>
+        <v>0.48</v>
       </c>
       <c r="H99" t="n">
-        <v>41.03</v>
+        <v>47.42</v>
       </c>
       <c r="I99" s="6" t="inlineStr">
         <is>
@@ -4912,10 +4912,10 @@
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>2.603</v>
+        <v>1.238</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>2.607</v>
+        <v>1.067</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="7" t="inlineStr"/>
@@ -4928,28 +4928,28 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>8524</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>TALIWRK</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D100" s="2" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="E100" s="3" t="n">
-        <v>-0.0217</v>
+        <v>0.595</v>
+      </c>
+      <c r="E100" s="8" t="n">
+        <v>-0.0325</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>1422000</v>
+        <v>1674800</v>
       </c>
       <c r="G100" s="5" t="n">
-        <v>0.71</v>
+        <v>0.29</v>
       </c>
       <c r="H100" t="n">
-        <v>34.68</v>
+        <v>57.47</v>
       </c>
       <c r="I100" s="6" t="inlineStr">
         <is>
@@ -4957,10 +4957,10 @@
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.243</v>
+        <v>0.57</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>0.256</v>
+        <v>0.47</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="7" t="inlineStr"/>
@@ -4973,39 +4973,39 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0325</t>
+          <t>0056</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>NCT</t>
         </is>
       </c>
       <c r="D101" s="2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="E101" s="10" t="n">
-        <v>0</v>
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E101" s="8" t="n">
+        <v>-0.008800000000000001</v>
       </c>
       <c r="F101" s="4" t="n">
-        <v>1400700</v>
+        <v>1673000</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>0.71</v>
+        <v>0.8</v>
       </c>
       <c r="H101" t="n">
-        <v>51.14</v>
-      </c>
-      <c r="I101" s="8" t="inlineStr">
+        <v>48.02</v>
+      </c>
+      <c r="I101" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>1.091</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>1.097</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="7" t="inlineStr"/>
@@ -5018,28 +5018,28 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D102" s="2" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="E102" s="9" t="n">
-        <v>0.009000000000000001</v>
+        <v>0.59</v>
+      </c>
+      <c r="E102" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>1385100</v>
+        <v>1616500</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>0.32</v>
+        <v>0.37</v>
       </c>
       <c r="H102" t="n">
-        <v>59.59</v>
+        <v>49.06</v>
       </c>
       <c r="I102" s="6" t="inlineStr">
         <is>
@@ -5047,10 +5047,10 @@
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>1.056</v>
+        <v>0.598</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>0.914</v>
+        <v>0.586</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="7" t="inlineStr"/>
@@ -5063,39 +5063,39 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D103" s="2" t="n">
-        <v>0.585</v>
-      </c>
-      <c r="E103" s="3" t="n">
-        <v>-0.008500000000000001</v>
+        <v>0.82</v>
+      </c>
+      <c r="E103" s="10" t="n">
+        <v>0.0314</v>
       </c>
       <c r="F103" s="4" t="n">
-        <v>1375900</v>
+        <v>1613200</v>
       </c>
       <c r="G103" s="5" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="H103" t="n">
-        <v>47.94</v>
-      </c>
-      <c r="I103" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.7</v>
+      </c>
+      <c r="I103" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.597</v>
+        <v>0.794</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>0.586</v>
+        <v>0.772</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="7" t="inlineStr"/>
@@ -5108,39 +5108,39 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>5248</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>BAUTO</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D104" s="2" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E104" s="9" t="n">
-        <v>0.0227</v>
+        <v>0.47</v>
+      </c>
+      <c r="E104" s="8" t="n">
+        <v>-0.0105</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v>1367600</v>
+        <v>1602000</v>
       </c>
       <c r="G104" s="5" t="n">
-        <v>0.84</v>
+        <v>0.19</v>
       </c>
       <c r="H104" t="n">
-        <v>51.19</v>
-      </c>
-      <c r="I104" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.57</v>
+      </c>
+      <c r="I104" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.893</v>
+        <v>0.506</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>0.908</v>
+        <v>0.524</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="7" t="inlineStr"/>
@@ -5153,28 +5153,28 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>0192</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>INTA</t>
         </is>
       </c>
       <c r="D105" s="2" t="n">
-        <v>0.785</v>
-      </c>
-      <c r="E105" s="3" t="n">
-        <v>-0.0126</v>
+        <v>0.38</v>
+      </c>
+      <c r="E105" s="8" t="n">
+        <v>-0.013</v>
       </c>
       <c r="F105" s="4" t="n">
-        <v>1364700</v>
+        <v>1594400</v>
       </c>
       <c r="G105" s="5" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="H105" t="n">
-        <v>15.53</v>
+        <v>41.3</v>
       </c>
       <c r="I105" s="6" t="inlineStr">
         <is>
@@ -5182,10 +5182,10 @@
         </is>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.394</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>1.078</v>
+        <v>0.389</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="7" t="inlineStr"/>
@@ -5198,39 +5198,39 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0056</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>NCT</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D106" s="2" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="E106" s="3" t="n">
-        <v>-0.008800000000000001</v>
+        <v>2.5</v>
+      </c>
+      <c r="E106" s="8" t="n">
+        <v>-0.0234</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v>1360000</v>
+        <v>1577200</v>
       </c>
       <c r="G106" s="5" t="n">
-        <v>0.65</v>
+        <v>0.26</v>
       </c>
       <c r="H106" t="n">
-        <v>48.02</v>
-      </c>
-      <c r="I106" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.66</v>
+      </c>
+      <c r="I106" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.5629999999999999</v>
+        <v>2.604</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>0.5620000000000001</v>
+        <v>2.607</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="7" t="inlineStr"/>
@@ -5243,28 +5243,28 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="E107" s="3" t="n">
-        <v>-0.0209</v>
+        <v>2.42</v>
+      </c>
+      <c r="E107" s="10" t="n">
+        <v>0.0168</v>
       </c>
       <c r="F107" s="4" t="n">
-        <v>1308700</v>
+        <v>1540600</v>
       </c>
       <c r="G107" s="5" t="n">
-        <v>0.45</v>
+        <v>0.13</v>
       </c>
       <c r="H107" t="n">
-        <v>47.21</v>
+        <v>47.95</v>
       </c>
       <c r="I107" s="6" t="inlineStr">
         <is>
@@ -5272,10 +5272,10 @@
         </is>
       </c>
       <c r="J107" s="2" t="n">
-        <v>3.841</v>
+        <v>2.444</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>3.68</v>
+        <v>2.385</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="7" t="inlineStr"/>
@@ -5288,28 +5288,28 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>8524</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>TALIWRK</t>
         </is>
       </c>
       <c r="D108" s="2" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="E108" s="10" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="E108" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>1308600</v>
+        <v>1540500</v>
       </c>
       <c r="G108" s="5" t="n">
-        <v>0.14</v>
+        <v>0.77</v>
       </c>
       <c r="H108" t="n">
-        <v>41.23</v>
+        <v>37.06</v>
       </c>
       <c r="I108" s="6" t="inlineStr">
         <is>
@@ -5317,10 +5317,10 @@
         </is>
       </c>
       <c r="J108" s="2" t="n">
-        <v>1.298</v>
+        <v>0.244</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>1.314</v>
+        <v>0.256</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="7" t="inlineStr"/>
@@ -5333,28 +5333,28 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>5162</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>VSTECS</t>
         </is>
       </c>
       <c r="D109" s="2" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E109" s="3" t="n">
-        <v>-0.0353</v>
+        <v>1.51</v>
+      </c>
+      <c r="E109" s="8" t="n">
+        <v>-0.0258</v>
       </c>
       <c r="F109" s="4" t="n">
-        <v>1305300</v>
+        <v>1528100</v>
       </c>
       <c r="G109" s="5" t="n">
-        <v>0.37</v>
+        <v>0.88</v>
       </c>
       <c r="H109" t="n">
-        <v>50.64</v>
+        <v>36.69</v>
       </c>
       <c r="I109" s="6" t="inlineStr">
         <is>
@@ -5362,10 +5362,10 @@
         </is>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.826</v>
+        <v>1.622</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>0.781</v>
+        <v>1.665</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="7" t="inlineStr"/>
@@ -5378,39 +5378,39 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>TENAGA</t>
         </is>
       </c>
       <c r="D110" s="2" t="n">
-        <v>0.665</v>
-      </c>
-      <c r="E110" s="3" t="n">
-        <v>-0.0292</v>
+        <v>12.94</v>
+      </c>
+      <c r="E110" s="8" t="n">
+        <v>-0.0046</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>1303300</v>
+        <v>1516100</v>
       </c>
       <c r="G110" s="5" t="n">
-        <v>0.48</v>
+        <v>0.19</v>
       </c>
       <c r="H110" t="n">
-        <v>58.27</v>
-      </c>
-      <c r="I110" s="8" t="inlineStr">
+        <v>42.45</v>
+      </c>
+      <c r="I110" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.647</v>
+        <v>13.012</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>0.5570000000000001</v>
+        <v>13.414</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="7" t="inlineStr"/>
@@ -5423,28 +5423,28 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D111" s="2" t="n">
-        <v>2.76</v>
+        <v>1.25</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>-0.0143</v>
+        <v>0</v>
       </c>
       <c r="F111" s="4" t="n">
-        <v>1299100</v>
+        <v>1510800</v>
       </c>
       <c r="G111" s="5" t="n">
-        <v>0.35</v>
+        <v>0.16</v>
       </c>
       <c r="H111" t="n">
-        <v>39.45</v>
+        <v>41.23</v>
       </c>
       <c r="I111" s="6" t="inlineStr">
         <is>
@@ -5452,10 +5452,10 @@
         </is>
       </c>
       <c r="J111" s="2" t="n">
-        <v>2.895</v>
+        <v>1.298</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>3.012</v>
+        <v>1.314</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="7" t="inlineStr"/>
@@ -5468,39 +5468,39 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>5932</t>
+          <t>5248</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>BPURI</t>
+          <t>BAUTO</t>
         </is>
       </c>
       <c r="D112" s="2" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="E112" s="3" t="n">
-        <v>-0.0233</v>
+        <v>0.9</v>
+      </c>
+      <c r="E112" s="10" t="n">
+        <v>0.0227</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>1297400</v>
+        <v>1504300</v>
       </c>
       <c r="G112" s="5" t="n">
-        <v>1.89</v>
+        <v>0.92</v>
       </c>
       <c r="H112" t="n">
-        <v>38.22</v>
-      </c>
-      <c r="I112" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.19</v>
+      </c>
+      <c r="I112" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.223</v>
+        <v>0.893</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>0.232</v>
+        <v>0.908</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="7" t="inlineStr"/>
@@ -5513,28 +5513,28 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>0298</t>
+          <t>5053</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>WENTEL</t>
+          <t>OSK</t>
         </is>
       </c>
       <c r="D113" s="2" t="n">
-        <v>0.235</v>
-      </c>
-      <c r="E113" s="3" t="n">
-        <v>-0.0408</v>
+        <v>1.63</v>
+      </c>
+      <c r="E113" s="8" t="n">
+        <v>-0.0121</v>
       </c>
       <c r="F113" s="4" t="n">
-        <v>1295300</v>
+        <v>1501400</v>
       </c>
       <c r="G113" s="5" t="n">
-        <v>0.76</v>
+        <v>1.05</v>
       </c>
       <c r="H113" t="n">
-        <v>36.24</v>
+        <v>30.22</v>
       </c>
       <c r="I113" s="6" t="inlineStr">
         <is>
@@ -5542,10 +5542,10 @@
         </is>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.254</v>
+        <v>1.728</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>0.274</v>
+        <v>1.884</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="7" t="inlineStr"/>
@@ -5558,28 +5558,28 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>5162</t>
+          <t>5329</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>VSTECS</t>
+          <t>AZAMJAYA</t>
         </is>
       </c>
       <c r="D114" s="2" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="E114" s="3" t="n">
-        <v>-0.0258</v>
+        <v>0.95</v>
+      </c>
+      <c r="E114" s="8" t="n">
+        <v>-0.0452</v>
       </c>
       <c r="F114" s="4" t="n">
-        <v>1266100</v>
+        <v>1492600</v>
       </c>
       <c r="G114" s="5" t="n">
-        <v>0.73</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="H114" t="n">
-        <v>36.69</v>
+        <v>45.49</v>
       </c>
       <c r="I114" s="6" t="inlineStr">
         <is>
@@ -5587,10 +5587,10 @@
         </is>
       </c>
       <c r="J114" s="2" t="n">
-        <v>1.622</v>
+        <v>0.969</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>1.665</v>
+        <v>0.976</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="7" t="inlineStr"/>
@@ -5603,28 +5603,28 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>0245</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>UWC</t>
+          <t>MNHLDG</t>
         </is>
       </c>
       <c r="D115" s="2" t="n">
-        <v>7.22</v>
-      </c>
-      <c r="E115" s="3" t="n">
-        <v>-0.011</v>
+        <v>3.81</v>
+      </c>
+      <c r="E115" s="8" t="n">
+        <v>-0.0052</v>
       </c>
       <c r="F115" s="4" t="n">
-        <v>1261100</v>
+        <v>1487200</v>
       </c>
       <c r="G115" s="5" t="n">
-        <v>0.29</v>
+        <v>0.51</v>
       </c>
       <c r="H115" t="n">
-        <v>49.64</v>
+        <v>49.9</v>
       </c>
       <c r="I115" s="6" t="inlineStr">
         <is>
@@ -5632,10 +5632,10 @@
         </is>
       </c>
       <c r="J115" s="2" t="n">
-        <v>7.344</v>
+        <v>3.846</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>6.896</v>
+        <v>3.681</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="7" t="inlineStr"/>
@@ -5648,28 +5648,28 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D116" s="2" t="n">
-        <v>0.465</v>
-      </c>
-      <c r="E116" s="3" t="n">
-        <v>-0.0211</v>
+        <v>0.78</v>
+      </c>
+      <c r="E116" s="8" t="n">
+        <v>-0.0189</v>
       </c>
       <c r="F116" s="4" t="n">
-        <v>1228200</v>
+        <v>1468200</v>
       </c>
       <c r="G116" s="5" t="n">
-        <v>0.14</v>
+        <v>0.67</v>
       </c>
       <c r="H116" t="n">
-        <v>34.4</v>
+        <v>15.27</v>
       </c>
       <c r="I116" s="6" t="inlineStr">
         <is>
@@ -5677,10 +5677,10 @@
         </is>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.505</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="K116" s="2" t="n">
-        <v>0.524</v>
+        <v>1.078</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="7" t="inlineStr"/>
@@ -5693,39 +5693,39 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>0278</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>EDELTEQ</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D117" s="2" t="n">
-        <v>0.415</v>
+        <v>1.11</v>
       </c>
       <c r="E117" s="3" t="n">
-        <v>-0.0349</v>
+        <v>0</v>
       </c>
       <c r="F117" s="4" t="n">
-        <v>1215900</v>
+        <v>1464100</v>
       </c>
       <c r="G117" s="5" t="n">
-        <v>0.22</v>
+        <v>0.33</v>
       </c>
       <c r="H117" t="n">
-        <v>57.05</v>
-      </c>
-      <c r="I117" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>58.81</v>
+      </c>
+      <c r="I117" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.39</v>
+        <v>1.055</v>
       </c>
       <c r="K117" s="2" t="n">
-        <v>0.36</v>
+        <v>0.914</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="7" t="inlineStr"/>
@@ -5738,28 +5738,28 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>5329</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>AZAMJAYA</t>
+          <t>UWC</t>
         </is>
       </c>
       <c r="D118" s="2" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="E118" s="3" t="n">
-        <v>-0.0352</v>
+        <v>7.23</v>
+      </c>
+      <c r="E118" s="8" t="n">
+        <v>-0.009599999999999999</v>
       </c>
       <c r="F118" s="4" t="n">
-        <v>1202200</v>
+        <v>1451400</v>
       </c>
       <c r="G118" s="5" t="n">
-        <v>7.36</v>
+        <v>0.34</v>
       </c>
       <c r="H118" t="n">
-        <v>47.43</v>
+        <v>49.86</v>
       </c>
       <c r="I118" s="6" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.97</v>
+        <v>7.345</v>
       </c>
       <c r="K118" s="2" t="n">
-        <v>0.977</v>
+        <v>6.896</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="7" t="inlineStr"/>
@@ -5783,39 +5783,39 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>0325</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="D119" s="2" t="n">
-        <v>0.8149999999999999</v>
-      </c>
-      <c r="E119" s="9" t="n">
-        <v>0.0252</v>
+        <v>1.1</v>
+      </c>
+      <c r="E119" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F119" s="4" t="n">
-        <v>1198800</v>
+        <v>1400700</v>
       </c>
       <c r="G119" s="5" t="n">
-        <v>0.21</v>
+        <v>0.71</v>
       </c>
       <c r="H119" t="n">
-        <v>64.98999999999999</v>
-      </c>
-      <c r="I119" s="8" t="inlineStr">
+        <v>51.14</v>
+      </c>
+      <c r="I119" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.793</v>
+        <v>1.091</v>
       </c>
       <c r="K119" s="2" t="n">
-        <v>0.771</v>
+        <v>1.097</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="7" t="inlineStr"/>
@@ -5828,38 +5828,40 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>0470</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>BFIELD</t>
+          <t>AWC</t>
         </is>
       </c>
       <c r="D120" s="2" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="E120" s="3" t="n">
-        <v>-0.0118</v>
+        <v>0.67</v>
+      </c>
+      <c r="E120" s="8" t="n">
+        <v>-0.0219</v>
       </c>
       <c r="F120" s="4" t="n">
-        <v>1185200</v>
+        <v>1391000</v>
       </c>
       <c r="G120" s="5" t="n">
-        <v>0.21</v>
+        <v>0.52</v>
       </c>
       <c r="H120" t="n">
-        <v>17.86</v>
-      </c>
-      <c r="I120" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.56</v>
+      </c>
+      <c r="I120" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="K120" s="2" t="n"/>
+        <v>0.647</v>
+      </c>
+      <c r="K120" s="2" t="n">
+        <v>0.5570000000000001</v>
+      </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="7" t="inlineStr"/>
     </row>
@@ -5871,28 +5873,28 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D121" s="2" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="E121" s="3" t="n">
-        <v>-0.0145</v>
+        <v>0.825</v>
+      </c>
+      <c r="E121" s="8" t="n">
+        <v>-0.0294</v>
       </c>
       <c r="F121" s="4" t="n">
-        <v>1182400</v>
+        <v>1384000</v>
       </c>
       <c r="G121" s="5" t="n">
-        <v>0.08</v>
+        <v>0.39</v>
       </c>
       <c r="H121" t="n">
-        <v>39.44</v>
+        <v>51.48</v>
       </c>
       <c r="I121" s="6" t="inlineStr">
         <is>
@@ -5900,10 +5902,10 @@
         </is>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.75</v>
+        <v>0.826</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>0.723</v>
+        <v>0.781</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="7" t="inlineStr"/>
@@ -5916,39 +5918,39 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>8494</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>LBICAP</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D122" s="2" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="E122" s="10" t="n">
-        <v>0</v>
+        <v>2.76</v>
+      </c>
+      <c r="E122" s="8" t="n">
+        <v>-0.0143</v>
       </c>
       <c r="F122" s="4" t="n">
-        <v>1141000</v>
+        <v>1362200</v>
       </c>
       <c r="G122" s="5" t="n">
-        <v>6.51</v>
+        <v>0.36</v>
       </c>
       <c r="H122" t="n">
-        <v>79.44</v>
-      </c>
-      <c r="I122" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.45</v>
+      </c>
+      <c r="I122" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.463</v>
+        <v>2.895</v>
       </c>
       <c r="K122" s="2" t="n">
-        <v>0.405</v>
+        <v>3.012</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="7" t="inlineStr"/>
@@ -5961,39 +5963,39 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>0278</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>EDELTEQ</t>
         </is>
       </c>
       <c r="D123" s="2" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="E123" s="3" t="n">
-        <v>-0.0323</v>
+        <v>0.42</v>
+      </c>
+      <c r="E123" s="8" t="n">
+        <v>-0.0233</v>
       </c>
       <c r="F123" s="4" t="n">
-        <v>1107500</v>
+        <v>1353500</v>
       </c>
       <c r="G123" s="5" t="n">
-        <v>0.45</v>
+        <v>0.24</v>
       </c>
       <c r="H123" t="n">
-        <v>53.86</v>
-      </c>
-      <c r="I123" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.16</v>
+      </c>
+      <c r="I123" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.734</v>
+        <v>0.39</v>
       </c>
       <c r="K123" s="2" t="n">
-        <v>0.704</v>
+        <v>0.36</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="7" t="inlineStr"/>
@@ -6015,19 +6017,19 @@
         </is>
       </c>
       <c r="D124" s="2" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="E124" s="3" t="n">
-        <v>-0.0172</v>
+        <v>1.15</v>
+      </c>
+      <c r="E124" s="8" t="n">
+        <v>-0.0086</v>
       </c>
       <c r="F124" s="4" t="n">
-        <v>1104200</v>
+        <v>1332900</v>
       </c>
       <c r="G124" s="5" t="n">
-        <v>0.26</v>
+        <v>0.32</v>
       </c>
       <c r="H124" t="n">
-        <v>49.11</v>
+        <v>50.8</v>
       </c>
       <c r="I124" s="6" t="inlineStr">
         <is>
@@ -6051,28 +6053,28 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>5272</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>RANHILL</t>
         </is>
       </c>
       <c r="D125" s="2" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="E125" s="3" t="n">
-        <v>-0.0273</v>
+        <v>3.12</v>
+      </c>
+      <c r="E125" s="8" t="n">
+        <v>-0.0064</v>
       </c>
       <c r="F125" s="4" t="n">
-        <v>1095900</v>
+        <v>1328500</v>
       </c>
       <c r="G125" s="5" t="n">
-        <v>0.21</v>
+        <v>0.84</v>
       </c>
       <c r="H125" t="n">
-        <v>32.47</v>
+        <v>50.69</v>
       </c>
       <c r="I125" s="6" t="inlineStr">
         <is>
@@ -6080,10 +6082,10 @@
         </is>
       </c>
       <c r="J125" s="2" t="n">
-        <v>2.807</v>
+        <v>3.17</v>
       </c>
       <c r="K125" s="2" t="n">
-        <v>2.877</v>
+        <v>2.876</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="7" t="inlineStr"/>
@@ -6096,28 +6098,28 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>0045</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>SSB8</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D126" s="2" t="n">
-        <v>0.635</v>
+        <v>0.865</v>
       </c>
       <c r="E126" s="10" t="n">
-        <v>0</v>
+        <v>0.0058</v>
       </c>
       <c r="F126" s="4" t="n">
-        <v>1024300</v>
+        <v>1312000</v>
       </c>
       <c r="G126" s="5" t="n">
-        <v>0.27</v>
+        <v>0.42</v>
       </c>
       <c r="H126" t="n">
-        <v>50.64</v>
+        <v>52.3</v>
       </c>
       <c r="I126" s="6" t="inlineStr">
         <is>
@@ -6125,10 +6127,10 @@
         </is>
       </c>
       <c r="J126" s="2" t="n">
-        <v>0.639</v>
+        <v>0.864</v>
       </c>
       <c r="K126" s="2" t="n">
-        <v>0.615</v>
+        <v>0.859</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="7" t="inlineStr"/>
@@ -6141,39 +6143,39 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>0450</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>MFGROUP</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D127" s="2" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="E127" s="3" t="n">
-        <v>-0.0175</v>
+        <v>2.82</v>
+      </c>
+      <c r="E127" s="10" t="n">
+        <v>0.0036</v>
       </c>
       <c r="F127" s="4" t="n">
-        <v>1006700</v>
+        <v>1305800</v>
       </c>
       <c r="G127" s="5" t="n">
-        <v>1.06</v>
+        <v>0.14</v>
       </c>
       <c r="H127" t="n">
-        <v>55.75</v>
-      </c>
-      <c r="I127" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.66</v>
+      </c>
+      <c r="I127" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J127" s="2" t="n">
-        <v>0.276</v>
+        <v>2.794</v>
       </c>
       <c r="K127" s="2" t="n">
-        <v>0.267</v>
+        <v>2.664</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="7" t="inlineStr"/>
@@ -6186,28 +6188,28 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>5932</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>BPURI</t>
         </is>
       </c>
       <c r="D128" s="2" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="E128" s="3" t="n">
-        <v>-0.0059</v>
+        <v>0.21</v>
+      </c>
+      <c r="E128" s="8" t="n">
+        <v>-0.0233</v>
       </c>
       <c r="F128" s="4" t="n">
-        <v>1004700</v>
+        <v>1297400</v>
       </c>
       <c r="G128" s="5" t="n">
-        <v>0.34</v>
+        <v>1.89</v>
       </c>
       <c r="H128" t="n">
-        <v>16.62</v>
+        <v>38.22</v>
       </c>
       <c r="I128" s="6" t="inlineStr">
         <is>
@@ -6215,10 +6217,10 @@
         </is>
       </c>
       <c r="J128" s="2" t="n">
-        <v>0.915</v>
+        <v>0.223</v>
       </c>
       <c r="K128" s="2" t="n">
-        <v>0.973</v>
+        <v>0.232</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="7" t="inlineStr"/>
@@ -6231,28 +6233,28 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>0151</t>
+          <t>0298</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>KGB</t>
+          <t>WENTEL</t>
         </is>
       </c>
       <c r="D129" s="2" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="E129" s="3" t="n">
-        <v>-0.006</v>
+        <v>0.235</v>
+      </c>
+      <c r="E129" s="8" t="n">
+        <v>-0.0408</v>
       </c>
       <c r="F129" s="4" t="n">
-        <v>992000</v>
+        <v>1295300</v>
       </c>
       <c r="G129" s="5" t="n">
-        <v>0.44</v>
+        <v>0.76</v>
       </c>
       <c r="H129" t="n">
-        <v>41.33</v>
+        <v>36.24</v>
       </c>
       <c r="I129" s="6" t="inlineStr">
         <is>
@@ -6260,10 +6262,10 @@
         </is>
       </c>
       <c r="J129" s="2" t="n">
-        <v>8.622999999999999</v>
+        <v>0.254</v>
       </c>
       <c r="K129" s="2" t="n">
-        <v>8.694000000000001</v>
+        <v>0.274</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="7" t="inlineStr"/>
@@ -6276,28 +6278,28 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>SUNREIT</t>
         </is>
       </c>
       <c r="D130" s="2" t="n">
-        <v>2.8</v>
+        <v>2.02</v>
       </c>
       <c r="E130" s="3" t="n">
-        <v>-0.0036</v>
+        <v>0</v>
       </c>
       <c r="F130" s="4" t="n">
-        <v>990400</v>
+        <v>1276800</v>
       </c>
       <c r="G130" s="5" t="n">
-        <v>0.11</v>
+        <v>0.4</v>
       </c>
       <c r="H130" t="n">
-        <v>52.45</v>
+        <v>44.02</v>
       </c>
       <c r="I130" s="6" t="inlineStr">
         <is>
@@ -6305,10 +6307,10 @@
         </is>
       </c>
       <c r="J130" s="2" t="n">
-        <v>2.792</v>
+        <v>2.044</v>
       </c>
       <c r="K130" s="2" t="n">
-        <v>2.664</v>
+        <v>2.071</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="7" t="inlineStr"/>
@@ -6321,28 +6323,28 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>0233</t>
+          <t>0470</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>PEKAT</t>
+          <t>BFIELD</t>
         </is>
       </c>
       <c r="D131" s="2" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="E131" s="9" t="n">
-        <v>0.0109</v>
+        <v>0.425</v>
+      </c>
+      <c r="E131" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F131" s="4" t="n">
-        <v>967100</v>
+        <v>1267200</v>
       </c>
       <c r="G131" s="5" t="n">
-        <v>0.27</v>
+        <v>0.23</v>
       </c>
       <c r="H131" t="n">
-        <v>58.67</v>
+        <v>19.3</v>
       </c>
       <c r="I131" s="6" t="inlineStr">
         <is>
@@ -6350,11 +6352,9 @@
         </is>
       </c>
       <c r="J131" s="2" t="n">
-        <v>2.678</v>
-      </c>
-      <c r="K131" s="2" t="n">
-        <v>2.261</v>
-      </c>
+        <v>0.46</v>
+      </c>
+      <c r="K131" s="2" t="n"/>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="7" t="inlineStr"/>
     </row>
@@ -6366,28 +6366,28 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>1619</t>
+          <t>0233</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>DRBHCOM</t>
+          <t>PEKAT</t>
         </is>
       </c>
       <c r="D132" s="2" t="n">
-        <v>0.795</v>
-      </c>
-      <c r="E132" s="3" t="n">
-        <v>-0.0245</v>
+        <v>2.81</v>
+      </c>
+      <c r="E132" s="10" t="n">
+        <v>0.0181</v>
       </c>
       <c r="F132" s="4" t="n">
-        <v>915100</v>
+        <v>1239100</v>
       </c>
       <c r="G132" s="5" t="n">
-        <v>1.86</v>
+        <v>0.34</v>
       </c>
       <c r="H132" t="n">
-        <v>15.15</v>
+        <v>59.35</v>
       </c>
       <c r="I132" s="6" t="inlineStr">
         <is>
@@ -6395,10 +6395,10 @@
         </is>
       </c>
       <c r="J132" s="2" t="n">
-        <v>0.884</v>
+        <v>2.68</v>
       </c>
       <c r="K132" s="2" t="n">
-        <v>0.9379999999999999</v>
+        <v>2.262</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="7" t="inlineStr"/>
@@ -6411,28 +6411,28 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D133" s="2" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="E133" s="3" t="n">
-        <v>-0.0379</v>
+        <v>2.49</v>
+      </c>
+      <c r="E133" s="8" t="n">
+        <v>-0.0273</v>
       </c>
       <c r="F133" s="4" t="n">
-        <v>908400</v>
+        <v>1207200</v>
       </c>
       <c r="G133" s="5" t="n">
-        <v>0.29</v>
+        <v>0.23</v>
       </c>
       <c r="H133" t="n">
-        <v>49.69</v>
+        <v>32.47</v>
       </c>
       <c r="I133" s="6" t="inlineStr">
         <is>
@@ -6440,10 +6440,10 @@
         </is>
       </c>
       <c r="J133" s="2" t="n">
-        <v>1.287</v>
+        <v>2.807</v>
       </c>
       <c r="K133" s="2" t="n">
-        <v>1.225</v>
+        <v>2.877</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="7" t="inlineStr"/>
@@ -6456,39 +6456,39 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>0168</t>
+          <t>8494</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>BMGREEN</t>
+          <t>LBICAP</t>
         </is>
       </c>
       <c r="D134" s="2" t="n">
-        <v>1.39</v>
+        <v>0.505</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>-0.0544</v>
+        <v>0</v>
       </c>
       <c r="F134" s="4" t="n">
-        <v>890200</v>
+        <v>1191600</v>
       </c>
       <c r="G134" s="5" t="n">
-        <v>0.93</v>
+        <v>6.8</v>
       </c>
       <c r="H134" t="n">
-        <v>29.55</v>
-      </c>
-      <c r="I134" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>79.44</v>
+      </c>
+      <c r="I134" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J134" s="2" t="n">
-        <v>1.553</v>
+        <v>0.463</v>
       </c>
       <c r="K134" s="2" t="n">
-        <v>1.648</v>
+        <v>0.405</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="7" t="inlineStr"/>
@@ -6501,28 +6501,28 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>0151</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>KGB</t>
         </is>
       </c>
       <c r="D135" s="2" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="E135" s="9" t="n">
-        <v>0.0126</v>
+        <v>8.359999999999999</v>
+      </c>
+      <c r="E135" s="10" t="n">
+        <v>0.0012</v>
       </c>
       <c r="F135" s="4" t="n">
-        <v>882500</v>
+        <v>1191500</v>
       </c>
       <c r="G135" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.52</v>
       </c>
       <c r="H135" t="n">
-        <v>46.52</v>
+        <v>42.66</v>
       </c>
       <c r="I135" s="6" t="inlineStr">
         <is>
@@ -6530,10 +6530,10 @@
         </is>
       </c>
       <c r="J135" s="2" t="n">
-        <v>2.443</v>
+        <v>8.629</v>
       </c>
       <c r="K135" s="2" t="n">
-        <v>2.384</v>
+        <v>8.695</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="7" t="inlineStr"/>
@@ -6546,39 +6546,39 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>0045</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>SSB8</t>
         </is>
       </c>
       <c r="D136" s="2" t="n">
-        <v>6.39</v>
-      </c>
-      <c r="E136" s="3" t="n">
-        <v>-0.0169</v>
+        <v>0.63</v>
+      </c>
+      <c r="E136" s="8" t="n">
+        <v>-0.007900000000000001</v>
       </c>
       <c r="F136" s="4" t="n">
-        <v>878800</v>
+        <v>1172700</v>
       </c>
       <c r="G136" s="5" t="n">
-        <v>0.15</v>
+        <v>0.31</v>
       </c>
       <c r="H136" t="n">
-        <v>55.18</v>
-      </c>
-      <c r="I136" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.81</v>
+      </c>
+      <c r="I136" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J136" s="2" t="n">
-        <v>6.162</v>
+        <v>0.638</v>
       </c>
       <c r="K136" s="2" t="n">
-        <v>5.91</v>
+        <v>0.614</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="7" t="inlineStr"/>
@@ -6591,39 +6591,39 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>7498</t>
+          <t>0337</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>RALCO</t>
+          <t>SET</t>
         </is>
       </c>
       <c r="D137" s="2" t="n">
-        <v>1.02</v>
+        <v>0.245</v>
       </c>
       <c r="E137" s="10" t="n">
-        <v>0</v>
+        <v>0.0208</v>
       </c>
       <c r="F137" s="4" t="n">
-        <v>878700</v>
+        <v>1158600</v>
       </c>
       <c r="G137" s="5" t="n">
-        <v>1.28</v>
+        <v>0.59</v>
       </c>
       <c r="H137" t="n">
-        <v>59.46</v>
-      </c>
-      <c r="I137" s="8" t="inlineStr">
+        <v>53.4</v>
+      </c>
+      <c r="I137" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J137" s="2" t="n">
-        <v>1.004</v>
+        <v>0.24</v>
       </c>
       <c r="K137" s="2" t="n">
-        <v>0.984</v>
+        <v>0.242</v>
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" s="7" t="inlineStr"/>
@@ -6636,28 +6636,28 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>ATECH</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D138" s="2" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="E138" s="3" t="n">
-        <v>-0.0318</v>
+        <v>0.75</v>
+      </c>
+      <c r="E138" s="8" t="n">
+        <v>-0.0323</v>
       </c>
       <c r="F138" s="4" t="n">
-        <v>857700</v>
+        <v>1140800</v>
       </c>
       <c r="G138" s="5" t="n">
-        <v>0.37</v>
+        <v>0.46</v>
       </c>
       <c r="H138" t="n">
-        <v>47.23</v>
+        <v>53.86</v>
       </c>
       <c r="I138" s="6" t="inlineStr">
         <is>
@@ -6665,10 +6665,10 @@
         </is>
       </c>
       <c r="J138" s="2" t="n">
-        <v>0.775</v>
+        <v>0.734</v>
       </c>
       <c r="K138" s="2" t="n">
-        <v>0.769</v>
+        <v>0.704</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" s="7" t="inlineStr"/>
@@ -6681,39 +6681,39 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>SPSETIA</t>
         </is>
       </c>
       <c r="D139" s="2" t="n">
-        <v>7.19</v>
-      </c>
-      <c r="E139" s="3" t="n">
-        <v>-0.0178</v>
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="E139" s="10" t="n">
+        <v>0.0147</v>
       </c>
       <c r="F139" s="4" t="n">
-        <v>831200</v>
+        <v>1137500</v>
       </c>
       <c r="G139" s="5" t="n">
-        <v>0.08</v>
+        <v>0.17</v>
       </c>
       <c r="H139" t="n">
-        <v>30.74</v>
-      </c>
-      <c r="I139" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.21</v>
+      </c>
+      <c r="I139" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J139" s="2" t="n">
-        <v>7.453</v>
+        <v>0.725</v>
       </c>
       <c r="K139" s="2" t="n">
-        <v>7.948</v>
+        <v>0.791</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" s="7" t="inlineStr"/>
@@ -6726,28 +6726,28 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>6971</t>
+          <t>1619</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>KOBAY</t>
+          <t>DRBHCOM</t>
         </is>
       </c>
       <c r="D140" s="2" t="n">
-        <v>2.06</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="E140" s="3" t="n">
-        <v>-0.019</v>
+        <v>0</v>
       </c>
       <c r="F140" s="4" t="n">
-        <v>812100</v>
+        <v>1132700</v>
       </c>
       <c r="G140" s="5" t="n">
-        <v>0.66</v>
+        <v>2.3</v>
       </c>
       <c r="H140" t="n">
-        <v>42.97</v>
+        <v>17.34</v>
       </c>
       <c r="I140" s="6" t="inlineStr">
         <is>
@@ -6755,10 +6755,10 @@
         </is>
       </c>
       <c r="J140" s="2" t="n">
-        <v>2.124</v>
+        <v>0.885</v>
       </c>
       <c r="K140" s="2" t="n">
-        <v>2.28</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" s="7" t="inlineStr"/>
@@ -6771,39 +6771,39 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>PENTA</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D141" s="2" t="n">
-        <v>5.47</v>
-      </c>
-      <c r="E141" s="3" t="n">
-        <v>-0.0232</v>
+        <v>6.41</v>
+      </c>
+      <c r="E141" s="8" t="n">
+        <v>-0.0138</v>
       </c>
       <c r="F141" s="4" t="n">
-        <v>811800</v>
+        <v>1101700</v>
       </c>
       <c r="G141" s="5" t="n">
-        <v>0.21</v>
+        <v>0.19</v>
       </c>
       <c r="H141" t="n">
-        <v>49.98</v>
-      </c>
-      <c r="I141" s="8" t="inlineStr">
+        <v>55.51</v>
+      </c>
+      <c r="I141" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J141" s="2" t="n">
-        <v>5.51</v>
+        <v>6.164</v>
       </c>
       <c r="K141" s="2" t="n">
-        <v>5.393</v>
+        <v>5.91</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" s="7" t="inlineStr"/>
@@ -6816,39 +6816,39 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>5272</t>
+          <t>7160</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>RANHILL</t>
+          <t>PENTA</t>
         </is>
       </c>
       <c r="D142" s="2" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="E142" s="3" t="n">
-        <v>-0.0064</v>
+        <v>5.46</v>
+      </c>
+      <c r="E142" s="8" t="n">
+        <v>-0.025</v>
       </c>
       <c r="F142" s="4" t="n">
-        <v>802200</v>
+        <v>1097600</v>
       </c>
       <c r="G142" s="5" t="n">
-        <v>0.51</v>
+        <v>0.29</v>
       </c>
       <c r="H142" t="n">
-        <v>50.69</v>
-      </c>
-      <c r="I142" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.74</v>
+      </c>
+      <c r="I142" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J142" s="2" t="n">
-        <v>3.17</v>
+        <v>5.509</v>
       </c>
       <c r="K142" s="2" t="n">
-        <v>2.876</v>
+        <v>5.393</v>
       </c>
       <c r="L142" t="inlineStr"/>
       <c r="M142" s="7" t="inlineStr"/>
@@ -6861,39 +6861,39 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D143" s="2" t="n">
-        <v>3.93</v>
-      </c>
-      <c r="E143" s="9" t="n">
-        <v>0.0026</v>
+        <v>7.2</v>
+      </c>
+      <c r="E143" s="8" t="n">
+        <v>-0.0164</v>
       </c>
       <c r="F143" s="4" t="n">
-        <v>800800</v>
+        <v>1095800</v>
       </c>
       <c r="G143" s="5" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="H143" t="n">
-        <v>51.6</v>
-      </c>
-      <c r="I143" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>31.05</v>
+      </c>
+      <c r="I143" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J143" s="2" t="n">
-        <v>3.957</v>
+        <v>7.454</v>
       </c>
       <c r="K143" s="2" t="n">
-        <v>3.555</v>
+        <v>7.948</v>
       </c>
       <c r="L143" t="inlineStr"/>
       <c r="M143" s="7" t="inlineStr"/>
@@ -6906,28 +6906,28 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>0099</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>SCICOM</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D144" s="2" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="E144" s="10" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E144" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F144" s="4" t="n">
-        <v>791600</v>
+        <v>1091100</v>
       </c>
       <c r="G144" s="5" t="n">
-        <v>1.07</v>
+        <v>0.13</v>
       </c>
       <c r="H144" t="n">
-        <v>39.81</v>
+        <v>50.51</v>
       </c>
       <c r="I144" s="6" t="inlineStr">
         <is>
@@ -6935,10 +6935,10 @@
         </is>
       </c>
       <c r="J144" s="2" t="n">
-        <v>2.196</v>
+        <v>0.354</v>
       </c>
       <c r="K144" s="2" t="n">
-        <v>2.235</v>
+        <v>0.327</v>
       </c>
       <c r="L144" t="inlineStr"/>
       <c r="M144" s="7" t="inlineStr"/>
@@ -6951,28 +6951,28 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>0223</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>SAMAIDEN</t>
         </is>
       </c>
       <c r="D145" s="2" t="n">
-        <v>12.82</v>
-      </c>
-      <c r="E145" s="3" t="n">
-        <v>-0.0138</v>
+        <v>2.9</v>
+      </c>
+      <c r="E145" s="10" t="n">
+        <v>0.014</v>
       </c>
       <c r="F145" s="4" t="n">
-        <v>776700</v>
+        <v>1063700</v>
       </c>
       <c r="G145" s="5" t="n">
-        <v>0.1</v>
+        <v>0.21</v>
       </c>
       <c r="H145" t="n">
-        <v>37.85</v>
+        <v>59.52</v>
       </c>
       <c r="I145" s="6" t="inlineStr">
         <is>
@@ -6980,10 +6980,10 @@
         </is>
       </c>
       <c r="J145" s="2" t="n">
-        <v>13</v>
+        <v>2.784</v>
       </c>
       <c r="K145" s="2" t="n">
-        <v>13.412</v>
+        <v>2.212</v>
       </c>
       <c r="L145" t="inlineStr"/>
       <c r="M145" s="7" t="inlineStr"/>
@@ -6996,28 +6996,28 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D146" s="2" t="n">
-        <v>0.735</v>
-      </c>
-      <c r="E146" s="3" t="n">
-        <v>-0.02</v>
+        <v>3.97</v>
+      </c>
+      <c r="E146" s="10" t="n">
+        <v>0.0128</v>
       </c>
       <c r="F146" s="4" t="n">
-        <v>766100</v>
+        <v>1058100</v>
       </c>
       <c r="G146" s="5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="H146" t="n">
-        <v>51.27</v>
+        <v>52.85</v>
       </c>
       <c r="I146" s="6" t="inlineStr">
         <is>
@@ -7025,10 +7025,10 @@
         </is>
       </c>
       <c r="J146" s="2" t="n">
-        <v>0.741</v>
+        <v>3.961</v>
       </c>
       <c r="K146" s="2" t="n">
-        <v>0.676</v>
+        <v>3.556</v>
       </c>
       <c r="L146" t="inlineStr"/>
       <c r="M146" s="7" t="inlineStr"/>
@@ -7041,28 +7041,28 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>0099</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>DAYANG</t>
+          <t>SCICOM</t>
         </is>
       </c>
       <c r="D147" s="2" t="n">
-        <v>1.32</v>
+        <v>2.17</v>
       </c>
       <c r="E147" s="10" t="n">
-        <v>0</v>
+        <v>0.0383</v>
       </c>
       <c r="F147" s="4" t="n">
-        <v>723500</v>
+        <v>1056800</v>
       </c>
       <c r="G147" s="5" t="n">
-        <v>0.36</v>
+        <v>1.43</v>
       </c>
       <c r="H147" t="n">
-        <v>27.74</v>
+        <v>46.79</v>
       </c>
       <c r="I147" s="6" t="inlineStr">
         <is>
@@ -7070,10 +7070,10 @@
         </is>
       </c>
       <c r="J147" s="2" t="n">
-        <v>1.404</v>
+        <v>2.204</v>
       </c>
       <c r="K147" s="2" t="n">
-        <v>1.466</v>
+        <v>2.236</v>
       </c>
       <c r="L147" t="inlineStr"/>
       <c r="M147" s="7" t="inlineStr"/>
@@ -7086,28 +7086,28 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D148" s="2" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="E148" s="10" t="n">
-        <v>0</v>
+        <v>0.84</v>
+      </c>
+      <c r="E148" s="8" t="n">
+        <v>-0.0059</v>
       </c>
       <c r="F148" s="4" t="n">
-        <v>723400</v>
+        <v>1029900</v>
       </c>
       <c r="G148" s="5" t="n">
-        <v>0.14</v>
+        <v>0.35</v>
       </c>
       <c r="H148" t="n">
-        <v>58.22</v>
+        <v>16.62</v>
       </c>
       <c r="I148" s="6" t="inlineStr">
         <is>
@@ -7115,10 +7115,10 @@
         </is>
       </c>
       <c r="J148" s="2" t="n">
-        <v>2.78</v>
+        <v>0.915</v>
       </c>
       <c r="K148" s="2" t="n">
-        <v>2.212</v>
+        <v>0.973</v>
       </c>
       <c r="L148" t="inlineStr"/>
       <c r="M148" s="7" t="inlineStr"/>
@@ -7131,39 +7131,39 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>5211</t>
+          <t>0450</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>SUNWAY</t>
+          <t>MFGROUP</t>
         </is>
       </c>
       <c r="D149" s="2" t="n">
-        <v>4.22</v>
-      </c>
-      <c r="E149" s="9" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.28</v>
+      </c>
+      <c r="E149" s="8" t="n">
+        <v>-0.0175</v>
       </c>
       <c r="F149" s="4" t="n">
-        <v>702600</v>
+        <v>1006700</v>
       </c>
       <c r="G149" s="5" t="n">
-        <v>0.15</v>
+        <v>1.06</v>
       </c>
       <c r="H149" t="n">
-        <v>35.14</v>
-      </c>
-      <c r="I149" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.75</v>
+      </c>
+      <c r="I149" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J149" s="2" t="n">
-        <v>4.411</v>
+        <v>0.276</v>
       </c>
       <c r="K149" s="2" t="n">
-        <v>4.719</v>
+        <v>0.267</v>
       </c>
       <c r="L149" t="inlineStr"/>
       <c r="M149" s="7" t="inlineStr"/>
@@ -7176,28 +7176,28 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>5299</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>IGBCR</t>
+          <t>ATECH</t>
         </is>
       </c>
       <c r="D150" s="2" t="n">
-        <v>0.615</v>
-      </c>
-      <c r="E150" s="9" t="n">
-        <v>0.008199999999999999</v>
+        <v>0.755</v>
+      </c>
+      <c r="E150" s="8" t="n">
+        <v>-0.0382</v>
       </c>
       <c r="F150" s="4" t="n">
-        <v>639200</v>
+        <v>1005400</v>
       </c>
       <c r="G150" s="5" t="n">
-        <v>2.72</v>
+        <v>0.43</v>
       </c>
       <c r="H150" t="n">
-        <v>51.11</v>
+        <v>46.3</v>
       </c>
       <c r="I150" s="6" t="inlineStr">
         <is>
@@ -7205,10 +7205,10 @@
         </is>
       </c>
       <c r="J150" s="2" t="n">
-        <v>0.614</v>
+        <v>0.775</v>
       </c>
       <c r="K150" s="2" t="n">
-        <v>0.613</v>
+        <v>0.769</v>
       </c>
       <c r="L150" t="inlineStr"/>
       <c r="M150" s="7" t="inlineStr"/>
@@ -7221,28 +7221,28 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D151" s="2" t="n">
-        <v>1.01</v>
+        <v>0.75</v>
       </c>
       <c r="E151" s="3" t="n">
-        <v>-0.0098</v>
+        <v>0</v>
       </c>
       <c r="F151" s="4" t="n">
-        <v>638100</v>
+        <v>962000</v>
       </c>
       <c r="G151" s="5" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="H151" t="n">
-        <v>47.81</v>
+        <v>53.87</v>
       </c>
       <c r="I151" s="6" t="inlineStr">
         <is>
@@ -7250,10 +7250,10 @@
         </is>
       </c>
       <c r="J151" s="2" t="n">
-        <v>1.044</v>
+        <v>0.743</v>
       </c>
       <c r="K151" s="2" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.677</v>
       </c>
       <c r="L151" t="inlineStr"/>
       <c r="M151" s="7" t="inlineStr"/>
@@ -7266,28 +7266,28 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>5258</t>
+          <t>0168</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>BIMB</t>
+          <t>BMGREEN</t>
         </is>
       </c>
       <c r="D152" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E152" s="3" t="n">
-        <v>-0.005</v>
+        <v>1.39</v>
+      </c>
+      <c r="E152" s="8" t="n">
+        <v>-0.0544</v>
       </c>
       <c r="F152" s="4" t="n">
-        <v>625300</v>
+        <v>933200</v>
       </c>
       <c r="G152" s="5" t="n">
-        <v>0.73</v>
+        <v>0.97</v>
       </c>
       <c r="H152" t="n">
-        <v>34.83</v>
+        <v>29.55</v>
       </c>
       <c r="I152" s="6" t="inlineStr">
         <is>
@@ -7295,10 +7295,10 @@
         </is>
       </c>
       <c r="J152" s="2" t="n">
-        <v>2.037</v>
+        <v>1.553</v>
       </c>
       <c r="K152" s="2" t="n">
-        <v>2.081</v>
+        <v>1.648</v>
       </c>
       <c r="L152" t="inlineStr"/>
       <c r="M152" s="7" t="inlineStr"/>
@@ -7311,39 +7311,39 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>0271</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>WELLS</t>
+          <t>CPETECH</t>
         </is>
       </c>
       <c r="D153" s="2" t="n">
-        <v>0.555</v>
-      </c>
-      <c r="E153" s="9" t="n">
-        <v>0.0091</v>
+        <v>1.27</v>
+      </c>
+      <c r="E153" s="8" t="n">
+        <v>-0.0379</v>
       </c>
       <c r="F153" s="4" t="n">
-        <v>622500</v>
+        <v>923900</v>
       </c>
       <c r="G153" s="5" t="n">
-        <v>0.54</v>
+        <v>0.29</v>
       </c>
       <c r="H153" t="n">
-        <v>42.07</v>
-      </c>
-      <c r="I153" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.69</v>
+      </c>
+      <c r="I153" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J153" s="2" t="n">
-        <v>0.5679999999999999</v>
+        <v>1.287</v>
       </c>
       <c r="K153" s="2" t="n">
-        <v>0.611</v>
+        <v>1.225</v>
       </c>
       <c r="L153" t="inlineStr"/>
       <c r="M153" s="7" t="inlineStr"/>
@@ -7356,28 +7356,28 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>3417</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>E&amp;O</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D154" s="2" t="n">
-        <v>0.745</v>
-      </c>
-      <c r="E154" s="3" t="n">
-        <v>-0.0067</v>
+        <v>1.15</v>
+      </c>
+      <c r="E154" s="10" t="n">
+        <v>0.0177</v>
       </c>
       <c r="F154" s="4" t="n">
-        <v>607700</v>
+        <v>897000</v>
       </c>
       <c r="G154" s="5" t="n">
-        <v>0.45</v>
+        <v>0.11</v>
       </c>
       <c r="H154" t="n">
-        <v>40.03</v>
+        <v>57.19</v>
       </c>
       <c r="I154" s="6" t="inlineStr">
         <is>
@@ -7385,10 +7385,10 @@
         </is>
       </c>
       <c r="J154" s="2" t="n">
-        <v>0.764</v>
+        <v>1.114</v>
       </c>
       <c r="K154" s="2" t="n">
-        <v>0.769</v>
+        <v>0.888</v>
       </c>
       <c r="L154" t="inlineStr"/>
       <c r="M154" s="7" t="inlineStr"/>
@@ -7401,39 +7401,39 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>6947</t>
+          <t>7498</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>RALCO</t>
         </is>
       </c>
       <c r="D155" s="2" t="n">
-        <v>2.5</v>
+        <v>1.02</v>
       </c>
       <c r="E155" s="3" t="n">
-        <v>-0.0196</v>
+        <v>0</v>
       </c>
       <c r="F155" s="4" t="n">
-        <v>594500</v>
+        <v>878700</v>
       </c>
       <c r="G155" s="5" t="n">
-        <v>0.2</v>
+        <v>1.28</v>
       </c>
       <c r="H155" t="n">
-        <v>39.11</v>
-      </c>
-      <c r="I155" s="8" t="inlineStr">
+        <v>59.46</v>
+      </c>
+      <c r="I155" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J155" s="2" t="n">
-        <v>2.559</v>
+        <v>1.004</v>
       </c>
       <c r="K155" s="2" t="n">
-        <v>2.685</v>
+        <v>0.984</v>
       </c>
       <c r="L155" t="inlineStr"/>
       <c r="M155" s="7" t="inlineStr"/>
@@ -7446,28 +7446,28 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>6971</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>KOBAY</t>
         </is>
       </c>
       <c r="D156" s="2" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="E156" s="3" t="n">
-        <v>-0.0299</v>
+        <v>2.06</v>
+      </c>
+      <c r="E156" s="8" t="n">
+        <v>-0.019</v>
       </c>
       <c r="F156" s="4" t="n">
-        <v>594100</v>
+        <v>862400</v>
       </c>
       <c r="G156" s="5" t="n">
-        <v>0.18</v>
+        <v>0.71</v>
       </c>
       <c r="H156" t="n">
-        <v>33.63</v>
+        <v>42.97</v>
       </c>
       <c r="I156" s="6" t="inlineStr">
         <is>
@@ -7475,10 +7475,10 @@
         </is>
       </c>
       <c r="J156" s="2" t="n">
-        <v>0.723</v>
+        <v>2.124</v>
       </c>
       <c r="K156" s="2" t="n">
-        <v>0.744</v>
+        <v>2.28</v>
       </c>
       <c r="L156" t="inlineStr"/>
       <c r="M156" s="7" t="inlineStr"/>
@@ -7491,28 +7491,28 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>JPG</t>
+          <t>SUNWAY</t>
         </is>
       </c>
       <c r="D157" s="2" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="E157" s="9" t="n">
-        <v>0.0117</v>
+        <v>4.21</v>
+      </c>
+      <c r="E157" s="10" t="n">
+        <v>0.0072</v>
       </c>
       <c r="F157" s="4" t="n">
-        <v>576800</v>
+        <v>814800</v>
       </c>
       <c r="G157" s="5" t="n">
-        <v>0.1</v>
+        <v>0.17</v>
       </c>
       <c r="H157" t="n">
-        <v>39.28</v>
+        <v>34.43</v>
       </c>
       <c r="I157" s="6" t="inlineStr">
         <is>
@@ -7520,10 +7520,10 @@
         </is>
       </c>
       <c r="J157" s="2" t="n">
-        <v>1.775</v>
+        <v>4.41</v>
       </c>
       <c r="K157" s="2" t="n">
-        <v>1.888</v>
+        <v>4.719</v>
       </c>
       <c r="L157" t="inlineStr"/>
       <c r="M157" s="7" t="inlineStr"/>
@@ -7536,39 +7536,39 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>6947</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>DUFU</t>
+          <t>CDB</t>
         </is>
       </c>
       <c r="D158" s="2" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="E158" s="3" t="n">
-        <v>-0.0195</v>
+        <v>2.49</v>
+      </c>
+      <c r="E158" s="8" t="n">
+        <v>-0.0235</v>
       </c>
       <c r="F158" s="4" t="n">
-        <v>573800</v>
+        <v>769200</v>
       </c>
       <c r="G158" s="5" t="n">
-        <v>0.18</v>
+        <v>0.26</v>
       </c>
       <c r="H158" t="n">
-        <v>51.22</v>
-      </c>
-      <c r="I158" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>38.18</v>
+      </c>
+      <c r="I158" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J158" s="2" t="n">
-        <v>3.027</v>
+        <v>2.558</v>
       </c>
       <c r="K158" s="2" t="n">
-        <v>2.856</v>
+        <v>2.685</v>
       </c>
       <c r="L158" t="inlineStr"/>
       <c r="M158" s="7" t="inlineStr"/>
@@ -7590,19 +7590,19 @@
         </is>
       </c>
       <c r="D159" s="2" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="E159" s="9" t="n">
-        <v>0.005500000000000001</v>
+        <v>0.905</v>
+      </c>
+      <c r="E159" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F159" s="4" t="n">
-        <v>557200</v>
+        <v>739200</v>
       </c>
       <c r="G159" s="5" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="H159" t="n">
-        <v>33.51</v>
+        <v>31.25</v>
       </c>
       <c r="I159" s="6" t="inlineStr">
         <is>
@@ -7610,7 +7610,7 @@
         </is>
       </c>
       <c r="J159" s="2" t="n">
-        <v>0.945</v>
+        <v>0.944</v>
       </c>
       <c r="K159" s="2" t="n">
         <v>1.002</v>
@@ -7626,39 +7626,39 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>5212</t>
+          <t>0271</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>PAVREIT</t>
+          <t>WELLS</t>
         </is>
       </c>
       <c r="D160" s="2" t="n">
-        <v>1.56</v>
+        <v>0.555</v>
       </c>
       <c r="E160" s="10" t="n">
-        <v>0</v>
+        <v>0.0091</v>
       </c>
       <c r="F160" s="4" t="n">
-        <v>547100</v>
+        <v>730000</v>
       </c>
       <c r="G160" s="5" t="n">
-        <v>0.16</v>
+        <v>0.64</v>
       </c>
       <c r="H160" t="n">
-        <v>47.18</v>
-      </c>
-      <c r="I160" s="8" t="inlineStr">
+        <v>42.07</v>
+      </c>
+      <c r="I160" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J160" s="2" t="n">
-        <v>1.568</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="K160" s="2" t="n">
-        <v>1.601</v>
+        <v>0.611</v>
       </c>
       <c r="L160" t="inlineStr"/>
       <c r="M160" s="7" t="inlineStr"/>
@@ -7671,28 +7671,28 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>SEG</t>
+          <t>DAYANG</t>
         </is>
       </c>
       <c r="D161" s="2" t="n">
-        <v>0.625</v>
+        <v>1.32</v>
       </c>
       <c r="E161" s="3" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0</v>
       </c>
       <c r="F161" s="4" t="n">
-        <v>538500</v>
+        <v>729700</v>
       </c>
       <c r="G161" s="5" t="n">
-        <v>0.47</v>
+        <v>0.37</v>
       </c>
       <c r="H161" t="n">
-        <v>34.58</v>
+        <v>27.74</v>
       </c>
       <c r="I161" s="6" t="inlineStr">
         <is>
@@ -7700,10 +7700,10 @@
         </is>
       </c>
       <c r="J161" s="2" t="n">
-        <v>0.631</v>
+        <v>1.404</v>
       </c>
       <c r="K161" s="2" t="n">
-        <v>0.631</v>
+        <v>1.466</v>
       </c>
       <c r="L161" t="inlineStr"/>
       <c r="M161" s="7" t="inlineStr"/>
@@ -7716,28 +7716,28 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>SUNREIT</t>
+          <t>DUFU</t>
         </is>
       </c>
       <c r="D162" s="2" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="E162" s="10" t="n">
-        <v>0</v>
+        <v>3.03</v>
+      </c>
+      <c r="E162" s="8" t="n">
+        <v>-0.013</v>
       </c>
       <c r="F162" s="4" t="n">
-        <v>515800</v>
+        <v>679900</v>
       </c>
       <c r="G162" s="5" t="n">
-        <v>0.16</v>
+        <v>0.22</v>
       </c>
       <c r="H162" t="n">
-        <v>44.02</v>
+        <v>52.14</v>
       </c>
       <c r="I162" s="6" t="inlineStr">
         <is>
@@ -7745,16 +7745,1006 @@
         </is>
       </c>
       <c r="J162" s="2" t="n">
-        <v>2.044</v>
+        <v>3.029</v>
       </c>
       <c r="K162" s="2" t="n">
-        <v>2.071</v>
+        <v>2.856</v>
       </c>
       <c r="L162" t="inlineStr"/>
       <c r="M162" s="7" t="inlineStr"/>
     </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>5299</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>IGBCR</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="E163" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F163" s="4" t="n">
+        <v>667100</v>
+      </c>
+      <c r="G163" s="5" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="H163" t="n">
+        <v>44.28</v>
+      </c>
+      <c r="I163" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J163" s="2" t="n">
+        <v>0.614</v>
+      </c>
+      <c r="K163" s="2" t="n">
+        <v>0.613</v>
+      </c>
+      <c r="L163" t="inlineStr"/>
+      <c r="M163" s="7" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>0097</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>VITROX</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E164" s="8" t="n">
+        <v>-0.0189</v>
+      </c>
+      <c r="F164" s="4" t="n">
+        <v>667000</v>
+      </c>
+      <c r="G164" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H164" t="n">
+        <v>53.02</v>
+      </c>
+      <c r="I164" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J164" s="2" t="n">
+        <v>10.407</v>
+      </c>
+      <c r="K164" s="2" t="n">
+        <v>9.755000000000001</v>
+      </c>
+      <c r="L164" t="inlineStr"/>
+      <c r="M164" s="7" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>5323</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>JPG</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="E165" s="10" t="n">
+        <v>0.0175</v>
+      </c>
+      <c r="F165" s="4" t="n">
+        <v>655700</v>
+      </c>
+      <c r="G165" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H165" t="n">
+        <v>41.01</v>
+      </c>
+      <c r="I165" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J165" s="2" t="n">
+        <v>1.776</v>
+      </c>
+      <c r="K165" s="2" t="n">
+        <v>1.888</v>
+      </c>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" s="7" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>7293</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>YINSON</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="E166" s="10" t="n">
+        <v>0.004699999999999999</v>
+      </c>
+      <c r="F166" s="4" t="n">
+        <v>651100</v>
+      </c>
+      <c r="G166" s="5" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H166" t="n">
+        <v>55.88</v>
+      </c>
+      <c r="I166" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J166" s="2" t="n">
+        <v>2.111</v>
+      </c>
+      <c r="K166" s="2" t="n">
+        <v>2.063</v>
+      </c>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" s="7" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>3417</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>E&amp;O</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="n">
+        <v>0.745</v>
+      </c>
+      <c r="E167" s="8" t="n">
+        <v>-0.0067</v>
+      </c>
+      <c r="F167" s="4" t="n">
+        <v>649700</v>
+      </c>
+      <c r="G167" s="5" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="H167" t="n">
+        <v>40.03</v>
+      </c>
+      <c r="I167" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J167" s="2" t="n">
+        <v>0.764</v>
+      </c>
+      <c r="K167" s="2" t="n">
+        <v>0.769</v>
+      </c>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" s="7" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>0296</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>HEGROUP</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="E168" s="8" t="n">
+        <v>-0.0098</v>
+      </c>
+      <c r="F168" s="4" t="n">
+        <v>645700</v>
+      </c>
+      <c r="G168" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H168" t="n">
+        <v>47.81</v>
+      </c>
+      <c r="I168" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J168" s="2" t="n">
+        <v>1.044</v>
+      </c>
+      <c r="K168" s="2" t="n">
+        <v>0.9419999999999999</v>
+      </c>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" s="7" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>0167</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>MCLEAN</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="E169" s="8" t="n">
+        <v>-0.0224</v>
+      </c>
+      <c r="F169" s="4" t="n">
+        <v>641300</v>
+      </c>
+      <c r="G169" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H169" t="n">
+        <v>34.29</v>
+      </c>
+      <c r="I169" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J169" s="2" t="n">
+        <v>0.724</v>
+      </c>
+      <c r="K169" s="2" t="n">
+        <v>0.744</v>
+      </c>
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" s="7" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>5258</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>BIMB</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E170" s="8" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="F170" s="4" t="n">
+        <v>639600</v>
+      </c>
+      <c r="G170" s="5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H170" t="n">
+        <v>34.83</v>
+      </c>
+      <c r="I170" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J170" s="2" t="n">
+        <v>2.037</v>
+      </c>
+      <c r="K170" s="2" t="n">
+        <v>2.081</v>
+      </c>
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" s="7" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>0359</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>HKB</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="E171" s="8" t="n">
+        <v>-0.0127</v>
+      </c>
+      <c r="F171" s="4" t="n">
+        <v>612300</v>
+      </c>
+      <c r="G171" s="5" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H171" t="n">
+        <v>67.27</v>
+      </c>
+      <c r="I171" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="K171" s="2" t="n">
+        <v>0.648</v>
+      </c>
+      <c r="L171" t="inlineStr"/>
+      <c r="M171" s="7" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>6139</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>TAKAFUL</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="E172" s="8" t="n">
+        <v>-0.0138</v>
+      </c>
+      <c r="F172" s="4" t="n">
+        <v>606500</v>
+      </c>
+      <c r="G172" s="5" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="H172" t="n">
+        <v>34.01</v>
+      </c>
+      <c r="I172" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J172" s="2" t="n">
+        <v>2.927</v>
+      </c>
+      <c r="K172" s="2" t="n">
+        <v>3.063</v>
+      </c>
+      <c r="L172" t="inlineStr"/>
+      <c r="M172" s="7" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>5236</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>MATRIX</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="E173" s="8" t="n">
+        <v>-0.0286</v>
+      </c>
+      <c r="F173" s="4" t="n">
+        <v>604400</v>
+      </c>
+      <c r="G173" s="5" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H173" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="I173" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="n">
+        <v>1.084</v>
+      </c>
+      <c r="K173" s="2" t="n">
+        <v>1.132</v>
+      </c>
+      <c r="L173" t="inlineStr"/>
+      <c r="M173" s="7" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>5212</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>PAVREIT</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="E174" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F174" s="4" t="n">
+        <v>575000</v>
+      </c>
+      <c r="G174" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H174" t="n">
+        <v>47.18</v>
+      </c>
+      <c r="I174" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J174" s="2" t="n">
+        <v>1.568</v>
+      </c>
+      <c r="K174" s="2" t="n">
+        <v>1.601</v>
+      </c>
+      <c r="L174" t="inlineStr"/>
+      <c r="M174" s="7" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>1015</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>AMBANK</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="E175" s="8" t="n">
+        <v>-0.0283</v>
+      </c>
+      <c r="F175" s="4" t="n">
+        <v>545900</v>
+      </c>
+      <c r="G175" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H175" t="n">
+        <v>35.84</v>
+      </c>
+      <c r="I175" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="n">
+        <v>6.389</v>
+      </c>
+      <c r="K175" s="2" t="n">
+        <v>6.754</v>
+      </c>
+      <c r="L175" t="inlineStr"/>
+      <c r="M175" s="7" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>5337</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>ECOSHOP</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="E176" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F176" s="4" t="n">
+        <v>545400</v>
+      </c>
+      <c r="G176" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H176" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="I176" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J176" s="2" t="n">
+        <v>1.448</v>
+      </c>
+      <c r="K176" s="2" t="n">
+        <v>1.464</v>
+      </c>
+      <c r="L176" t="inlineStr"/>
+      <c r="M176" s="7" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>0293</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>KJTS</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="E177" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F177" s="4" t="n">
+        <v>543600</v>
+      </c>
+      <c r="G177" s="5" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H177" t="n">
+        <v>31.12</v>
+      </c>
+      <c r="I177" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J177" s="2" t="n">
+        <v>0.951</v>
+      </c>
+      <c r="K177" s="2" t="n">
+        <v>1.023</v>
+      </c>
+      <c r="L177" t="inlineStr"/>
+      <c r="M177" s="7" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>5005</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>UNISEM</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="E178" s="8" t="n">
+        <v>-0.0284</v>
+      </c>
+      <c r="F178" s="4" t="n">
+        <v>540400</v>
+      </c>
+      <c r="G178" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H178" t="n">
+        <v>43.13</v>
+      </c>
+      <c r="I178" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J178" s="2" t="n">
+        <v>4.283</v>
+      </c>
+      <c r="K178" s="2" t="n">
+        <v>4.325</v>
+      </c>
+      <c r="L178" t="inlineStr"/>
+      <c r="M178" s="7" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>9792</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>SEG</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E179" s="8" t="n">
+        <v>-0.007900000000000001</v>
+      </c>
+      <c r="F179" s="4" t="n">
+        <v>538500</v>
+      </c>
+      <c r="G179" s="5" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="H179" t="n">
+        <v>34.58</v>
+      </c>
+      <c r="I179" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J179" s="2" t="n">
+        <v>0.631</v>
+      </c>
+      <c r="K179" s="2" t="n">
+        <v>0.631</v>
+      </c>
+      <c r="L179" t="inlineStr"/>
+      <c r="M179" s="7" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>5306</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>FFB</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="E180" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F180" s="4" t="n">
+        <v>534900</v>
+      </c>
+      <c r="G180" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H180" t="n">
+        <v>27.14</v>
+      </c>
+      <c r="I180" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J180" s="2" t="n">
+        <v>1.821</v>
+      </c>
+      <c r="K180" s="2" t="n">
+        <v>1.962</v>
+      </c>
+      <c r="L180" t="inlineStr"/>
+      <c r="M180" s="7" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>5288</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>SIMEPROP</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="E181" s="8" t="n">
+        <v>-0.007800000000000001</v>
+      </c>
+      <c r="F181" s="4" t="n">
+        <v>531300</v>
+      </c>
+      <c r="G181" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H181" t="n">
+        <v>51.93</v>
+      </c>
+      <c r="I181" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J181" s="2" t="n">
+        <v>1.259</v>
+      </c>
+      <c r="K181" s="2" t="n">
+        <v>1.277</v>
+      </c>
+      <c r="L181" t="inlineStr"/>
+      <c r="M181" s="7" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>0376</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>IAB</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="E182" s="8" t="n">
+        <v>-0.028</v>
+      </c>
+      <c r="F182" s="4" t="n">
+        <v>525500</v>
+      </c>
+      <c r="G182" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H182" t="n">
+        <v>33.46</v>
+      </c>
+      <c r="I182" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J182" s="2" t="n">
+        <v>1.196</v>
+      </c>
+      <c r="K182" s="2" t="n">
+        <v>1.291</v>
+      </c>
+      <c r="L182" t="inlineStr"/>
+      <c r="M182" s="7" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>4758</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>ANCOMNY</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="E183" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F183" s="4" t="n">
+        <v>516100</v>
+      </c>
+      <c r="G183" s="5" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H183" t="n">
+        <v>33.01</v>
+      </c>
+      <c r="I183" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J183" s="2" t="n">
+        <v>0.844</v>
+      </c>
+      <c r="K183" s="2" t="n">
+        <v>0.861</v>
+      </c>
+      <c r="L183" t="inlineStr"/>
+      <c r="M183" s="7" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>5246</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>WPRTS</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="E184" s="8" t="n">
+        <v>-0.0074</v>
+      </c>
+      <c r="F184" s="4" t="n">
+        <v>513400</v>
+      </c>
+      <c r="G184" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H184" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="I184" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J184" s="2" t="n">
+        <v>6.752</v>
+      </c>
+      <c r="K184" s="2" t="n">
+        <v>6.826</v>
+      </c>
+      <c r="L184" t="inlineStr"/>
+      <c r="M184" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M162"/>
+  <autoFilter ref="A1:M184"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-19/bursa-report-2026-10-19.xlsx
+++ b/docs/downloads/2026-10-19/bursa-report-2026-10-19.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-19" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-19'!$A$1:$M$184</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-19'!$A$1:$M$188</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -35,13 +35,13 @@
       <color rgb="00FFFFFF"/>
     </font>
     <font>
-      <color rgb="00898781"/>
-    </font>
-    <font>
       <color rgb="00D03B3B"/>
     </font>
     <font>
       <color rgb="000CA30C"/>
+    </font>
+    <font>
+      <color rgb="00898781"/>
     </font>
   </fonts>
   <fills count="3">
@@ -78,12 +78,12 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M184"/>
+  <dimension ref="A1:M188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -552,19 +552,19 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.055</v>
+        <v>0.05</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0</v>
+        <v>-0.09089999999999999</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>62710900</v>
+        <v>65509800</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="H2" t="n">
-        <v>23.16</v>
+        <v>22.63</v>
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
@@ -597,19 +597,19 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="E3" s="8" t="n">
-        <v>-0.0588</v>
+        <v>0.325</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>-0.0441</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>47628600</v>
+        <v>51037200</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.61</v>
+        <v>0.66</v>
       </c>
       <c r="H3" t="n">
-        <v>59.82</v>
+        <v>61.81</v>
       </c>
       <c r="I3" s="6" t="inlineStr">
         <is>
@@ -642,21 +642,21 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.9</v>
+        <v>0.895</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0</v>
+        <v>-0.005600000000000001</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>42961200</v>
+        <v>44623200</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.63</v>
+        <v>0.66</v>
       </c>
       <c r="H4" t="n">
-        <v>66.28</v>
-      </c>
-      <c r="I4" s="9" t="inlineStr">
+        <v>65.20999999999999</v>
+      </c>
+      <c r="I4" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -687,19 +687,19 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.135</v>
-      </c>
-      <c r="E5" s="8" t="n">
-        <v>-0.06900000000000001</v>
+        <v>0.13</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>-0.1034</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>27879200</v>
+        <v>29378500</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.41</v>
+        <v>0.43</v>
       </c>
       <c r="H5" t="n">
-        <v>40.3</v>
+        <v>38.6</v>
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
@@ -723,39 +723,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="E6" s="10" t="n">
-        <v>0.0299</v>
+        <v>0.44</v>
+      </c>
+      <c r="E6" s="9" t="n">
+        <v>0.0476</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>21902100</v>
+        <v>28448600</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.87</v>
+        <v>0.82</v>
       </c>
       <c r="H6" t="n">
-        <v>78.11</v>
-      </c>
-      <c r="I6" s="9" t="inlineStr">
+        <v>77.98</v>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.618</v>
+        <v>0.384</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.531</v>
+        <v>0.278</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="7" t="inlineStr"/>
@@ -768,39 +768,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>0095</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="E7" s="3" t="n">
+        <v>0.155</v>
+      </c>
+      <c r="E7" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>17494600</v>
+        <v>24094800</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="H7" t="n">
-        <v>74.48999999999999</v>
-      </c>
-      <c r="I7" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.61</v>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.382</v>
+        <v>0.155</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.277</v>
+        <v>0.156</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="7" t="inlineStr"/>
@@ -813,39 +813,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>4.69</v>
-      </c>
-      <c r="E8" s="8" t="n">
-        <v>-0.029</v>
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>0.0299</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>15886300</v>
+        <v>23496400</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="H8" t="n">
-        <v>45.45</v>
-      </c>
-      <c r="I8" s="9" t="inlineStr">
+        <v>78.11</v>
+      </c>
+      <c r="I8" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>4.726</v>
+        <v>0.618</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>4.847</v>
+        <v>0.531</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="7" t="inlineStr"/>
@@ -869,14 +869,14 @@
       <c r="D9" s="2" t="n">
         <v>0.045</v>
       </c>
-      <c r="E9" s="8" t="n">
+      <c r="E9" s="3" t="n">
         <v>-0.1</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>14934300</v>
+        <v>20034300</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>13.41</v>
+        <v>17.98</v>
       </c>
       <c r="H9" t="n">
         <v>29.14</v>
@@ -903,39 +903,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0.31</v>
+        <v>4.7</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0</v>
+        <v>-0.0269</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>12273000</v>
+        <v>17805100</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.63</v>
+        <v>0.95</v>
       </c>
       <c r="H10" t="n">
-        <v>54.55</v>
-      </c>
-      <c r="I10" s="9" t="inlineStr">
+        <v>46.13</v>
+      </c>
+      <c r="I10" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.309</v>
+        <v>4.727</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0.3</v>
+        <v>4.847</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="7" t="inlineStr"/>
@@ -948,39 +948,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0.285</v>
-      </c>
-      <c r="E11" s="8" t="n">
-        <v>-0.0806</v>
+        <v>0.31</v>
+      </c>
+      <c r="E11" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>12201200</v>
+        <v>14261000</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>1.4</v>
+        <v>0.73</v>
       </c>
       <c r="H11" t="n">
-        <v>45.31</v>
-      </c>
-      <c r="I11" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.55</v>
+      </c>
+      <c r="I11" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.299</v>
+        <v>0.309</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0.28</v>
+        <v>0.3</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="7" t="inlineStr"/>
@@ -1002,21 +1002,21 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="E12" s="8" t="n">
-        <v>-0.0112</v>
+        <v>0.435</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>-0.0225</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>11959500</v>
+        <v>13715500</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.59</v>
+        <v>0.68</v>
       </c>
       <c r="H12" t="n">
-        <v>57.56</v>
-      </c>
-      <c r="I12" s="9" t="inlineStr">
+        <v>56.12</v>
+      </c>
+      <c r="I12" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -1038,39 +1038,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0095</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MAG</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="E13" s="3" t="n">
+        <v>0.865</v>
+      </c>
+      <c r="E13" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>11914800</v>
+        <v>12626700</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.34</v>
+        <v>0.64</v>
       </c>
       <c r="H13" t="n">
-        <v>48.61</v>
-      </c>
-      <c r="I13" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>45.57</v>
+      </c>
+      <c r="I13" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.155</v>
+        <v>0.868</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0.156</v>
+        <v>0.869</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="7" t="inlineStr"/>
@@ -1083,28 +1083,28 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="E14" s="8" t="n">
-        <v>-0.0222</v>
+        <v>0.285</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>-0.0806</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>9870500</v>
+        <v>12285600</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.27</v>
+        <v>1.41</v>
       </c>
       <c r="H14" t="n">
-        <v>37.57</v>
+        <v>45.31</v>
       </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
@@ -1112,10 +1112,10 @@
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.478</v>
+        <v>0.299</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0.482</v>
+        <v>0.28</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="7" t="inlineStr"/>
@@ -1128,39 +1128,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>4251</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>IBHD</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0.215</v>
-      </c>
-      <c r="E15" s="8" t="n">
-        <v>-0.0227</v>
+        <v>0.44</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>-0.0222</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>9440100</v>
+        <v>12201100</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>32.41</v>
+        <v>0.34</v>
       </c>
       <c r="H15" t="n">
-        <v>53.06</v>
-      </c>
-      <c r="I15" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.57</v>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.212</v>
+        <v>0.478</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0.217</v>
+        <v>0.482</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="7" t="inlineStr"/>
@@ -1173,39 +1173,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>4251</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>IBHD</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0.865</v>
+        <v>0.215</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0</v>
+        <v>-0.0227</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>8277900</v>
+        <v>9440100</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.42</v>
+        <v>32.41</v>
       </c>
       <c r="H16" t="n">
-        <v>45.57</v>
-      </c>
-      <c r="I16" s="9" t="inlineStr">
+        <v>53.06</v>
+      </c>
+      <c r="I16" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.868</v>
+        <v>0.212</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0.869</v>
+        <v>0.217</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="7" t="inlineStr"/>
@@ -1218,39 +1218,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0081</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>REKATECH</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="E17" s="8" t="n">
-        <v>-0.1111</v>
+        <v>2</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>-0.009899999999999999</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>7943500</v>
+        <v>9138100</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>21.48</v>
+        <v>0.31</v>
       </c>
       <c r="H17" t="n">
-        <v>70.23999999999999</v>
-      </c>
-      <c r="I17" s="9" t="inlineStr">
+        <v>57.95</v>
+      </c>
+      <c r="I17" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.026</v>
+        <v>1.928</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0.024</v>
+        <v>1.74</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="7" t="inlineStr"/>
@@ -1263,39 +1263,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="E18" s="8" t="n">
-        <v>-0.0198</v>
+        <v>0.775</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>-0.0064</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>7713600</v>
+        <v>8985000</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.26</v>
+        <v>0.59</v>
       </c>
       <c r="H18" t="n">
-        <v>56.58</v>
-      </c>
-      <c r="I18" s="9" t="inlineStr">
+        <v>49.91</v>
+      </c>
+      <c r="I18" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>1.926</v>
+        <v>0.775</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>1.74</v>
+        <v>0.776</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="7" t="inlineStr"/>
@@ -1317,19 +1317,19 @@
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="E19" s="8" t="n">
-        <v>-0.03759999999999999</v>
+        <v>2.58</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>-0.0301</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>7234700</v>
+        <v>8073700</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="H19" t="n">
-        <v>46.31</v>
+        <v>47.37</v>
       </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>2.641</v>
+        <v>2.643</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>2.553</v>
+        <v>2.554</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="7" t="inlineStr"/>
@@ -1353,39 +1353,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E20" s="8" t="n">
-        <v>-0.0064</v>
+        <v>0.98</v>
+      </c>
+      <c r="E20" s="9" t="n">
+        <v>0.0208</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>7034000</v>
+        <v>7986300</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.46</v>
+        <v>1.38</v>
       </c>
       <c r="H20" t="n">
-        <v>49.91</v>
-      </c>
-      <c r="I20" s="9" t="inlineStr">
+        <v>68.93000000000001</v>
+      </c>
+      <c r="I20" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.775</v>
+        <v>0.926</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0.776</v>
+        <v>0.877</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="7" t="inlineStr"/>
@@ -1398,33 +1398,40 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>0081</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SLG</t>
+          <t>REKATECH</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>0.25</v>
+        <v>0.04</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>0</v>
+        <v>-0.1111</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>6915700</v>
+        <v>7943500</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="I21" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="n"/>
-      <c r="K21" s="2" t="n"/>
+        <v>21.48</v>
+      </c>
+      <c r="H21" t="n">
+        <v>70.23999999999999</v>
+      </c>
+      <c r="I21" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="K21" s="2" t="n">
+        <v>0.024</v>
+      </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="7" t="inlineStr"/>
     </row>
@@ -1436,39 +1443,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="E22" s="8" t="n">
-        <v>-0.0042</v>
+        <v>0.62</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>-0.008</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>6899700</v>
+        <v>7850300</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.27</v>
+        <v>0.72</v>
       </c>
       <c r="H22" t="n">
-        <v>44.85</v>
-      </c>
-      <c r="I22" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.27</v>
+      </c>
+      <c r="I22" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>4.897</v>
+        <v>0.617</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>4.728</v>
+        <v>0.615</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="7" t="inlineStr"/>
@@ -1481,33 +1488,40 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0477</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ECOSYS</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>0.755</v>
-      </c>
-      <c r="E23" s="8" t="n">
-        <v>-0.0382</v>
+        <v>4.78</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>-0.0042</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>6716300</v>
+        <v>7470900</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="I23" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="n"/>
-      <c r="K23" s="2" t="n"/>
+        <v>0.29</v>
+      </c>
+      <c r="H23" t="n">
+        <v>44.85</v>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="n">
+        <v>4.897</v>
+      </c>
+      <c r="K23" s="2" t="n">
+        <v>4.728</v>
+      </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="7" t="inlineStr"/>
     </row>
@@ -1519,40 +1533,33 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>0477</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>ECOSYS</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>0.82</v>
+        <v>0.76</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>0</v>
+        <v>-0.0318</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>6697200</v>
+        <v>7465000</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="H24" t="n">
-        <v>57.16</v>
-      </c>
-      <c r="I24" s="9" t="inlineStr">
+        <v>0.1</v>
+      </c>
+      <c r="I24" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J24" s="2" t="n">
-        <v>0.8139999999999999</v>
-      </c>
-      <c r="K24" s="2" t="n">
-        <v>0.8110000000000001</v>
-      </c>
+      <c r="J24" s="2" t="n"/>
+      <c r="K24" s="2" t="n"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="7" t="inlineStr"/>
     </row>
@@ -1573,19 +1580,19 @@
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="E25" s="8" t="n">
-        <v>-0.0198</v>
+        <v>1</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>-0.009899999999999999</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>6651400</v>
+        <v>7079000</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.84</v>
+        <v>0.89</v>
       </c>
       <c r="H25" t="n">
-        <v>43.57</v>
+        <v>44.77</v>
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
@@ -1593,7 +1600,7 @@
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>1.049</v>
+        <v>1.05</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>0.959</v>
@@ -1609,40 +1616,33 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>3891</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MUIIND</t>
+          <t>SLG</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="E26" s="3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E26" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>6510400</v>
+        <v>6915900</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="H26" t="n">
-        <v>46.69</v>
+        <v>0.28</v>
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J26" s="2" t="n">
-        <v>0.041</v>
-      </c>
-      <c r="K26" s="2" t="n">
-        <v>0.042</v>
-      </c>
+      <c r="J26" s="2" t="n"/>
+      <c r="K26" s="2" t="n"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="7" t="inlineStr"/>
     </row>
@@ -1654,39 +1654,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>0</v>
+        <v>6.67</v>
+      </c>
+      <c r="E27" s="9" t="n">
+        <v>0.0262</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>6500600</v>
+        <v>6700300</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.6</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H27" t="n">
-        <v>56.82</v>
-      </c>
-      <c r="I27" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>28.27</v>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.617</v>
+        <v>7.208</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0.615</v>
+        <v>7.606</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="7" t="inlineStr"/>
@@ -1699,39 +1699,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>0.405</v>
-      </c>
-      <c r="E28" s="3" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="E28" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>6303700</v>
+        <v>6697200</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.51</v>
+        <v>0.41</v>
       </c>
       <c r="H28" t="n">
-        <v>55.08</v>
-      </c>
-      <c r="I28" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.16</v>
+      </c>
+      <c r="I28" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.391</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0.378</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="7" t="inlineStr"/>
@@ -1744,28 +1744,28 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>6.67</v>
+        <v>0.405</v>
       </c>
       <c r="E29" s="10" t="n">
-        <v>0.0262</v>
+        <v>0</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>6143200</v>
+        <v>6621700</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.63</v>
+        <v>0.53</v>
       </c>
       <c r="H29" t="n">
-        <v>28.27</v>
+        <v>55.08</v>
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
@@ -1773,10 +1773,10 @@
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>7.208</v>
+        <v>0.391</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>7.606</v>
+        <v>0.378</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="7" t="inlineStr"/>
@@ -1789,28 +1789,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>3891</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>MUIIND</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E30" s="3" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E30" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>6072500</v>
+        <v>6610400</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>1.95</v>
+        <v>3.9</v>
       </c>
       <c r="H30" t="n">
-        <v>49.08</v>
+        <v>46.69</v>
       </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
@@ -1818,10 +1818,10 @@
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.295</v>
+        <v>0.041</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0.295</v>
+        <v>0.042</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="7" t="inlineStr"/>
@@ -1834,28 +1834,28 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>5156</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>XDL</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>0.005</v>
+        <v>1.42</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0.0207</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>5950100</v>
+        <v>6587900</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>2.42</v>
+        <v>0.59</v>
       </c>
       <c r="H31" t="n">
-        <v>44.81</v>
+        <v>21.41</v>
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
@@ -1863,10 +1863,10 @@
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.007</v>
+        <v>1.691</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0.007</v>
+        <v>1.944</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="7" t="inlineStr"/>
@@ -1879,28 +1879,28 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="E32" s="8" t="n">
-        <v>-0.0207</v>
+        <v>0.295</v>
+      </c>
+      <c r="E32" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>5807800</v>
+        <v>6072500</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.52</v>
+        <v>1.95</v>
       </c>
       <c r="H32" t="n">
-        <v>21.41</v>
+        <v>49.08</v>
       </c>
       <c r="I32" s="6" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>1.691</v>
+        <v>0.295</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>1.944</v>
+        <v>0.295</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="7" t="inlineStr"/>
@@ -1924,28 +1924,28 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="E33" s="8" t="n">
-        <v>-0.0182</v>
+        <v>0.545</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>-0.018</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>5682000</v>
+        <v>5961600</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.59</v>
+        <v>0.29</v>
       </c>
       <c r="H33" t="n">
-        <v>51.15</v>
+        <v>46.22</v>
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
@@ -1953,10 +1953,10 @@
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>1.077</v>
+        <v>0.573</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>1.045</v>
+        <v>0.541</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="7" t="inlineStr"/>
@@ -1969,28 +1969,28 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>5156</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>XDL</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="E34" s="8" t="n">
-        <v>-0.0049</v>
+        <v>0.005</v>
+      </c>
+      <c r="E34" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>5371800</v>
+        <v>5950100</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.41</v>
+        <v>2.42</v>
       </c>
       <c r="H34" t="n">
-        <v>33.2</v>
+        <v>44.81</v>
       </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
@@ -1998,10 +1998,10 @@
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>2.148</v>
+        <v>0.007</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>2.234</v>
+        <v>0.007</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="7" t="inlineStr"/>
@@ -2014,28 +2014,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>0.435</v>
-      </c>
-      <c r="E35" s="10" t="n">
-        <v>0.0357</v>
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>-0.0504</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>5359700</v>
+        <v>5918900</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.79</v>
+        <v>0.66</v>
       </c>
       <c r="H35" t="n">
-        <v>53.65</v>
+        <v>35.76</v>
       </c>
       <c r="I35" s="6" t="inlineStr">
         <is>
@@ -2043,10 +2043,10 @@
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.425</v>
+        <v>0.647</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0.416</v>
+        <v>0.62</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="7" t="inlineStr"/>
@@ -2059,39 +2059,39 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="E36" s="10" t="n">
-        <v>0.0208</v>
+        <v>0.435</v>
+      </c>
+      <c r="E36" s="9" t="n">
+        <v>0.0357</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>5348300</v>
+        <v>5905100</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="H36" t="n">
-        <v>68.93000000000001</v>
-      </c>
-      <c r="I36" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.65</v>
+      </c>
+      <c r="I36" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.926</v>
+        <v>0.425</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0.877</v>
+        <v>0.416</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="7" t="inlineStr"/>
@@ -2104,39 +2104,39 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="E37" s="8" t="n">
-        <v>-0.0325</v>
+        <v>1.08</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>-0.0182</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>5221300</v>
+        <v>5707000</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.59</v>
       </c>
       <c r="H37" t="n">
-        <v>38.78</v>
-      </c>
-      <c r="I37" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.15</v>
+      </c>
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>1.235</v>
+        <v>1.077</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>1.323</v>
+        <v>1.045</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="7" t="inlineStr"/>
@@ -2149,39 +2149,39 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="E38" s="8" t="n">
-        <v>-0.027</v>
+        <v>1.19</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>-0.0325</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>5209000</v>
+        <v>5607700</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.25</v>
+        <v>0.74</v>
       </c>
       <c r="H38" t="n">
-        <v>45.4</v>
-      </c>
-      <c r="I38" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>38.78</v>
+      </c>
+      <c r="I38" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.572</v>
+        <v>1.235</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0.541</v>
+        <v>1.323</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="7" t="inlineStr"/>
@@ -2194,33 +2194,40 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0472</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ECOGRP</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="E39" s="8" t="n">
-        <v>-0.1111</v>
+        <v>2.02</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>-0.0049</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>5102500</v>
+        <v>5527900</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.42</v>
+      </c>
+      <c r="H39" t="n">
+        <v>33.2</v>
       </c>
       <c r="I39" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J39" s="2" t="n"/>
-      <c r="K39" s="2" t="n"/>
+      <c r="J39" s="2" t="n">
+        <v>2.148</v>
+      </c>
+      <c r="K39" s="2" t="n">
+        <v>2.234</v>
+      </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="7" t="inlineStr"/>
     </row>
@@ -2232,39 +2239,39 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>6203</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>KHEESAN</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E40" s="10" t="n">
-        <v>0.0526</v>
+        <v>9.869999999999999</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>-0.012</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>4951800</v>
+        <v>5489100</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>2.89</v>
+        <v>0.41</v>
       </c>
       <c r="H40" t="n">
-        <v>58.17</v>
-      </c>
-      <c r="I40" s="9" t="inlineStr">
+        <v>40.09</v>
+      </c>
+      <c r="I40" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.09</v>
+        <v>9.997999999999999</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0.095</v>
+        <v>10.147</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="7" t="inlineStr"/>
@@ -2277,40 +2284,33 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>0472</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>ECOGRP</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="E41" s="10" t="n">
-        <v>0.0484</v>
+        <v>0.12</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>-0.1111</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>4928500</v>
+        <v>5484300</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="H41" t="n">
-        <v>60.08</v>
+        <v>0.08</v>
       </c>
       <c r="I41" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J41" s="2" t="n">
-        <v>3.658</v>
-      </c>
-      <c r="K41" s="2" t="n">
-        <v>3.009</v>
-      </c>
+      <c r="J41" s="2" t="n"/>
+      <c r="K41" s="2" t="n"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="7" t="inlineStr"/>
     </row>
@@ -2322,39 +2322,39 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>9.869999999999999</v>
-      </c>
-      <c r="E42" s="8" t="n">
-        <v>-0.012</v>
+        <v>3.9</v>
+      </c>
+      <c r="E42" s="9" t="n">
+        <v>0.0484</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>4900900</v>
+        <v>5202300</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.37</v>
+        <v>0.55</v>
       </c>
       <c r="H42" t="n">
-        <v>40.09</v>
-      </c>
-      <c r="I42" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>60.08</v>
+      </c>
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>9.997999999999999</v>
+        <v>3.658</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>10.147</v>
+        <v>3.009</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="7" t="inlineStr"/>
@@ -2367,28 +2367,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>6769</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>JKGLAND</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>0.1</v>
+        <v>1.63</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>0</v>
+        <v>-0.024</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>4861300</v>
+        <v>5037700</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>19.59</v>
+        <v>1.05</v>
       </c>
       <c r="H43" t="n">
-        <v>39.48</v>
+        <v>35.32</v>
       </c>
       <c r="I43" s="6" t="inlineStr">
         <is>
@@ -2396,10 +2396,10 @@
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.103</v>
+        <v>1.724</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0.107</v>
+        <v>1.767</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="7" t="inlineStr"/>
@@ -2412,39 +2412,39 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="E44" s="3" t="n">
-        <v>0</v>
+        <v>2.34</v>
+      </c>
+      <c r="E44" s="9" t="n">
+        <v>0.0218</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>4813700</v>
+        <v>5036800</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.78</v>
+        <v>1.42</v>
       </c>
       <c r="H44" t="n">
-        <v>61.53</v>
-      </c>
-      <c r="I44" s="9" t="inlineStr">
+        <v>60.87</v>
+      </c>
+      <c r="I44" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>1.197</v>
+        <v>2.226</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>1.188</v>
+        <v>2.167</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="7" t="inlineStr"/>
@@ -2457,39 +2457,39 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="E45" s="8" t="n">
-        <v>-0.0299</v>
+        <v>1.27</v>
+      </c>
+      <c r="E45" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>4764500</v>
+        <v>5032400</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>1</v>
+        <v>0.82</v>
       </c>
       <c r="H45" t="n">
-        <v>34.42</v>
-      </c>
-      <c r="I45" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.53</v>
+      </c>
+      <c r="I45" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>1.723</v>
+        <v>1.197</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>1.767</v>
+        <v>1.188</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="7" t="inlineStr"/>
@@ -2502,39 +2502,39 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>6203</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>KHEESAN</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="E46" s="10" t="n">
-        <v>0.0218</v>
+        <v>0.1</v>
+      </c>
+      <c r="E46" s="9" t="n">
+        <v>0.0526</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>4755800</v>
+        <v>4951800</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>1.34</v>
+        <v>2.89</v>
       </c>
       <c r="H46" t="n">
-        <v>60.87</v>
-      </c>
-      <c r="I46" s="9" t="inlineStr">
+        <v>58.17</v>
+      </c>
+      <c r="I46" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>2.226</v>
+        <v>0.09</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>2.167</v>
+        <v>0.095</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="7" t="inlineStr"/>
@@ -2547,39 +2547,39 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0280</t>
+          <t>6769</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>MBN</t>
+          <t>JKGLAND</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="E47" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E47" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>4710200</v>
+        <v>4861300</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>1.95</v>
+        <v>19.59</v>
       </c>
       <c r="H47" t="n">
-        <v>56.48</v>
-      </c>
-      <c r="I47" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.48</v>
+      </c>
+      <c r="I47" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.155</v>
+        <v>0.103</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0.154</v>
+        <v>0.107</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="7" t="inlineStr"/>
@@ -2592,39 +2592,39 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="E48" s="3" t="n">
-        <v>0</v>
+        <v>2.68</v>
+      </c>
+      <c r="E48" s="9" t="n">
+        <v>0.019</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>4587200</v>
+        <v>4752900</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.62</v>
+        <v>0.38</v>
       </c>
       <c r="H48" t="n">
-        <v>55.92</v>
-      </c>
-      <c r="I48" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.03</v>
+      </c>
+      <c r="I48" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.371</v>
+        <v>2.761</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0.369</v>
+        <v>2.738</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="7" t="inlineStr"/>
@@ -2637,39 +2637,39 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>0280</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>MBN</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="E49" s="8" t="n">
-        <v>-0.0353</v>
+        <v>0.155</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>-0.0313</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>4521800</v>
+        <v>4739100</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.58</v>
+        <v>1.96</v>
       </c>
       <c r="H49" t="n">
-        <v>22.61</v>
-      </c>
-      <c r="I49" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.98</v>
+      </c>
+      <c r="I49" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.526</v>
+        <v>0.155</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0.614</v>
+        <v>0.154</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="7" t="inlineStr"/>
@@ -2682,39 +2682,39 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>0.335</v>
-      </c>
-      <c r="E50" s="8" t="n">
-        <v>-0.0147</v>
+        <v>0.375</v>
+      </c>
+      <c r="E50" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>4456700</v>
+        <v>4660000</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.47</v>
+        <v>0.63</v>
       </c>
       <c r="H50" t="n">
-        <v>47.31</v>
-      </c>
-      <c r="I50" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.92</v>
+      </c>
+      <c r="I50" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.346</v>
+        <v>0.371</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0.334</v>
+        <v>0.369</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="7" t="inlineStr"/>
@@ -2727,28 +2727,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>0.555</v>
-      </c>
-      <c r="E51" s="8" t="n">
-        <v>-0.0672</v>
+        <v>0.255</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>-0.0192</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>4433800</v>
+        <v>4652200</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.49</v>
+        <v>0.55</v>
       </c>
       <c r="H51" t="n">
-        <v>34.6</v>
+        <v>27.74</v>
       </c>
       <c r="I51" s="6" t="inlineStr">
         <is>
@@ -2756,10 +2756,10 @@
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.646</v>
+        <v>0.276</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0.619</v>
+        <v>0.301</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="7" t="inlineStr"/>
@@ -2772,28 +2772,28 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="E52" s="10" t="n">
-        <v>0.0114</v>
+        <v>0.41</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>-0.0353</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>4339900</v>
+        <v>4621600</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.34</v>
+        <v>0.59</v>
       </c>
       <c r="H52" t="n">
-        <v>42.31</v>
+        <v>22.61</v>
       </c>
       <c r="I52" s="6" t="inlineStr">
         <is>
@@ -2801,10 +2801,10 @@
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>2.759</v>
+        <v>0.526</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>2.738</v>
+        <v>0.614</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="7" t="inlineStr"/>
@@ -2817,28 +2817,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>0.525</v>
-      </c>
-      <c r="E53" s="8" t="n">
-        <v>-0.0187</v>
+        <v>0.335</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>-0.0147</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>4228800</v>
+        <v>4555500</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>1.71</v>
+        <v>0.48</v>
       </c>
       <c r="H53" t="n">
-        <v>36.53</v>
+        <v>47.31</v>
       </c>
       <c r="I53" s="6" t="inlineStr">
         <is>
@@ -2846,10 +2846,10 @@
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.544</v>
+        <v>0.346</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0.572</v>
+        <v>0.334</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="7" t="inlineStr"/>
@@ -2862,28 +2862,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>5.21</v>
-      </c>
-      <c r="E54" s="10" t="n">
-        <v>0.0117</v>
+        <v>7.15</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>-0.0069</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>4170000</v>
+        <v>4481700</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="H54" t="n">
-        <v>38.17</v>
+        <v>32.9</v>
       </c>
       <c r="I54" s="6" t="inlineStr">
         <is>
@@ -2891,10 +2891,10 @@
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>5.504</v>
+        <v>7.505</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>5.45</v>
+        <v>7.684</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="7" t="inlineStr"/>
@@ -2907,28 +2907,28 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>0175</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>HHRG</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>7.15</v>
-      </c>
-      <c r="E55" s="8" t="n">
-        <v>-0.0069</v>
+        <v>0.12</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>-0.04</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>4120800</v>
+        <v>4452900</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.25</v>
+        <v>0.19</v>
       </c>
       <c r="H55" t="n">
-        <v>32.9</v>
+        <v>34.67</v>
       </c>
       <c r="I55" s="6" t="inlineStr">
         <is>
@@ -2936,10 +2936,10 @@
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>7.505</v>
+        <v>0.143</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>7.684</v>
+        <v>0.148</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="7" t="inlineStr"/>
@@ -2952,39 +2952,39 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="E56" s="8" t="n">
-        <v>-0.006</v>
+        <v>0.455</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>-0.0215</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>4012200</v>
+        <v>4353600</v>
       </c>
       <c r="G56" s="5" t="n">
         <v>0.59</v>
       </c>
       <c r="H56" t="n">
-        <v>52.91</v>
-      </c>
-      <c r="I56" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>28.78</v>
+      </c>
+      <c r="I56" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>1.628</v>
+        <v>0.498</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>1.695</v>
+        <v>0.556</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="7" t="inlineStr"/>
@@ -2997,28 +2997,28 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0175</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>HHRG</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="E57" s="8" t="n">
-        <v>-0.04</v>
+        <v>5.21</v>
+      </c>
+      <c r="E57" s="9" t="n">
+        <v>0.0117</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>3984900</v>
+        <v>4281700</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.17</v>
+        <v>0.3</v>
       </c>
       <c r="H57" t="n">
-        <v>34.67</v>
+        <v>38.17</v>
       </c>
       <c r="I57" s="6" t="inlineStr">
         <is>
@@ -3026,10 +3026,10 @@
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.143</v>
+        <v>5.504</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0.148</v>
+        <v>5.45</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="7" t="inlineStr"/>
@@ -3042,28 +3042,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>0.455</v>
-      </c>
-      <c r="E58" s="8" t="n">
-        <v>-0.0215</v>
+        <v>0.52</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>-0.028</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>3964500</v>
+        <v>4268100</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.53</v>
+        <v>1.73</v>
       </c>
       <c r="H58" t="n">
-        <v>28.78</v>
+        <v>34.76</v>
       </c>
       <c r="I58" s="6" t="inlineStr">
         <is>
@@ -3071,10 +3071,10 @@
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.498</v>
+        <v>0.543</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0.556</v>
+        <v>0.572</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="7" t="inlineStr"/>
@@ -3087,39 +3087,39 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="E59" s="8" t="n">
-        <v>-0.011</v>
+        <v>2.09</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>-0.0048</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>3945300</v>
+        <v>4256300</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.16</v>
+        <v>0.25</v>
       </c>
       <c r="H59" t="n">
-        <v>27.11</v>
-      </c>
-      <c r="I59" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.26</v>
+      </c>
+      <c r="I59" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.507</v>
+        <v>2.108</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0.677</v>
+        <v>2.101</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="7" t="inlineStr"/>
@@ -3132,39 +3132,39 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="E60" s="8" t="n">
-        <v>-0.05139999999999999</v>
+        <v>1.65</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>-0.012</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>3769700</v>
+        <v>4253300</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>1.23</v>
+        <v>0.63</v>
       </c>
       <c r="H60" t="n">
-        <v>27.43</v>
-      </c>
-      <c r="I60" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.49</v>
+      </c>
+      <c r="I60" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.896</v>
+        <v>1.627</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>0.953</v>
+        <v>1.695</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="7" t="inlineStr"/>
@@ -3177,39 +3177,39 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>0.985</v>
-      </c>
-      <c r="E61" s="8" t="n">
-        <v>-0.08800000000000001</v>
+        <v>0.52</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>-0.0095</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>3680600</v>
+        <v>4095900</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.93</v>
+        <v>0.34</v>
       </c>
       <c r="H61" t="n">
-        <v>64.31999999999999</v>
-      </c>
-      <c r="I61" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.4</v>
+      </c>
+      <c r="I61" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.84</v>
+        <v>0.52</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0.572</v>
+        <v>0.461</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="7" t="inlineStr"/>
@@ -3222,28 +3222,28 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="E62" s="8" t="n">
-        <v>-0.0286</v>
+        <v>0.45</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>-0.011</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>3617000</v>
+        <v>4008300</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.3</v>
+        <v>0.16</v>
       </c>
       <c r="H62" t="n">
-        <v>50.37</v>
+        <v>27.11</v>
       </c>
       <c r="I62" s="6" t="inlineStr">
         <is>
@@ -3251,10 +3251,10 @@
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.519</v>
+        <v>0.507</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>0.461</v>
+        <v>0.677</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="7" t="inlineStr"/>
@@ -3267,28 +3267,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>MRCB</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>0.255</v>
-      </c>
-      <c r="E63" s="8" t="n">
-        <v>-0.0192</v>
+        <v>0.835</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>-0.0457</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>3550500</v>
+        <v>3827300</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.42</v>
+        <v>1.25</v>
       </c>
       <c r="H63" t="n">
-        <v>27.74</v>
+        <v>28.22</v>
       </c>
       <c r="I63" s="6" t="inlineStr">
         <is>
@@ -3296,10 +3296,10 @@
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.276</v>
+        <v>0.897</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0.301</v>
+        <v>0.953</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="7" t="inlineStr"/>
@@ -3312,39 +3312,39 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>1.18</v>
+        <v>1</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>-0.0741</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>3528000</v>
+        <v>3729500</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.49</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H64" t="n">
-        <v>52.34</v>
-      </c>
-      <c r="I64" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.56</v>
+      </c>
+      <c r="I64" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>1.17</v>
+        <v>0.841</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>1.136</v>
+        <v>0.573</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="7" t="inlineStr"/>
@@ -3357,28 +3357,28 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="E65" s="3" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="E65" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>3269500</v>
+        <v>3599100</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0.14</v>
+        <v>0.5</v>
       </c>
       <c r="H65" t="n">
-        <v>42.99</v>
+        <v>52.34</v>
       </c>
       <c r="I65" s="6" t="inlineStr">
         <is>
@@ -3386,10 +3386,10 @@
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.19</v>
+        <v>1.17</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>0.186</v>
+        <v>1.136</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="7" t="inlineStr"/>
@@ -3402,28 +3402,28 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E66" s="8" t="n">
-        <v>-0.0189</v>
+        <v>0.175</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>-0.0278</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>3206600</v>
+        <v>3336900</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>0.44</v>
+        <v>0.15</v>
       </c>
       <c r="H66" t="n">
-        <v>42.45</v>
+        <v>40.18</v>
       </c>
       <c r="I66" s="6" t="inlineStr">
         <is>
@@ -3431,10 +3431,10 @@
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.273</v>
+        <v>0.189</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0.294</v>
+        <v>0.185</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="7" t="inlineStr"/>
@@ -3447,39 +3447,39 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="E67" s="8" t="n">
-        <v>-0.0095</v>
+        <v>0.55</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>-0.0351</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>3077400</v>
+        <v>3218400</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>0.18</v>
+        <v>0.62</v>
       </c>
       <c r="H67" t="n">
-        <v>45.7</v>
-      </c>
-      <c r="I67" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.98</v>
+      </c>
+      <c r="I67" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>2.107</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>2.101</v>
+        <v>0.516</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="7" t="inlineStr"/>
@@ -3492,28 +3492,28 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="E68" s="10" t="n">
-        <v>0.0204</v>
+        <v>0.26</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>-0.0189</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>2969400</v>
+        <v>3208300</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>0.36</v>
+        <v>0.45</v>
       </c>
       <c r="H68" t="n">
-        <v>43.98</v>
+        <v>42.45</v>
       </c>
       <c r="I68" s="6" t="inlineStr">
         <is>
@@ -3521,10 +3521,10 @@
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.77</v>
+        <v>0.273</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0.771</v>
+        <v>0.294</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="7" t="inlineStr"/>
@@ -3537,39 +3537,39 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
         <v>0.405</v>
       </c>
-      <c r="E69" s="8" t="n">
-        <v>-0.0357</v>
+      <c r="E69" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>2900800</v>
+        <v>3151300</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>0.3</v>
+        <v>1.62</v>
       </c>
       <c r="H69" t="n">
-        <v>41.34</v>
-      </c>
-      <c r="I69" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>35.96</v>
+      </c>
+      <c r="I69" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.437</v>
+        <v>0.416</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0.434</v>
+        <v>0.433</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="7" t="inlineStr"/>
@@ -3582,39 +3582,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="E70" s="8" t="n">
-        <v>-0.04389999999999999</v>
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="E70" s="9" t="n">
+        <v>0.0252</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>2819700</v>
+        <v>3099200</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="H70" t="n">
-        <v>48.83</v>
-      </c>
-      <c r="I70" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.98999999999999</v>
+      </c>
+      <c r="I70" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.793</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>0.516</v>
+        <v>0.771</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="7" t="inlineStr"/>
@@ -3627,28 +3627,28 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>0.885</v>
-      </c>
-      <c r="E71" s="8" t="n">
-        <v>-0.038</v>
+        <v>0.755</v>
+      </c>
+      <c r="E71" s="9" t="n">
+        <v>0.0272</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>2814700</v>
+        <v>3056700</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>1.69</v>
+        <v>0.37</v>
       </c>
       <c r="H71" t="n">
-        <v>46.99</v>
+        <v>45.47</v>
       </c>
       <c r="I71" s="6" t="inlineStr">
         <is>
@@ -3656,10 +3656,10 @@
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.913</v>
+        <v>0.77</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>0.874</v>
+        <v>0.771</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="7" t="inlineStr"/>
@@ -3672,40 +3672,38 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>0469</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>GTA</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>0.405</v>
+        <v>0.24</v>
       </c>
       <c r="E72" s="3" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>2797300</v>
+        <v>3027200</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>1.44</v>
+        <v>0.85</v>
       </c>
       <c r="H72" t="n">
-        <v>35.96</v>
-      </c>
-      <c r="I72" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>16.11</v>
+      </c>
+      <c r="I72" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.416</v>
-      </c>
-      <c r="K72" s="2" t="n">
-        <v>0.433</v>
-      </c>
+        <v>0.272</v>
+      </c>
+      <c r="K72" s="2" t="n"/>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="7" t="inlineStr"/>
     </row>
@@ -3717,39 +3715,39 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="E73" s="10" t="n">
-        <v>0.0097</v>
+        <v>0.41</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>-0.0238</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>2708900</v>
+        <v>3015300</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>0.88</v>
+        <v>0.32</v>
       </c>
       <c r="H73" t="n">
-        <v>82.95999999999999</v>
-      </c>
-      <c r="I73" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.4</v>
+      </c>
+      <c r="I73" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>2.83</v>
+        <v>0.438</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>2.43</v>
+        <v>0.434</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="7" t="inlineStr"/>
@@ -3773,19 +3771,19 @@
       <c r="D74" s="2" t="n">
         <v>0.465</v>
       </c>
-      <c r="E74" s="10" t="n">
+      <c r="E74" s="9" t="n">
         <v>0.022</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>2642900</v>
+        <v>2995200</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="H74" t="n">
         <v>56.6</v>
       </c>
-      <c r="I74" s="9" t="inlineStr">
+      <c r="I74" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -3807,28 +3805,28 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>5041</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>PBA</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E75" s="8" t="n">
-        <v>-0.0196</v>
+        <v>0.915</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>-0.0054</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>2639000</v>
+        <v>2881500</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>8.08</v>
+        <v>1.73</v>
       </c>
       <c r="H75" t="n">
-        <v>32</v>
+        <v>51.22</v>
       </c>
       <c r="I75" s="6" t="inlineStr">
         <is>
@@ -3836,10 +3834,10 @@
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>2.091</v>
+        <v>0.916</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>2.156</v>
+        <v>0.874</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="7" t="inlineStr"/>
@@ -3852,39 +3850,39 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0388</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>SEMICO</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E76" s="3" t="n">
-        <v>0</v>
+        <v>1.91</v>
+      </c>
+      <c r="E76" s="9" t="n">
+        <v>0.0214</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>2632800</v>
+        <v>2846100</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>0.78</v>
+        <v>0.5</v>
       </c>
       <c r="H76" t="n">
-        <v>70.16</v>
-      </c>
-      <c r="I76" s="9" t="inlineStr">
+        <v>47.22</v>
+      </c>
+      <c r="I76" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.617</v>
+        <v>1.921</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>0.605</v>
+        <v>1.95</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="7" t="inlineStr"/>
@@ -3897,28 +3895,28 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="E77" s="8" t="n">
-        <v>-0.0394</v>
+        <v>5.74</v>
+      </c>
+      <c r="E77" s="9" t="n">
+        <v>0.008800000000000001</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>2612200</v>
+        <v>2846000</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>0.62</v>
+        <v>0.38</v>
       </c>
       <c r="H77" t="n">
-        <v>23.54</v>
+        <v>30.7</v>
       </c>
       <c r="I77" s="6" t="inlineStr">
         <is>
@@ -3926,10 +3924,10 @@
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>1.393</v>
+        <v>6.023</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>1.561</v>
+        <v>6.309</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="7" t="inlineStr"/>
@@ -3942,39 +3940,39 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="E78" s="10" t="n">
-        <v>0.0214</v>
+        <v>1.22</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>-0.0394</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>2607500</v>
+        <v>2809000</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>0.46</v>
+        <v>0.67</v>
       </c>
       <c r="H78" t="n">
-        <v>47.22</v>
-      </c>
-      <c r="I78" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>23.54</v>
+      </c>
+      <c r="I78" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>1.921</v>
+        <v>1.393</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>1.95</v>
+        <v>1.561</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="7" t="inlineStr"/>
@@ -3987,38 +3985,40 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0469</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>GTA</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="E79" s="8" t="n">
-        <v>-0.04</v>
+        <v>3.12</v>
+      </c>
+      <c r="E79" s="9" t="n">
+        <v>0.0097</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>2593100</v>
+        <v>2724300</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>0.73</v>
+        <v>0.88</v>
       </c>
       <c r="H79" t="n">
-        <v>16.11</v>
-      </c>
-      <c r="I79" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>82.95999999999999</v>
+      </c>
+      <c r="I79" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.272</v>
-      </c>
-      <c r="K79" s="2" t="n"/>
+        <v>2.83</v>
+      </c>
+      <c r="K79" s="2" t="n">
+        <v>2.43</v>
+      </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="7" t="inlineStr"/>
     </row>
@@ -4030,28 +4030,28 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>5041</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>VELESTO</t>
+          <t>PBA</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>0.205</v>
-      </c>
-      <c r="E80" s="10" t="n">
-        <v>0.009899999999999999</v>
+        <v>2</v>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>-0.0196</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>2521000</v>
+        <v>2673600</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>0.11</v>
+        <v>8.19</v>
       </c>
       <c r="H80" t="n">
-        <v>39.23</v>
+        <v>32</v>
       </c>
       <c r="I80" s="6" t="inlineStr">
         <is>
@@ -4059,10 +4059,10 @@
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.218</v>
+        <v>2.091</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0.235</v>
+        <v>2.156</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="7" t="inlineStr"/>
@@ -4075,39 +4075,39 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0261</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>COSMOS</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>0.42</v>
+        <v>0.625</v>
       </c>
       <c r="E81" s="10" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>2300300</v>
+        <v>2632800</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>6.9</v>
+        <v>0.78</v>
       </c>
       <c r="H81" t="n">
-        <v>70.20999999999999</v>
-      </c>
-      <c r="I81" s="9" t="inlineStr">
+        <v>70.16</v>
+      </c>
+      <c r="I81" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.382</v>
+        <v>0.617</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>0.363</v>
+        <v>0.605</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="7" t="inlineStr"/>
@@ -4120,28 +4120,28 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>IOIPG</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="E82" s="10" t="n">
-        <v>0.0285</v>
+        <v>0.205</v>
+      </c>
+      <c r="E82" s="9" t="n">
+        <v>0.009899999999999999</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>2255800</v>
+        <v>2609400</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>0.38</v>
+        <v>0.12</v>
       </c>
       <c r="H82" t="n">
-        <v>36.23</v>
+        <v>39.23</v>
       </c>
       <c r="I82" s="6" t="inlineStr">
         <is>
@@ -4149,10 +4149,10 @@
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>3.37</v>
+        <v>0.218</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>3.604</v>
+        <v>0.235</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="7" t="inlineStr"/>
@@ -4165,39 +4165,39 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>4.47</v>
-      </c>
-      <c r="E83" s="10" t="n">
-        <v>0.0347</v>
+        <v>0.68</v>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>-0.0145</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>2229300</v>
+        <v>2516600</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>0.42</v>
+        <v>0.17</v>
       </c>
       <c r="H83" t="n">
-        <v>53.31</v>
-      </c>
-      <c r="I83" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.44</v>
+      </c>
+      <c r="I83" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>4.363</v>
+        <v>0.75</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>4.432</v>
+        <v>0.723</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="7" t="inlineStr"/>
@@ -4210,28 +4210,28 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>IOIPG</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>5.74</v>
-      </c>
-      <c r="E84" s="10" t="n">
-        <v>0.008800000000000001</v>
+        <v>3.24</v>
+      </c>
+      <c r="E84" s="9" t="n">
+        <v>0.0253</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>2227800</v>
+        <v>2510900</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>0.3</v>
+        <v>0.42</v>
       </c>
       <c r="H84" t="n">
-        <v>30.7</v>
+        <v>35.23</v>
       </c>
       <c r="I84" s="6" t="inlineStr">
         <is>
@@ -4239,10 +4239,10 @@
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>6.023</v>
+        <v>3.369</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>6.309</v>
+        <v>3.604</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="7" t="inlineStr"/>
@@ -4255,28 +4255,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="E85" s="8" t="n">
-        <v>-0.0223</v>
+        <v>0.28</v>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>-0.0175</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>2176600</v>
+        <v>2499600</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>0.28</v>
+        <v>0.41</v>
       </c>
       <c r="H85" t="n">
-        <v>43.95</v>
+        <v>21.33</v>
       </c>
       <c r="I85" s="6" t="inlineStr">
         <is>
@@ -4284,10 +4284,10 @@
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.928</v>
+        <v>0.333</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>0.847</v>
+        <v>0.372</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="7" t="inlineStr"/>
@@ -4300,39 +4300,39 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>0261</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>COSMOS</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="E86" s="8" t="n">
-        <v>-0.015</v>
+        <v>0.41</v>
+      </c>
+      <c r="E86" s="9" t="n">
+        <v>0.025</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>2055300</v>
+        <v>2496000</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>0.86</v>
+        <v>7.48</v>
       </c>
       <c r="H86" t="n">
-        <v>57.19</v>
-      </c>
-      <c r="I86" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>67.38</v>
+      </c>
+      <c r="I86" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>1.261</v>
+        <v>0.381</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>1.173</v>
+        <v>0.363</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="7" t="inlineStr"/>
@@ -4345,28 +4345,28 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="E87" s="8" t="n">
-        <v>-0.0175</v>
+        <v>0.885</v>
+      </c>
+      <c r="E87" s="3" t="n">
+        <v>-0.0112</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>2013000</v>
+        <v>2455400</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="H87" t="n">
-        <v>21.33</v>
+        <v>45.18</v>
       </c>
       <c r="I87" s="6" t="inlineStr">
         <is>
@@ -4374,10 +4374,10 @@
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.333</v>
+        <v>0.929</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>0.372</v>
+        <v>0.847</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="7" t="inlineStr"/>
@@ -4390,38 +4390,40 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>0.355</v>
-      </c>
-      <c r="E88" s="8" t="n">
-        <v>-0.0274</v>
+        <v>4.46</v>
+      </c>
+      <c r="E88" s="9" t="n">
+        <v>0.03240000000000001</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>2007000</v>
+        <v>2390800</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
       <c r="H88" t="n">
-        <v>60.83</v>
-      </c>
-      <c r="I88" s="9" t="inlineStr">
+        <v>52.98</v>
+      </c>
+      <c r="I88" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.318</v>
-      </c>
-      <c r="K88" s="2" t="n"/>
+        <v>4.362</v>
+      </c>
+      <c r="K88" s="2" t="n">
+        <v>4.432</v>
+      </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="7" t="inlineStr"/>
     </row>
@@ -4442,19 +4444,19 @@
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>0.925</v>
-      </c>
-      <c r="E89" s="8" t="n">
-        <v>-0.0054</v>
+        <v>0.915</v>
+      </c>
+      <c r="E89" s="3" t="n">
+        <v>-0.0161</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>1996400</v>
+        <v>2301200</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>0.51</v>
+        <v>0.59</v>
       </c>
       <c r="H89" t="n">
-        <v>25.84</v>
+        <v>24.01</v>
       </c>
       <c r="I89" s="6" t="inlineStr">
         <is>
@@ -4462,10 +4464,10 @@
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.97</v>
+        <v>0.969</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>1.053</v>
+        <v>1.052</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="7" t="inlineStr"/>
@@ -4478,39 +4480,39 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0372</t>
+          <t>0056</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>CHEEDING</t>
+          <t>NCT</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E90" s="8" t="n">
-        <v>-0.0291</v>
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="E90" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>1976300</v>
+        <v>2297000</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>0.45</v>
+        <v>1.1</v>
       </c>
       <c r="H90" t="n">
-        <v>29.93</v>
-      </c>
-      <c r="I90" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.44</v>
+      </c>
+      <c r="I90" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.581</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>0.599</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="7" t="inlineStr"/>
@@ -4532,21 +4534,21 @@
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="E91" s="8" t="n">
-        <v>-0.008500000000000001</v>
+        <v>0.585</v>
+      </c>
+      <c r="E91" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>1972700</v>
+        <v>2223000</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>0.47</v>
+        <v>0.53</v>
       </c>
       <c r="H91" t="n">
-        <v>67.36</v>
-      </c>
-      <c r="I91" s="9" t="inlineStr">
+        <v>68.69</v>
+      </c>
+      <c r="I91" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -4568,28 +4570,28 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>5053</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>DATASONIC</t>
+          <t>OSK</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="E92" s="8" t="n">
-        <v>-0.0175</v>
+        <v>1.63</v>
+      </c>
+      <c r="E92" s="3" t="n">
+        <v>-0.0121</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>1913700</v>
+        <v>2182800</v>
       </c>
       <c r="G92" s="5" t="n">
-        <v>0.16</v>
+        <v>1.53</v>
       </c>
       <c r="H92" t="n">
-        <v>46.28</v>
+        <v>30.22</v>
       </c>
       <c r="I92" s="6" t="inlineStr">
         <is>
@@ -4597,10 +4599,10 @@
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.291</v>
+        <v>1.728</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>0.283</v>
+        <v>1.884</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="7" t="inlineStr"/>
@@ -4613,28 +4615,28 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>0.735</v>
-      </c>
-      <c r="E93" s="8" t="n">
-        <v>-0.0329</v>
+        <v>1.3</v>
+      </c>
+      <c r="E93" s="3" t="n">
+        <v>-0.0226</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>1860500</v>
+        <v>2094700</v>
       </c>
       <c r="G93" s="5" t="n">
-        <v>0.35</v>
+        <v>0.87</v>
       </c>
       <c r="H93" t="n">
-        <v>48.09</v>
+        <v>56.17</v>
       </c>
       <c r="I93" s="6" t="inlineStr">
         <is>
@@ -4642,10 +4644,10 @@
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.761</v>
+        <v>1.26</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>0.6850000000000001</v>
+        <v>1.173</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="7" t="inlineStr"/>
@@ -4658,39 +4660,39 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>0.335</v>
+        <v>0.735</v>
       </c>
       <c r="E94" s="3" t="n">
-        <v>0</v>
+        <v>-0.0329</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>1806200</v>
+        <v>2084400</v>
       </c>
       <c r="G94" s="5" t="n">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="H94" t="n">
-        <v>47.09</v>
-      </c>
-      <c r="I94" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.09</v>
+      </c>
+      <c r="I94" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.335</v>
+        <v>0.761</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>0.343</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="7" t="inlineStr"/>
@@ -4703,28 +4705,28 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>5271</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>PECCA</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>1.35</v>
+        <v>0.835</v>
       </c>
       <c r="E95" s="3" t="n">
-        <v>0</v>
+        <v>-0.0176</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>1795400</v>
+        <v>2043700</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>0.92</v>
+        <v>0.57</v>
       </c>
       <c r="H95" t="n">
-        <v>43.62</v>
+        <v>53.24</v>
       </c>
       <c r="I95" s="6" t="inlineStr">
         <is>
@@ -4732,10 +4734,10 @@
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>1.367</v>
+        <v>0.827</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>1.343</v>
+        <v>0.781</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="7" t="inlineStr"/>
@@ -4748,40 +4750,38 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="E96" s="8" t="n">
-        <v>-0.0145</v>
+        <v>0.36</v>
+      </c>
+      <c r="E96" s="3" t="n">
+        <v>-0.0137</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>1750200</v>
+        <v>2018800</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>0.12</v>
+        <v>0.35</v>
       </c>
       <c r="H96" t="n">
-        <v>39.44</v>
-      </c>
-      <c r="I96" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.55</v>
+      </c>
+      <c r="I96" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="K96" s="2" t="n">
-        <v>0.723</v>
-      </c>
+        <v>0.319</v>
+      </c>
+      <c r="K96" s="2" t="n"/>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="7" t="inlineStr"/>
     </row>
@@ -4793,39 +4793,39 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>DATASONIC</t>
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>0.635</v>
+        <v>0.28</v>
       </c>
       <c r="E97" s="3" t="n">
-        <v>0</v>
+        <v>-0.0175</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>1715400</v>
+        <v>2014600</v>
       </c>
       <c r="G97" s="5" t="n">
-        <v>0.77</v>
+        <v>0.17</v>
       </c>
       <c r="H97" t="n">
-        <v>50.9</v>
-      </c>
-      <c r="I97" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.28</v>
+      </c>
+      <c r="I97" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.637</v>
+        <v>0.291</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>0.622</v>
+        <v>0.283</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="7" t="inlineStr"/>
@@ -4838,28 +4838,28 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>0372</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>CHEEDING</t>
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E98" s="8" t="n">
-        <v>-0.0155</v>
+        <v>0.5</v>
+      </c>
+      <c r="E98" s="3" t="n">
+        <v>-0.0291</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>1685000</v>
+        <v>1976300</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>0.19</v>
+        <v>0.45</v>
       </c>
       <c r="H98" t="n">
-        <v>40.95</v>
+        <v>29.93</v>
       </c>
       <c r="I98" s="6" t="inlineStr">
         <is>
@@ -4867,10 +4867,10 @@
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.678</v>
+        <v>0.581</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.599</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="7" t="inlineStr"/>
@@ -4883,28 +4883,28 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D99" s="2" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="E99" s="8" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0.635</v>
+      </c>
+      <c r="E99" s="3" t="n">
+        <v>-0.0155</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v>1685000</v>
+        <v>1907900</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>0.48</v>
+        <v>0.21</v>
       </c>
       <c r="H99" t="n">
-        <v>47.42</v>
+        <v>40.95</v>
       </c>
       <c r="I99" s="6" t="inlineStr">
         <is>
@@ -4912,10 +4912,10 @@
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>1.238</v>
+        <v>0.678</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>1.067</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="7" t="inlineStr"/>
@@ -4928,28 +4928,28 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>PECCA</t>
         </is>
       </c>
       <c r="D100" s="2" t="n">
-        <v>0.595</v>
-      </c>
-      <c r="E100" s="8" t="n">
-        <v>-0.0325</v>
+        <v>1.35</v>
+      </c>
+      <c r="E100" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>1674800</v>
+        <v>1849200</v>
       </c>
       <c r="G100" s="5" t="n">
-        <v>0.29</v>
+        <v>0.95</v>
       </c>
       <c r="H100" t="n">
-        <v>57.47</v>
+        <v>43.62</v>
       </c>
       <c r="I100" s="6" t="inlineStr">
         <is>
@@ -4957,10 +4957,10 @@
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.57</v>
+        <v>1.367</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>0.47</v>
+        <v>1.343</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="7" t="inlineStr"/>
@@ -4973,39 +4973,39 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0056</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>NCT</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D101" s="2" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="E101" s="8" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.61</v>
+      </c>
+      <c r="E101" s="3" t="n">
+        <v>-0.008100000000000001</v>
       </c>
       <c r="F101" s="4" t="n">
-        <v>1673000</v>
+        <v>1842000</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>0.8</v>
+        <v>0.32</v>
       </c>
       <c r="H101" t="n">
-        <v>48.02</v>
-      </c>
-      <c r="I101" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>59.95</v>
+      </c>
+      <c r="I101" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.571</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.47</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="7" t="inlineStr"/>
@@ -5018,39 +5018,39 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="D102" s="2" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="E102" s="3" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="E102" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>1616500</v>
+        <v>1830900</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>0.37</v>
+        <v>0.39</v>
       </c>
       <c r="H102" t="n">
-        <v>49.06</v>
-      </c>
-      <c r="I102" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.09</v>
+      </c>
+      <c r="I102" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.598</v>
+        <v>0.335</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>0.586</v>
+        <v>0.343</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="7" t="inlineStr"/>
@@ -5063,39 +5063,39 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>5162</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>VSTECS</t>
         </is>
       </c>
       <c r="D103" s="2" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E103" s="10" t="n">
-        <v>0.0314</v>
+        <v>1.5</v>
+      </c>
+      <c r="E103" s="3" t="n">
+        <v>-0.0323</v>
       </c>
       <c r="F103" s="4" t="n">
-        <v>1613200</v>
+        <v>1807600</v>
       </c>
       <c r="G103" s="5" t="n">
-        <v>0.29</v>
+        <v>1.04</v>
       </c>
       <c r="H103" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="I103" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.96</v>
+      </c>
+      <c r="I103" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.794</v>
+        <v>1.621</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>0.772</v>
+        <v>1.664</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="7" t="inlineStr"/>
@@ -5108,39 +5108,39 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D104" s="2" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="E104" s="8" t="n">
-        <v>-0.0105</v>
+        <v>0.635</v>
+      </c>
+      <c r="E104" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v>1602000</v>
+        <v>1715400</v>
       </c>
       <c r="G104" s="5" t="n">
-        <v>0.19</v>
+        <v>0.77</v>
       </c>
       <c r="H104" t="n">
-        <v>35.57</v>
-      </c>
-      <c r="I104" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.9</v>
+      </c>
+      <c r="I104" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.506</v>
+        <v>0.637</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>0.524</v>
+        <v>0.622</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="7" t="inlineStr"/>
@@ -5153,28 +5153,28 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>0192</t>
+          <t>0245</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>INTA</t>
+          <t>MNHLDG</t>
         </is>
       </c>
       <c r="D105" s="2" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E105" s="8" t="n">
-        <v>-0.013</v>
+        <v>3.82</v>
+      </c>
+      <c r="E105" s="3" t="n">
+        <v>-0.0026</v>
       </c>
       <c r="F105" s="4" t="n">
-        <v>1594400</v>
+        <v>1695000</v>
       </c>
       <c r="G105" s="5" t="n">
-        <v>0.59</v>
+        <v>0.58</v>
       </c>
       <c r="H105" t="n">
-        <v>41.3</v>
+        <v>50.38</v>
       </c>
       <c r="I105" s="6" t="inlineStr">
         <is>
@@ -5182,10 +5182,10 @@
         </is>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.394</v>
+        <v>3.847</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>0.389</v>
+        <v>3.682</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="7" t="inlineStr"/>
@@ -5198,28 +5198,28 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D106" s="2" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E106" s="8" t="n">
-        <v>-0.0234</v>
+        <v>2.42</v>
+      </c>
+      <c r="E106" s="9" t="n">
+        <v>0.0168</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v>1577200</v>
+        <v>1693300</v>
       </c>
       <c r="G106" s="5" t="n">
-        <v>0.26</v>
+        <v>0.14</v>
       </c>
       <c r="H106" t="n">
-        <v>41.66</v>
+        <v>47.95</v>
       </c>
       <c r="I106" s="6" t="inlineStr">
         <is>
@@ -5227,10 +5227,10 @@
         </is>
       </c>
       <c r="J106" s="2" t="n">
-        <v>2.604</v>
+        <v>2.444</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>2.607</v>
+        <v>2.385</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="7" t="inlineStr"/>
@@ -5243,28 +5243,28 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="E107" s="10" t="n">
-        <v>0.0168</v>
+        <v>1.18</v>
+      </c>
+      <c r="E107" s="3" t="n">
+        <v>-0.008399999999999999</v>
       </c>
       <c r="F107" s="4" t="n">
-        <v>1540600</v>
+        <v>1687100</v>
       </c>
       <c r="G107" s="5" t="n">
-        <v>0.13</v>
+        <v>0.48</v>
       </c>
       <c r="H107" t="n">
-        <v>47.95</v>
+        <v>47.42</v>
       </c>
       <c r="I107" s="6" t="inlineStr">
         <is>
@@ -5272,10 +5272,10 @@
         </is>
       </c>
       <c r="J107" s="2" t="n">
-        <v>2.444</v>
+        <v>1.238</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>2.385</v>
+        <v>1.067</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="7" t="inlineStr"/>
@@ -5288,28 +5288,28 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>8524</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>TALIWRK</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D108" s="2" t="n">
-        <v>0.23</v>
+        <v>0.785</v>
       </c>
       <c r="E108" s="3" t="n">
-        <v>0</v>
+        <v>-0.0126</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>1540500</v>
+        <v>1669500</v>
       </c>
       <c r="G108" s="5" t="n">
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
       <c r="H108" t="n">
-        <v>37.06</v>
+        <v>15.53</v>
       </c>
       <c r="I108" s="6" t="inlineStr">
         <is>
@@ -5317,10 +5317,10 @@
         </is>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.244</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>0.256</v>
+        <v>1.078</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="7" t="inlineStr"/>
@@ -5333,39 +5333,39 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>5162</t>
+          <t>5248</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>VSTECS</t>
+          <t>BAUTO</t>
         </is>
       </c>
       <c r="D109" s="2" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="E109" s="8" t="n">
-        <v>-0.0258</v>
+        <v>0.895</v>
+      </c>
+      <c r="E109" s="9" t="n">
+        <v>0.017</v>
       </c>
       <c r="F109" s="4" t="n">
-        <v>1528100</v>
+        <v>1666500</v>
       </c>
       <c r="G109" s="5" t="n">
-        <v>0.88</v>
+        <v>1.02</v>
       </c>
       <c r="H109" t="n">
-        <v>36.69</v>
-      </c>
-      <c r="I109" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.48</v>
+      </c>
+      <c r="I109" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J109" s="2" t="n">
-        <v>1.622</v>
+        <v>0.892</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>1.665</v>
+        <v>0.908</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="7" t="inlineStr"/>
@@ -5389,19 +5389,19 @@
       <c r="D110" s="2" t="n">
         <v>12.94</v>
       </c>
-      <c r="E110" s="8" t="n">
+      <c r="E110" s="3" t="n">
         <v>-0.0046</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>1516100</v>
+        <v>1653300</v>
       </c>
       <c r="G110" s="5" t="n">
-        <v>0.19</v>
+        <v>0.21</v>
       </c>
       <c r="H110" t="n">
         <v>42.45</v>
       </c>
-      <c r="I110" s="9" t="inlineStr">
+      <c r="I110" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -5423,39 +5423,39 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D111" s="2" t="n">
-        <v>1.25</v>
+        <v>7.19</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.0178</v>
       </c>
       <c r="F111" s="4" t="n">
-        <v>1510800</v>
+        <v>1646100</v>
       </c>
       <c r="G111" s="5" t="n">
         <v>0.16</v>
       </c>
       <c r="H111" t="n">
-        <v>41.23</v>
-      </c>
-      <c r="I111" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>30.74</v>
+      </c>
+      <c r="I111" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J111" s="2" t="n">
-        <v>1.298</v>
+        <v>7.453</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>1.314</v>
+        <v>7.948</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="7" t="inlineStr"/>
@@ -5468,39 +5468,39 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>5248</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>BAUTO</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D112" s="2" t="n">
-        <v>0.9</v>
+        <v>0.59</v>
       </c>
       <c r="E112" s="10" t="n">
-        <v>0.0227</v>
+        <v>0</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>1504300</v>
+        <v>1631000</v>
       </c>
       <c r="G112" s="5" t="n">
-        <v>0.92</v>
+        <v>0.37</v>
       </c>
       <c r="H112" t="n">
-        <v>51.19</v>
-      </c>
-      <c r="I112" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.06</v>
+      </c>
+      <c r="I112" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.893</v>
+        <v>0.598</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>0.908</v>
+        <v>0.586</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="7" t="inlineStr"/>
@@ -5513,28 +5513,28 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>5053</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>OSK</t>
+          <t>SPSETIA</t>
         </is>
       </c>
       <c r="D113" s="2" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="E113" s="8" t="n">
-        <v>-0.0121</v>
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="E113" s="9" t="n">
+        <v>0.0147</v>
       </c>
       <c r="F113" s="4" t="n">
-        <v>1501400</v>
+        <v>1625000</v>
       </c>
       <c r="G113" s="5" t="n">
-        <v>1.05</v>
+        <v>0.24</v>
       </c>
       <c r="H113" t="n">
-        <v>30.22</v>
+        <v>33.21</v>
       </c>
       <c r="I113" s="6" t="inlineStr">
         <is>
@@ -5542,10 +5542,10 @@
         </is>
       </c>
       <c r="J113" s="2" t="n">
-        <v>1.728</v>
+        <v>0.725</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>1.884</v>
+        <v>0.791</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="7" t="inlineStr"/>
@@ -5558,28 +5558,28 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>5329</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>AZAMJAYA</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D114" s="2" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="E114" s="8" t="n">
-        <v>-0.0452</v>
+        <v>0.475</v>
+      </c>
+      <c r="E114" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F114" s="4" t="n">
-        <v>1492600</v>
+        <v>1622000</v>
       </c>
       <c r="G114" s="5" t="n">
-        <v>9.140000000000001</v>
+        <v>0.19</v>
       </c>
       <c r="H114" t="n">
-        <v>45.49</v>
+        <v>36.82</v>
       </c>
       <c r="I114" s="6" t="inlineStr">
         <is>
@@ -5587,10 +5587,10 @@
         </is>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.969</v>
+        <v>0.506</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>0.976</v>
+        <v>0.524</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="7" t="inlineStr"/>
@@ -5603,28 +5603,28 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>0192</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>INTA</t>
         </is>
       </c>
       <c r="D115" s="2" t="n">
-        <v>3.81</v>
-      </c>
-      <c r="E115" s="8" t="n">
-        <v>-0.0052</v>
+        <v>0.375</v>
+      </c>
+      <c r="E115" s="3" t="n">
+        <v>-0.026</v>
       </c>
       <c r="F115" s="4" t="n">
-        <v>1487200</v>
+        <v>1619800</v>
       </c>
       <c r="G115" s="5" t="n">
-        <v>0.51</v>
+        <v>0.6</v>
       </c>
       <c r="H115" t="n">
-        <v>49.9</v>
+        <v>38.98</v>
       </c>
       <c r="I115" s="6" t="inlineStr">
         <is>
@@ -5632,10 +5632,10 @@
         </is>
       </c>
       <c r="J115" s="2" t="n">
-        <v>3.846</v>
+        <v>0.393</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>3.681</v>
+        <v>0.389</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="7" t="inlineStr"/>
@@ -5648,28 +5648,28 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>5272</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>RANHILL</t>
         </is>
       </c>
       <c r="D116" s="2" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="E116" s="8" t="n">
-        <v>-0.0189</v>
+        <v>3.12</v>
+      </c>
+      <c r="E116" s="3" t="n">
+        <v>-0.0064</v>
       </c>
       <c r="F116" s="4" t="n">
-        <v>1468200</v>
+        <v>1608900</v>
       </c>
       <c r="G116" s="5" t="n">
-        <v>0.67</v>
+        <v>1.01</v>
       </c>
       <c r="H116" t="n">
-        <v>15.27</v>
+        <v>50.69</v>
       </c>
       <c r="I116" s="6" t="inlineStr">
         <is>
@@ -5677,10 +5677,10 @@
         </is>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.9370000000000001</v>
+        <v>3.17</v>
       </c>
       <c r="K116" s="2" t="n">
-        <v>1.078</v>
+        <v>2.876</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="7" t="inlineStr"/>
@@ -5704,14 +5704,14 @@
       <c r="D117" s="2" t="n">
         <v>1.11</v>
       </c>
-      <c r="E117" s="3" t="n">
+      <c r="E117" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F117" s="4" t="n">
-        <v>1464100</v>
+        <v>1602300</v>
       </c>
       <c r="G117" s="5" t="n">
-        <v>0.33</v>
+        <v>0.37</v>
       </c>
       <c r="H117" t="n">
         <v>58.81</v>
@@ -5738,28 +5738,28 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>UWC</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D118" s="2" t="n">
-        <v>7.23</v>
-      </c>
-      <c r="E118" s="8" t="n">
-        <v>-0.009599999999999999</v>
+        <v>2.5</v>
+      </c>
+      <c r="E118" s="3" t="n">
+        <v>-0.0234</v>
       </c>
       <c r="F118" s="4" t="n">
-        <v>1451400</v>
+        <v>1595100</v>
       </c>
       <c r="G118" s="5" t="n">
-        <v>0.34</v>
+        <v>0.26</v>
       </c>
       <c r="H118" t="n">
-        <v>49.86</v>
+        <v>41.66</v>
       </c>
       <c r="I118" s="6" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="J118" s="2" t="n">
-        <v>7.345</v>
+        <v>2.604</v>
       </c>
       <c r="K118" s="2" t="n">
-        <v>6.896</v>
+        <v>2.607</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="7" t="inlineStr"/>
@@ -5783,39 +5783,39 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>0325</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D119" s="2" t="n">
-        <v>1.1</v>
+        <v>1.24</v>
       </c>
       <c r="E119" s="3" t="n">
-        <v>0</v>
+        <v>-0.008</v>
       </c>
       <c r="F119" s="4" t="n">
-        <v>1400700</v>
+        <v>1586700</v>
       </c>
       <c r="G119" s="5" t="n">
-        <v>0.71</v>
+        <v>0.17</v>
       </c>
       <c r="H119" t="n">
-        <v>51.14</v>
-      </c>
-      <c r="I119" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.01</v>
+      </c>
+      <c r="I119" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J119" s="2" t="n">
-        <v>1.091</v>
+        <v>1.297</v>
       </c>
       <c r="K119" s="2" t="n">
-        <v>1.097</v>
+        <v>1.314</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="7" t="inlineStr"/>
@@ -5828,39 +5828,39 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>8524</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>TALIWRK</t>
         </is>
       </c>
       <c r="D120" s="2" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="E120" s="8" t="n">
-        <v>-0.0219</v>
+        <v>0.225</v>
+      </c>
+      <c r="E120" s="3" t="n">
+        <v>-0.0217</v>
       </c>
       <c r="F120" s="4" t="n">
-        <v>1391000</v>
+        <v>1578300</v>
       </c>
       <c r="G120" s="5" t="n">
-        <v>0.52</v>
+        <v>0.79</v>
       </c>
       <c r="H120" t="n">
-        <v>59.56</v>
-      </c>
-      <c r="I120" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.68</v>
+      </c>
+      <c r="I120" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.647</v>
+        <v>0.243</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.256</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="7" t="inlineStr"/>
@@ -5873,28 +5873,28 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>UWC</t>
         </is>
       </c>
       <c r="D121" s="2" t="n">
-        <v>0.825</v>
-      </c>
-      <c r="E121" s="8" t="n">
-        <v>-0.0294</v>
+        <v>7.25</v>
+      </c>
+      <c r="E121" s="3" t="n">
+        <v>-0.0068</v>
       </c>
       <c r="F121" s="4" t="n">
-        <v>1384000</v>
+        <v>1576000</v>
       </c>
       <c r="G121" s="5" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="H121" t="n">
-        <v>51.48</v>
+        <v>50.3</v>
       </c>
       <c r="I121" s="6" t="inlineStr">
         <is>
@@ -5902,10 +5902,10 @@
         </is>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.826</v>
+        <v>7.347</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>0.781</v>
+        <v>6.897</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="7" t="inlineStr"/>
@@ -5918,28 +5918,28 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>0217</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>PWRWELL</t>
         </is>
       </c>
       <c r="D122" s="2" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="E122" s="8" t="n">
-        <v>-0.0143</v>
+        <v>1.14</v>
+      </c>
+      <c r="E122" s="3" t="n">
+        <v>-0.0172</v>
       </c>
       <c r="F122" s="4" t="n">
-        <v>1362200</v>
+        <v>1553800</v>
       </c>
       <c r="G122" s="5" t="n">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="H122" t="n">
-        <v>39.45</v>
+        <v>49.11</v>
       </c>
       <c r="I122" s="6" t="inlineStr">
         <is>
@@ -5947,10 +5947,10 @@
         </is>
       </c>
       <c r="J122" s="2" t="n">
-        <v>2.895</v>
+        <v>1.159</v>
       </c>
       <c r="K122" s="2" t="n">
-        <v>3.012</v>
+        <v>1.1</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="7" t="inlineStr"/>
@@ -5963,39 +5963,39 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>0278</t>
+          <t>0325</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>EDELTEQ</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="D123" s="2" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="E123" s="8" t="n">
-        <v>-0.0233</v>
+        <v>1.1</v>
+      </c>
+      <c r="E123" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F123" s="4" t="n">
-        <v>1353500</v>
+        <v>1535500</v>
       </c>
       <c r="G123" s="5" t="n">
-        <v>0.24</v>
+        <v>0.78</v>
       </c>
       <c r="H123" t="n">
-        <v>58.16</v>
-      </c>
-      <c r="I123" s="9" t="inlineStr">
+        <v>51.14</v>
+      </c>
+      <c r="I123" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.39</v>
+        <v>1.091</v>
       </c>
       <c r="K123" s="2" t="n">
-        <v>0.36</v>
+        <v>1.097</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="7" t="inlineStr"/>
@@ -6008,28 +6008,28 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>5329</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>AZAMJAYA</t>
         </is>
       </c>
       <c r="D124" s="2" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="E124" s="8" t="n">
-        <v>-0.0086</v>
+        <v>0.95</v>
+      </c>
+      <c r="E124" s="3" t="n">
+        <v>-0.0452</v>
       </c>
       <c r="F124" s="4" t="n">
-        <v>1332900</v>
+        <v>1492600</v>
       </c>
       <c r="G124" s="5" t="n">
-        <v>0.32</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="H124" t="n">
-        <v>50.8</v>
+        <v>45.49</v>
       </c>
       <c r="I124" s="6" t="inlineStr">
         <is>
@@ -6037,10 +6037,10 @@
         </is>
       </c>
       <c r="J124" s="2" t="n">
-        <v>1.159</v>
+        <v>0.969</v>
       </c>
       <c r="K124" s="2" t="n">
-        <v>1.1</v>
+        <v>0.976</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="7" t="inlineStr"/>
@@ -6053,28 +6053,28 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>5272</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>RANHILL</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D125" s="2" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="E125" s="8" t="n">
-        <v>-0.0064</v>
+        <v>0.845</v>
+      </c>
+      <c r="E125" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F125" s="4" t="n">
-        <v>1328500</v>
+        <v>1490000</v>
       </c>
       <c r="G125" s="5" t="n">
-        <v>0.84</v>
+        <v>0.51</v>
       </c>
       <c r="H125" t="n">
-        <v>50.69</v>
+        <v>17.21</v>
       </c>
       <c r="I125" s="6" t="inlineStr">
         <is>
@@ -6082,10 +6082,10 @@
         </is>
       </c>
       <c r="J125" s="2" t="n">
-        <v>3.17</v>
+        <v>0.916</v>
       </c>
       <c r="K125" s="2" t="n">
-        <v>2.876</v>
+        <v>0.973</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="7" t="inlineStr"/>
@@ -6098,39 +6098,39 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>0239</t>
+          <t>0278</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>ECOMATE</t>
+          <t>EDELTEQ</t>
         </is>
       </c>
       <c r="D126" s="2" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E126" s="10" t="n">
-        <v>0.0058</v>
+        <v>0.415</v>
+      </c>
+      <c r="E126" s="3" t="n">
+        <v>-0.0349</v>
       </c>
       <c r="F126" s="4" t="n">
-        <v>1312000</v>
+        <v>1470500</v>
       </c>
       <c r="G126" s="5" t="n">
-        <v>0.42</v>
+        <v>0.26</v>
       </c>
       <c r="H126" t="n">
-        <v>52.3</v>
-      </c>
-      <c r="I126" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.05</v>
+      </c>
+      <c r="I126" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J126" s="2" t="n">
-        <v>0.864</v>
+        <v>0.39</v>
       </c>
       <c r="K126" s="2" t="n">
-        <v>0.859</v>
+        <v>0.36</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="7" t="inlineStr"/>
@@ -6143,28 +6143,28 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>0233</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>PEKAT</t>
         </is>
       </c>
       <c r="D127" s="2" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="E127" s="10" t="n">
-        <v>0.0036</v>
+        <v>2.85</v>
+      </c>
+      <c r="E127" s="9" t="n">
+        <v>0.0326</v>
       </c>
       <c r="F127" s="4" t="n">
-        <v>1305800</v>
+        <v>1403900</v>
       </c>
       <c r="G127" s="5" t="n">
-        <v>0.14</v>
+        <v>0.39</v>
       </c>
       <c r="H127" t="n">
-        <v>53.66</v>
+        <v>60.65</v>
       </c>
       <c r="I127" s="6" t="inlineStr">
         <is>
@@ -6172,10 +6172,10 @@
         </is>
       </c>
       <c r="J127" s="2" t="n">
-        <v>2.794</v>
+        <v>2.684</v>
       </c>
       <c r="K127" s="2" t="n">
-        <v>2.664</v>
+        <v>2.263</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="7" t="inlineStr"/>
@@ -6188,39 +6188,39 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>5932</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>BPURI</t>
+          <t>AWC</t>
         </is>
       </c>
       <c r="D128" s="2" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="E128" s="8" t="n">
-        <v>-0.0233</v>
+        <v>0.675</v>
+      </c>
+      <c r="E128" s="3" t="n">
+        <v>-0.0146</v>
       </c>
       <c r="F128" s="4" t="n">
-        <v>1297400</v>
+        <v>1402800</v>
       </c>
       <c r="G128" s="5" t="n">
-        <v>1.89</v>
+        <v>0.52</v>
       </c>
       <c r="H128" t="n">
-        <v>38.22</v>
-      </c>
-      <c r="I128" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.9</v>
+      </c>
+      <c r="I128" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J128" s="2" t="n">
-        <v>0.223</v>
+        <v>0.648</v>
       </c>
       <c r="K128" s="2" t="n">
-        <v>0.232</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="7" t="inlineStr"/>
@@ -6233,28 +6233,28 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>0298</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>WENTEL</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D129" s="2" t="n">
-        <v>0.235</v>
-      </c>
-      <c r="E129" s="8" t="n">
-        <v>-0.0408</v>
+        <v>2.77</v>
+      </c>
+      <c r="E129" s="3" t="n">
+        <v>-0.0107</v>
       </c>
       <c r="F129" s="4" t="n">
-        <v>1295300</v>
+        <v>1400000</v>
       </c>
       <c r="G129" s="5" t="n">
-        <v>0.76</v>
+        <v>0.37</v>
       </c>
       <c r="H129" t="n">
-        <v>36.24</v>
+        <v>39.95</v>
       </c>
       <c r="I129" s="6" t="inlineStr">
         <is>
@@ -6262,10 +6262,10 @@
         </is>
       </c>
       <c r="J129" s="2" t="n">
-        <v>0.254</v>
+        <v>2.896</v>
       </c>
       <c r="K129" s="2" t="n">
-        <v>0.274</v>
+        <v>3.013</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="7" t="inlineStr"/>
@@ -6278,28 +6278,28 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>SUNREIT</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D130" s="2" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="E130" s="3" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E130" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F130" s="4" t="n">
-        <v>1276800</v>
+        <v>1395800</v>
       </c>
       <c r="G130" s="5" t="n">
-        <v>0.4</v>
+        <v>0.17</v>
       </c>
       <c r="H130" t="n">
-        <v>44.02</v>
+        <v>50.51</v>
       </c>
       <c r="I130" s="6" t="inlineStr">
         <is>
@@ -6307,10 +6307,10 @@
         </is>
       </c>
       <c r="J130" s="2" t="n">
-        <v>2.044</v>
+        <v>0.354</v>
       </c>
       <c r="K130" s="2" t="n">
-        <v>2.071</v>
+        <v>0.327</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="7" t="inlineStr"/>
@@ -6323,28 +6323,28 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>0470</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>BFIELD</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D131" s="2" t="n">
-        <v>0.425</v>
-      </c>
-      <c r="E131" s="3" t="n">
-        <v>0</v>
+        <v>2.82</v>
+      </c>
+      <c r="E131" s="9" t="n">
+        <v>0.0036</v>
       </c>
       <c r="F131" s="4" t="n">
-        <v>1267200</v>
+        <v>1368800</v>
       </c>
       <c r="G131" s="5" t="n">
-        <v>0.23</v>
+        <v>0.15</v>
       </c>
       <c r="H131" t="n">
-        <v>19.3</v>
+        <v>53.66</v>
       </c>
       <c r="I131" s="6" t="inlineStr">
         <is>
@@ -6352,9 +6352,11 @@
         </is>
       </c>
       <c r="J131" s="2" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="K131" s="2" t="n"/>
+        <v>2.794</v>
+      </c>
+      <c r="K131" s="2" t="n">
+        <v>2.664</v>
+      </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="7" t="inlineStr"/>
     </row>
@@ -6366,28 +6368,28 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>0233</t>
+          <t>0151</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>PEKAT</t>
+          <t>KGB</t>
         </is>
       </c>
       <c r="D132" s="2" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="E132" s="10" t="n">
-        <v>0.0181</v>
+        <v>8.390000000000001</v>
+      </c>
+      <c r="E132" s="9" t="n">
+        <v>0.0048</v>
       </c>
       <c r="F132" s="4" t="n">
-        <v>1239100</v>
+        <v>1344300</v>
       </c>
       <c r="G132" s="5" t="n">
-        <v>0.34</v>
+        <v>0.59</v>
       </c>
       <c r="H132" t="n">
-        <v>59.35</v>
+        <v>43.5</v>
       </c>
       <c r="I132" s="6" t="inlineStr">
         <is>
@@ -6395,10 +6397,10 @@
         </is>
       </c>
       <c r="J132" s="2" t="n">
-        <v>2.68</v>
+        <v>8.631</v>
       </c>
       <c r="K132" s="2" t="n">
-        <v>2.262</v>
+        <v>8.695</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="7" t="inlineStr"/>
@@ -6411,28 +6413,28 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>SUNREIT</t>
         </is>
       </c>
       <c r="D133" s="2" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="E133" s="8" t="n">
-        <v>-0.0273</v>
+        <v>2.02</v>
+      </c>
+      <c r="E133" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F133" s="4" t="n">
-        <v>1207200</v>
+        <v>1324700</v>
       </c>
       <c r="G133" s="5" t="n">
-        <v>0.23</v>
+        <v>0.41</v>
       </c>
       <c r="H133" t="n">
-        <v>32.47</v>
+        <v>44.02</v>
       </c>
       <c r="I133" s="6" t="inlineStr">
         <is>
@@ -6440,10 +6442,10 @@
         </is>
       </c>
       <c r="J133" s="2" t="n">
-        <v>2.807</v>
+        <v>2.044</v>
       </c>
       <c r="K133" s="2" t="n">
-        <v>2.877</v>
+        <v>2.071</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="7" t="inlineStr"/>
@@ -6456,39 +6458,39 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>8494</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>LBICAP</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D134" s="2" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>0.865</v>
+      </c>
+      <c r="E134" s="9" t="n">
+        <v>0.0058</v>
       </c>
       <c r="F134" s="4" t="n">
-        <v>1191600</v>
+        <v>1312000</v>
       </c>
       <c r="G134" s="5" t="n">
-        <v>6.8</v>
+        <v>0.42</v>
       </c>
       <c r="H134" t="n">
-        <v>79.44</v>
-      </c>
-      <c r="I134" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.3</v>
+      </c>
+      <c r="I134" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J134" s="2" t="n">
-        <v>0.463</v>
+        <v>0.864</v>
       </c>
       <c r="K134" s="2" t="n">
-        <v>0.405</v>
+        <v>0.859</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="7" t="inlineStr"/>
@@ -6501,28 +6503,28 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>0151</t>
+          <t>0470</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>KGB</t>
+          <t>BFIELD</t>
         </is>
       </c>
       <c r="D135" s="2" t="n">
-        <v>8.359999999999999</v>
-      </c>
-      <c r="E135" s="10" t="n">
-        <v>0.0012</v>
+        <v>0.42</v>
+      </c>
+      <c r="E135" s="3" t="n">
+        <v>-0.0118</v>
       </c>
       <c r="F135" s="4" t="n">
-        <v>1191500</v>
+        <v>1307700</v>
       </c>
       <c r="G135" s="5" t="n">
-        <v>0.52</v>
+        <v>0.24</v>
       </c>
       <c r="H135" t="n">
-        <v>42.66</v>
+        <v>17.86</v>
       </c>
       <c r="I135" s="6" t="inlineStr">
         <is>
@@ -6530,11 +6532,9 @@
         </is>
       </c>
       <c r="J135" s="2" t="n">
-        <v>8.629</v>
-      </c>
-      <c r="K135" s="2" t="n">
-        <v>8.695</v>
-      </c>
+        <v>0.46</v>
+      </c>
+      <c r="K135" s="2" t="n"/>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="7" t="inlineStr"/>
     </row>
@@ -6546,28 +6546,28 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>0045</t>
+          <t>5932</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>SSB8</t>
+          <t>BPURI</t>
         </is>
       </c>
       <c r="D136" s="2" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E136" s="8" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.21</v>
+      </c>
+      <c r="E136" s="3" t="n">
+        <v>-0.0233</v>
       </c>
       <c r="F136" s="4" t="n">
-        <v>1172700</v>
+        <v>1297400</v>
       </c>
       <c r="G136" s="5" t="n">
-        <v>0.31</v>
+        <v>1.89</v>
       </c>
       <c r="H136" t="n">
-        <v>48.81</v>
+        <v>38.22</v>
       </c>
       <c r="I136" s="6" t="inlineStr">
         <is>
@@ -6575,10 +6575,10 @@
         </is>
       </c>
       <c r="J136" s="2" t="n">
-        <v>0.638</v>
+        <v>0.223</v>
       </c>
       <c r="K136" s="2" t="n">
-        <v>0.614</v>
+        <v>0.232</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="7" t="inlineStr"/>
@@ -6591,39 +6591,39 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>0337</t>
+          <t>0298</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>SET</t>
+          <t>WENTEL</t>
         </is>
       </c>
       <c r="D137" s="2" t="n">
-        <v>0.245</v>
-      </c>
-      <c r="E137" s="10" t="n">
-        <v>0.0208</v>
+        <v>0.235</v>
+      </c>
+      <c r="E137" s="3" t="n">
+        <v>-0.0408</v>
       </c>
       <c r="F137" s="4" t="n">
-        <v>1158600</v>
+        <v>1295300</v>
       </c>
       <c r="G137" s="5" t="n">
-        <v>0.59</v>
+        <v>0.76</v>
       </c>
       <c r="H137" t="n">
-        <v>53.4</v>
-      </c>
-      <c r="I137" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.24</v>
+      </c>
+      <c r="I137" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J137" s="2" t="n">
-        <v>0.24</v>
+        <v>0.254</v>
       </c>
       <c r="K137" s="2" t="n">
-        <v>0.242</v>
+        <v>0.274</v>
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" s="7" t="inlineStr"/>
@@ -6636,39 +6636,39 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>7160</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>PENTA</t>
         </is>
       </c>
       <c r="D138" s="2" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="E138" s="8" t="n">
-        <v>-0.0323</v>
+        <v>5.49</v>
+      </c>
+      <c r="E138" s="3" t="n">
+        <v>-0.0196</v>
       </c>
       <c r="F138" s="4" t="n">
-        <v>1140800</v>
+        <v>1294200</v>
       </c>
       <c r="G138" s="5" t="n">
-        <v>0.46</v>
+        <v>0.34</v>
       </c>
       <c r="H138" t="n">
-        <v>53.86</v>
-      </c>
-      <c r="I138" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.47</v>
+      </c>
+      <c r="I138" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J138" s="2" t="n">
-        <v>0.734</v>
+        <v>5.512</v>
       </c>
       <c r="K138" s="2" t="n">
-        <v>0.704</v>
+        <v>5.393</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" s="7" t="inlineStr"/>
@@ -6681,28 +6681,28 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>SPSETIA</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D139" s="2" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="E139" s="10" t="n">
-        <v>0.0147</v>
+        <v>3.96</v>
+      </c>
+      <c r="E139" s="9" t="n">
+        <v>0.0102</v>
       </c>
       <c r="F139" s="4" t="n">
-        <v>1137500</v>
+        <v>1288600</v>
       </c>
       <c r="G139" s="5" t="n">
-        <v>0.17</v>
+        <v>0.13</v>
       </c>
       <c r="H139" t="n">
-        <v>33.21</v>
+        <v>52.54</v>
       </c>
       <c r="I139" s="6" t="inlineStr">
         <is>
@@ -6710,10 +6710,10 @@
         </is>
       </c>
       <c r="J139" s="2" t="n">
-        <v>0.725</v>
+        <v>3.96</v>
       </c>
       <c r="K139" s="2" t="n">
-        <v>0.791</v>
+        <v>3.556</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" s="7" t="inlineStr"/>
@@ -6726,39 +6726,39 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>1619</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>DRBHCOM</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D140" s="2" t="n">
-        <v>0.8149999999999999</v>
+        <v>6.45</v>
       </c>
       <c r="E140" s="3" t="n">
-        <v>0</v>
+        <v>-0.0077</v>
       </c>
       <c r="F140" s="4" t="n">
-        <v>1132700</v>
+        <v>1273800</v>
       </c>
       <c r="G140" s="5" t="n">
-        <v>2.3</v>
+        <v>0.22</v>
       </c>
       <c r="H140" t="n">
-        <v>17.34</v>
-      </c>
-      <c r="I140" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.2</v>
+      </c>
+      <c r="I140" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J140" s="2" t="n">
-        <v>0.885</v>
+        <v>6.168</v>
       </c>
       <c r="K140" s="2" t="n">
-        <v>0.9379999999999999</v>
+        <v>5.911</v>
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" s="7" t="inlineStr"/>
@@ -6771,39 +6771,39 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D141" s="2" t="n">
-        <v>6.41</v>
-      </c>
-      <c r="E141" s="8" t="n">
-        <v>-0.0138</v>
+        <v>2.49</v>
+      </c>
+      <c r="E141" s="3" t="n">
+        <v>-0.0273</v>
       </c>
       <c r="F141" s="4" t="n">
-        <v>1101700</v>
+        <v>1272900</v>
       </c>
       <c r="G141" s="5" t="n">
-        <v>0.19</v>
+        <v>0.25</v>
       </c>
       <c r="H141" t="n">
-        <v>55.51</v>
-      </c>
-      <c r="I141" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>32.47</v>
+      </c>
+      <c r="I141" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J141" s="2" t="n">
-        <v>6.164</v>
+        <v>2.807</v>
       </c>
       <c r="K141" s="2" t="n">
-        <v>5.91</v>
+        <v>2.877</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" s="7" t="inlineStr"/>
@@ -6816,39 +6816,39 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>PENTA</t>
+          <t>ATECH</t>
         </is>
       </c>
       <c r="D142" s="2" t="n">
-        <v>5.46</v>
-      </c>
-      <c r="E142" s="8" t="n">
-        <v>-0.025</v>
+        <v>0.77</v>
+      </c>
+      <c r="E142" s="3" t="n">
+        <v>-0.0191</v>
       </c>
       <c r="F142" s="4" t="n">
-        <v>1097600</v>
+        <v>1266700</v>
       </c>
       <c r="G142" s="5" t="n">
-        <v>0.29</v>
+        <v>0.54</v>
       </c>
       <c r="H142" t="n">
-        <v>49.74</v>
-      </c>
-      <c r="I142" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.22</v>
+      </c>
+      <c r="I142" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J142" s="2" t="n">
-        <v>5.509</v>
+        <v>0.776</v>
       </c>
       <c r="K142" s="2" t="n">
-        <v>5.393</v>
+        <v>0.769</v>
       </c>
       <c r="L142" t="inlineStr"/>
       <c r="M142" s="7" t="inlineStr"/>
@@ -6861,39 +6861,39 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>0223</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>SAMAIDEN</t>
         </is>
       </c>
       <c r="D143" s="2" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="E143" s="8" t="n">
-        <v>-0.0164</v>
+        <v>2.92</v>
+      </c>
+      <c r="E143" s="9" t="n">
+        <v>0.021</v>
       </c>
       <c r="F143" s="4" t="n">
-        <v>1095800</v>
+        <v>1260000</v>
       </c>
       <c r="G143" s="5" t="n">
-        <v>0.11</v>
+        <v>0.25</v>
       </c>
       <c r="H143" t="n">
-        <v>31.05</v>
-      </c>
-      <c r="I143" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>60.14</v>
+      </c>
+      <c r="I143" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J143" s="2" t="n">
-        <v>7.454</v>
+        <v>2.786</v>
       </c>
       <c r="K143" s="2" t="n">
-        <v>7.948</v>
+        <v>2.213</v>
       </c>
       <c r="L143" t="inlineStr"/>
       <c r="M143" s="7" t="inlineStr"/>
@@ -6906,28 +6906,28 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>0045</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>SSB8</t>
         </is>
       </c>
       <c r="D144" s="2" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E144" s="3" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="E144" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F144" s="4" t="n">
-        <v>1091100</v>
+        <v>1210100</v>
       </c>
       <c r="G144" s="5" t="n">
-        <v>0.13</v>
+        <v>0.32</v>
       </c>
       <c r="H144" t="n">
-        <v>50.51</v>
+        <v>50.64</v>
       </c>
       <c r="I144" s="6" t="inlineStr">
         <is>
@@ -6935,10 +6935,10 @@
         </is>
       </c>
       <c r="J144" s="2" t="n">
-        <v>0.354</v>
+        <v>0.639</v>
       </c>
       <c r="K144" s="2" t="n">
-        <v>0.327</v>
+        <v>0.615</v>
       </c>
       <c r="L144" t="inlineStr"/>
       <c r="M144" s="7" t="inlineStr"/>
@@ -6951,28 +6951,28 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>CPETECH</t>
         </is>
       </c>
       <c r="D145" s="2" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="E145" s="10" t="n">
-        <v>0.014</v>
+        <v>1.28</v>
+      </c>
+      <c r="E145" s="3" t="n">
+        <v>-0.0303</v>
       </c>
       <c r="F145" s="4" t="n">
-        <v>1063700</v>
+        <v>1202000</v>
       </c>
       <c r="G145" s="5" t="n">
-        <v>0.21</v>
+        <v>0.38</v>
       </c>
       <c r="H145" t="n">
-        <v>59.52</v>
+        <v>50.47</v>
       </c>
       <c r="I145" s="6" t="inlineStr">
         <is>
@@ -6980,10 +6980,10 @@
         </is>
       </c>
       <c r="J145" s="2" t="n">
-        <v>2.784</v>
+        <v>1.288</v>
       </c>
       <c r="K145" s="2" t="n">
-        <v>2.212</v>
+        <v>1.225</v>
       </c>
       <c r="L145" t="inlineStr"/>
       <c r="M145" s="7" t="inlineStr"/>
@@ -6996,28 +6996,28 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D146" s="2" t="n">
-        <v>3.97</v>
-      </c>
-      <c r="E146" s="10" t="n">
-        <v>0.0128</v>
+        <v>0.75</v>
+      </c>
+      <c r="E146" s="3" t="n">
+        <v>-0.0323</v>
       </c>
       <c r="F146" s="4" t="n">
-        <v>1058100</v>
+        <v>1194100</v>
       </c>
       <c r="G146" s="5" t="n">
-        <v>0.1</v>
+        <v>0.49</v>
       </c>
       <c r="H146" t="n">
-        <v>52.85</v>
+        <v>53.86</v>
       </c>
       <c r="I146" s="6" t="inlineStr">
         <is>
@@ -7025,10 +7025,10 @@
         </is>
       </c>
       <c r="J146" s="2" t="n">
-        <v>3.961</v>
+        <v>0.734</v>
       </c>
       <c r="K146" s="2" t="n">
-        <v>3.556</v>
+        <v>0.704</v>
       </c>
       <c r="L146" t="inlineStr"/>
       <c r="M146" s="7" t="inlineStr"/>
@@ -7041,39 +7041,39 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>0099</t>
+          <t>8494</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>SCICOM</t>
+          <t>LBICAP</t>
         </is>
       </c>
       <c r="D147" s="2" t="n">
-        <v>2.17</v>
+        <v>0.505</v>
       </c>
       <c r="E147" s="10" t="n">
-        <v>0.0383</v>
+        <v>0</v>
       </c>
       <c r="F147" s="4" t="n">
-        <v>1056800</v>
+        <v>1191600</v>
       </c>
       <c r="G147" s="5" t="n">
-        <v>1.43</v>
+        <v>6.8</v>
       </c>
       <c r="H147" t="n">
-        <v>46.79</v>
-      </c>
-      <c r="I147" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>79.44</v>
+      </c>
+      <c r="I147" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J147" s="2" t="n">
-        <v>2.204</v>
+        <v>0.463</v>
       </c>
       <c r="K147" s="2" t="n">
-        <v>2.236</v>
+        <v>0.405</v>
       </c>
       <c r="L147" t="inlineStr"/>
       <c r="M147" s="7" t="inlineStr"/>
@@ -7086,28 +7086,28 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>1619</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>DRBHCOM</t>
         </is>
       </c>
       <c r="D148" s="2" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="E148" s="8" t="n">
-        <v>-0.0059</v>
+        <v>0.805</v>
+      </c>
+      <c r="E148" s="3" t="n">
+        <v>-0.0123</v>
       </c>
       <c r="F148" s="4" t="n">
-        <v>1029900</v>
+        <v>1160800</v>
       </c>
       <c r="G148" s="5" t="n">
-        <v>0.35</v>
+        <v>2.35</v>
       </c>
       <c r="H148" t="n">
-        <v>16.62</v>
+        <v>16.17</v>
       </c>
       <c r="I148" s="6" t="inlineStr">
         <is>
@@ -7115,10 +7115,10 @@
         </is>
       </c>
       <c r="J148" s="2" t="n">
-        <v>0.915</v>
+        <v>0.885</v>
       </c>
       <c r="K148" s="2" t="n">
-        <v>0.973</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="L148" t="inlineStr"/>
       <c r="M148" s="7" t="inlineStr"/>
@@ -7131,39 +7131,39 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>0450</t>
+          <t>0337</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>MFGROUP</t>
+          <t>SET</t>
         </is>
       </c>
       <c r="D149" s="2" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="E149" s="8" t="n">
-        <v>-0.0175</v>
+        <v>0.245</v>
+      </c>
+      <c r="E149" s="9" t="n">
+        <v>0.0208</v>
       </c>
       <c r="F149" s="4" t="n">
-        <v>1006700</v>
+        <v>1158600</v>
       </c>
       <c r="G149" s="5" t="n">
-        <v>1.06</v>
+        <v>0.59</v>
       </c>
       <c r="H149" t="n">
-        <v>55.75</v>
-      </c>
-      <c r="I149" s="9" t="inlineStr">
+        <v>53.4</v>
+      </c>
+      <c r="I149" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J149" s="2" t="n">
-        <v>0.276</v>
+        <v>0.24</v>
       </c>
       <c r="K149" s="2" t="n">
-        <v>0.267</v>
+        <v>0.242</v>
       </c>
       <c r="L149" t="inlineStr"/>
       <c r="M149" s="7" t="inlineStr"/>
@@ -7176,28 +7176,28 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>0277</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>ATECH</t>
+          <t>CLOUDPT</t>
         </is>
       </c>
       <c r="D150" s="2" t="n">
-        <v>0.755</v>
-      </c>
-      <c r="E150" s="8" t="n">
-        <v>-0.0382</v>
+        <v>0.475</v>
+      </c>
+      <c r="E150" s="3" t="n">
+        <v>-0.0404</v>
       </c>
       <c r="F150" s="4" t="n">
-        <v>1005400</v>
+        <v>1142500</v>
       </c>
       <c r="G150" s="5" t="n">
-        <v>0.43</v>
+        <v>0.51</v>
       </c>
       <c r="H150" t="n">
-        <v>46.3</v>
+        <v>45.11</v>
       </c>
       <c r="I150" s="6" t="inlineStr">
         <is>
@@ -7205,10 +7205,10 @@
         </is>
       </c>
       <c r="J150" s="2" t="n">
-        <v>0.775</v>
+        <v>0.491</v>
       </c>
       <c r="K150" s="2" t="n">
-        <v>0.769</v>
+        <v>0.485</v>
       </c>
       <c r="L150" t="inlineStr"/>
       <c r="M150" s="7" t="inlineStr"/>
@@ -7221,28 +7221,28 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>5337</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>ECOSHOP</t>
         </is>
       </c>
       <c r="D151" s="2" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="E151" s="3" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="E151" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F151" s="4" t="n">
-        <v>962000</v>
+        <v>1077600</v>
       </c>
       <c r="G151" s="5" t="n">
-        <v>0.14</v>
+        <v>0.26</v>
       </c>
       <c r="H151" t="n">
-        <v>53.87</v>
+        <v>41.9</v>
       </c>
       <c r="I151" s="6" t="inlineStr">
         <is>
@@ -7250,10 +7250,10 @@
         </is>
       </c>
       <c r="J151" s="2" t="n">
-        <v>0.743</v>
+        <v>1.448</v>
       </c>
       <c r="K151" s="2" t="n">
-        <v>0.677</v>
+        <v>1.464</v>
       </c>
       <c r="L151" t="inlineStr"/>
       <c r="M151" s="7" t="inlineStr"/>
@@ -7266,28 +7266,28 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>0168</t>
+          <t>0099</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>BMGREEN</t>
+          <t>SCICOM</t>
         </is>
       </c>
       <c r="D152" s="2" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="E152" s="8" t="n">
-        <v>-0.0544</v>
+        <v>2.14</v>
+      </c>
+      <c r="E152" s="9" t="n">
+        <v>0.0239</v>
       </c>
       <c r="F152" s="4" t="n">
-        <v>933200</v>
+        <v>1067100</v>
       </c>
       <c r="G152" s="5" t="n">
-        <v>0.97</v>
+        <v>1.44</v>
       </c>
       <c r="H152" t="n">
-        <v>29.55</v>
+        <v>44.38</v>
       </c>
       <c r="I152" s="6" t="inlineStr">
         <is>
@@ -7295,10 +7295,10 @@
         </is>
       </c>
       <c r="J152" s="2" t="n">
-        <v>1.553</v>
+        <v>2.201</v>
       </c>
       <c r="K152" s="2" t="n">
-        <v>1.648</v>
+        <v>2.236</v>
       </c>
       <c r="L152" t="inlineStr"/>
       <c r="M152" s="7" t="inlineStr"/>
@@ -7311,28 +7311,28 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>5789</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>LBS</t>
         </is>
       </c>
       <c r="D153" s="2" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="E153" s="8" t="n">
-        <v>-0.0379</v>
+        <v>0.375</v>
+      </c>
+      <c r="E153" s="9" t="n">
+        <v>0.0135</v>
       </c>
       <c r="F153" s="4" t="n">
-        <v>923900</v>
+        <v>1054400</v>
       </c>
       <c r="G153" s="5" t="n">
-        <v>0.29</v>
+        <v>0.68</v>
       </c>
       <c r="H153" t="n">
-        <v>49.69</v>
+        <v>39.13</v>
       </c>
       <c r="I153" s="6" t="inlineStr">
         <is>
@@ -7340,10 +7340,10 @@
         </is>
       </c>
       <c r="J153" s="2" t="n">
-        <v>1.287</v>
+        <v>0.379</v>
       </c>
       <c r="K153" s="2" t="n">
-        <v>1.225</v>
+        <v>0.391</v>
       </c>
       <c r="L153" t="inlineStr"/>
       <c r="M153" s="7" t="inlineStr"/>
@@ -7356,28 +7356,28 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D154" s="2" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="E154" s="10" t="n">
-        <v>0.0177</v>
+        <v>0.745</v>
+      </c>
+      <c r="E154" s="3" t="n">
+        <v>-0.0067</v>
       </c>
       <c r="F154" s="4" t="n">
-        <v>897000</v>
+        <v>1037600</v>
       </c>
       <c r="G154" s="5" t="n">
-        <v>0.11</v>
+        <v>0.15</v>
       </c>
       <c r="H154" t="n">
-        <v>57.19</v>
+        <v>52.97</v>
       </c>
       <c r="I154" s="6" t="inlineStr">
         <is>
@@ -7385,10 +7385,10 @@
         </is>
       </c>
       <c r="J154" s="2" t="n">
-        <v>1.114</v>
+        <v>0.742</v>
       </c>
       <c r="K154" s="2" t="n">
-        <v>0.888</v>
+        <v>0.676</v>
       </c>
       <c r="L154" t="inlineStr"/>
       <c r="M154" s="7" t="inlineStr"/>
@@ -7401,39 +7401,39 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>7498</t>
+          <t>0450</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>RALCO</t>
+          <t>MFGROUP</t>
         </is>
       </c>
       <c r="D155" s="2" t="n">
-        <v>1.02</v>
+        <v>0.28</v>
       </c>
       <c r="E155" s="3" t="n">
-        <v>0</v>
+        <v>-0.0175</v>
       </c>
       <c r="F155" s="4" t="n">
-        <v>878700</v>
+        <v>1006700</v>
       </c>
       <c r="G155" s="5" t="n">
-        <v>1.28</v>
+        <v>1.06</v>
       </c>
       <c r="H155" t="n">
-        <v>59.46</v>
-      </c>
-      <c r="I155" s="9" t="inlineStr">
+        <v>55.75</v>
+      </c>
+      <c r="I155" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J155" s="2" t="n">
-        <v>1.004</v>
+        <v>0.276</v>
       </c>
       <c r="K155" s="2" t="n">
-        <v>0.984</v>
+        <v>0.267</v>
       </c>
       <c r="L155" t="inlineStr"/>
       <c r="M155" s="7" t="inlineStr"/>
@@ -7446,28 +7446,28 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>6971</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>KOBAY</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D156" s="2" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="E156" s="8" t="n">
-        <v>-0.019</v>
+        <v>0.3</v>
+      </c>
+      <c r="E156" s="3" t="n">
+        <v>-0.0164</v>
       </c>
       <c r="F156" s="4" t="n">
-        <v>862400</v>
+        <v>1002700</v>
       </c>
       <c r="G156" s="5" t="n">
-        <v>0.71</v>
+        <v>0.16</v>
       </c>
       <c r="H156" t="n">
-        <v>42.97</v>
+        <v>40.49</v>
       </c>
       <c r="I156" s="6" t="inlineStr">
         <is>
@@ -7475,10 +7475,10 @@
         </is>
       </c>
       <c r="J156" s="2" t="n">
-        <v>2.124</v>
+        <v>0.316</v>
       </c>
       <c r="K156" s="2" t="n">
-        <v>2.28</v>
+        <v>0.336</v>
       </c>
       <c r="L156" t="inlineStr"/>
       <c r="M156" s="7" t="inlineStr"/>
@@ -7491,28 +7491,28 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>5211</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>SUNWAY</t>
+          <t>AMBANK</t>
         </is>
       </c>
       <c r="D157" s="2" t="n">
-        <v>4.21</v>
-      </c>
-      <c r="E157" s="10" t="n">
-        <v>0.0072</v>
+        <v>6.16</v>
+      </c>
+      <c r="E157" s="3" t="n">
+        <v>-0.0299</v>
       </c>
       <c r="F157" s="4" t="n">
-        <v>814800</v>
+        <v>967200</v>
       </c>
       <c r="G157" s="5" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="H157" t="n">
-        <v>34.43</v>
+        <v>35.5</v>
       </c>
       <c r="I157" s="6" t="inlineStr">
         <is>
@@ -7520,10 +7520,10 @@
         </is>
       </c>
       <c r="J157" s="2" t="n">
-        <v>4.41</v>
+        <v>6.388</v>
       </c>
       <c r="K157" s="2" t="n">
-        <v>4.719</v>
+        <v>6.754</v>
       </c>
       <c r="L157" t="inlineStr"/>
       <c r="M157" s="7" t="inlineStr"/>
@@ -7536,39 +7536,39 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>6947</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D158" s="2" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="E158" s="8" t="n">
-        <v>-0.0235</v>
+        <v>1.16</v>
+      </c>
+      <c r="E158" s="9" t="n">
+        <v>0.0265</v>
       </c>
       <c r="F158" s="4" t="n">
-        <v>769200</v>
+        <v>949000</v>
       </c>
       <c r="G158" s="5" t="n">
-        <v>0.26</v>
+        <v>0.12</v>
       </c>
       <c r="H158" t="n">
-        <v>38.18</v>
-      </c>
-      <c r="I158" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>57.9</v>
+      </c>
+      <c r="I158" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J158" s="2" t="n">
-        <v>2.558</v>
+        <v>1.114</v>
       </c>
       <c r="K158" s="2" t="n">
-        <v>2.685</v>
+        <v>0.888</v>
       </c>
       <c r="L158" t="inlineStr"/>
       <c r="M158" s="7" t="inlineStr"/>
@@ -7581,28 +7581,28 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>4383</t>
+          <t>0168</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>JTIASA</t>
+          <t>BMGREEN</t>
         </is>
       </c>
       <c r="D159" s="2" t="n">
-        <v>0.905</v>
+        <v>1.4</v>
       </c>
       <c r="E159" s="3" t="n">
-        <v>0</v>
+        <v>-0.0476</v>
       </c>
       <c r="F159" s="4" t="n">
-        <v>739200</v>
+        <v>933700</v>
       </c>
       <c r="G159" s="5" t="n">
-        <v>0.4</v>
+        <v>0.97</v>
       </c>
       <c r="H159" t="n">
-        <v>31.25</v>
+        <v>30.17</v>
       </c>
       <c r="I159" s="6" t="inlineStr">
         <is>
@@ -7610,10 +7610,10 @@
         </is>
       </c>
       <c r="J159" s="2" t="n">
-        <v>0.944</v>
+        <v>1.554</v>
       </c>
       <c r="K159" s="2" t="n">
-        <v>1.002</v>
+        <v>1.648</v>
       </c>
       <c r="L159" t="inlineStr"/>
       <c r="M159" s="7" t="inlineStr"/>
@@ -7626,39 +7626,39 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>0271</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>WELLS</t>
+          <t>DUFU</t>
         </is>
       </c>
       <c r="D160" s="2" t="n">
-        <v>0.555</v>
-      </c>
-      <c r="E160" s="10" t="n">
-        <v>0.0091</v>
+        <v>3.03</v>
+      </c>
+      <c r="E160" s="3" t="n">
+        <v>-0.013</v>
       </c>
       <c r="F160" s="4" t="n">
-        <v>730000</v>
+        <v>910600</v>
       </c>
       <c r="G160" s="5" t="n">
-        <v>0.64</v>
+        <v>0.29</v>
       </c>
       <c r="H160" t="n">
-        <v>42.07</v>
-      </c>
-      <c r="I160" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.14</v>
+      </c>
+      <c r="I160" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J160" s="2" t="n">
-        <v>0.5679999999999999</v>
+        <v>3.029</v>
       </c>
       <c r="K160" s="2" t="n">
-        <v>0.611</v>
+        <v>2.856</v>
       </c>
       <c r="L160" t="inlineStr"/>
       <c r="M160" s="7" t="inlineStr"/>
@@ -7671,39 +7671,39 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>6947</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>DAYANG</t>
+          <t>CDB</t>
         </is>
       </c>
       <c r="D161" s="2" t="n">
-        <v>1.32</v>
+        <v>2.48</v>
       </c>
       <c r="E161" s="3" t="n">
-        <v>0</v>
+        <v>-0.0275</v>
       </c>
       <c r="F161" s="4" t="n">
-        <v>729700</v>
+        <v>905200</v>
       </c>
       <c r="G161" s="5" t="n">
-        <v>0.37</v>
+        <v>0.3</v>
       </c>
       <c r="H161" t="n">
-        <v>27.74</v>
-      </c>
-      <c r="I161" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>37.3</v>
+      </c>
+      <c r="I161" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J161" s="2" t="n">
-        <v>1.404</v>
+        <v>2.557</v>
       </c>
       <c r="K161" s="2" t="n">
-        <v>1.466</v>
+        <v>2.685</v>
       </c>
       <c r="L161" t="inlineStr"/>
       <c r="M161" s="7" t="inlineStr"/>
@@ -7716,28 +7716,28 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>DUFU</t>
+          <t>SUNWAY</t>
         </is>
       </c>
       <c r="D162" s="2" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="E162" s="8" t="n">
-        <v>-0.013</v>
+        <v>4.21</v>
+      </c>
+      <c r="E162" s="9" t="n">
+        <v>0.0072</v>
       </c>
       <c r="F162" s="4" t="n">
-        <v>679900</v>
+        <v>884400</v>
       </c>
       <c r="G162" s="5" t="n">
-        <v>0.22</v>
+        <v>0.18</v>
       </c>
       <c r="H162" t="n">
-        <v>52.14</v>
+        <v>34.43</v>
       </c>
       <c r="I162" s="6" t="inlineStr">
         <is>
@@ -7745,10 +7745,10 @@
         </is>
       </c>
       <c r="J162" s="2" t="n">
-        <v>3.029</v>
+        <v>4.41</v>
       </c>
       <c r="K162" s="2" t="n">
-        <v>2.856</v>
+        <v>4.719</v>
       </c>
       <c r="L162" t="inlineStr"/>
       <c r="M162" s="7" t="inlineStr"/>
@@ -7761,28 +7761,28 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>5299</t>
+          <t>6971</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>IGBCR</t>
+          <t>KOBAY</t>
         </is>
       </c>
       <c r="D163" s="2" t="n">
-        <v>0.61</v>
+        <v>2.05</v>
       </c>
       <c r="E163" s="3" t="n">
-        <v>0</v>
+        <v>-0.0238</v>
       </c>
       <c r="F163" s="4" t="n">
-        <v>667100</v>
+        <v>878800</v>
       </c>
       <c r="G163" s="5" t="n">
-        <v>2.84</v>
+        <v>0.72</v>
       </c>
       <c r="H163" t="n">
-        <v>44.28</v>
+        <v>42.39</v>
       </c>
       <c r="I163" s="6" t="inlineStr">
         <is>
@@ -7790,10 +7790,10 @@
         </is>
       </c>
       <c r="J163" s="2" t="n">
-        <v>0.614</v>
+        <v>2.123</v>
       </c>
       <c r="K163" s="2" t="n">
-        <v>0.613</v>
+        <v>2.28</v>
       </c>
       <c r="L163" t="inlineStr"/>
       <c r="M163" s="7" t="inlineStr"/>
@@ -7806,39 +7806,39 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>0097</t>
+          <t>7498</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>VITROX</t>
+          <t>RALCO</t>
         </is>
       </c>
       <c r="D164" s="2" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E164" s="8" t="n">
-        <v>-0.0189</v>
+        <v>1.02</v>
+      </c>
+      <c r="E164" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F164" s="4" t="n">
-        <v>667000</v>
+        <v>878700</v>
       </c>
       <c r="G164" s="5" t="n">
-        <v>0.19</v>
+        <v>1.28</v>
       </c>
       <c r="H164" t="n">
-        <v>53.02</v>
-      </c>
-      <c r="I164" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.46</v>
+      </c>
+      <c r="I164" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J164" s="2" t="n">
-        <v>10.407</v>
+        <v>1.004</v>
       </c>
       <c r="K164" s="2" t="n">
-        <v>9.755000000000001</v>
+        <v>0.984</v>
       </c>
       <c r="L164" t="inlineStr"/>
       <c r="M164" s="7" t="inlineStr"/>
@@ -7851,28 +7851,28 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>JPG</t>
+          <t>DAYANG</t>
         </is>
       </c>
       <c r="D165" s="2" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="E165" s="10" t="n">
-        <v>0.0175</v>
+        <v>1.3</v>
+      </c>
+      <c r="E165" s="3" t="n">
+        <v>-0.0152</v>
       </c>
       <c r="F165" s="4" t="n">
-        <v>655700</v>
+        <v>851000</v>
       </c>
       <c r="G165" s="5" t="n">
-        <v>0.11</v>
+        <v>0.43</v>
       </c>
       <c r="H165" t="n">
-        <v>41.01</v>
+        <v>25.64</v>
       </c>
       <c r="I165" s="6" t="inlineStr">
         <is>
@@ -7880,10 +7880,10 @@
         </is>
       </c>
       <c r="J165" s="2" t="n">
-        <v>1.776</v>
+        <v>1.402</v>
       </c>
       <c r="K165" s="2" t="n">
-        <v>1.888</v>
+        <v>1.465</v>
       </c>
       <c r="L165" t="inlineStr"/>
       <c r="M165" s="7" t="inlineStr"/>
@@ -7896,39 +7896,39 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>7293</t>
+          <t>5005</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>YINSON</t>
+          <t>UNISEM</t>
         </is>
       </c>
       <c r="D166" s="2" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="E166" s="10" t="n">
-        <v>0.004699999999999999</v>
+        <v>4.15</v>
+      </c>
+      <c r="E166" s="3" t="n">
+        <v>-0.0189</v>
       </c>
       <c r="F166" s="4" t="n">
-        <v>651100</v>
+        <v>843900</v>
       </c>
       <c r="G166" s="5" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="H166" t="n">
-        <v>55.88</v>
-      </c>
-      <c r="I166" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.31</v>
+      </c>
+      <c r="I166" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J166" s="2" t="n">
-        <v>2.111</v>
+        <v>4.287</v>
       </c>
       <c r="K166" s="2" t="n">
-        <v>2.063</v>
+        <v>4.326</v>
       </c>
       <c r="L166" t="inlineStr"/>
       <c r="M166" s="7" t="inlineStr"/>
@@ -7941,39 +7941,39 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>3417</t>
+          <t>7293</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>E&amp;O</t>
+          <t>YINSON</t>
         </is>
       </c>
       <c r="D167" s="2" t="n">
-        <v>0.745</v>
-      </c>
-      <c r="E167" s="8" t="n">
-        <v>-0.0067</v>
+        <v>2.13</v>
+      </c>
+      <c r="E167" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F167" s="4" t="n">
-        <v>649700</v>
+        <v>777300</v>
       </c>
       <c r="G167" s="5" t="n">
-        <v>0.48</v>
+        <v>0.37</v>
       </c>
       <c r="H167" t="n">
-        <v>40.03</v>
-      </c>
-      <c r="I167" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.7</v>
+      </c>
+      <c r="I167" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J167" s="2" t="n">
-        <v>0.764</v>
+        <v>2.11</v>
       </c>
       <c r="K167" s="2" t="n">
-        <v>0.769</v>
+        <v>2.062</v>
       </c>
       <c r="L167" t="inlineStr"/>
       <c r="M167" s="7" t="inlineStr"/>
@@ -7986,28 +7986,28 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>5323</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>JPG</t>
         </is>
       </c>
       <c r="D168" s="2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="E168" s="8" t="n">
-        <v>-0.0098</v>
+        <v>1.74</v>
+      </c>
+      <c r="E168" s="9" t="n">
+        <v>0.0175</v>
       </c>
       <c r="F168" s="4" t="n">
-        <v>645700</v>
+        <v>776600</v>
       </c>
       <c r="G168" s="5" t="n">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
       <c r="H168" t="n">
-        <v>47.81</v>
+        <v>41.01</v>
       </c>
       <c r="I168" s="6" t="inlineStr">
         <is>
@@ -8015,10 +8015,10 @@
         </is>
       </c>
       <c r="J168" s="2" t="n">
-        <v>1.044</v>
+        <v>1.776</v>
       </c>
       <c r="K168" s="2" t="n">
-        <v>0.9419999999999999</v>
+        <v>1.888</v>
       </c>
       <c r="L168" t="inlineStr"/>
       <c r="M168" s="7" t="inlineStr"/>
@@ -8031,28 +8031,28 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>4383</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>JTIASA</t>
         </is>
       </c>
       <c r="D169" s="2" t="n">
-        <v>0.655</v>
-      </c>
-      <c r="E169" s="8" t="n">
-        <v>-0.0224</v>
+        <v>0.905</v>
+      </c>
+      <c r="E169" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F169" s="4" t="n">
-        <v>641300</v>
+        <v>739200</v>
       </c>
       <c r="G169" s="5" t="n">
-        <v>0.19</v>
+        <v>0.4</v>
       </c>
       <c r="H169" t="n">
-        <v>34.29</v>
+        <v>31.25</v>
       </c>
       <c r="I169" s="6" t="inlineStr">
         <is>
@@ -8060,10 +8060,10 @@
         </is>
       </c>
       <c r="J169" s="2" t="n">
-        <v>0.724</v>
+        <v>0.944</v>
       </c>
       <c r="K169" s="2" t="n">
-        <v>0.744</v>
+        <v>1.002</v>
       </c>
       <c r="L169" t="inlineStr"/>
       <c r="M169" s="7" t="inlineStr"/>
@@ -8076,39 +8076,39 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>5258</t>
+          <t>0271</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>BIMB</t>
+          <t>WELLS</t>
         </is>
       </c>
       <c r="D170" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E170" s="8" t="n">
-        <v>-0.005</v>
+        <v>0.555</v>
+      </c>
+      <c r="E170" s="9" t="n">
+        <v>0.0091</v>
       </c>
       <c r="F170" s="4" t="n">
-        <v>639600</v>
+        <v>730000</v>
       </c>
       <c r="G170" s="5" t="n">
-        <v>0.75</v>
+        <v>0.64</v>
       </c>
       <c r="H170" t="n">
-        <v>34.83</v>
-      </c>
-      <c r="I170" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>42.07</v>
+      </c>
+      <c r="I170" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J170" s="2" t="n">
-        <v>2.037</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="K170" s="2" t="n">
-        <v>2.081</v>
+        <v>0.611</v>
       </c>
       <c r="L170" t="inlineStr"/>
       <c r="M170" s="7" t="inlineStr"/>
@@ -8121,39 +8121,39 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>0359</t>
+          <t>5299</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>HKB</t>
+          <t>IGBCR</t>
         </is>
       </c>
       <c r="D171" s="2" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E171" s="8" t="n">
-        <v>-0.0127</v>
+        <v>0.61</v>
+      </c>
+      <c r="E171" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F171" s="4" t="n">
-        <v>612300</v>
+        <v>729700</v>
       </c>
       <c r="G171" s="5" t="n">
-        <v>0.27</v>
+        <v>3.1</v>
       </c>
       <c r="H171" t="n">
-        <v>67.27</v>
-      </c>
-      <c r="I171" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.28</v>
+      </c>
+      <c r="I171" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J171" s="2" t="n">
-        <v>0.73</v>
+        <v>0.614</v>
       </c>
       <c r="K171" s="2" t="n">
-        <v>0.648</v>
+        <v>0.613</v>
       </c>
       <c r="L171" t="inlineStr"/>
       <c r="M171" s="7" t="inlineStr"/>
@@ -8166,39 +8166,39 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>0097</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>TAKAFUL</t>
+          <t>VITROX</t>
         </is>
       </c>
       <c r="D172" s="2" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="E172" s="8" t="n">
-        <v>-0.0138</v>
+        <v>10.46</v>
+      </c>
+      <c r="E172" s="3" t="n">
+        <v>-0.0132</v>
       </c>
       <c r="F172" s="4" t="n">
-        <v>606500</v>
+        <v>718000</v>
       </c>
       <c r="G172" s="5" t="n">
-        <v>0.47</v>
+        <v>0.2</v>
       </c>
       <c r="H172" t="n">
-        <v>34.01</v>
-      </c>
-      <c r="I172" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>54.18</v>
+      </c>
+      <c r="I172" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J172" s="2" t="n">
-        <v>2.927</v>
+        <v>10.413</v>
       </c>
       <c r="K172" s="2" t="n">
-        <v>3.063</v>
+        <v>9.757</v>
       </c>
       <c r="L172" t="inlineStr"/>
       <c r="M172" s="7" t="inlineStr"/>
@@ -8211,28 +8211,28 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>5236</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>MATRIX</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D173" s="2" t="n">
         <v>1.02</v>
       </c>
-      <c r="E173" s="8" t="n">
-        <v>-0.0286</v>
+      <c r="E173" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F173" s="4" t="n">
-        <v>604400</v>
+        <v>714700</v>
       </c>
       <c r="G173" s="5" t="n">
-        <v>0.45</v>
+        <v>0.17</v>
       </c>
       <c r="H173" t="n">
-        <v>33.2</v>
+        <v>49.25</v>
       </c>
       <c r="I173" s="6" t="inlineStr">
         <is>
@@ -8240,10 +8240,10 @@
         </is>
       </c>
       <c r="J173" s="2" t="n">
-        <v>1.084</v>
+        <v>1.045</v>
       </c>
       <c r="K173" s="2" t="n">
-        <v>1.132</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="L173" t="inlineStr"/>
       <c r="M173" s="7" t="inlineStr"/>
@@ -8256,39 +8256,39 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>5212</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>PAVREIT</t>
+          <t>WPRTS</t>
         </is>
       </c>
       <c r="D174" s="2" t="n">
-        <v>1.56</v>
+        <v>6.74</v>
       </c>
       <c r="E174" s="3" t="n">
-        <v>0</v>
+        <v>-0.003</v>
       </c>
       <c r="F174" s="4" t="n">
-        <v>575000</v>
+        <v>695300</v>
       </c>
       <c r="G174" s="5" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="H174" t="n">
-        <v>47.18</v>
-      </c>
-      <c r="I174" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.63</v>
+      </c>
+      <c r="I174" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J174" s="2" t="n">
-        <v>1.568</v>
+        <v>6.755</v>
       </c>
       <c r="K174" s="2" t="n">
-        <v>1.601</v>
+        <v>6.826</v>
       </c>
       <c r="L174" t="inlineStr"/>
       <c r="M174" s="7" t="inlineStr"/>
@@ -8301,28 +8301,28 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>5258</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>AMBANK</t>
+          <t>BIMB</t>
         </is>
       </c>
       <c r="D175" s="2" t="n">
-        <v>6.17</v>
-      </c>
-      <c r="E175" s="8" t="n">
-        <v>-0.0283</v>
+        <v>2</v>
+      </c>
+      <c r="E175" s="3" t="n">
+        <v>-0.005</v>
       </c>
       <c r="F175" s="4" t="n">
-        <v>545900</v>
+        <v>668700</v>
       </c>
       <c r="G175" s="5" t="n">
-        <v>0.09</v>
+        <v>0.78</v>
       </c>
       <c r="H175" t="n">
-        <v>35.84</v>
+        <v>34.83</v>
       </c>
       <c r="I175" s="6" t="inlineStr">
         <is>
@@ -8330,10 +8330,10 @@
         </is>
       </c>
       <c r="J175" s="2" t="n">
-        <v>6.389</v>
+        <v>2.037</v>
       </c>
       <c r="K175" s="2" t="n">
-        <v>6.754</v>
+        <v>2.081</v>
       </c>
       <c r="L175" t="inlineStr"/>
       <c r="M175" s="7" t="inlineStr"/>
@@ -8346,39 +8346,39 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>5337</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>ECOSHOP</t>
+          <t>SIMEPROP</t>
         </is>
       </c>
       <c r="D176" s="2" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="E176" s="3" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="E176" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F176" s="4" t="n">
-        <v>545400</v>
+        <v>659300</v>
       </c>
       <c r="G176" s="5" t="n">
-        <v>0.13</v>
+        <v>0.15</v>
       </c>
       <c r="H176" t="n">
-        <v>41.9</v>
-      </c>
-      <c r="I176" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.38</v>
+      </c>
+      <c r="I176" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J176" s="2" t="n">
-        <v>1.448</v>
+        <v>1.26</v>
       </c>
       <c r="K176" s="2" t="n">
-        <v>1.464</v>
+        <v>1.278</v>
       </c>
       <c r="L176" t="inlineStr"/>
       <c r="M176" s="7" t="inlineStr"/>
@@ -8391,28 +8391,28 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>0293</t>
+          <t>3417</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>KJTS</t>
+          <t>E&amp;O</t>
         </is>
       </c>
       <c r="D177" s="2" t="n">
-        <v>0.84</v>
+        <v>0.745</v>
       </c>
       <c r="E177" s="3" t="n">
-        <v>0</v>
+        <v>-0.0067</v>
       </c>
       <c r="F177" s="4" t="n">
-        <v>543600</v>
+        <v>659100</v>
       </c>
       <c r="G177" s="5" t="n">
-        <v>0.45</v>
+        <v>0.49</v>
       </c>
       <c r="H177" t="n">
-        <v>31.12</v>
+        <v>40.03</v>
       </c>
       <c r="I177" s="6" t="inlineStr">
         <is>
@@ -8420,10 +8420,10 @@
         </is>
       </c>
       <c r="J177" s="2" t="n">
-        <v>0.951</v>
+        <v>0.764</v>
       </c>
       <c r="K177" s="2" t="n">
-        <v>1.023</v>
+        <v>0.769</v>
       </c>
       <c r="L177" t="inlineStr"/>
       <c r="M177" s="7" t="inlineStr"/>
@@ -8436,28 +8436,28 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>5005</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>UNISEM</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D178" s="2" t="n">
-        <v>4.11</v>
-      </c>
-      <c r="E178" s="8" t="n">
-        <v>-0.0284</v>
+        <v>0.655</v>
+      </c>
+      <c r="E178" s="3" t="n">
+        <v>-0.0224</v>
       </c>
       <c r="F178" s="4" t="n">
-        <v>540400</v>
+        <v>650600</v>
       </c>
       <c r="G178" s="5" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="H178" t="n">
-        <v>43.13</v>
+        <v>34.29</v>
       </c>
       <c r="I178" s="6" t="inlineStr">
         <is>
@@ -8465,10 +8465,10 @@
         </is>
       </c>
       <c r="J178" s="2" t="n">
-        <v>4.283</v>
+        <v>0.724</v>
       </c>
       <c r="K178" s="2" t="n">
-        <v>4.325</v>
+        <v>0.744</v>
       </c>
       <c r="L178" t="inlineStr"/>
       <c r="M178" s="7" t="inlineStr"/>
@@ -8481,28 +8481,28 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>5236</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>SEG</t>
+          <t>MATRIX</t>
         </is>
       </c>
       <c r="D179" s="2" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E179" s="8" t="n">
-        <v>-0.007900000000000001</v>
+        <v>1.03</v>
+      </c>
+      <c r="E179" s="3" t="n">
+        <v>-0.019</v>
       </c>
       <c r="F179" s="4" t="n">
-        <v>538500</v>
+        <v>631400</v>
       </c>
       <c r="G179" s="5" t="n">
         <v>0.47</v>
       </c>
       <c r="H179" t="n">
-        <v>34.58</v>
+        <v>34.63</v>
       </c>
       <c r="I179" s="6" t="inlineStr">
         <is>
@@ -8510,10 +8510,10 @@
         </is>
       </c>
       <c r="J179" s="2" t="n">
-        <v>0.631</v>
+        <v>1.085</v>
       </c>
       <c r="K179" s="2" t="n">
-        <v>0.631</v>
+        <v>1.133</v>
       </c>
       <c r="L179" t="inlineStr"/>
       <c r="M179" s="7" t="inlineStr"/>
@@ -8526,39 +8526,39 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>FFB</t>
+          <t>TAKAFUL</t>
         </is>
       </c>
       <c r="D180" s="2" t="n">
-        <v>1.72</v>
+        <v>2.86</v>
       </c>
       <c r="E180" s="3" t="n">
-        <v>0</v>
+        <v>-0.0138</v>
       </c>
       <c r="F180" s="4" t="n">
-        <v>534900</v>
+        <v>628600</v>
       </c>
       <c r="G180" s="5" t="n">
-        <v>0.17</v>
+        <v>0.49</v>
       </c>
       <c r="H180" t="n">
-        <v>27.14</v>
-      </c>
-      <c r="I180" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>34.01</v>
+      </c>
+      <c r="I180" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J180" s="2" t="n">
-        <v>1.821</v>
+        <v>2.927</v>
       </c>
       <c r="K180" s="2" t="n">
-        <v>1.962</v>
+        <v>3.063</v>
       </c>
       <c r="L180" t="inlineStr"/>
       <c r="M180" s="7" t="inlineStr"/>
@@ -8571,39 +8571,39 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>0359</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>SIMEPROP</t>
+          <t>HKB</t>
         </is>
       </c>
       <c r="D181" s="2" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="E181" s="8" t="n">
-        <v>-0.007800000000000001</v>
+        <v>0.775</v>
+      </c>
+      <c r="E181" s="3" t="n">
+        <v>-0.0127</v>
       </c>
       <c r="F181" s="4" t="n">
-        <v>531300</v>
+        <v>624800</v>
       </c>
       <c r="G181" s="5" t="n">
-        <v>0.12</v>
+        <v>0.27</v>
       </c>
       <c r="H181" t="n">
-        <v>51.93</v>
-      </c>
-      <c r="I181" s="9" t="inlineStr">
+        <v>67.27</v>
+      </c>
+      <c r="I181" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J181" s="2" t="n">
-        <v>1.259</v>
+        <v>0.73</v>
       </c>
       <c r="K181" s="2" t="n">
-        <v>1.277</v>
+        <v>0.648</v>
       </c>
       <c r="L181" t="inlineStr"/>
       <c r="M181" s="7" t="inlineStr"/>
@@ -8616,39 +8616,39 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>0376</t>
+          <t>5212</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>IAB</t>
+          <t>PAVREIT</t>
         </is>
       </c>
       <c r="D182" s="2" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="E182" s="8" t="n">
-        <v>-0.028</v>
+        <v>1.56</v>
+      </c>
+      <c r="E182" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F182" s="4" t="n">
-        <v>525500</v>
+        <v>576200</v>
       </c>
       <c r="G182" s="5" t="n">
-        <v>0.21</v>
+        <v>0.17</v>
       </c>
       <c r="H182" t="n">
-        <v>33.46</v>
-      </c>
-      <c r="I182" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.18</v>
+      </c>
+      <c r="I182" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J182" s="2" t="n">
-        <v>1.196</v>
+        <v>1.568</v>
       </c>
       <c r="K182" s="2" t="n">
-        <v>1.291</v>
+        <v>1.601</v>
       </c>
       <c r="L182" t="inlineStr"/>
       <c r="M182" s="7" t="inlineStr"/>
@@ -8661,28 +8661,28 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>4758</t>
+          <t>5306</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>ANCOMNY</t>
+          <t>FFB</t>
         </is>
       </c>
       <c r="D183" s="2" t="n">
-        <v>0.8149999999999999</v>
-      </c>
-      <c r="E183" s="3" t="n">
-        <v>0</v>
+        <v>1.73</v>
+      </c>
+      <c r="E183" s="9" t="n">
+        <v>0.0058</v>
       </c>
       <c r="F183" s="4" t="n">
-        <v>516100</v>
+        <v>557900</v>
       </c>
       <c r="G183" s="5" t="n">
-        <v>0.31</v>
+        <v>0.17</v>
       </c>
       <c r="H183" t="n">
-        <v>33.01</v>
+        <v>29.4</v>
       </c>
       <c r="I183" s="6" t="inlineStr">
         <is>
@@ -8690,10 +8690,10 @@
         </is>
       </c>
       <c r="J183" s="2" t="n">
-        <v>0.844</v>
+        <v>1.822</v>
       </c>
       <c r="K183" s="2" t="n">
-        <v>0.861</v>
+        <v>1.962</v>
       </c>
       <c r="L183" t="inlineStr"/>
       <c r="M183" s="7" t="inlineStr"/>
@@ -8706,28 +8706,28 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>5246</t>
+          <t>0293</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>WPRTS</t>
+          <t>KJTS</t>
         </is>
       </c>
       <c r="D184" s="2" t="n">
-        <v>6.71</v>
-      </c>
-      <c r="E184" s="8" t="n">
-        <v>-0.0074</v>
+        <v>0.85</v>
+      </c>
+      <c r="E184" s="9" t="n">
+        <v>0.0119</v>
       </c>
       <c r="F184" s="4" t="n">
-        <v>513400</v>
+        <v>548300</v>
       </c>
       <c r="G184" s="5" t="n">
-        <v>0.12</v>
+        <v>0.45</v>
       </c>
       <c r="H184" t="n">
-        <v>46.6</v>
+        <v>33.01</v>
       </c>
       <c r="I184" s="6" t="inlineStr">
         <is>
@@ -8735,16 +8735,196 @@
         </is>
       </c>
       <c r="J184" s="2" t="n">
-        <v>6.752</v>
+        <v>0.951</v>
       </c>
       <c r="K184" s="2" t="n">
-        <v>6.826</v>
+        <v>1.023</v>
       </c>
       <c r="L184" t="inlineStr"/>
       <c r="M184" s="7" t="inlineStr"/>
     </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>0376</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>IAB</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="E185" s="3" t="n">
+        <v>-0.028</v>
+      </c>
+      <c r="F185" s="4" t="n">
+        <v>547600</v>
+      </c>
+      <c r="G185" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H185" t="n">
+        <v>33.46</v>
+      </c>
+      <c r="I185" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J185" s="2" t="n">
+        <v>1.196</v>
+      </c>
+      <c r="K185" s="2" t="n">
+        <v>1.291</v>
+      </c>
+      <c r="L185" t="inlineStr"/>
+      <c r="M185" s="7" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>9792</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>SEG</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E186" s="3" t="n">
+        <v>-0.007900000000000001</v>
+      </c>
+      <c r="F186" s="4" t="n">
+        <v>538500</v>
+      </c>
+      <c r="G186" s="5" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="H186" t="n">
+        <v>34.58</v>
+      </c>
+      <c r="I186" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J186" s="2" t="n">
+        <v>0.631</v>
+      </c>
+      <c r="K186" s="2" t="n">
+        <v>0.631</v>
+      </c>
+      <c r="L186" t="inlineStr"/>
+      <c r="M186" s="7" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>4758</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>ANCOMNY</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="E187" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F187" s="4" t="n">
+        <v>537200</v>
+      </c>
+      <c r="G187" s="5" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H187" t="n">
+        <v>33.01</v>
+      </c>
+      <c r="I187" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J187" s="2" t="n">
+        <v>0.844</v>
+      </c>
+      <c r="K187" s="2" t="n">
+        <v>0.861</v>
+      </c>
+      <c r="L187" t="inlineStr"/>
+      <c r="M187" s="7" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>9059</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>TSH</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="E188" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F188" s="4" t="n">
+        <v>500500</v>
+      </c>
+      <c r="G188" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H188" t="n">
+        <v>30.66</v>
+      </c>
+      <c r="I188" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J188" s="2" t="n">
+        <v>1.238</v>
+      </c>
+      <c r="K188" s="2" t="n">
+        <v>1.308</v>
+      </c>
+      <c r="L188" t="inlineStr"/>
+      <c r="M188" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M184"/>
+  <autoFilter ref="A1:M188"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-19/bursa-report-2026-10-19.xlsx
+++ b/docs/downloads/2026-10-19/bursa-report-2026-10-19.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-19" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-19'!$A$1:$M$188</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-19'!$A$1:$M$194</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -35,13 +35,13 @@
       <color rgb="00FFFFFF"/>
     </font>
     <font>
+      <color rgb="00898781"/>
+    </font>
+    <font>
       <color rgb="00D03B3B"/>
     </font>
     <font>
       <color rgb="000CA30C"/>
-    </font>
-    <font>
-      <color rgb="00898781"/>
     </font>
   </fonts>
   <fills count="3">
@@ -78,12 +78,12 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M188"/>
+  <dimension ref="A1:M194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -552,19 +552,19 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.05</v>
+        <v>0.055</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>-0.09089999999999999</v>
+        <v>0</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>65509800</v>
+        <v>67159400</v>
       </c>
       <c r="G2" s="5" t="n">
         <v>0.17</v>
       </c>
       <c r="H2" t="n">
-        <v>22.63</v>
+        <v>23.16</v>
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
@@ -599,14 +599,14 @@
       <c r="D3" s="2" t="n">
         <v>0.325</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" s="8" t="n">
         <v>-0.0441</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>51037200</v>
+        <v>52176300</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="H3" t="n">
         <v>61.81</v>
@@ -644,19 +644,19 @@
       <c r="D4" s="2" t="n">
         <v>0.895</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" s="8" t="n">
         <v>-0.005600000000000001</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>44623200</v>
+        <v>46292300</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
       <c r="H4" t="n">
         <v>65.20999999999999</v>
       </c>
-      <c r="I4" s="8" t="inlineStr">
+      <c r="I4" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -689,14 +689,14 @@
       <c r="D5" s="2" t="n">
         <v>0.13</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="E5" s="8" t="n">
         <v>-0.1034</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>29378500</v>
+        <v>29865400</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="H5" t="n">
         <v>38.6</v>
@@ -734,19 +734,19 @@
       <c r="D6" s="2" t="n">
         <v>0.44</v>
       </c>
-      <c r="E6" s="9" t="n">
+      <c r="E6" s="10" t="n">
         <v>0.0476</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>28448600</v>
+        <v>29551000</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.82</v>
+        <v>0.85</v>
       </c>
       <c r="H6" t="n">
         <v>77.98</v>
       </c>
-      <c r="I6" s="8" t="inlineStr">
+      <c r="I6" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -779,14 +779,14 @@
       <c r="D7" s="2" t="n">
         <v>0.155</v>
       </c>
-      <c r="E7" s="10" t="n">
+      <c r="E7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>24094800</v>
+        <v>27594800</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="H7" t="n">
         <v>48.61</v>
@@ -824,11 +824,11 @@
       <c r="D8" s="2" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="E8" s="9" t="n">
+      <c r="E8" s="10" t="n">
         <v>0.0299</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>23496400</v>
+        <v>23506400</v>
       </c>
       <c r="G8" s="5" t="n">
         <v>0.93</v>
@@ -836,7 +836,7 @@
       <c r="H8" t="n">
         <v>78.11</v>
       </c>
-      <c r="I8" s="8" t="inlineStr">
+      <c r="I8" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -869,14 +869,14 @@
       <c r="D9" s="2" t="n">
         <v>0.045</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="E9" s="8" t="n">
         <v>-0.1</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>20034300</v>
+        <v>23034300</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>17.98</v>
+        <v>20.68</v>
       </c>
       <c r="H9" t="n">
         <v>29.14</v>
@@ -914,19 +914,19 @@
       <c r="D10" s="2" t="n">
         <v>4.7</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="E10" s="8" t="n">
         <v>-0.0269</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>17805100</v>
+        <v>18440000</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.95</v>
+        <v>0.98</v>
       </c>
       <c r="H10" t="n">
         <v>46.13</v>
       </c>
-      <c r="I10" s="8" t="inlineStr">
+      <c r="I10" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -948,39 +948,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="E11" s="10" t="n">
-        <v>0</v>
+        <v>0.285</v>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>-0.0806</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>14261000</v>
+        <v>14792600</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.73</v>
+        <v>1.7</v>
       </c>
       <c r="H11" t="n">
-        <v>54.55</v>
-      </c>
-      <c r="I11" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.31</v>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.309</v>
+        <v>0.299</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="7" t="inlineStr"/>
@@ -993,39 +993,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0.435</v>
+        <v>0.31</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>-0.0225</v>
+        <v>0</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>13715500</v>
+        <v>14261000</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.68</v>
+        <v>0.73</v>
       </c>
       <c r="H12" t="n">
-        <v>56.12</v>
-      </c>
-      <c r="I12" s="8" t="inlineStr">
+        <v>54.55</v>
+      </c>
+      <c r="I12" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.423</v>
+        <v>0.309</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0.367</v>
+        <v>0.3</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="7" t="inlineStr"/>
@@ -1038,39 +1038,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E13" s="10" t="n">
-        <v>0</v>
+        <v>0.44</v>
+      </c>
+      <c r="E13" s="8" t="n">
+        <v>-0.0112</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>12626700</v>
+        <v>14021200</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.64</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>45.57</v>
-      </c>
-      <c r="I13" s="8" t="inlineStr">
+        <v>57.56</v>
+      </c>
+      <c r="I13" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.868</v>
+        <v>0.423</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0.869</v>
+        <v>0.367</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="7" t="inlineStr"/>
@@ -1083,39 +1083,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0.285</v>
+        <v>0.865</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>-0.0806</v>
+        <v>0</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>12285600</v>
+        <v>12889200</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>1.41</v>
+        <v>0.65</v>
       </c>
       <c r="H14" t="n">
-        <v>45.31</v>
-      </c>
-      <c r="I14" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>45.57</v>
+      </c>
+      <c r="I14" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.299</v>
+        <v>0.868</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0.28</v>
+        <v>0.869</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="7" t="inlineStr"/>
@@ -1139,11 +1139,11 @@
       <c r="D15" s="2" t="n">
         <v>0.44</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="E15" s="8" t="n">
         <v>-0.0222</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>12201100</v>
+        <v>12274600</v>
       </c>
       <c r="G15" s="5" t="n">
         <v>0.34</v>
@@ -1184,7 +1184,7 @@
       <c r="D16" s="2" t="n">
         <v>0.215</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="E16" s="8" t="n">
         <v>-0.0227</v>
       </c>
       <c r="F16" s="4" t="n">
@@ -1196,7 +1196,7 @@
       <c r="H16" t="n">
         <v>53.06</v>
       </c>
-      <c r="I16" s="8" t="inlineStr">
+      <c r="I16" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -1227,27 +1227,27 @@
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E17" s="3" t="n">
-        <v>-0.009899999999999999</v>
+        <v>2.01</v>
+      </c>
+      <c r="E17" s="8" t="n">
+        <v>-0.005</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>9138100</v>
+        <v>9139500</v>
       </c>
       <c r="G17" s="5" t="n">
         <v>0.31</v>
       </c>
       <c r="H17" t="n">
-        <v>57.95</v>
-      </c>
-      <c r="I17" s="8" t="inlineStr">
+        <v>58.66</v>
+      </c>
+      <c r="I17" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1.928</v>
+        <v>1.929</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>1.74</v>
@@ -1274,11 +1274,11 @@
       <c r="D18" s="2" t="n">
         <v>0.775</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="E18" s="8" t="n">
         <v>-0.0064</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>8985000</v>
+        <v>8985100</v>
       </c>
       <c r="G18" s="5" t="n">
         <v>0.59</v>
@@ -1286,7 +1286,7 @@
       <c r="H18" t="n">
         <v>49.91</v>
       </c>
-      <c r="I18" s="8" t="inlineStr">
+      <c r="I18" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -1317,19 +1317,19 @@
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v>-0.0301</v>
+        <v>2.59</v>
+      </c>
+      <c r="E19" s="8" t="n">
+        <v>-0.0263</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>8073700</v>
+        <v>8110300</v>
       </c>
       <c r="G19" s="5" t="n">
         <v>0.45</v>
       </c>
       <c r="H19" t="n">
-        <v>47.37</v>
+        <v>47.92</v>
       </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
@@ -1337,7 +1337,7 @@
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>2.643</v>
+        <v>2.644</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>2.554</v>
@@ -1364,19 +1364,19 @@
       <c r="D20" s="2" t="n">
         <v>0.98</v>
       </c>
-      <c r="E20" s="9" t="n">
+      <c r="E20" s="10" t="n">
         <v>0.0208</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>7986300</v>
+        <v>8008600</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="H20" t="n">
         <v>68.93000000000001</v>
       </c>
-      <c r="I20" s="8" t="inlineStr">
+      <c r="I20" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -1409,19 +1409,19 @@
       <c r="D21" s="2" t="n">
         <v>0.04</v>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="E21" s="8" t="n">
         <v>-0.1111</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>7943500</v>
+        <v>7994500</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>21.48</v>
+        <v>21.61</v>
       </c>
       <c r="H21" t="n">
         <v>70.23999999999999</v>
       </c>
-      <c r="I21" s="8" t="inlineStr">
+      <c r="I21" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -1454,7 +1454,7 @@
       <c r="D22" s="2" t="n">
         <v>0.62</v>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="E22" s="8" t="n">
         <v>-0.008</v>
       </c>
       <c r="F22" s="4" t="n">
@@ -1466,7 +1466,7 @@
       <c r="H22" t="n">
         <v>53.27</v>
       </c>
-      <c r="I22" s="8" t="inlineStr">
+      <c r="I22" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -1488,40 +1488,33 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>0477</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>ECOSYS</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="E23" s="3" t="n">
-        <v>-0.0042</v>
+        <v>0.765</v>
+      </c>
+      <c r="E23" s="8" t="n">
+        <v>-0.0255</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>7470900</v>
+        <v>7549100</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="H23" t="n">
-        <v>44.85</v>
-      </c>
-      <c r="I23" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="n">
-        <v>4.897</v>
-      </c>
-      <c r="K23" s="2" t="n">
-        <v>4.728</v>
-      </c>
+        <v>0.1</v>
+      </c>
+      <c r="I23" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="n"/>
+      <c r="K23" s="2" t="n"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="7" t="inlineStr"/>
     </row>
@@ -1533,33 +1526,40 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0477</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ECOSYS</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="E24" s="3" t="n">
-        <v>-0.0318</v>
+        <v>4.78</v>
+      </c>
+      <c r="E24" s="8" t="n">
+        <v>-0.0042</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>7465000</v>
+        <v>7514700</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I24" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="n"/>
-      <c r="K24" s="2" t="n"/>
+        <v>0.3</v>
+      </c>
+      <c r="H24" t="n">
+        <v>44.85</v>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="n">
+        <v>4.897</v>
+      </c>
+      <c r="K24" s="2" t="n">
+        <v>4.728</v>
+      </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="7" t="inlineStr"/>
     </row>
@@ -1571,28 +1571,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>-0.009899999999999999</v>
+        <v>6.66</v>
+      </c>
+      <c r="E25" s="10" t="n">
+        <v>0.0246</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>7079000</v>
+        <v>7162900</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.89</v>
+        <v>0.74</v>
       </c>
       <c r="H25" t="n">
-        <v>44.77</v>
+        <v>27.81</v>
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
@@ -1600,10 +1600,10 @@
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>1.05</v>
+        <v>7.207</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0.959</v>
+        <v>7.606</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="7" t="inlineStr"/>
@@ -1616,33 +1616,40 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>SLG</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E26" s="10" t="n">
-        <v>0</v>
+        <v>0.995</v>
+      </c>
+      <c r="E26" s="8" t="n">
+        <v>-0.0149</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>6915900</v>
+        <v>7111000</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.28</v>
+        <v>0.89</v>
+      </c>
+      <c r="H26" t="n">
+        <v>44.16</v>
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J26" s="2" t="n"/>
-      <c r="K26" s="2" t="n"/>
+      <c r="J26" s="2" t="n">
+        <v>1.049</v>
+      </c>
+      <c r="K26" s="2" t="n">
+        <v>0.959</v>
+      </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="7" t="inlineStr"/>
     </row>
@@ -1654,40 +1661,33 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>SLG</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>6.67</v>
-      </c>
-      <c r="E27" s="9" t="n">
-        <v>0.0262</v>
+        <v>0.25</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>6700300</v>
+        <v>6916800</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="H27" t="n">
-        <v>28.27</v>
+        <v>0.28</v>
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J27" s="2" t="n">
-        <v>7.208</v>
-      </c>
-      <c r="K27" s="2" t="n">
-        <v>7.606</v>
-      </c>
+      <c r="J27" s="2" t="n"/>
+      <c r="K27" s="2" t="n"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="7" t="inlineStr"/>
     </row>
@@ -1699,39 +1699,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E28" s="10" t="n">
-        <v>0</v>
+        <v>1.43</v>
+      </c>
+      <c r="E28" s="8" t="n">
+        <v>-0.0138</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>6697200</v>
+        <v>6732400</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.41</v>
+        <v>0.6</v>
       </c>
       <c r="H28" t="n">
-        <v>57.16</v>
-      </c>
-      <c r="I28" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>21.76</v>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.8139999999999999</v>
+        <v>1.692</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0.8110000000000001</v>
+        <v>1.945</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="7" t="inlineStr"/>
@@ -1744,39 +1744,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>0.405</v>
-      </c>
-      <c r="E29" s="10" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="E29" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>6621700</v>
+        <v>6706200</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.53</v>
+        <v>0.41</v>
       </c>
       <c r="H29" t="n">
-        <v>55.08</v>
-      </c>
-      <c r="I29" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.16</v>
+      </c>
+      <c r="I29" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.391</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0.378</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="7" t="inlineStr"/>
@@ -1789,28 +1789,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>3891</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>MUIIND</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="E30" s="10" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="E30" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>6610400</v>
+        <v>6645700</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>3.9</v>
+        <v>0.54</v>
       </c>
       <c r="H30" t="n">
-        <v>46.69</v>
+        <v>55.08</v>
       </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
@@ -1818,10 +1818,10 @@
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.041</v>
+        <v>0.391</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0.042</v>
+        <v>0.378</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="7" t="inlineStr"/>
@@ -1834,28 +1834,28 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>3891</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>MUIIND</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>1.42</v>
+        <v>0.04</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-0.0207</v>
+        <v>0</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>6587900</v>
+        <v>6610400</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.59</v>
+        <v>3.9</v>
       </c>
       <c r="H31" t="n">
-        <v>21.41</v>
+        <v>46.69</v>
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
@@ -1863,10 +1863,10 @@
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>1.691</v>
+        <v>0.041</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>1.944</v>
+        <v>0.042</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="7" t="inlineStr"/>
@@ -1879,28 +1879,28 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>7079</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>TWL</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E32" s="10" t="n">
-        <v>0</v>
+        <v>0.02</v>
+      </c>
+      <c r="E32" s="8" t="n">
+        <v>-0.2</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>6072500</v>
+        <v>6250000</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>1.95</v>
+        <v>0.42</v>
       </c>
       <c r="H32" t="n">
-        <v>49.08</v>
+        <v>37.62</v>
       </c>
       <c r="I32" s="6" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.295</v>
+        <v>0.024</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0.295</v>
+        <v>0.024</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="7" t="inlineStr"/>
@@ -1924,28 +1924,28 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="E33" s="3" t="n">
-        <v>-0.018</v>
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="E33" s="8" t="n">
+        <v>-0.0504</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>5961600</v>
+        <v>6108900</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.29</v>
+        <v>0.68</v>
       </c>
       <c r="H33" t="n">
-        <v>46.22</v>
+        <v>35.76</v>
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
@@ -1953,10 +1953,10 @@
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.573</v>
+        <v>0.647</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0.541</v>
+        <v>0.62</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="7" t="inlineStr"/>
@@ -1969,28 +1969,28 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>5156</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>XDL</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="E34" s="10" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="E34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>5950100</v>
+        <v>6072500</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>2.42</v>
+        <v>1.95</v>
       </c>
       <c r="H34" t="n">
-        <v>44.81</v>
+        <v>49.08</v>
       </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
@@ -1998,10 +1998,10 @@
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.007</v>
+        <v>0.295</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0.007</v>
+        <v>0.295</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="7" t="inlineStr"/>
@@ -2014,28 +2014,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>0.5649999999999999</v>
-      </c>
-      <c r="E35" s="3" t="n">
-        <v>-0.0504</v>
+        <v>0.545</v>
+      </c>
+      <c r="E35" s="8" t="n">
+        <v>-0.018</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>5918900</v>
+        <v>5976600</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.66</v>
+        <v>0.29</v>
       </c>
       <c r="H35" t="n">
-        <v>35.76</v>
+        <v>46.22</v>
       </c>
       <c r="I35" s="6" t="inlineStr">
         <is>
@@ -2043,10 +2043,10 @@
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.647</v>
+        <v>0.573</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0.62</v>
+        <v>0.541</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="7" t="inlineStr"/>
@@ -2059,28 +2059,28 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>5156</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>XDL</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>0.435</v>
-      </c>
-      <c r="E36" s="9" t="n">
-        <v>0.0357</v>
+        <v>0.005</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>5905100</v>
+        <v>5950100</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.87</v>
+        <v>2.42</v>
       </c>
       <c r="H36" t="n">
-        <v>53.65</v>
+        <v>44.81</v>
       </c>
       <c r="I36" s="6" t="inlineStr">
         <is>
@@ -2088,10 +2088,10 @@
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.425</v>
+        <v>0.007</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0.416</v>
+        <v>0.007</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="7" t="inlineStr"/>
@@ -2104,28 +2104,28 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="E37" s="3" t="n">
-        <v>-0.0182</v>
+        <v>0.43</v>
+      </c>
+      <c r="E37" s="10" t="n">
+        <v>0.0238</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>5707000</v>
+        <v>5910600</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.59</v>
+        <v>0.87</v>
       </c>
       <c r="H37" t="n">
-        <v>51.15</v>
+        <v>52.5</v>
       </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
@@ -2133,10 +2133,10 @@
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>1.077</v>
+        <v>0.424</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>1.045</v>
+        <v>0.416</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="7" t="inlineStr"/>
@@ -2149,40 +2149,33 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>0472</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>ECOGRP</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="E38" s="3" t="n">
-        <v>-0.0325</v>
+        <v>0.12</v>
+      </c>
+      <c r="E38" s="8" t="n">
+        <v>-0.1111</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>5607700</v>
+        <v>5826300</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="H38" t="n">
-        <v>38.78</v>
-      </c>
-      <c r="I38" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="n">
-        <v>1.235</v>
-      </c>
-      <c r="K38" s="2" t="n">
-        <v>1.323</v>
-      </c>
+        <v>0.08</v>
+      </c>
+      <c r="I38" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="n"/>
+      <c r="K38" s="2" t="n"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="7" t="inlineStr"/>
     </row>
@@ -2194,28 +2187,28 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="E39" s="3" t="n">
-        <v>-0.0049</v>
+        <v>1.07</v>
+      </c>
+      <c r="E39" s="8" t="n">
+        <v>-0.0273</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>5527900</v>
+        <v>5716100</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.42</v>
+        <v>0.59</v>
       </c>
       <c r="H39" t="n">
-        <v>33.2</v>
+        <v>49.74</v>
       </c>
       <c r="I39" s="6" t="inlineStr">
         <is>
@@ -2223,10 +2216,10 @@
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>2.148</v>
+        <v>1.076</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>2.234</v>
+        <v>1.045</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="7" t="inlineStr"/>
@@ -2239,39 +2232,39 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>9.869999999999999</v>
-      </c>
-      <c r="E40" s="3" t="n">
-        <v>-0.012</v>
+        <v>1.19</v>
+      </c>
+      <c r="E40" s="8" t="n">
+        <v>-0.0325</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>5489100</v>
+        <v>5683400</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.41</v>
+        <v>0.75</v>
       </c>
       <c r="H40" t="n">
-        <v>40.09</v>
-      </c>
-      <c r="I40" s="8" t="inlineStr">
+        <v>38.78</v>
+      </c>
+      <c r="I40" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>9.997999999999999</v>
+        <v>1.235</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>10.147</v>
+        <v>1.323</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="7" t="inlineStr"/>
@@ -2284,33 +2277,40 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0472</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ECOGRP</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v>-0.1111</v>
+        <v>9.880000000000001</v>
+      </c>
+      <c r="E41" s="8" t="n">
+        <v>-0.011</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>5484300</v>
+        <v>5593500</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="I41" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="n"/>
-      <c r="K41" s="2" t="n"/>
+        <v>0.42</v>
+      </c>
+      <c r="H41" t="n">
+        <v>40.55</v>
+      </c>
+      <c r="I41" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="n">
+        <v>9.999000000000001</v>
+      </c>
+      <c r="K41" s="2" t="n">
+        <v>10.147</v>
+      </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="7" t="inlineStr"/>
     </row>
@@ -2322,28 +2322,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="E42" s="9" t="n">
-        <v>0.0484</v>
+        <v>2.01</v>
+      </c>
+      <c r="E42" s="8" t="n">
+        <v>-0.009899999999999999</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>5202300</v>
+        <v>5579200</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.55</v>
+        <v>0.43</v>
       </c>
       <c r="H42" t="n">
-        <v>60.08</v>
+        <v>32.51</v>
       </c>
       <c r="I42" s="6" t="inlineStr">
         <is>
@@ -2351,10 +2351,10 @@
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>3.658</v>
+        <v>2.147</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>3.009</v>
+        <v>2.233</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="7" t="inlineStr"/>
@@ -2367,28 +2367,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="E43" s="3" t="n">
-        <v>-0.024</v>
+        <v>3.85</v>
+      </c>
+      <c r="E43" s="10" t="n">
+        <v>0.0349</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>5037700</v>
+        <v>5309400</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>1.05</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H43" t="n">
-        <v>35.32</v>
+        <v>58.99</v>
       </c>
       <c r="I43" s="6" t="inlineStr">
         <is>
@@ -2396,10 +2396,10 @@
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>1.724</v>
+        <v>3.653</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>1.767</v>
+        <v>3.008</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="7" t="inlineStr"/>
@@ -2412,39 +2412,39 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="E44" s="9" t="n">
-        <v>0.0218</v>
+        <v>1.64</v>
+      </c>
+      <c r="E44" s="8" t="n">
+        <v>-0.018</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>5036800</v>
+        <v>5248100</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>1.42</v>
+        <v>1.1</v>
       </c>
       <c r="H44" t="n">
-        <v>60.87</v>
-      </c>
-      <c r="I44" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.28</v>
+      </c>
+      <c r="I44" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>2.226</v>
+        <v>1.725</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>2.167</v>
+        <v>1.768</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="7" t="inlineStr"/>
@@ -2457,39 +2457,39 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>1.27</v>
+        <v>2.34</v>
       </c>
       <c r="E45" s="10" t="n">
-        <v>0</v>
+        <v>0.0218</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>5032400</v>
+        <v>5078000</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.82</v>
+        <v>1.43</v>
       </c>
       <c r="H45" t="n">
-        <v>61.53</v>
-      </c>
-      <c r="I45" s="8" t="inlineStr">
+        <v>60.87</v>
+      </c>
+      <c r="I45" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>1.197</v>
+        <v>2.226</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>1.188</v>
+        <v>2.167</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="7" t="inlineStr"/>
@@ -2502,39 +2502,39 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>6203</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>KHEESAN</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E46" s="9" t="n">
-        <v>0.0526</v>
+        <v>1.27</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>4951800</v>
+        <v>5033100</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>2.89</v>
+        <v>0.82</v>
       </c>
       <c r="H46" t="n">
-        <v>58.17</v>
-      </c>
-      <c r="I46" s="8" t="inlineStr">
+        <v>61.53</v>
+      </c>
+      <c r="I46" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.09</v>
+        <v>1.197</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0.095</v>
+        <v>1.188</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="7" t="inlineStr"/>
@@ -2547,39 +2547,39 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>6769</t>
+          <t>6203</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>JKGLAND</t>
+          <t>KHEESAN</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>0.1</v>
+        <v>0.105</v>
       </c>
       <c r="E47" s="10" t="n">
-        <v>0</v>
+        <v>0.1053</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>4861300</v>
+        <v>4990300</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>19.59</v>
+        <v>2.91</v>
       </c>
       <c r="H47" t="n">
-        <v>39.48</v>
-      </c>
-      <c r="I47" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.33</v>
+      </c>
+      <c r="I47" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.103</v>
+        <v>0.091</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0.107</v>
+        <v>0.095</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="7" t="inlineStr"/>
@@ -2592,28 +2592,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>6769</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>JKGLAND</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="E48" s="9" t="n">
-        <v>0.019</v>
+        <v>0.1</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>4752900</v>
+        <v>4861300</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.38</v>
+        <v>19.59</v>
       </c>
       <c r="H48" t="n">
-        <v>44.03</v>
+        <v>39.48</v>
       </c>
       <c r="I48" s="6" t="inlineStr">
         <is>
@@ -2621,10 +2621,10 @@
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>2.761</v>
+        <v>0.103</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>2.738</v>
+        <v>0.107</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="7" t="inlineStr"/>
@@ -2648,19 +2648,19 @@
       <c r="D49" s="2" t="n">
         <v>0.155</v>
       </c>
-      <c r="E49" s="3" t="n">
+      <c r="E49" s="8" t="n">
         <v>-0.0313</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>4739100</v>
+        <v>4786100</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="H49" t="n">
         <v>50.98</v>
       </c>
-      <c r="I49" s="8" t="inlineStr">
+      <c r="I49" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -2682,39 +2682,39 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="E50" s="10" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="E50" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>4660000</v>
+        <v>4785700</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.63</v>
+        <v>0.19</v>
       </c>
       <c r="H50" t="n">
-        <v>55.92</v>
-      </c>
-      <c r="I50" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>27.76</v>
+      </c>
+      <c r="I50" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.371</v>
+        <v>0.507</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0.369</v>
+        <v>0.677</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="7" t="inlineStr"/>
@@ -2738,14 +2738,14 @@
       <c r="D51" s="2" t="n">
         <v>0.255</v>
       </c>
-      <c r="E51" s="3" t="n">
+      <c r="E51" s="8" t="n">
         <v>-0.0192</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>4652200</v>
+        <v>4763800</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H51" t="n">
         <v>27.74</v>
@@ -2772,28 +2772,28 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="E52" s="3" t="n">
-        <v>-0.0353</v>
+        <v>2.67</v>
+      </c>
+      <c r="E52" s="10" t="n">
+        <v>0.0152</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>4621600</v>
+        <v>4756900</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.59</v>
+        <v>0.38</v>
       </c>
       <c r="H52" t="n">
-        <v>22.61</v>
+        <v>43.18</v>
       </c>
       <c r="I52" s="6" t="inlineStr">
         <is>
@@ -2801,10 +2801,10 @@
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.526</v>
+        <v>2.76</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0.614</v>
+        <v>2.738</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="7" t="inlineStr"/>
@@ -2817,28 +2817,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>0.335</v>
-      </c>
-      <c r="E53" s="3" t="n">
-        <v>-0.0147</v>
+        <v>0.415</v>
+      </c>
+      <c r="E53" s="8" t="n">
+        <v>-0.0235</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>4555500</v>
+        <v>4695500</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.48</v>
+        <v>0.6</v>
       </c>
       <c r="H53" t="n">
-        <v>47.31</v>
+        <v>23.04</v>
       </c>
       <c r="I53" s="6" t="inlineStr">
         <is>
@@ -2846,10 +2846,10 @@
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.346</v>
+        <v>0.527</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0.334</v>
+        <v>0.614</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="7" t="inlineStr"/>
@@ -2862,39 +2862,39 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>7.15</v>
+        <v>0.375</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>-0.0069</v>
+        <v>0</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>4481700</v>
+        <v>4660000</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.27</v>
+        <v>0.63</v>
       </c>
       <c r="H54" t="n">
-        <v>32.9</v>
-      </c>
-      <c r="I54" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.92</v>
+      </c>
+      <c r="I54" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>7.505</v>
+        <v>0.371</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>7.684</v>
+        <v>0.369</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="7" t="inlineStr"/>
@@ -2907,28 +2907,28 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0175</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>HHRG</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="E55" s="3" t="n">
-        <v>-0.04</v>
+        <v>0.335</v>
+      </c>
+      <c r="E55" s="8" t="n">
+        <v>-0.0147</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>4452900</v>
+        <v>4630700</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.19</v>
+        <v>0.49</v>
       </c>
       <c r="H55" t="n">
-        <v>34.67</v>
+        <v>47.31</v>
       </c>
       <c r="I55" s="6" t="inlineStr">
         <is>
@@ -2936,10 +2936,10 @@
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.143</v>
+        <v>0.346</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0.148</v>
+        <v>0.334</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="7" t="inlineStr"/>
@@ -2952,28 +2952,28 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>0.455</v>
-      </c>
-      <c r="E56" s="3" t="n">
-        <v>-0.0215</v>
+        <v>7.16</v>
+      </c>
+      <c r="E56" s="8" t="n">
+        <v>-0.005600000000000001</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>4353600</v>
+        <v>4559500</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.59</v>
+        <v>0.28</v>
       </c>
       <c r="H56" t="n">
-        <v>28.78</v>
+        <v>33.16</v>
       </c>
       <c r="I56" s="6" t="inlineStr">
         <is>
@@ -2981,10 +2981,10 @@
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.498</v>
+        <v>7.505</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0.556</v>
+        <v>7.684</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="7" t="inlineStr"/>
@@ -2997,39 +2997,39 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>5.21</v>
-      </c>
-      <c r="E57" s="9" t="n">
-        <v>0.0117</v>
+        <v>2.09</v>
+      </c>
+      <c r="E57" s="8" t="n">
+        <v>-0.0048</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>4281700</v>
+        <v>4479200</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.3</v>
+        <v>0.26</v>
       </c>
       <c r="H57" t="n">
-        <v>38.17</v>
-      </c>
-      <c r="I57" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.26</v>
+      </c>
+      <c r="I57" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>5.504</v>
+        <v>2.108</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>5.45</v>
+        <v>2.101</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="7" t="inlineStr"/>
@@ -3042,28 +3042,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>0175</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>HHRG</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="E58" s="3" t="n">
-        <v>-0.028</v>
+        <v>0.12</v>
+      </c>
+      <c r="E58" s="8" t="n">
+        <v>-0.04</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>4268100</v>
+        <v>4452900</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>1.73</v>
+        <v>0.19</v>
       </c>
       <c r="H58" t="n">
-        <v>34.76</v>
+        <v>34.67</v>
       </c>
       <c r="I58" s="6" t="inlineStr">
         <is>
@@ -3071,10 +3071,10 @@
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.543</v>
+        <v>0.143</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0.572</v>
+        <v>0.148</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="7" t="inlineStr"/>
@@ -3087,39 +3087,39 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="E59" s="3" t="n">
-        <v>-0.0048</v>
+        <v>5.22</v>
+      </c>
+      <c r="E59" s="10" t="n">
+        <v>0.0136</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>4256300</v>
+        <v>4406200</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="H59" t="n">
-        <v>47.26</v>
-      </c>
-      <c r="I59" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.63</v>
+      </c>
+      <c r="I59" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>2.108</v>
+        <v>5.505</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>2.101</v>
+        <v>5.45</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="7" t="inlineStr"/>
@@ -3132,39 +3132,39 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="E60" s="3" t="n">
-        <v>-0.012</v>
+        <v>0.525</v>
+      </c>
+      <c r="E60" s="8" t="n">
+        <v>-0.0187</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>4253300</v>
+        <v>4355900</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.63</v>
+        <v>1.77</v>
       </c>
       <c r="H60" t="n">
-        <v>51.49</v>
-      </c>
-      <c r="I60" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.53</v>
+      </c>
+      <c r="I60" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>1.627</v>
+        <v>0.544</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>1.695</v>
+        <v>0.572</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="7" t="inlineStr"/>
@@ -3177,28 +3177,28 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="E61" s="3" t="n">
-        <v>-0.0095</v>
+        <v>0.455</v>
+      </c>
+      <c r="E61" s="8" t="n">
+        <v>-0.0215</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>4095900</v>
+        <v>4353700</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.34</v>
+        <v>0.59</v>
       </c>
       <c r="H61" t="n">
-        <v>52.4</v>
+        <v>28.78</v>
       </c>
       <c r="I61" s="6" t="inlineStr">
         <is>
@@ -3206,10 +3206,10 @@
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.52</v>
+        <v>0.498</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0.461</v>
+        <v>0.556</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="7" t="inlineStr"/>
@@ -3222,39 +3222,39 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="E62" s="3" t="n">
-        <v>-0.011</v>
+        <v>1.65</v>
+      </c>
+      <c r="E62" s="8" t="n">
+        <v>-0.012</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>4008300</v>
+        <v>4288300</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.16</v>
+        <v>0.64</v>
       </c>
       <c r="H62" t="n">
-        <v>27.11</v>
-      </c>
-      <c r="I62" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.49</v>
+      </c>
+      <c r="I62" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.507</v>
+        <v>1.627</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>0.677</v>
+        <v>1.695</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="7" t="inlineStr"/>
@@ -3267,28 +3267,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>0.835</v>
+        <v>0.525</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>-0.0457</v>
+        <v>0</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>3827300</v>
+        <v>4236800</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>1.25</v>
+        <v>0.35</v>
       </c>
       <c r="H63" t="n">
-        <v>28.22</v>
+        <v>53.48</v>
       </c>
       <c r="I63" s="6" t="inlineStr">
         <is>
@@ -3296,10 +3296,10 @@
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.897</v>
+        <v>0.521</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0.953</v>
+        <v>0.461</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="7" t="inlineStr"/>
@@ -3312,39 +3312,39 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E64" s="3" t="n">
-        <v>-0.0741</v>
+        <v>0.835</v>
+      </c>
+      <c r="E64" s="8" t="n">
+        <v>-0.0457</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>3729500</v>
+        <v>3907200</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.27</v>
       </c>
       <c r="H64" t="n">
-        <v>65.56</v>
-      </c>
-      <c r="I64" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>28.22</v>
+      </c>
+      <c r="I64" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.841</v>
+        <v>0.897</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>0.573</v>
+        <v>0.953</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="7" t="inlineStr"/>
@@ -3357,39 +3357,39 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="E65" s="10" t="n">
-        <v>0</v>
+        <v>0.995</v>
+      </c>
+      <c r="E65" s="8" t="n">
+        <v>-0.07870000000000001</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>3599100</v>
+        <v>3794500</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0.5</v>
+        <v>0.96</v>
       </c>
       <c r="H65" t="n">
-        <v>52.34</v>
-      </c>
-      <c r="I65" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.14</v>
+      </c>
+      <c r="I65" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>1.17</v>
+        <v>0.841</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>1.136</v>
+        <v>0.573</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="7" t="inlineStr"/>
@@ -3402,28 +3402,28 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>0.175</v>
-      </c>
-      <c r="E66" s="3" t="n">
-        <v>-0.0278</v>
+        <v>1.17</v>
+      </c>
+      <c r="E66" s="8" t="n">
+        <v>-0.008500000000000001</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>3336900</v>
+        <v>3599900</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>0.15</v>
+        <v>0.5</v>
       </c>
       <c r="H66" t="n">
-        <v>40.18</v>
+        <v>50.99</v>
       </c>
       <c r="I66" s="6" t="inlineStr">
         <is>
@@ -3431,10 +3431,10 @@
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.189</v>
+        <v>1.169</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0.185</v>
+        <v>1.136</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="7" t="inlineStr"/>
@@ -3447,28 +3447,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="E67" s="3" t="n">
-        <v>-0.0351</v>
+        <v>0.175</v>
+      </c>
+      <c r="E67" s="8" t="n">
+        <v>-0.0278</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>3218400</v>
+        <v>3339200</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>0.62</v>
+        <v>0.15</v>
       </c>
       <c r="H67" t="n">
-        <v>49.98</v>
+        <v>40.18</v>
       </c>
       <c r="I67" s="6" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.189</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>0.516</v>
+        <v>0.185</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="7" t="inlineStr"/>
@@ -3492,28 +3492,28 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E68" s="3" t="n">
-        <v>-0.0189</v>
+        <v>0.555</v>
+      </c>
+      <c r="E68" s="8" t="n">
+        <v>-0.0263</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>3208300</v>
+        <v>3267600</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>0.45</v>
+        <v>0.63</v>
       </c>
       <c r="H68" t="n">
-        <v>42.45</v>
+        <v>51.18</v>
       </c>
       <c r="I68" s="6" t="inlineStr">
         <is>
@@ -3521,10 +3521,10 @@
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.273</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0.294</v>
+        <v>0.516</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="7" t="inlineStr"/>
@@ -3537,39 +3537,39 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>0.405</v>
-      </c>
-      <c r="E69" s="10" t="n">
-        <v>0</v>
+        <v>0.26</v>
+      </c>
+      <c r="E69" s="8" t="n">
+        <v>-0.0189</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>3151300</v>
+        <v>3246100</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>1.62</v>
+        <v>0.45</v>
       </c>
       <c r="H69" t="n">
-        <v>35.96</v>
-      </c>
-      <c r="I69" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.45</v>
+      </c>
+      <c r="I69" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.416</v>
+        <v>0.273</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0.433</v>
+        <v>0.294</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="7" t="inlineStr"/>
@@ -3582,39 +3582,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>0.8149999999999999</v>
-      </c>
-      <c r="E70" s="9" t="n">
-        <v>0.0252</v>
+        <v>0.405</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>3099200</v>
+        <v>3151300</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>0.55</v>
+        <v>1.62</v>
       </c>
       <c r="H70" t="n">
-        <v>64.98999999999999</v>
-      </c>
-      <c r="I70" s="8" t="inlineStr">
+        <v>35.96</v>
+      </c>
+      <c r="I70" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.793</v>
+        <v>0.416</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>0.771</v>
+        <v>0.433</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="7" t="inlineStr"/>
@@ -3627,36 +3627,36 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>0.755</v>
-      </c>
-      <c r="E71" s="9" t="n">
-        <v>0.0272</v>
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="E71" s="10" t="n">
+        <v>0.0252</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>3056700</v>
+        <v>3099200</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>0.37</v>
+        <v>0.55</v>
       </c>
       <c r="H71" t="n">
-        <v>45.47</v>
-      </c>
-      <c r="I71" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.98999999999999</v>
+      </c>
+      <c r="I71" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.77</v>
+        <v>0.793</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0.771</v>
@@ -3672,28 +3672,28 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0469</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>GTA</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="E72" s="3" t="n">
-        <v>-0.04</v>
+        <v>0.41</v>
+      </c>
+      <c r="E72" s="8" t="n">
+        <v>-0.0238</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>3027200</v>
+        <v>3068400</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>0.85</v>
+        <v>0.32</v>
       </c>
       <c r="H72" t="n">
-        <v>16.11</v>
+        <v>42.4</v>
       </c>
       <c r="I72" s="6" t="inlineStr">
         <is>
@@ -3701,9 +3701,11 @@
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.272</v>
-      </c>
-      <c r="K72" s="2" t="n"/>
+        <v>0.438</v>
+      </c>
+      <c r="K72" s="2" t="n">
+        <v>0.434</v>
+      </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="7" t="inlineStr"/>
     </row>
@@ -3715,28 +3717,28 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="E73" s="3" t="n">
-        <v>-0.0238</v>
+        <v>0.755</v>
+      </c>
+      <c r="E73" s="10" t="n">
+        <v>0.0272</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>3015300</v>
+        <v>3057300</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>0.32</v>
+        <v>0.37</v>
       </c>
       <c r="H73" t="n">
-        <v>42.4</v>
+        <v>45.47</v>
       </c>
       <c r="I73" s="6" t="inlineStr">
         <is>
@@ -3744,10 +3746,10 @@
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.438</v>
+        <v>0.77</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>0.434</v>
+        <v>0.771</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="7" t="inlineStr"/>
@@ -3760,40 +3762,38 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0395</t>
+          <t>0469</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>OGX</t>
+          <t>GTA</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>0.465</v>
-      </c>
-      <c r="E74" s="9" t="n">
-        <v>0.022</v>
+        <v>0.235</v>
+      </c>
+      <c r="E74" s="8" t="n">
+        <v>-0.06</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>2995200</v>
+        <v>3030200</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>1.14</v>
+        <v>0.85</v>
       </c>
       <c r="H74" t="n">
-        <v>56.6</v>
-      </c>
-      <c r="I74" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>15.55</v>
+      </c>
+      <c r="I74" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.447</v>
-      </c>
-      <c r="K74" s="2" t="n">
-        <v>0.449</v>
-      </c>
+        <v>0.271</v>
+      </c>
+      <c r="K74" s="2" t="n"/>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="7" t="inlineStr"/>
     </row>
@@ -3805,28 +3805,28 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>9237</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>SCIB</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>0.915</v>
-      </c>
-      <c r="E75" s="3" t="n">
-        <v>-0.0054</v>
+        <v>0.12</v>
+      </c>
+      <c r="E75" s="8" t="n">
+        <v>-0.04</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>2881500</v>
+        <v>3024700</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="H75" t="n">
-        <v>51.22</v>
+        <v>51.19</v>
       </c>
       <c r="I75" s="6" t="inlineStr">
         <is>
@@ -3834,10 +3834,10 @@
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.916</v>
+        <v>0.119</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>0.874</v>
+        <v>0.119</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="7" t="inlineStr"/>
@@ -3850,39 +3850,39 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>0395</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>OGX</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="E76" s="9" t="n">
-        <v>0.0214</v>
+        <v>0.465</v>
+      </c>
+      <c r="E76" s="10" t="n">
+        <v>0.022</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>2846100</v>
+        <v>2996300</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>0.5</v>
+        <v>1.14</v>
       </c>
       <c r="H76" t="n">
-        <v>47.22</v>
-      </c>
-      <c r="I76" s="8" t="inlineStr">
+        <v>56.6</v>
+      </c>
+      <c r="I76" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>1.921</v>
+        <v>0.447</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>1.95</v>
+        <v>0.449</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="7" t="inlineStr"/>
@@ -3895,39 +3895,39 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>5.74</v>
-      </c>
-      <c r="E77" s="9" t="n">
-        <v>0.008800000000000001</v>
+        <v>1.91</v>
+      </c>
+      <c r="E77" s="10" t="n">
+        <v>0.0214</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>2846000</v>
+        <v>2962400</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>0.38</v>
+        <v>0.52</v>
       </c>
       <c r="H77" t="n">
-        <v>30.7</v>
-      </c>
-      <c r="I77" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.22</v>
+      </c>
+      <c r="I77" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>6.023</v>
+        <v>1.921</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>6.309</v>
+        <v>1.95</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="7" t="inlineStr"/>
@@ -3940,28 +3940,28 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="E78" s="3" t="n">
-        <v>-0.0394</v>
+        <v>5.74</v>
+      </c>
+      <c r="E78" s="10" t="n">
+        <v>0.008800000000000001</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>2809000</v>
+        <v>2902500</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>0.67</v>
+        <v>0.39</v>
       </c>
       <c r="H78" t="n">
-        <v>23.54</v>
+        <v>30.7</v>
       </c>
       <c r="I78" s="6" t="inlineStr">
         <is>
@@ -3969,10 +3969,10 @@
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>1.393</v>
+        <v>6.023</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>1.561</v>
+        <v>6.309</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="7" t="inlineStr"/>
@@ -3985,39 +3985,39 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="E79" s="9" t="n">
-        <v>0.0097</v>
+        <v>1.22</v>
+      </c>
+      <c r="E79" s="8" t="n">
+        <v>-0.0394</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>2724300</v>
+        <v>2887800</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>0.88</v>
+        <v>0.68</v>
       </c>
       <c r="H79" t="n">
-        <v>82.95999999999999</v>
-      </c>
-      <c r="I79" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>23.54</v>
+      </c>
+      <c r="I79" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>2.83</v>
+        <v>1.393</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>2.43</v>
+        <v>1.561</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="7" t="inlineStr"/>
@@ -4030,28 +4030,28 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>5041</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>PBA</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E80" s="3" t="n">
-        <v>-0.0196</v>
+        <v>0.915</v>
+      </c>
+      <c r="E80" s="8" t="n">
+        <v>-0.0054</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>2673600</v>
+        <v>2881500</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>8.19</v>
+        <v>1.73</v>
       </c>
       <c r="H80" t="n">
-        <v>32</v>
+        <v>51.22</v>
       </c>
       <c r="I80" s="6" t="inlineStr">
         <is>
@@ -4059,10 +4059,10 @@
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>2.091</v>
+        <v>0.916</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>2.156</v>
+        <v>0.874</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="7" t="inlineStr"/>
@@ -4075,39 +4075,39 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0388</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>SEMICO</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>0.625</v>
+        <v>0.205</v>
       </c>
       <c r="E81" s="10" t="n">
-        <v>0</v>
+        <v>0.009899999999999999</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>2632800</v>
+        <v>2774400</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>0.78</v>
+        <v>0.12</v>
       </c>
       <c r="H81" t="n">
-        <v>70.16</v>
-      </c>
-      <c r="I81" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.23</v>
+      </c>
+      <c r="I81" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.617</v>
+        <v>0.218</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>0.605</v>
+        <v>0.235</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="7" t="inlineStr"/>
@@ -4120,39 +4120,39 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>VELESTO</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>0.205</v>
-      </c>
-      <c r="E82" s="9" t="n">
-        <v>0.009899999999999999</v>
+        <v>3.11</v>
+      </c>
+      <c r="E82" s="10" t="n">
+        <v>0.006500000000000001</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>2609400</v>
+        <v>2738100</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>0.12</v>
+        <v>0.89</v>
       </c>
       <c r="H82" t="n">
-        <v>39.23</v>
-      </c>
-      <c r="I82" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>82.68000000000001</v>
+      </c>
+      <c r="I82" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.218</v>
+        <v>2.829</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>0.235</v>
+        <v>2.43</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="7" t="inlineStr"/>
@@ -4165,28 +4165,28 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>5041</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>PBA</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="E83" s="3" t="n">
-        <v>-0.0145</v>
+        <v>2.01</v>
+      </c>
+      <c r="E83" s="8" t="n">
+        <v>-0.0147</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>2516600</v>
+        <v>2677000</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>0.17</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H83" t="n">
-        <v>39.44</v>
+        <v>33.07</v>
       </c>
       <c r="I83" s="6" t="inlineStr">
         <is>
@@ -4194,10 +4194,10 @@
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.75</v>
+        <v>2.092</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>0.723</v>
+        <v>2.156</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="7" t="inlineStr"/>
@@ -4210,39 +4210,39 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>IOIPG</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="E84" s="9" t="n">
-        <v>0.0253</v>
+        <v>0.625</v>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>2510900</v>
+        <v>2632800</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>0.42</v>
+        <v>0.78</v>
       </c>
       <c r="H84" t="n">
-        <v>35.23</v>
-      </c>
-      <c r="I84" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>70.16</v>
+      </c>
+      <c r="I84" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>3.369</v>
+        <v>0.617</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>3.604</v>
+        <v>0.605</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="7" t="inlineStr"/>
@@ -4255,28 +4255,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>IOIPG</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="E85" s="3" t="n">
-        <v>-0.0175</v>
+        <v>3.24</v>
+      </c>
+      <c r="E85" s="10" t="n">
+        <v>0.0253</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>2499600</v>
+        <v>2527300</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>0.41</v>
+        <v>0.43</v>
       </c>
       <c r="H85" t="n">
-        <v>21.33</v>
+        <v>35.23</v>
       </c>
       <c r="I85" s="6" t="inlineStr">
         <is>
@@ -4284,10 +4284,10 @@
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.333</v>
+        <v>3.369</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>0.372</v>
+        <v>3.604</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="7" t="inlineStr"/>
@@ -4300,39 +4300,39 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0261</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>COSMOS</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="E86" s="9" t="n">
-        <v>0.025</v>
+        <v>0.68</v>
+      </c>
+      <c r="E86" s="8" t="n">
+        <v>-0.0145</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>2496000</v>
+        <v>2517700</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>7.48</v>
+        <v>0.17</v>
       </c>
       <c r="H86" t="n">
-        <v>67.38</v>
-      </c>
-      <c r="I86" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.44</v>
+      </c>
+      <c r="I86" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.381</v>
+        <v>0.75</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>0.363</v>
+        <v>0.723</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="7" t="inlineStr"/>
@@ -4345,28 +4345,28 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>0.885</v>
-      </c>
-      <c r="E87" s="3" t="n">
-        <v>-0.0112</v>
+        <v>0.28</v>
+      </c>
+      <c r="E87" s="8" t="n">
+        <v>-0.0175</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>2455400</v>
+        <v>2510700</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>0.32</v>
+        <v>0.42</v>
       </c>
       <c r="H87" t="n">
-        <v>45.18</v>
+        <v>21.33</v>
       </c>
       <c r="I87" s="6" t="inlineStr">
         <is>
@@ -4374,10 +4374,10 @@
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.929</v>
+        <v>0.333</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>0.847</v>
+        <v>0.372</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="7" t="inlineStr"/>
@@ -4390,39 +4390,39 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>0261</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>COSMOS</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>4.46</v>
-      </c>
-      <c r="E88" s="9" t="n">
-        <v>0.03240000000000001</v>
+        <v>0.41</v>
+      </c>
+      <c r="E88" s="10" t="n">
+        <v>0.025</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>2390800</v>
+        <v>2507800</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>0.45</v>
+        <v>7.52</v>
       </c>
       <c r="H88" t="n">
-        <v>52.98</v>
-      </c>
-      <c r="I88" s="8" t="inlineStr">
+        <v>67.38</v>
+      </c>
+      <c r="I88" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>4.362</v>
+        <v>0.381</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>4.432</v>
+        <v>0.363</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="7" t="inlineStr"/>
@@ -4435,28 +4435,28 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>0.915</v>
-      </c>
-      <c r="E89" s="3" t="n">
-        <v>-0.0161</v>
+        <v>0.88</v>
+      </c>
+      <c r="E89" s="8" t="n">
+        <v>-0.0168</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>2301200</v>
+        <v>2496400</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>0.59</v>
+        <v>0.32</v>
       </c>
       <c r="H89" t="n">
-        <v>24.01</v>
+        <v>44.55</v>
       </c>
       <c r="I89" s="6" t="inlineStr">
         <is>
@@ -4464,10 +4464,10 @@
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.969</v>
+        <v>0.929</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>1.052</v>
+        <v>0.847</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="7" t="inlineStr"/>
@@ -4480,39 +4480,39 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0056</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>NCT</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>0.5649999999999999</v>
+        <v>4.45</v>
       </c>
       <c r="E90" s="10" t="n">
-        <v>0</v>
+        <v>0.0301</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>2297000</v>
+        <v>2442900</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>1.1</v>
+        <v>0.46</v>
       </c>
       <c r="H90" t="n">
-        <v>51.44</v>
-      </c>
-      <c r="I90" s="8" t="inlineStr">
+        <v>52.64</v>
+      </c>
+      <c r="I90" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.5629999999999999</v>
+        <v>4.361</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>0.5620000000000001</v>
+        <v>4.431</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="7" t="inlineStr"/>
@@ -4525,39 +4525,39 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>0.585</v>
-      </c>
-      <c r="E91" s="10" t="n">
-        <v>0</v>
+        <v>0.92</v>
+      </c>
+      <c r="E91" s="8" t="n">
+        <v>-0.0108</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>2223000</v>
+        <v>2356600</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>0.53</v>
+        <v>0.6</v>
       </c>
       <c r="H91" t="n">
-        <v>68.69</v>
-      </c>
-      <c r="I91" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>24.89</v>
+      </c>
+      <c r="I91" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.509</v>
+        <v>0.969</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>0.468</v>
+        <v>1.052</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="7" t="inlineStr"/>
@@ -4570,39 +4570,39 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>5053</t>
+          <t>0056</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>OSK</t>
+          <t>NCT</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>1.63</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>-0.0121</v>
+        <v>0</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>2182800</v>
+        <v>2297000</v>
       </c>
       <c r="G92" s="5" t="n">
-        <v>1.53</v>
+        <v>1.1</v>
       </c>
       <c r="H92" t="n">
-        <v>30.22</v>
-      </c>
-      <c r="I92" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.44</v>
+      </c>
+      <c r="I92" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>1.728</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>1.884</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="7" t="inlineStr"/>
@@ -4615,39 +4615,39 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>1.3</v>
+        <v>0.585</v>
       </c>
       <c r="E93" s="3" t="n">
-        <v>-0.0226</v>
+        <v>0</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>2094700</v>
+        <v>2250300</v>
       </c>
       <c r="G93" s="5" t="n">
-        <v>0.87</v>
+        <v>0.54</v>
       </c>
       <c r="H93" t="n">
-        <v>56.17</v>
-      </c>
-      <c r="I93" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.69</v>
+      </c>
+      <c r="I93" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>1.26</v>
+        <v>0.509</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>1.173</v>
+        <v>0.468</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="7" t="inlineStr"/>
@@ -4660,28 +4660,28 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>5053</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>OSK</t>
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>0.735</v>
-      </c>
-      <c r="E94" s="3" t="n">
-        <v>-0.0329</v>
+        <v>1.64</v>
+      </c>
+      <c r="E94" s="8" t="n">
+        <v>-0.0061</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>2084400</v>
+        <v>2209300</v>
       </c>
       <c r="G94" s="5" t="n">
-        <v>0.39</v>
+        <v>1.55</v>
       </c>
       <c r="H94" t="n">
-        <v>48.09</v>
+        <v>31.11</v>
       </c>
       <c r="I94" s="6" t="inlineStr">
         <is>
@@ -4689,10 +4689,10 @@
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.761</v>
+        <v>1.729</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>0.6850000000000001</v>
+        <v>1.884</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="7" t="inlineStr"/>
@@ -4705,28 +4705,28 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>0.835</v>
-      </c>
-      <c r="E95" s="3" t="n">
-        <v>-0.0176</v>
+        <v>0.73</v>
+      </c>
+      <c r="E95" s="8" t="n">
+        <v>-0.0395</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>2043700</v>
+        <v>2144700</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>0.57</v>
+        <v>0.4</v>
       </c>
       <c r="H95" t="n">
-        <v>53.24</v>
+        <v>47.28</v>
       </c>
       <c r="I95" s="6" t="inlineStr">
         <is>
@@ -4734,10 +4734,10 @@
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.827</v>
+        <v>0.761</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>0.781</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="7" t="inlineStr"/>
@@ -4750,38 +4750,40 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="E96" s="3" t="n">
-        <v>-0.0137</v>
+        <v>1.3</v>
+      </c>
+      <c r="E96" s="8" t="n">
+        <v>-0.0226</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>2018800</v>
+        <v>2098300</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>0.35</v>
+        <v>0.87</v>
       </c>
       <c r="H96" t="n">
-        <v>62.55</v>
-      </c>
-      <c r="I96" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>56.17</v>
+      </c>
+      <c r="I96" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.319</v>
-      </c>
-      <c r="K96" s="2" t="n"/>
+        <v>1.26</v>
+      </c>
+      <c r="K96" s="2" t="n">
+        <v>1.173</v>
+      </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="7" t="inlineStr"/>
     </row>
@@ -4793,28 +4795,28 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>DATASONIC</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="E97" s="3" t="n">
-        <v>-0.0175</v>
+        <v>0.835</v>
+      </c>
+      <c r="E97" s="8" t="n">
+        <v>-0.0176</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>2014600</v>
+        <v>2076200</v>
       </c>
       <c r="G97" s="5" t="n">
-        <v>0.17</v>
+        <v>0.58</v>
       </c>
       <c r="H97" t="n">
-        <v>46.28</v>
+        <v>53.24</v>
       </c>
       <c r="I97" s="6" t="inlineStr">
         <is>
@@ -4822,10 +4824,10 @@
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.291</v>
+        <v>0.827</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>0.283</v>
+        <v>0.781</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="7" t="inlineStr"/>
@@ -4838,28 +4840,28 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0372</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>CHEEDING</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E98" s="3" t="n">
-        <v>-0.0291</v>
+        <v>0.64</v>
+      </c>
+      <c r="E98" s="8" t="n">
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>1976300</v>
+        <v>2062600</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>0.45</v>
+        <v>0.23</v>
       </c>
       <c r="H98" t="n">
-        <v>29.93</v>
+        <v>41.76</v>
       </c>
       <c r="I98" s="6" t="inlineStr">
         <is>
@@ -4867,10 +4869,10 @@
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.581</v>
+        <v>0.678</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>0.599</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="7" t="inlineStr"/>
@@ -4883,28 +4885,28 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>DATASONIC</t>
         </is>
       </c>
       <c r="D99" s="2" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E99" s="3" t="n">
-        <v>-0.0155</v>
+        <v>0.28</v>
+      </c>
+      <c r="E99" s="8" t="n">
+        <v>-0.0175</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v>1907900</v>
+        <v>2034600</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>0.21</v>
+        <v>0.17</v>
       </c>
       <c r="H99" t="n">
-        <v>40.95</v>
+        <v>46.28</v>
       </c>
       <c r="I99" s="6" t="inlineStr">
         <is>
@@ -4912,10 +4914,10 @@
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.678</v>
+        <v>0.291</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.283</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="7" t="inlineStr"/>
@@ -4928,40 +4930,38 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>5271</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>PECCA</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D100" s="2" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="E100" s="10" t="n">
-        <v>0</v>
+        <v>0.36</v>
+      </c>
+      <c r="E100" s="8" t="n">
+        <v>-0.0137</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>1849200</v>
+        <v>2020100</v>
       </c>
       <c r="G100" s="5" t="n">
-        <v>0.95</v>
+        <v>0.35</v>
       </c>
       <c r="H100" t="n">
-        <v>43.62</v>
-      </c>
-      <c r="I100" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.55</v>
+      </c>
+      <c r="I100" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>1.367</v>
-      </c>
-      <c r="K100" s="2" t="n">
-        <v>1.343</v>
-      </c>
+        <v>0.319</v>
+      </c>
+      <c r="K100" s="2" t="n"/>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="7" t="inlineStr"/>
     </row>
@@ -4973,28 +4973,28 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>0372</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>CHEEDING</t>
         </is>
       </c>
       <c r="D101" s="2" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="E101" s="3" t="n">
-        <v>-0.008100000000000001</v>
+        <v>0.5</v>
+      </c>
+      <c r="E101" s="8" t="n">
+        <v>-0.0291</v>
       </c>
       <c r="F101" s="4" t="n">
-        <v>1842000</v>
+        <v>1976800</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>0.32</v>
+        <v>0.45</v>
       </c>
       <c r="H101" t="n">
-        <v>59.95</v>
+        <v>29.93</v>
       </c>
       <c r="I101" s="6" t="inlineStr">
         <is>
@@ -5002,10 +5002,10 @@
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.571</v>
+        <v>0.581</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>0.47</v>
+        <v>0.599</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="7" t="inlineStr"/>
@@ -5029,19 +5029,19 @@
       <c r="D102" s="2" t="n">
         <v>0.335</v>
       </c>
-      <c r="E102" s="10" t="n">
+      <c r="E102" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>1830900</v>
+        <v>1952200</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>0.39</v>
+        <v>0.41</v>
       </c>
       <c r="H102" t="n">
         <v>47.09</v>
       </c>
-      <c r="I102" s="8" t="inlineStr">
+      <c r="I102" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -5063,28 +5063,28 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>5162</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>VSTECS</t>
+          <t>PECCA</t>
         </is>
       </c>
       <c r="D103" s="2" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>-0.0323</v>
+        <v>0</v>
       </c>
       <c r="F103" s="4" t="n">
-        <v>1807600</v>
+        <v>1849200</v>
       </c>
       <c r="G103" s="5" t="n">
-        <v>1.04</v>
+        <v>0.95</v>
       </c>
       <c r="H103" t="n">
-        <v>35.96</v>
+        <v>43.62</v>
       </c>
       <c r="I103" s="6" t="inlineStr">
         <is>
@@ -5092,10 +5092,10 @@
         </is>
       </c>
       <c r="J103" s="2" t="n">
-        <v>1.621</v>
+        <v>1.367</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>1.664</v>
+        <v>1.343</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="7" t="inlineStr"/>
@@ -5108,39 +5108,39 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D104" s="2" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E104" s="10" t="n">
-        <v>0</v>
+        <v>0.61</v>
+      </c>
+      <c r="E104" s="8" t="n">
+        <v>-0.008100000000000001</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v>1715400</v>
+        <v>1842200</v>
       </c>
       <c r="G104" s="5" t="n">
-        <v>0.77</v>
+        <v>0.32</v>
       </c>
       <c r="H104" t="n">
-        <v>50.9</v>
-      </c>
-      <c r="I104" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>59.95</v>
+      </c>
+      <c r="I104" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.637</v>
+        <v>0.571</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>0.622</v>
+        <v>0.47</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="7" t="inlineStr"/>
@@ -5153,28 +5153,28 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>5162</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>VSTECS</t>
         </is>
       </c>
       <c r="D105" s="2" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="E105" s="3" t="n">
-        <v>-0.0026</v>
+        <v>1.51</v>
+      </c>
+      <c r="E105" s="8" t="n">
+        <v>-0.0258</v>
       </c>
       <c r="F105" s="4" t="n">
-        <v>1695000</v>
+        <v>1822900</v>
       </c>
       <c r="G105" s="5" t="n">
-        <v>0.58</v>
+        <v>1.05</v>
       </c>
       <c r="H105" t="n">
-        <v>50.38</v>
+        <v>36.69</v>
       </c>
       <c r="I105" s="6" t="inlineStr">
         <is>
@@ -5182,10 +5182,10 @@
         </is>
       </c>
       <c r="J105" s="2" t="n">
-        <v>3.847</v>
+        <v>1.622</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>3.682</v>
+        <v>1.665</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="7" t="inlineStr"/>
@@ -5198,28 +5198,28 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D106" s="2" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="E106" s="9" t="n">
-        <v>0.0168</v>
+        <v>0.595</v>
+      </c>
+      <c r="E106" s="10" t="n">
+        <v>0.008500000000000001</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v>1693300</v>
+        <v>1812700</v>
       </c>
       <c r="G106" s="5" t="n">
-        <v>0.14</v>
+        <v>0.41</v>
       </c>
       <c r="H106" t="n">
-        <v>47.95</v>
+        <v>50.22</v>
       </c>
       <c r="I106" s="6" t="inlineStr">
         <is>
@@ -5227,10 +5227,10 @@
         </is>
       </c>
       <c r="J106" s="2" t="n">
-        <v>2.444</v>
+        <v>0.598</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>2.385</v>
+        <v>0.586</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="7" t="inlineStr"/>
@@ -5243,39 +5243,39 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>1.18</v>
+        <v>0.635</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0</v>
       </c>
       <c r="F107" s="4" t="n">
-        <v>1687100</v>
+        <v>1780400</v>
       </c>
       <c r="G107" s="5" t="n">
-        <v>0.48</v>
+        <v>0.8</v>
       </c>
       <c r="H107" t="n">
-        <v>47.42</v>
-      </c>
-      <c r="I107" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.9</v>
+      </c>
+      <c r="I107" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J107" s="2" t="n">
-        <v>1.238</v>
+        <v>0.637</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>1.067</v>
+        <v>0.622</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="7" t="inlineStr"/>
@@ -5299,14 +5299,14 @@
       <c r="D108" s="2" t="n">
         <v>0.785</v>
       </c>
-      <c r="E108" s="3" t="n">
+      <c r="E108" s="8" t="n">
         <v>-0.0126</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>1669500</v>
+        <v>1775400</v>
       </c>
       <c r="G108" s="5" t="n">
-        <v>0.76</v>
+        <v>0.8</v>
       </c>
       <c r="H108" t="n">
         <v>15.53</v>
@@ -5333,39 +5333,39 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>5248</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>BAUTO</t>
+          <t>TENAGA</t>
         </is>
       </c>
       <c r="D109" s="2" t="n">
-        <v>0.895</v>
-      </c>
-      <c r="E109" s="9" t="n">
-        <v>0.017</v>
+        <v>12.9</v>
+      </c>
+      <c r="E109" s="8" t="n">
+        <v>-0.0077</v>
       </c>
       <c r="F109" s="4" t="n">
-        <v>1666500</v>
+        <v>1763300</v>
       </c>
       <c r="G109" s="5" t="n">
-        <v>1.02</v>
+        <v>0.22</v>
       </c>
       <c r="H109" t="n">
-        <v>49.48</v>
-      </c>
-      <c r="I109" s="8" t="inlineStr">
+        <v>40.8</v>
+      </c>
+      <c r="I109" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.892</v>
+        <v>13.008</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>0.908</v>
+        <v>13.413</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="7" t="inlineStr"/>
@@ -5378,39 +5378,39 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D110" s="2" t="n">
-        <v>12.94</v>
-      </c>
-      <c r="E110" s="3" t="n">
-        <v>-0.0046</v>
+        <v>2.42</v>
+      </c>
+      <c r="E110" s="10" t="n">
+        <v>0.0168</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>1653300</v>
+        <v>1743900</v>
       </c>
       <c r="G110" s="5" t="n">
-        <v>0.21</v>
+        <v>0.15</v>
       </c>
       <c r="H110" t="n">
-        <v>42.45</v>
-      </c>
-      <c r="I110" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.95</v>
+      </c>
+      <c r="I110" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J110" s="2" t="n">
-        <v>13.012</v>
+        <v>2.444</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>13.414</v>
+        <v>2.385</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="7" t="inlineStr"/>
@@ -5423,39 +5423,39 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D111" s="2" t="n">
-        <v>7.19</v>
-      </c>
-      <c r="E111" s="3" t="n">
-        <v>-0.0178</v>
+        <v>1.2</v>
+      </c>
+      <c r="E111" s="10" t="n">
+        <v>0.008399999999999999</v>
       </c>
       <c r="F111" s="4" t="n">
-        <v>1646100</v>
+        <v>1725200</v>
       </c>
       <c r="G111" s="5" t="n">
-        <v>0.16</v>
+        <v>0.49</v>
       </c>
       <c r="H111" t="n">
-        <v>30.74</v>
-      </c>
-      <c r="I111" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.45</v>
+      </c>
+      <c r="I111" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J111" s="2" t="n">
-        <v>7.453</v>
+        <v>1.24</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>7.948</v>
+        <v>1.068</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="7" t="inlineStr"/>
@@ -5468,28 +5468,28 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>0245</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>MNHLDG</t>
         </is>
       </c>
       <c r="D112" s="2" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="E112" s="8" t="n">
+        <v>-0.0026</v>
+      </c>
+      <c r="F112" s="4" t="n">
+        <v>1712000</v>
+      </c>
+      <c r="G112" s="5" t="n">
         <v>0.59</v>
       </c>
-      <c r="E112" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F112" s="4" t="n">
-        <v>1631000</v>
-      </c>
-      <c r="G112" s="5" t="n">
-        <v>0.37</v>
-      </c>
       <c r="H112" t="n">
-        <v>49.06</v>
+        <v>50.38</v>
       </c>
       <c r="I112" s="6" t="inlineStr">
         <is>
@@ -5497,10 +5497,10 @@
         </is>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.598</v>
+        <v>3.847</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>0.586</v>
+        <v>3.682</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="7" t="inlineStr"/>
@@ -5513,39 +5513,39 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>SPSETIA</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D113" s="2" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="E113" s="9" t="n">
-        <v>0.0147</v>
+        <v>7.19</v>
+      </c>
+      <c r="E113" s="8" t="n">
+        <v>-0.0178</v>
       </c>
       <c r="F113" s="4" t="n">
-        <v>1625000</v>
+        <v>1700900</v>
       </c>
       <c r="G113" s="5" t="n">
-        <v>0.24</v>
+        <v>0.17</v>
       </c>
       <c r="H113" t="n">
-        <v>33.21</v>
-      </c>
-      <c r="I113" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>30.74</v>
+      </c>
+      <c r="I113" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.725</v>
+        <v>7.453</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>0.791</v>
+        <v>7.948</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="7" t="inlineStr"/>
@@ -5558,39 +5558,39 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>5248</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>BAUTO</t>
         </is>
       </c>
       <c r="D114" s="2" t="n">
-        <v>0.475</v>
+        <v>0.89</v>
       </c>
       <c r="E114" s="10" t="n">
-        <v>0</v>
+        <v>0.0114</v>
       </c>
       <c r="F114" s="4" t="n">
-        <v>1622000</v>
+        <v>1670800</v>
       </c>
       <c r="G114" s="5" t="n">
-        <v>0.19</v>
+        <v>1.03</v>
       </c>
       <c r="H114" t="n">
-        <v>36.82</v>
-      </c>
-      <c r="I114" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.66</v>
+      </c>
+      <c r="I114" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.506</v>
+        <v>0.892</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>0.524</v>
+        <v>0.907</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="7" t="inlineStr"/>
@@ -5603,28 +5603,28 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>0192</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>INTA</t>
+          <t>SPSETIA</t>
         </is>
       </c>
       <c r="D115" s="2" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="E115" s="3" t="n">
-        <v>-0.026</v>
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="E115" s="10" t="n">
+        <v>0.0147</v>
       </c>
       <c r="F115" s="4" t="n">
-        <v>1619800</v>
+        <v>1660600</v>
       </c>
       <c r="G115" s="5" t="n">
-        <v>0.6</v>
+        <v>0.24</v>
       </c>
       <c r="H115" t="n">
-        <v>38.98</v>
+        <v>33.21</v>
       </c>
       <c r="I115" s="6" t="inlineStr">
         <is>
@@ -5632,10 +5632,10 @@
         </is>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.393</v>
+        <v>0.725</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>0.389</v>
+        <v>0.791</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="7" t="inlineStr"/>
@@ -5648,28 +5648,28 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>5272</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>RANHILL</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D116" s="2" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="E116" s="3" t="n">
-        <v>-0.0064</v>
+        <v>1.13</v>
+      </c>
+      <c r="E116" s="10" t="n">
+        <v>0.018</v>
       </c>
       <c r="F116" s="4" t="n">
-        <v>1608900</v>
+        <v>1646300</v>
       </c>
       <c r="G116" s="5" t="n">
-        <v>1.01</v>
+        <v>0.38</v>
       </c>
       <c r="H116" t="n">
-        <v>50.69</v>
+        <v>60.33</v>
       </c>
       <c r="I116" s="6" t="inlineStr">
         <is>
@@ -5677,10 +5677,10 @@
         </is>
       </c>
       <c r="J116" s="2" t="n">
-        <v>3.17</v>
+        <v>1.057</v>
       </c>
       <c r="K116" s="2" t="n">
-        <v>2.876</v>
+        <v>0.914</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="7" t="inlineStr"/>
@@ -5693,28 +5693,28 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>5272</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>RANHILL</t>
         </is>
       </c>
       <c r="D117" s="2" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="E117" s="10" t="n">
-        <v>0</v>
+        <v>3.13</v>
+      </c>
+      <c r="E117" s="8" t="n">
+        <v>-0.0032</v>
       </c>
       <c r="F117" s="4" t="n">
-        <v>1602300</v>
+        <v>1638200</v>
       </c>
       <c r="G117" s="5" t="n">
-        <v>0.37</v>
+        <v>1.03</v>
       </c>
       <c r="H117" t="n">
-        <v>58.81</v>
+        <v>51.41</v>
       </c>
       <c r="I117" s="6" t="inlineStr">
         <is>
@@ -5722,10 +5722,10 @@
         </is>
       </c>
       <c r="J117" s="2" t="n">
-        <v>1.055</v>
+        <v>3.171</v>
       </c>
       <c r="K117" s="2" t="n">
-        <v>0.914</v>
+        <v>2.876</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="7" t="inlineStr"/>
@@ -5738,28 +5738,28 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>0192</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>INTA</t>
         </is>
       </c>
       <c r="D118" s="2" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E118" s="3" t="n">
-        <v>-0.0234</v>
+        <v>0.375</v>
+      </c>
+      <c r="E118" s="8" t="n">
+        <v>-0.026</v>
       </c>
       <c r="F118" s="4" t="n">
-        <v>1595100</v>
+        <v>1627600</v>
       </c>
       <c r="G118" s="5" t="n">
-        <v>0.26</v>
+        <v>0.61</v>
       </c>
       <c r="H118" t="n">
-        <v>41.66</v>
+        <v>38.98</v>
       </c>
       <c r="I118" s="6" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="J118" s="2" t="n">
-        <v>2.604</v>
+        <v>0.393</v>
       </c>
       <c r="K118" s="2" t="n">
-        <v>2.607</v>
+        <v>0.389</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="7" t="inlineStr"/>
@@ -5783,28 +5783,28 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D119" s="2" t="n">
-        <v>1.24</v>
+        <v>0.475</v>
       </c>
       <c r="E119" s="3" t="n">
-        <v>-0.008</v>
+        <v>0</v>
       </c>
       <c r="F119" s="4" t="n">
-        <v>1586700</v>
+        <v>1625200</v>
       </c>
       <c r="G119" s="5" t="n">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
       <c r="H119" t="n">
-        <v>40.01</v>
+        <v>36.82</v>
       </c>
       <c r="I119" s="6" t="inlineStr">
         <is>
@@ -5812,10 +5812,10 @@
         </is>
       </c>
       <c r="J119" s="2" t="n">
-        <v>1.297</v>
+        <v>0.506</v>
       </c>
       <c r="K119" s="2" t="n">
-        <v>1.314</v>
+        <v>0.524</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="7" t="inlineStr"/>
@@ -5828,28 +5828,28 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>8524</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>TALIWRK</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D120" s="2" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="E120" s="3" t="n">
-        <v>-0.0217</v>
+        <v>2.51</v>
+      </c>
+      <c r="E120" s="8" t="n">
+        <v>-0.0195</v>
       </c>
       <c r="F120" s="4" t="n">
-        <v>1578300</v>
+        <v>1616100</v>
       </c>
       <c r="G120" s="5" t="n">
-        <v>0.79</v>
+        <v>0.27</v>
       </c>
       <c r="H120" t="n">
-        <v>34.68</v>
+        <v>42.31</v>
       </c>
       <c r="I120" s="6" t="inlineStr">
         <is>
@@ -5857,10 +5857,10 @@
         </is>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.243</v>
+        <v>2.605</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>0.256</v>
+        <v>2.607</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="7" t="inlineStr"/>
@@ -5873,28 +5873,28 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>UWC</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D121" s="2" t="n">
-        <v>7.25</v>
+        <v>1.25</v>
       </c>
       <c r="E121" s="3" t="n">
-        <v>-0.0068</v>
+        <v>0</v>
       </c>
       <c r="F121" s="4" t="n">
-        <v>1576000</v>
+        <v>1596000</v>
       </c>
       <c r="G121" s="5" t="n">
-        <v>0.37</v>
+        <v>0.17</v>
       </c>
       <c r="H121" t="n">
-        <v>50.3</v>
+        <v>41.23</v>
       </c>
       <c r="I121" s="6" t="inlineStr">
         <is>
@@ -5902,10 +5902,10 @@
         </is>
       </c>
       <c r="J121" s="2" t="n">
-        <v>7.347</v>
+        <v>1.298</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>6.897</v>
+        <v>1.314</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="7" t="inlineStr"/>
@@ -5918,28 +5918,28 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>8524</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>TALIWRK</t>
         </is>
       </c>
       <c r="D122" s="2" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="E122" s="3" t="n">
-        <v>-0.0172</v>
+        <v>0.225</v>
+      </c>
+      <c r="E122" s="8" t="n">
+        <v>-0.0217</v>
       </c>
       <c r="F122" s="4" t="n">
-        <v>1553800</v>
+        <v>1581800</v>
       </c>
       <c r="G122" s="5" t="n">
-        <v>0.37</v>
+        <v>0.79</v>
       </c>
       <c r="H122" t="n">
-        <v>49.11</v>
+        <v>34.68</v>
       </c>
       <c r="I122" s="6" t="inlineStr">
         <is>
@@ -5947,10 +5947,10 @@
         </is>
       </c>
       <c r="J122" s="2" t="n">
-        <v>1.159</v>
+        <v>0.243</v>
       </c>
       <c r="K122" s="2" t="n">
-        <v>1.1</v>
+        <v>0.256</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="7" t="inlineStr"/>
@@ -5963,39 +5963,39 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>0325</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>UWC</t>
         </is>
       </c>
       <c r="D123" s="2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="E123" s="10" t="n">
-        <v>0</v>
+        <v>7.26</v>
+      </c>
+      <c r="E123" s="8" t="n">
+        <v>-0.005500000000000001</v>
       </c>
       <c r="F123" s="4" t="n">
-        <v>1535500</v>
+        <v>1580000</v>
       </c>
       <c r="G123" s="5" t="n">
-        <v>0.78</v>
+        <v>0.37</v>
       </c>
       <c r="H123" t="n">
-        <v>51.14</v>
-      </c>
-      <c r="I123" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.52</v>
+      </c>
+      <c r="I123" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J123" s="2" t="n">
-        <v>1.091</v>
+        <v>7.347</v>
       </c>
       <c r="K123" s="2" t="n">
-        <v>1.097</v>
+        <v>6.897</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="7" t="inlineStr"/>
@@ -6008,28 +6008,28 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>5329</t>
+          <t>0217</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>AZAMJAYA</t>
+          <t>PWRWELL</t>
         </is>
       </c>
       <c r="D124" s="2" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="E124" s="3" t="n">
-        <v>-0.0452</v>
+        <v>1.14</v>
+      </c>
+      <c r="E124" s="8" t="n">
+        <v>-0.0172</v>
       </c>
       <c r="F124" s="4" t="n">
-        <v>1492600</v>
+        <v>1558700</v>
       </c>
       <c r="G124" s="5" t="n">
-        <v>9.140000000000001</v>
+        <v>0.37</v>
       </c>
       <c r="H124" t="n">
-        <v>45.49</v>
+        <v>49.11</v>
       </c>
       <c r="I124" s="6" t="inlineStr">
         <is>
@@ -6037,10 +6037,10 @@
         </is>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.969</v>
+        <v>1.159</v>
       </c>
       <c r="K124" s="2" t="n">
-        <v>0.976</v>
+        <v>1.1</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="7" t="inlineStr"/>
@@ -6053,39 +6053,39 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>0325</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="D125" s="2" t="n">
-        <v>0.845</v>
-      </c>
-      <c r="E125" s="10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E125" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F125" s="4" t="n">
-        <v>1490000</v>
+        <v>1535500</v>
       </c>
       <c r="G125" s="5" t="n">
-        <v>0.51</v>
+        <v>0.78</v>
       </c>
       <c r="H125" t="n">
-        <v>17.21</v>
-      </c>
-      <c r="I125" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.14</v>
+      </c>
+      <c r="I125" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J125" s="2" t="n">
-        <v>0.916</v>
+        <v>1.091</v>
       </c>
       <c r="K125" s="2" t="n">
-        <v>0.973</v>
+        <v>1.097</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="7" t="inlineStr"/>
@@ -6098,39 +6098,39 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>0278</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>EDELTEQ</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D126" s="2" t="n">
-        <v>0.415</v>
-      </c>
-      <c r="E126" s="3" t="n">
-        <v>-0.0349</v>
+        <v>0.84</v>
+      </c>
+      <c r="E126" s="8" t="n">
+        <v>-0.0059</v>
       </c>
       <c r="F126" s="4" t="n">
-        <v>1470500</v>
+        <v>1525000</v>
       </c>
       <c r="G126" s="5" t="n">
-        <v>0.26</v>
+        <v>0.52</v>
       </c>
       <c r="H126" t="n">
-        <v>57.05</v>
-      </c>
-      <c r="I126" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>16.62</v>
+      </c>
+      <c r="I126" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J126" s="2" t="n">
-        <v>0.39</v>
+        <v>0.915</v>
       </c>
       <c r="K126" s="2" t="n">
-        <v>0.36</v>
+        <v>0.973</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="7" t="inlineStr"/>
@@ -6143,28 +6143,28 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>0233</t>
+          <t>5329</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>PEKAT</t>
+          <t>AZAMJAYA</t>
         </is>
       </c>
       <c r="D127" s="2" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="E127" s="9" t="n">
-        <v>0.0326</v>
+        <v>0.95</v>
+      </c>
+      <c r="E127" s="8" t="n">
+        <v>-0.0452</v>
       </c>
       <c r="F127" s="4" t="n">
-        <v>1403900</v>
+        <v>1492600</v>
       </c>
       <c r="G127" s="5" t="n">
-        <v>0.39</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="H127" t="n">
-        <v>60.65</v>
+        <v>45.49</v>
       </c>
       <c r="I127" s="6" t="inlineStr">
         <is>
@@ -6172,10 +6172,10 @@
         </is>
       </c>
       <c r="J127" s="2" t="n">
-        <v>2.684</v>
+        <v>0.969</v>
       </c>
       <c r="K127" s="2" t="n">
-        <v>2.263</v>
+        <v>0.976</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="7" t="inlineStr"/>
@@ -6188,39 +6188,39 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>7160</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>PENTA</t>
         </is>
       </c>
       <c r="D128" s="2" t="n">
-        <v>0.675</v>
-      </c>
-      <c r="E128" s="3" t="n">
-        <v>-0.0146</v>
+        <v>5.51</v>
+      </c>
+      <c r="E128" s="8" t="n">
+        <v>-0.0161</v>
       </c>
       <c r="F128" s="4" t="n">
-        <v>1402800</v>
+        <v>1484000</v>
       </c>
       <c r="G128" s="5" t="n">
-        <v>0.52</v>
+        <v>0.39</v>
       </c>
       <c r="H128" t="n">
-        <v>60.9</v>
-      </c>
-      <c r="I128" s="8" t="inlineStr">
+        <v>50.98</v>
+      </c>
+      <c r="I128" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J128" s="2" t="n">
-        <v>0.648</v>
+        <v>5.514</v>
       </c>
       <c r="K128" s="2" t="n">
-        <v>0.5570000000000001</v>
+        <v>5.394</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="7" t="inlineStr"/>
@@ -6233,39 +6233,39 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>0278</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>EDELTEQ</t>
         </is>
       </c>
       <c r="D129" s="2" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="E129" s="3" t="n">
-        <v>-0.0107</v>
+        <v>0.415</v>
+      </c>
+      <c r="E129" s="8" t="n">
+        <v>-0.0349</v>
       </c>
       <c r="F129" s="4" t="n">
-        <v>1400000</v>
+        <v>1472600</v>
       </c>
       <c r="G129" s="5" t="n">
-        <v>0.37</v>
+        <v>0.26</v>
       </c>
       <c r="H129" t="n">
-        <v>39.95</v>
-      </c>
-      <c r="I129" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.05</v>
+      </c>
+      <c r="I129" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J129" s="2" t="n">
-        <v>2.896</v>
+        <v>0.39</v>
       </c>
       <c r="K129" s="2" t="n">
-        <v>3.013</v>
+        <v>0.36</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="7" t="inlineStr"/>
@@ -6278,28 +6278,28 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D130" s="2" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E130" s="10" t="n">
-        <v>0</v>
+        <v>2.77</v>
+      </c>
+      <c r="E130" s="8" t="n">
+        <v>-0.0107</v>
       </c>
       <c r="F130" s="4" t="n">
-        <v>1395800</v>
+        <v>1421500</v>
       </c>
       <c r="G130" s="5" t="n">
-        <v>0.17</v>
+        <v>0.38</v>
       </c>
       <c r="H130" t="n">
-        <v>50.51</v>
+        <v>39.95</v>
       </c>
       <c r="I130" s="6" t="inlineStr">
         <is>
@@ -6307,10 +6307,10 @@
         </is>
       </c>
       <c r="J130" s="2" t="n">
-        <v>0.354</v>
+        <v>2.896</v>
       </c>
       <c r="K130" s="2" t="n">
-        <v>0.327</v>
+        <v>3.013</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="7" t="inlineStr"/>
@@ -6323,39 +6323,39 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>AWC</t>
         </is>
       </c>
       <c r="D131" s="2" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="E131" s="9" t="n">
-        <v>0.0036</v>
+        <v>0.675</v>
+      </c>
+      <c r="E131" s="8" t="n">
+        <v>-0.0146</v>
       </c>
       <c r="F131" s="4" t="n">
-        <v>1368800</v>
+        <v>1416300</v>
       </c>
       <c r="G131" s="5" t="n">
-        <v>0.15</v>
+        <v>0.53</v>
       </c>
       <c r="H131" t="n">
-        <v>53.66</v>
-      </c>
-      <c r="I131" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.9</v>
+      </c>
+      <c r="I131" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J131" s="2" t="n">
-        <v>2.794</v>
+        <v>0.648</v>
       </c>
       <c r="K131" s="2" t="n">
-        <v>2.664</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="7" t="inlineStr"/>
@@ -6368,28 +6368,28 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>0151</t>
+          <t>0233</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>KGB</t>
+          <t>PEKAT</t>
         </is>
       </c>
       <c r="D132" s="2" t="n">
-        <v>8.390000000000001</v>
-      </c>
-      <c r="E132" s="9" t="n">
-        <v>0.0048</v>
+        <v>2.84</v>
+      </c>
+      <c r="E132" s="10" t="n">
+        <v>0.029</v>
       </c>
       <c r="F132" s="4" t="n">
-        <v>1344300</v>
+        <v>1415000</v>
       </c>
       <c r="G132" s="5" t="n">
-        <v>0.59</v>
+        <v>0.39</v>
       </c>
       <c r="H132" t="n">
-        <v>43.5</v>
+        <v>60.33</v>
       </c>
       <c r="I132" s="6" t="inlineStr">
         <is>
@@ -6397,10 +6397,10 @@
         </is>
       </c>
       <c r="J132" s="2" t="n">
-        <v>8.631</v>
+        <v>2.683</v>
       </c>
       <c r="K132" s="2" t="n">
-        <v>8.695</v>
+        <v>2.262</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="7" t="inlineStr"/>
@@ -6413,28 +6413,28 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>SUNREIT</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D133" s="2" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="E133" s="10" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E133" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F133" s="4" t="n">
-        <v>1324700</v>
+        <v>1413400</v>
       </c>
       <c r="G133" s="5" t="n">
-        <v>0.41</v>
+        <v>0.17</v>
       </c>
       <c r="H133" t="n">
-        <v>44.02</v>
+        <v>50.51</v>
       </c>
       <c r="I133" s="6" t="inlineStr">
         <is>
@@ -6442,10 +6442,10 @@
         </is>
       </c>
       <c r="J133" s="2" t="n">
-        <v>2.044</v>
+        <v>0.354</v>
       </c>
       <c r="K133" s="2" t="n">
-        <v>2.071</v>
+        <v>0.327</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="7" t="inlineStr"/>
@@ -6458,28 +6458,28 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>0239</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>ECOMATE</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D134" s="2" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E134" s="9" t="n">
-        <v>0.0058</v>
+        <v>2.82</v>
+      </c>
+      <c r="E134" s="10" t="n">
+        <v>0.0036</v>
       </c>
       <c r="F134" s="4" t="n">
-        <v>1312000</v>
+        <v>1381000</v>
       </c>
       <c r="G134" s="5" t="n">
-        <v>0.42</v>
+        <v>0.15</v>
       </c>
       <c r="H134" t="n">
-        <v>52.3</v>
+        <v>53.66</v>
       </c>
       <c r="I134" s="6" t="inlineStr">
         <is>
@@ -6487,10 +6487,10 @@
         </is>
       </c>
       <c r="J134" s="2" t="n">
-        <v>0.864</v>
+        <v>2.794</v>
       </c>
       <c r="K134" s="2" t="n">
-        <v>0.859</v>
+        <v>2.664</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="7" t="inlineStr"/>
@@ -6503,28 +6503,28 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>0470</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>BFIELD</t>
+          <t>CPETECH</t>
         </is>
       </c>
       <c r="D135" s="2" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="E135" s="3" t="n">
-        <v>-0.0118</v>
+        <v>1.31</v>
+      </c>
+      <c r="E135" s="8" t="n">
+        <v>-0.0076</v>
       </c>
       <c r="F135" s="4" t="n">
-        <v>1307700</v>
+        <v>1353200</v>
       </c>
       <c r="G135" s="5" t="n">
-        <v>0.24</v>
+        <v>0.43</v>
       </c>
       <c r="H135" t="n">
-        <v>17.86</v>
+        <v>52.99</v>
       </c>
       <c r="I135" s="6" t="inlineStr">
         <is>
@@ -6532,9 +6532,11 @@
         </is>
       </c>
       <c r="J135" s="2" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="K135" s="2" t="n"/>
+        <v>1.291</v>
+      </c>
+      <c r="K135" s="2" t="n">
+        <v>1.226</v>
+      </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="7" t="inlineStr"/>
     </row>
@@ -6546,28 +6548,28 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>5932</t>
+          <t>0151</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>BPURI</t>
+          <t>KGB</t>
         </is>
       </c>
       <c r="D136" s="2" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="E136" s="3" t="n">
-        <v>-0.0233</v>
+        <v>8.359999999999999</v>
+      </c>
+      <c r="E136" s="10" t="n">
+        <v>0.0012</v>
       </c>
       <c r="F136" s="4" t="n">
-        <v>1297400</v>
+        <v>1347200</v>
       </c>
       <c r="G136" s="5" t="n">
-        <v>1.89</v>
+        <v>0.59</v>
       </c>
       <c r="H136" t="n">
-        <v>38.22</v>
+        <v>42.66</v>
       </c>
       <c r="I136" s="6" t="inlineStr">
         <is>
@@ -6575,10 +6577,10 @@
         </is>
       </c>
       <c r="J136" s="2" t="n">
-        <v>0.223</v>
+        <v>8.629</v>
       </c>
       <c r="K136" s="2" t="n">
-        <v>0.232</v>
+        <v>8.695</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="7" t="inlineStr"/>
@@ -6591,28 +6593,28 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>0298</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>WENTEL</t>
+          <t>SUNREIT</t>
         </is>
       </c>
       <c r="D137" s="2" t="n">
-        <v>0.235</v>
-      </c>
-      <c r="E137" s="3" t="n">
-        <v>-0.0408</v>
+        <v>2.03</v>
+      </c>
+      <c r="E137" s="10" t="n">
+        <v>0.005</v>
       </c>
       <c r="F137" s="4" t="n">
-        <v>1295300</v>
+        <v>1341600</v>
       </c>
       <c r="G137" s="5" t="n">
-        <v>0.76</v>
+        <v>0.42</v>
       </c>
       <c r="H137" t="n">
-        <v>36.24</v>
+        <v>46.01</v>
       </c>
       <c r="I137" s="6" t="inlineStr">
         <is>
@@ -6620,10 +6622,10 @@
         </is>
       </c>
       <c r="J137" s="2" t="n">
-        <v>0.254</v>
+        <v>2.045</v>
       </c>
       <c r="K137" s="2" t="n">
-        <v>0.274</v>
+        <v>2.071</v>
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" s="7" t="inlineStr"/>
@@ -6636,39 +6638,39 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>PENTA</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D138" s="2" t="n">
-        <v>5.49</v>
-      </c>
-      <c r="E138" s="3" t="n">
-        <v>-0.0196</v>
+        <v>6.46</v>
+      </c>
+      <c r="E138" s="8" t="n">
+        <v>-0.0062</v>
       </c>
       <c r="F138" s="4" t="n">
-        <v>1294200</v>
+        <v>1320500</v>
       </c>
       <c r="G138" s="5" t="n">
-        <v>0.34</v>
+        <v>0.23</v>
       </c>
       <c r="H138" t="n">
-        <v>50.47</v>
-      </c>
-      <c r="I138" s="8" t="inlineStr">
+        <v>56.38</v>
+      </c>
+      <c r="I138" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J138" s="2" t="n">
-        <v>5.512</v>
+        <v>6.168</v>
       </c>
       <c r="K138" s="2" t="n">
-        <v>5.393</v>
+        <v>5.911</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" s="7" t="inlineStr"/>
@@ -6681,28 +6683,28 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>0470</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>BFIELD</t>
         </is>
       </c>
       <c r="D139" s="2" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="E139" s="9" t="n">
-        <v>0.0102</v>
+        <v>0.42</v>
+      </c>
+      <c r="E139" s="8" t="n">
+        <v>-0.0118</v>
       </c>
       <c r="F139" s="4" t="n">
-        <v>1288600</v>
+        <v>1319700</v>
       </c>
       <c r="G139" s="5" t="n">
-        <v>0.13</v>
+        <v>0.24</v>
       </c>
       <c r="H139" t="n">
-        <v>52.54</v>
+        <v>17.86</v>
       </c>
       <c r="I139" s="6" t="inlineStr">
         <is>
@@ -6710,11 +6712,9 @@
         </is>
       </c>
       <c r="J139" s="2" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="K139" s="2" t="n">
-        <v>3.556</v>
-      </c>
+        <v>0.46</v>
+      </c>
+      <c r="K139" s="2" t="n"/>
       <c r="L139" t="inlineStr"/>
       <c r="M139" s="7" t="inlineStr"/>
     </row>
@@ -6726,39 +6726,39 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>ATECH</t>
         </is>
       </c>
       <c r="D140" s="2" t="n">
-        <v>6.45</v>
-      </c>
-      <c r="E140" s="3" t="n">
-        <v>-0.0077</v>
+        <v>0.765</v>
+      </c>
+      <c r="E140" s="8" t="n">
+        <v>-0.0255</v>
       </c>
       <c r="F140" s="4" t="n">
-        <v>1273800</v>
+        <v>1318000</v>
       </c>
       <c r="G140" s="5" t="n">
-        <v>0.22</v>
+        <v>0.57</v>
       </c>
       <c r="H140" t="n">
-        <v>56.2</v>
-      </c>
-      <c r="I140" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.2</v>
+      </c>
+      <c r="I140" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J140" s="2" t="n">
-        <v>6.168</v>
+        <v>0.776</v>
       </c>
       <c r="K140" s="2" t="n">
-        <v>5.911</v>
+        <v>0.769</v>
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" s="7" t="inlineStr"/>
@@ -6771,28 +6771,28 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D141" s="2" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="E141" s="3" t="n">
-        <v>-0.0273</v>
+        <v>0.87</v>
+      </c>
+      <c r="E141" s="10" t="n">
+        <v>0.0116</v>
       </c>
       <c r="F141" s="4" t="n">
-        <v>1272900</v>
+        <v>1317700</v>
       </c>
       <c r="G141" s="5" t="n">
-        <v>0.25</v>
+        <v>0.42</v>
       </c>
       <c r="H141" t="n">
-        <v>32.47</v>
+        <v>57.35</v>
       </c>
       <c r="I141" s="6" t="inlineStr">
         <is>
@@ -6800,10 +6800,10 @@
         </is>
       </c>
       <c r="J141" s="2" t="n">
-        <v>2.807</v>
+        <v>0.864</v>
       </c>
       <c r="K141" s="2" t="n">
-        <v>2.877</v>
+        <v>0.86</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" s="7" t="inlineStr"/>
@@ -6816,28 +6816,28 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>5932</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>ATECH</t>
+          <t>BPURI</t>
         </is>
       </c>
       <c r="D142" s="2" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="E142" s="3" t="n">
-        <v>-0.0191</v>
+        <v>0.21</v>
+      </c>
+      <c r="E142" s="8" t="n">
+        <v>-0.0233</v>
       </c>
       <c r="F142" s="4" t="n">
-        <v>1266700</v>
+        <v>1297400</v>
       </c>
       <c r="G142" s="5" t="n">
-        <v>0.54</v>
+        <v>1.89</v>
       </c>
       <c r="H142" t="n">
-        <v>49.22</v>
+        <v>38.22</v>
       </c>
       <c r="I142" s="6" t="inlineStr">
         <is>
@@ -6845,10 +6845,10 @@
         </is>
       </c>
       <c r="J142" s="2" t="n">
-        <v>0.776</v>
+        <v>0.223</v>
       </c>
       <c r="K142" s="2" t="n">
-        <v>0.769</v>
+        <v>0.232</v>
       </c>
       <c r="L142" t="inlineStr"/>
       <c r="M142" s="7" t="inlineStr"/>
@@ -6861,28 +6861,28 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>0298</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>WENTEL</t>
         </is>
       </c>
       <c r="D143" s="2" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="E143" s="9" t="n">
-        <v>0.021</v>
+        <v>0.235</v>
+      </c>
+      <c r="E143" s="8" t="n">
+        <v>-0.0408</v>
       </c>
       <c r="F143" s="4" t="n">
-        <v>1260000</v>
+        <v>1295300</v>
       </c>
       <c r="G143" s="5" t="n">
-        <v>0.25</v>
+        <v>0.76</v>
       </c>
       <c r="H143" t="n">
-        <v>60.14</v>
+        <v>36.24</v>
       </c>
       <c r="I143" s="6" t="inlineStr">
         <is>
@@ -6890,10 +6890,10 @@
         </is>
       </c>
       <c r="J143" s="2" t="n">
-        <v>2.786</v>
+        <v>0.254</v>
       </c>
       <c r="K143" s="2" t="n">
-        <v>2.213</v>
+        <v>0.274</v>
       </c>
       <c r="L143" t="inlineStr"/>
       <c r="M143" s="7" t="inlineStr"/>
@@ -6906,28 +6906,28 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>0045</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>SSB8</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D144" s="2" t="n">
-        <v>0.635</v>
+        <v>3.97</v>
       </c>
       <c r="E144" s="10" t="n">
-        <v>0</v>
+        <v>0.0128</v>
       </c>
       <c r="F144" s="4" t="n">
-        <v>1210100</v>
+        <v>1289100</v>
       </c>
       <c r="G144" s="5" t="n">
-        <v>0.32</v>
+        <v>0.13</v>
       </c>
       <c r="H144" t="n">
-        <v>50.64</v>
+        <v>52.85</v>
       </c>
       <c r="I144" s="6" t="inlineStr">
         <is>
@@ -6935,10 +6935,10 @@
         </is>
       </c>
       <c r="J144" s="2" t="n">
-        <v>0.639</v>
+        <v>3.961</v>
       </c>
       <c r="K144" s="2" t="n">
-        <v>0.615</v>
+        <v>3.556</v>
       </c>
       <c r="L144" t="inlineStr"/>
       <c r="M144" s="7" t="inlineStr"/>
@@ -6951,28 +6951,28 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D145" s="2" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="E145" s="3" t="n">
-        <v>-0.0303</v>
+        <v>2.48</v>
+      </c>
+      <c r="E145" s="8" t="n">
+        <v>-0.0313</v>
       </c>
       <c r="F145" s="4" t="n">
-        <v>1202000</v>
+        <v>1280700</v>
       </c>
       <c r="G145" s="5" t="n">
-        <v>0.38</v>
+        <v>0.25</v>
       </c>
       <c r="H145" t="n">
-        <v>50.47</v>
+        <v>32.16</v>
       </c>
       <c r="I145" s="6" t="inlineStr">
         <is>
@@ -6980,10 +6980,10 @@
         </is>
       </c>
       <c r="J145" s="2" t="n">
-        <v>1.288</v>
+        <v>2.806</v>
       </c>
       <c r="K145" s="2" t="n">
-        <v>1.225</v>
+        <v>2.877</v>
       </c>
       <c r="L145" t="inlineStr"/>
       <c r="M145" s="7" t="inlineStr"/>
@@ -6996,28 +6996,28 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>0223</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>SAMAIDEN</t>
         </is>
       </c>
       <c r="D146" s="2" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="E146" s="3" t="n">
-        <v>-0.0323</v>
+        <v>2.92</v>
+      </c>
+      <c r="E146" s="10" t="n">
+        <v>0.021</v>
       </c>
       <c r="F146" s="4" t="n">
-        <v>1194100</v>
+        <v>1261600</v>
       </c>
       <c r="G146" s="5" t="n">
-        <v>0.49</v>
+        <v>0.25</v>
       </c>
       <c r="H146" t="n">
-        <v>53.86</v>
+        <v>60.14</v>
       </c>
       <c r="I146" s="6" t="inlineStr">
         <is>
@@ -7025,10 +7025,10 @@
         </is>
       </c>
       <c r="J146" s="2" t="n">
-        <v>0.734</v>
+        <v>2.786</v>
       </c>
       <c r="K146" s="2" t="n">
-        <v>0.704</v>
+        <v>2.213</v>
       </c>
       <c r="L146" t="inlineStr"/>
       <c r="M146" s="7" t="inlineStr"/>
@@ -7041,39 +7041,39 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>8494</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>LBICAP</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D147" s="2" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="E147" s="10" t="n">
-        <v>0</v>
+        <v>0.755</v>
+      </c>
+      <c r="E147" s="8" t="n">
+        <v>-0.0258</v>
       </c>
       <c r="F147" s="4" t="n">
-        <v>1191600</v>
+        <v>1238000</v>
       </c>
       <c r="G147" s="5" t="n">
-        <v>6.8</v>
+        <v>0.5</v>
       </c>
       <c r="H147" t="n">
-        <v>79.44</v>
-      </c>
-      <c r="I147" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>54.61</v>
+      </c>
+      <c r="I147" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J147" s="2" t="n">
-        <v>0.463</v>
+        <v>0.735</v>
       </c>
       <c r="K147" s="2" t="n">
-        <v>0.405</v>
+        <v>0.704</v>
       </c>
       <c r="L147" t="inlineStr"/>
       <c r="M147" s="7" t="inlineStr"/>
@@ -7086,28 +7086,28 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>1619</t>
+          <t>0045</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>DRBHCOM</t>
+          <t>SSB8</t>
         </is>
       </c>
       <c r="D148" s="2" t="n">
-        <v>0.805</v>
+        <v>0.635</v>
       </c>
       <c r="E148" s="3" t="n">
-        <v>-0.0123</v>
+        <v>0</v>
       </c>
       <c r="F148" s="4" t="n">
-        <v>1160800</v>
+        <v>1221700</v>
       </c>
       <c r="G148" s="5" t="n">
-        <v>2.35</v>
+        <v>0.32</v>
       </c>
       <c r="H148" t="n">
-        <v>16.17</v>
+        <v>50.64</v>
       </c>
       <c r="I148" s="6" t="inlineStr">
         <is>
@@ -7115,10 +7115,10 @@
         </is>
       </c>
       <c r="J148" s="2" t="n">
-        <v>0.885</v>
+        <v>0.639</v>
       </c>
       <c r="K148" s="2" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.615</v>
       </c>
       <c r="L148" t="inlineStr"/>
       <c r="M148" s="7" t="inlineStr"/>
@@ -7131,39 +7131,39 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>0337</t>
+          <t>8494</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>SET</t>
+          <t>LBICAP</t>
         </is>
       </c>
       <c r="D149" s="2" t="n">
-        <v>0.245</v>
-      </c>
-      <c r="E149" s="9" t="n">
-        <v>0.0208</v>
+        <v>0.505</v>
+      </c>
+      <c r="E149" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F149" s="4" t="n">
-        <v>1158600</v>
+        <v>1191600</v>
       </c>
       <c r="G149" s="5" t="n">
-        <v>0.59</v>
+        <v>6.8</v>
       </c>
       <c r="H149" t="n">
-        <v>53.4</v>
-      </c>
-      <c r="I149" s="8" t="inlineStr">
+        <v>79.44</v>
+      </c>
+      <c r="I149" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J149" s="2" t="n">
-        <v>0.24</v>
+        <v>0.463</v>
       </c>
       <c r="K149" s="2" t="n">
-        <v>0.242</v>
+        <v>0.405</v>
       </c>
       <c r="L149" t="inlineStr"/>
       <c r="M149" s="7" t="inlineStr"/>
@@ -7176,28 +7176,28 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>0277</t>
+          <t>1619</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>CLOUDPT</t>
+          <t>DRBHCOM</t>
         </is>
       </c>
       <c r="D150" s="2" t="n">
-        <v>0.475</v>
-      </c>
-      <c r="E150" s="3" t="n">
-        <v>-0.0404</v>
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E150" s="8" t="n">
+        <v>-0.0061</v>
       </c>
       <c r="F150" s="4" t="n">
-        <v>1142500</v>
+        <v>1165700</v>
       </c>
       <c r="G150" s="5" t="n">
-        <v>0.51</v>
+        <v>2.36</v>
       </c>
       <c r="H150" t="n">
-        <v>45.11</v>
+        <v>16.74</v>
       </c>
       <c r="I150" s="6" t="inlineStr">
         <is>
@@ -7205,10 +7205,10 @@
         </is>
       </c>
       <c r="J150" s="2" t="n">
-        <v>0.491</v>
+        <v>0.885</v>
       </c>
       <c r="K150" s="2" t="n">
-        <v>0.485</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="L150" t="inlineStr"/>
       <c r="M150" s="7" t="inlineStr"/>
@@ -7221,39 +7221,39 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>5337</t>
+          <t>0337</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>ECOSHOP</t>
+          <t>SET</t>
         </is>
       </c>
       <c r="D151" s="2" t="n">
-        <v>1.43</v>
+        <v>0.245</v>
       </c>
       <c r="E151" s="10" t="n">
-        <v>0</v>
+        <v>0.0208</v>
       </c>
       <c r="F151" s="4" t="n">
-        <v>1077600</v>
+        <v>1158600</v>
       </c>
       <c r="G151" s="5" t="n">
-        <v>0.26</v>
+        <v>0.59</v>
       </c>
       <c r="H151" t="n">
-        <v>41.9</v>
-      </c>
-      <c r="I151" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.4</v>
+      </c>
+      <c r="I151" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J151" s="2" t="n">
-        <v>1.448</v>
+        <v>0.24</v>
       </c>
       <c r="K151" s="2" t="n">
-        <v>1.464</v>
+        <v>0.242</v>
       </c>
       <c r="L151" t="inlineStr"/>
       <c r="M151" s="7" t="inlineStr"/>
@@ -7266,28 +7266,28 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>0099</t>
+          <t>0277</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>SCICOM</t>
+          <t>CLOUDPT</t>
         </is>
       </c>
       <c r="D152" s="2" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="E152" s="9" t="n">
-        <v>0.0239</v>
+        <v>0.475</v>
+      </c>
+      <c r="E152" s="8" t="n">
+        <v>-0.0404</v>
       </c>
       <c r="F152" s="4" t="n">
-        <v>1067100</v>
+        <v>1145700</v>
       </c>
       <c r="G152" s="5" t="n">
-        <v>1.44</v>
+        <v>0.51</v>
       </c>
       <c r="H152" t="n">
-        <v>44.38</v>
+        <v>45.11</v>
       </c>
       <c r="I152" s="6" t="inlineStr">
         <is>
@@ -7295,10 +7295,10 @@
         </is>
       </c>
       <c r="J152" s="2" t="n">
-        <v>2.201</v>
+        <v>0.491</v>
       </c>
       <c r="K152" s="2" t="n">
-        <v>2.236</v>
+        <v>0.485</v>
       </c>
       <c r="L152" t="inlineStr"/>
       <c r="M152" s="7" t="inlineStr"/>
@@ -7311,28 +7311,28 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>5789</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>LBS</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D153" s="2" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="E153" s="9" t="n">
-        <v>0.0135</v>
+        <v>0.3</v>
+      </c>
+      <c r="E153" s="8" t="n">
+        <v>-0.0164</v>
       </c>
       <c r="F153" s="4" t="n">
-        <v>1054400</v>
+        <v>1117200</v>
       </c>
       <c r="G153" s="5" t="n">
-        <v>0.68</v>
+        <v>0.18</v>
       </c>
       <c r="H153" t="n">
-        <v>39.13</v>
+        <v>40.49</v>
       </c>
       <c r="I153" s="6" t="inlineStr">
         <is>
@@ -7340,10 +7340,10 @@
         </is>
       </c>
       <c r="J153" s="2" t="n">
-        <v>0.379</v>
+        <v>0.316</v>
       </c>
       <c r="K153" s="2" t="n">
-        <v>0.391</v>
+        <v>0.336</v>
       </c>
       <c r="L153" t="inlineStr"/>
       <c r="M153" s="7" t="inlineStr"/>
@@ -7356,28 +7356,28 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>5337</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>ECOSHOP</t>
         </is>
       </c>
       <c r="D154" s="2" t="n">
-        <v>0.745</v>
+        <v>1.43</v>
       </c>
       <c r="E154" s="3" t="n">
-        <v>-0.0067</v>
+        <v>0</v>
       </c>
       <c r="F154" s="4" t="n">
-        <v>1037600</v>
+        <v>1111900</v>
       </c>
       <c r="G154" s="5" t="n">
-        <v>0.15</v>
+        <v>0.27</v>
       </c>
       <c r="H154" t="n">
-        <v>52.97</v>
+        <v>41.9</v>
       </c>
       <c r="I154" s="6" t="inlineStr">
         <is>
@@ -7385,10 +7385,10 @@
         </is>
       </c>
       <c r="J154" s="2" t="n">
-        <v>0.742</v>
+        <v>1.448</v>
       </c>
       <c r="K154" s="2" t="n">
-        <v>0.676</v>
+        <v>1.464</v>
       </c>
       <c r="L154" t="inlineStr"/>
       <c r="M154" s="7" t="inlineStr"/>
@@ -7401,39 +7401,39 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>0450</t>
+          <t>0099</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>MFGROUP</t>
+          <t>SCICOM</t>
         </is>
       </c>
       <c r="D155" s="2" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="E155" s="3" t="n">
-        <v>-0.0175</v>
+        <v>2.13</v>
+      </c>
+      <c r="E155" s="10" t="n">
+        <v>0.0191</v>
       </c>
       <c r="F155" s="4" t="n">
-        <v>1006700</v>
+        <v>1068500</v>
       </c>
       <c r="G155" s="5" t="n">
-        <v>1.06</v>
+        <v>1.44</v>
       </c>
       <c r="H155" t="n">
-        <v>55.75</v>
-      </c>
-      <c r="I155" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.52</v>
+      </c>
+      <c r="I155" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J155" s="2" t="n">
-        <v>0.276</v>
+        <v>2.2</v>
       </c>
       <c r="K155" s="2" t="n">
-        <v>0.267</v>
+        <v>2.236</v>
       </c>
       <c r="L155" t="inlineStr"/>
       <c r="M155" s="7" t="inlineStr"/>
@@ -7446,28 +7446,28 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>5318</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>DXN</t>
         </is>
       </c>
       <c r="D156" s="2" t="n">
-        <v>0.3</v>
+        <v>0.46</v>
       </c>
       <c r="E156" s="3" t="n">
-        <v>-0.0164</v>
+        <v>0</v>
       </c>
       <c r="F156" s="4" t="n">
-        <v>1002700</v>
+        <v>1068500</v>
       </c>
       <c r="G156" s="5" t="n">
-        <v>0.16</v>
+        <v>0.64</v>
       </c>
       <c r="H156" t="n">
-        <v>40.49</v>
+        <v>46.88</v>
       </c>
       <c r="I156" s="6" t="inlineStr">
         <is>
@@ -7475,10 +7475,10 @@
         </is>
       </c>
       <c r="J156" s="2" t="n">
-        <v>0.316</v>
+        <v>0.461</v>
       </c>
       <c r="K156" s="2" t="n">
-        <v>0.336</v>
+        <v>0.461</v>
       </c>
       <c r="L156" t="inlineStr"/>
       <c r="M156" s="7" t="inlineStr"/>
@@ -7491,28 +7491,28 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>5789</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>AMBANK</t>
+          <t>LBS</t>
         </is>
       </c>
       <c r="D157" s="2" t="n">
-        <v>6.16</v>
-      </c>
-      <c r="E157" s="3" t="n">
-        <v>-0.0299</v>
+        <v>0.375</v>
+      </c>
+      <c r="E157" s="10" t="n">
+        <v>0.0135</v>
       </c>
       <c r="F157" s="4" t="n">
-        <v>967200</v>
+        <v>1054700</v>
       </c>
       <c r="G157" s="5" t="n">
-        <v>0.15</v>
+        <v>0.68</v>
       </c>
       <c r="H157" t="n">
-        <v>35.5</v>
+        <v>39.13</v>
       </c>
       <c r="I157" s="6" t="inlineStr">
         <is>
@@ -7520,10 +7520,10 @@
         </is>
       </c>
       <c r="J157" s="2" t="n">
-        <v>6.388</v>
+        <v>0.379</v>
       </c>
       <c r="K157" s="2" t="n">
-        <v>6.754</v>
+        <v>0.391</v>
       </c>
       <c r="L157" t="inlineStr"/>
       <c r="M157" s="7" t="inlineStr"/>
@@ -7536,28 +7536,28 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D158" s="2" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="E158" s="9" t="n">
-        <v>0.0265</v>
+        <v>0.75</v>
+      </c>
+      <c r="E158" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F158" s="4" t="n">
-        <v>949000</v>
+        <v>1037700</v>
       </c>
       <c r="G158" s="5" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="H158" t="n">
-        <v>57.9</v>
+        <v>53.87</v>
       </c>
       <c r="I158" s="6" t="inlineStr">
         <is>
@@ -7565,10 +7565,10 @@
         </is>
       </c>
       <c r="J158" s="2" t="n">
-        <v>1.114</v>
+        <v>0.743</v>
       </c>
       <c r="K158" s="2" t="n">
-        <v>0.888</v>
+        <v>0.677</v>
       </c>
       <c r="L158" t="inlineStr"/>
       <c r="M158" s="7" t="inlineStr"/>
@@ -7581,39 +7581,39 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>0168</t>
+          <t>0450</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>BMGREEN</t>
+          <t>MFGROUP</t>
         </is>
       </c>
       <c r="D159" s="2" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="E159" s="3" t="n">
-        <v>-0.0476</v>
+        <v>0.28</v>
+      </c>
+      <c r="E159" s="8" t="n">
+        <v>-0.0175</v>
       </c>
       <c r="F159" s="4" t="n">
-        <v>933700</v>
+        <v>1006700</v>
       </c>
       <c r="G159" s="5" t="n">
-        <v>0.97</v>
+        <v>1.06</v>
       </c>
       <c r="H159" t="n">
-        <v>30.17</v>
-      </c>
-      <c r="I159" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.75</v>
+      </c>
+      <c r="I159" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J159" s="2" t="n">
-        <v>1.554</v>
+        <v>0.276</v>
       </c>
       <c r="K159" s="2" t="n">
-        <v>1.648</v>
+        <v>0.267</v>
       </c>
       <c r="L159" t="inlineStr"/>
       <c r="M159" s="7" t="inlineStr"/>
@@ -7626,39 +7626,39 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>0393</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>DUFU</t>
+          <t>TEAMSTR</t>
         </is>
       </c>
       <c r="D160" s="2" t="n">
-        <v>3.03</v>
+        <v>0.225</v>
       </c>
       <c r="E160" s="3" t="n">
-        <v>-0.013</v>
+        <v>0</v>
       </c>
       <c r="F160" s="4" t="n">
-        <v>910600</v>
+        <v>1000600</v>
       </c>
       <c r="G160" s="5" t="n">
-        <v>0.29</v>
+        <v>1.01</v>
       </c>
       <c r="H160" t="n">
-        <v>52.14</v>
-      </c>
-      <c r="I160" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>42.78</v>
+      </c>
+      <c r="I160" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J160" s="2" t="n">
-        <v>3.029</v>
+        <v>0.229</v>
       </c>
       <c r="K160" s="2" t="n">
-        <v>2.856</v>
+        <v>0.238</v>
       </c>
       <c r="L160" t="inlineStr"/>
       <c r="M160" s="7" t="inlineStr"/>
@@ -7671,39 +7671,39 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>6947</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>DUFU</t>
         </is>
       </c>
       <c r="D161" s="2" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="E161" s="3" t="n">
-        <v>-0.0275</v>
+        <v>3.03</v>
+      </c>
+      <c r="E161" s="8" t="n">
+        <v>-0.013</v>
       </c>
       <c r="F161" s="4" t="n">
-        <v>905200</v>
+        <v>979600</v>
       </c>
       <c r="G161" s="5" t="n">
-        <v>0.3</v>
+        <v>0.32</v>
       </c>
       <c r="H161" t="n">
-        <v>37.3</v>
-      </c>
-      <c r="I161" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.14</v>
+      </c>
+      <c r="I161" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J161" s="2" t="n">
-        <v>2.557</v>
+        <v>3.029</v>
       </c>
       <c r="K161" s="2" t="n">
-        <v>2.685</v>
+        <v>2.856</v>
       </c>
       <c r="L161" t="inlineStr"/>
       <c r="M161" s="7" t="inlineStr"/>
@@ -7716,28 +7716,28 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>5211</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>SUNWAY</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D162" s="2" t="n">
-        <v>4.21</v>
-      </c>
-      <c r="E162" s="9" t="n">
-        <v>0.0072</v>
+        <v>1.15</v>
+      </c>
+      <c r="E162" s="10" t="n">
+        <v>0.0177</v>
       </c>
       <c r="F162" s="4" t="n">
-        <v>884400</v>
+        <v>976800</v>
       </c>
       <c r="G162" s="5" t="n">
-        <v>0.18</v>
+        <v>0.12</v>
       </c>
       <c r="H162" t="n">
-        <v>34.43</v>
+        <v>57.19</v>
       </c>
       <c r="I162" s="6" t="inlineStr">
         <is>
@@ -7745,10 +7745,10 @@
         </is>
       </c>
       <c r="J162" s="2" t="n">
-        <v>4.41</v>
+        <v>1.114</v>
       </c>
       <c r="K162" s="2" t="n">
-        <v>4.719</v>
+        <v>0.888</v>
       </c>
       <c r="L162" t="inlineStr"/>
       <c r="M162" s="7" t="inlineStr"/>
@@ -7761,28 +7761,28 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>6971</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>KOBAY</t>
+          <t>AMBANK</t>
         </is>
       </c>
       <c r="D163" s="2" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="E163" s="3" t="n">
-        <v>-0.0238</v>
+        <v>6.17</v>
+      </c>
+      <c r="E163" s="8" t="n">
+        <v>-0.0283</v>
       </c>
       <c r="F163" s="4" t="n">
-        <v>878800</v>
+        <v>967900</v>
       </c>
       <c r="G163" s="5" t="n">
-        <v>0.72</v>
+        <v>0.15</v>
       </c>
       <c r="H163" t="n">
-        <v>42.39</v>
+        <v>35.84</v>
       </c>
       <c r="I163" s="6" t="inlineStr">
         <is>
@@ -7790,10 +7790,10 @@
         </is>
       </c>
       <c r="J163" s="2" t="n">
-        <v>2.123</v>
+        <v>6.389</v>
       </c>
       <c r="K163" s="2" t="n">
-        <v>2.28</v>
+        <v>6.754</v>
       </c>
       <c r="L163" t="inlineStr"/>
       <c r="M163" s="7" t="inlineStr"/>
@@ -7806,39 +7806,39 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>7498</t>
+          <t>0168</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>RALCO</t>
+          <t>BMGREEN</t>
         </is>
       </c>
       <c r="D164" s="2" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="E164" s="10" t="n">
-        <v>0</v>
+        <v>1.39</v>
+      </c>
+      <c r="E164" s="8" t="n">
+        <v>-0.0544</v>
       </c>
       <c r="F164" s="4" t="n">
-        <v>878700</v>
+        <v>948300</v>
       </c>
       <c r="G164" s="5" t="n">
-        <v>1.28</v>
+        <v>0.99</v>
       </c>
       <c r="H164" t="n">
-        <v>59.46</v>
-      </c>
-      <c r="I164" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>29.55</v>
+      </c>
+      <c r="I164" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J164" s="2" t="n">
-        <v>1.004</v>
+        <v>1.553</v>
       </c>
       <c r="K164" s="2" t="n">
-        <v>0.984</v>
+        <v>1.648</v>
       </c>
       <c r="L164" t="inlineStr"/>
       <c r="M164" s="7" t="inlineStr"/>
@@ -7851,39 +7851,39 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>6947</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>DAYANG</t>
+          <t>CDB</t>
         </is>
       </c>
       <c r="D165" s="2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="E165" s="3" t="n">
-        <v>-0.0152</v>
+        <v>2.47</v>
+      </c>
+      <c r="E165" s="8" t="n">
+        <v>-0.0314</v>
       </c>
       <c r="F165" s="4" t="n">
-        <v>851000</v>
+        <v>934000</v>
       </c>
       <c r="G165" s="5" t="n">
-        <v>0.43</v>
+        <v>0.31</v>
       </c>
       <c r="H165" t="n">
-        <v>25.64</v>
-      </c>
-      <c r="I165" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>36.45</v>
+      </c>
+      <c r="I165" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J165" s="2" t="n">
-        <v>1.402</v>
+        <v>2.556</v>
       </c>
       <c r="K165" s="2" t="n">
-        <v>1.465</v>
+        <v>2.685</v>
       </c>
       <c r="L165" t="inlineStr"/>
       <c r="M165" s="7" t="inlineStr"/>
@@ -7896,28 +7896,28 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>5005</t>
+          <t>6971</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>UNISEM</t>
+          <t>KOBAY</t>
         </is>
       </c>
       <c r="D166" s="2" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="E166" s="3" t="n">
-        <v>-0.0189</v>
+        <v>2.07</v>
+      </c>
+      <c r="E166" s="8" t="n">
+        <v>-0.0143</v>
       </c>
       <c r="F166" s="4" t="n">
-        <v>843900</v>
+        <v>926700</v>
       </c>
       <c r="G166" s="5" t="n">
-        <v>0.3</v>
+        <v>0.76</v>
       </c>
       <c r="H166" t="n">
-        <v>44.31</v>
+        <v>43.56</v>
       </c>
       <c r="I166" s="6" t="inlineStr">
         <is>
@@ -7925,10 +7925,10 @@
         </is>
       </c>
       <c r="J166" s="2" t="n">
-        <v>4.287</v>
+        <v>2.125</v>
       </c>
       <c r="K166" s="2" t="n">
-        <v>4.326</v>
+        <v>2.28</v>
       </c>
       <c r="L166" t="inlineStr"/>
       <c r="M166" s="7" t="inlineStr"/>
@@ -7941,39 +7941,39 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>7293</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>YINSON</t>
+          <t>SUNWAY</t>
         </is>
       </c>
       <c r="D167" s="2" t="n">
-        <v>2.13</v>
+        <v>4.21</v>
       </c>
       <c r="E167" s="10" t="n">
-        <v>0</v>
+        <v>0.0072</v>
       </c>
       <c r="F167" s="4" t="n">
-        <v>777300</v>
+        <v>902900</v>
       </c>
       <c r="G167" s="5" t="n">
-        <v>0.37</v>
+        <v>0.19</v>
       </c>
       <c r="H167" t="n">
-        <v>54.7</v>
-      </c>
-      <c r="I167" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.43</v>
+      </c>
+      <c r="I167" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J167" s="2" t="n">
-        <v>2.11</v>
+        <v>4.41</v>
       </c>
       <c r="K167" s="2" t="n">
-        <v>2.062</v>
+        <v>4.719</v>
       </c>
       <c r="L167" t="inlineStr"/>
       <c r="M167" s="7" t="inlineStr"/>
@@ -7986,28 +7986,28 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>JPG</t>
+          <t>DAYANG</t>
         </is>
       </c>
       <c r="D168" s="2" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="E168" s="9" t="n">
-        <v>0.0175</v>
+        <v>1.3</v>
+      </c>
+      <c r="E168" s="8" t="n">
+        <v>-0.0152</v>
       </c>
       <c r="F168" s="4" t="n">
-        <v>776600</v>
+        <v>892800</v>
       </c>
       <c r="G168" s="5" t="n">
-        <v>0.13</v>
+        <v>0.45</v>
       </c>
       <c r="H168" t="n">
-        <v>41.01</v>
+        <v>25.64</v>
       </c>
       <c r="I168" s="6" t="inlineStr">
         <is>
@@ -8015,10 +8015,10 @@
         </is>
       </c>
       <c r="J168" s="2" t="n">
-        <v>1.776</v>
+        <v>1.402</v>
       </c>
       <c r="K168" s="2" t="n">
-        <v>1.888</v>
+        <v>1.465</v>
       </c>
       <c r="L168" t="inlineStr"/>
       <c r="M168" s="7" t="inlineStr"/>
@@ -8031,39 +8031,39 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>4383</t>
+          <t>7498</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>JTIASA</t>
+          <t>RALCO</t>
         </is>
       </c>
       <c r="D169" s="2" t="n">
-        <v>0.905</v>
-      </c>
-      <c r="E169" s="10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="E169" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F169" s="4" t="n">
-        <v>739200</v>
+        <v>878700</v>
       </c>
       <c r="G169" s="5" t="n">
-        <v>0.4</v>
+        <v>1.28</v>
       </c>
       <c r="H169" t="n">
-        <v>31.25</v>
-      </c>
-      <c r="I169" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.46</v>
+      </c>
+      <c r="I169" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J169" s="2" t="n">
-        <v>0.944</v>
+        <v>1.004</v>
       </c>
       <c r="K169" s="2" t="n">
-        <v>1.002</v>
+        <v>0.984</v>
       </c>
       <c r="L169" t="inlineStr"/>
       <c r="M169" s="7" t="inlineStr"/>
@@ -8076,39 +8076,39 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>0271</t>
+          <t>5005</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>WELLS</t>
+          <t>UNISEM</t>
         </is>
       </c>
       <c r="D170" s="2" t="n">
-        <v>0.555</v>
-      </c>
-      <c r="E170" s="9" t="n">
-        <v>0.0091</v>
+        <v>4.14</v>
+      </c>
+      <c r="E170" s="8" t="n">
+        <v>-0.0213</v>
       </c>
       <c r="F170" s="4" t="n">
-        <v>730000</v>
+        <v>850600</v>
       </c>
       <c r="G170" s="5" t="n">
-        <v>0.64</v>
+        <v>0.3</v>
       </c>
       <c r="H170" t="n">
-        <v>42.07</v>
-      </c>
-      <c r="I170" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.01</v>
+      </c>
+      <c r="I170" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J170" s="2" t="n">
-        <v>0.5679999999999999</v>
+        <v>4.286</v>
       </c>
       <c r="K170" s="2" t="n">
-        <v>0.611</v>
+        <v>4.326</v>
       </c>
       <c r="L170" t="inlineStr"/>
       <c r="M170" s="7" t="inlineStr"/>
@@ -8121,28 +8121,28 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>5299</t>
+          <t>5323</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>IGBCR</t>
+          <t>JPG</t>
         </is>
       </c>
       <c r="D171" s="2" t="n">
-        <v>0.61</v>
+        <v>1.72</v>
       </c>
       <c r="E171" s="10" t="n">
-        <v>0</v>
+        <v>0.0058</v>
       </c>
       <c r="F171" s="4" t="n">
-        <v>729700</v>
+        <v>833500</v>
       </c>
       <c r="G171" s="5" t="n">
-        <v>3.1</v>
+        <v>0.14</v>
       </c>
       <c r="H171" t="n">
-        <v>44.28</v>
+        <v>37.45</v>
       </c>
       <c r="I171" s="6" t="inlineStr">
         <is>
@@ -8150,10 +8150,10 @@
         </is>
       </c>
       <c r="J171" s="2" t="n">
-        <v>0.614</v>
+        <v>1.774</v>
       </c>
       <c r="K171" s="2" t="n">
-        <v>0.613</v>
+        <v>1.888</v>
       </c>
       <c r="L171" t="inlineStr"/>
       <c r="M171" s="7" t="inlineStr"/>
@@ -8166,39 +8166,39 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>0097</t>
+          <t>7293</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>VITROX</t>
+          <t>YINSON</t>
         </is>
       </c>
       <c r="D172" s="2" t="n">
-        <v>10.46</v>
+        <v>2.13</v>
       </c>
       <c r="E172" s="3" t="n">
-        <v>-0.0132</v>
+        <v>0</v>
       </c>
       <c r="F172" s="4" t="n">
-        <v>718000</v>
+        <v>777700</v>
       </c>
       <c r="G172" s="5" t="n">
-        <v>0.2</v>
+        <v>0.37</v>
       </c>
       <c r="H172" t="n">
-        <v>54.18</v>
-      </c>
-      <c r="I172" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.7</v>
+      </c>
+      <c r="I172" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J172" s="2" t="n">
-        <v>10.413</v>
+        <v>2.11</v>
       </c>
       <c r="K172" s="2" t="n">
-        <v>9.757</v>
+        <v>2.062</v>
       </c>
       <c r="L172" t="inlineStr"/>
       <c r="M172" s="7" t="inlineStr"/>
@@ -8211,28 +8211,28 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>5299</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>IGBCR</t>
         </is>
       </c>
       <c r="D173" s="2" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="E173" s="10" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="E173" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F173" s="4" t="n">
-        <v>714700</v>
+        <v>753300</v>
       </c>
       <c r="G173" s="5" t="n">
-        <v>0.17</v>
+        <v>3.2</v>
       </c>
       <c r="H173" t="n">
-        <v>49.25</v>
+        <v>44.28</v>
       </c>
       <c r="I173" s="6" t="inlineStr">
         <is>
@@ -8240,10 +8240,10 @@
         </is>
       </c>
       <c r="J173" s="2" t="n">
-        <v>1.045</v>
+        <v>0.614</v>
       </c>
       <c r="K173" s="2" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.613</v>
       </c>
       <c r="L173" t="inlineStr"/>
       <c r="M173" s="7" t="inlineStr"/>
@@ -8256,28 +8256,28 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>5246</t>
+          <t>5306</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>WPRTS</t>
+          <t>FFB</t>
         </is>
       </c>
       <c r="D174" s="2" t="n">
-        <v>6.74</v>
-      </c>
-      <c r="E174" s="3" t="n">
-        <v>-0.003</v>
+        <v>1.73</v>
+      </c>
+      <c r="E174" s="10" t="n">
+        <v>0.0058</v>
       </c>
       <c r="F174" s="4" t="n">
-        <v>695300</v>
+        <v>750300</v>
       </c>
       <c r="G174" s="5" t="n">
-        <v>0.16</v>
+        <v>0.23</v>
       </c>
       <c r="H174" t="n">
-        <v>48.63</v>
+        <v>29.4</v>
       </c>
       <c r="I174" s="6" t="inlineStr">
         <is>
@@ -8285,10 +8285,10 @@
         </is>
       </c>
       <c r="J174" s="2" t="n">
-        <v>6.755</v>
+        <v>1.822</v>
       </c>
       <c r="K174" s="2" t="n">
-        <v>6.826</v>
+        <v>1.962</v>
       </c>
       <c r="L174" t="inlineStr"/>
       <c r="M174" s="7" t="inlineStr"/>
@@ -8301,28 +8301,28 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>5258</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>BIMB</t>
+          <t>WPRTS</t>
         </is>
       </c>
       <c r="D175" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E175" s="3" t="n">
-        <v>-0.005</v>
+        <v>6.75</v>
+      </c>
+      <c r="E175" s="8" t="n">
+        <v>-0.0015</v>
       </c>
       <c r="F175" s="4" t="n">
-        <v>668700</v>
+        <v>745500</v>
       </c>
       <c r="G175" s="5" t="n">
-        <v>0.78</v>
+        <v>0.18</v>
       </c>
       <c r="H175" t="n">
-        <v>34.83</v>
+        <v>49.34</v>
       </c>
       <c r="I175" s="6" t="inlineStr">
         <is>
@@ -8330,10 +8330,10 @@
         </is>
       </c>
       <c r="J175" s="2" t="n">
-        <v>2.037</v>
+        <v>6.756</v>
       </c>
       <c r="K175" s="2" t="n">
-        <v>2.081</v>
+        <v>6.827</v>
       </c>
       <c r="L175" t="inlineStr"/>
       <c r="M175" s="7" t="inlineStr"/>
@@ -8346,39 +8346,39 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>4383</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>SIMEPROP</t>
+          <t>JTIASA</t>
         </is>
       </c>
       <c r="D176" s="2" t="n">
-        <v>1.28</v>
+        <v>0.91</v>
       </c>
       <c r="E176" s="10" t="n">
-        <v>0</v>
+        <v>0.005500000000000001</v>
       </c>
       <c r="F176" s="4" t="n">
-        <v>659300</v>
+        <v>740200</v>
       </c>
       <c r="G176" s="5" t="n">
-        <v>0.15</v>
+        <v>0.4</v>
       </c>
       <c r="H176" t="n">
-        <v>54.38</v>
-      </c>
-      <c r="I176" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.51</v>
+      </c>
+      <c r="I176" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J176" s="2" t="n">
-        <v>1.26</v>
+        <v>0.945</v>
       </c>
       <c r="K176" s="2" t="n">
-        <v>1.278</v>
+        <v>1.002</v>
       </c>
       <c r="L176" t="inlineStr"/>
       <c r="M176" s="7" t="inlineStr"/>
@@ -8391,39 +8391,39 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>3417</t>
+          <t>0271</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>E&amp;O</t>
+          <t>WELLS</t>
         </is>
       </c>
       <c r="D177" s="2" t="n">
-        <v>0.745</v>
+        <v>0.55</v>
       </c>
       <c r="E177" s="3" t="n">
-        <v>-0.0067</v>
+        <v>0</v>
       </c>
       <c r="F177" s="4" t="n">
-        <v>659100</v>
+        <v>740000</v>
       </c>
       <c r="G177" s="5" t="n">
-        <v>0.49</v>
+        <v>0.65</v>
       </c>
       <c r="H177" t="n">
-        <v>40.03</v>
-      </c>
-      <c r="I177" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>40.11</v>
+      </c>
+      <c r="I177" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J177" s="2" t="n">
-        <v>0.764</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="K177" s="2" t="n">
-        <v>0.769</v>
+        <v>0.611</v>
       </c>
       <c r="L177" t="inlineStr"/>
       <c r="M177" s="7" t="inlineStr"/>
@@ -8436,28 +8436,28 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>0097</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>VITROX</t>
         </is>
       </c>
       <c r="D178" s="2" t="n">
-        <v>0.655</v>
-      </c>
-      <c r="E178" s="3" t="n">
-        <v>-0.0224</v>
+        <v>10.48</v>
+      </c>
+      <c r="E178" s="8" t="n">
+        <v>-0.0113</v>
       </c>
       <c r="F178" s="4" t="n">
-        <v>650600</v>
+        <v>720000</v>
       </c>
       <c r="G178" s="5" t="n">
         <v>0.2</v>
       </c>
       <c r="H178" t="n">
-        <v>34.29</v>
+        <v>54.58</v>
       </c>
       <c r="I178" s="6" t="inlineStr">
         <is>
@@ -8465,10 +8465,10 @@
         </is>
       </c>
       <c r="J178" s="2" t="n">
-        <v>0.724</v>
+        <v>10.415</v>
       </c>
       <c r="K178" s="2" t="n">
-        <v>0.744</v>
+        <v>9.757</v>
       </c>
       <c r="L178" t="inlineStr"/>
       <c r="M178" s="7" t="inlineStr"/>
@@ -8481,28 +8481,28 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>5236</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>MATRIX</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D179" s="2" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="E179" s="3" t="n">
-        <v>-0.019</v>
+        <v>0</v>
       </c>
       <c r="F179" s="4" t="n">
-        <v>631400</v>
+        <v>714800</v>
       </c>
       <c r="G179" s="5" t="n">
-        <v>0.47</v>
+        <v>0.17</v>
       </c>
       <c r="H179" t="n">
-        <v>34.63</v>
+        <v>49.25</v>
       </c>
       <c r="I179" s="6" t="inlineStr">
         <is>
@@ -8510,10 +8510,10 @@
         </is>
       </c>
       <c r="J179" s="2" t="n">
-        <v>1.085</v>
+        <v>1.045</v>
       </c>
       <c r="K179" s="2" t="n">
-        <v>1.133</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="L179" t="inlineStr"/>
       <c r="M179" s="7" t="inlineStr"/>
@@ -8526,39 +8526,39 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>5258</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>TAKAFUL</t>
+          <t>BIMB</t>
         </is>
       </c>
       <c r="D180" s="2" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="E180" s="3" t="n">
-        <v>-0.0138</v>
+        <v>2</v>
+      </c>
+      <c r="E180" s="8" t="n">
+        <v>-0.005</v>
       </c>
       <c r="F180" s="4" t="n">
-        <v>628600</v>
+        <v>696800</v>
       </c>
       <c r="G180" s="5" t="n">
-        <v>0.49</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H180" t="n">
-        <v>34.01</v>
-      </c>
-      <c r="I180" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.83</v>
+      </c>
+      <c r="I180" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J180" s="2" t="n">
-        <v>2.927</v>
+        <v>2.037</v>
       </c>
       <c r="K180" s="2" t="n">
-        <v>3.063</v>
+        <v>2.081</v>
       </c>
       <c r="L180" t="inlineStr"/>
       <c r="M180" s="7" t="inlineStr"/>
@@ -8571,39 +8571,39 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>0359</t>
+          <t>3417</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>HKB</t>
+          <t>E&amp;O</t>
         </is>
       </c>
       <c r="D181" s="2" t="n">
-        <v>0.775</v>
+        <v>0.75</v>
       </c>
       <c r="E181" s="3" t="n">
-        <v>-0.0127</v>
+        <v>0</v>
       </c>
       <c r="F181" s="4" t="n">
-        <v>624800</v>
+        <v>672500</v>
       </c>
       <c r="G181" s="5" t="n">
-        <v>0.27</v>
+        <v>0.5</v>
       </c>
       <c r="H181" t="n">
-        <v>67.27</v>
-      </c>
-      <c r="I181" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.96</v>
+      </c>
+      <c r="I181" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J181" s="2" t="n">
-        <v>0.73</v>
+        <v>0.765</v>
       </c>
       <c r="K181" s="2" t="n">
-        <v>0.648</v>
+        <v>0.769</v>
       </c>
       <c r="L181" t="inlineStr"/>
       <c r="M181" s="7" t="inlineStr"/>
@@ -8616,39 +8616,39 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>5212</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>PAVREIT</t>
+          <t>SIMEPROP</t>
         </is>
       </c>
       <c r="D182" s="2" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="E182" s="10" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="E182" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F182" s="4" t="n">
-        <v>576200</v>
+        <v>664000</v>
       </c>
       <c r="G182" s="5" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="H182" t="n">
-        <v>47.18</v>
-      </c>
-      <c r="I182" s="8" t="inlineStr">
+        <v>54.38</v>
+      </c>
+      <c r="I182" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J182" s="2" t="n">
-        <v>1.568</v>
+        <v>1.26</v>
       </c>
       <c r="K182" s="2" t="n">
-        <v>1.601</v>
+        <v>1.278</v>
       </c>
       <c r="L182" t="inlineStr"/>
       <c r="M182" s="7" t="inlineStr"/>
@@ -8661,28 +8661,28 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>FFB</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D183" s="2" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="E183" s="9" t="n">
-        <v>0.0058</v>
+        <v>0.655</v>
+      </c>
+      <c r="E183" s="8" t="n">
+        <v>-0.0224</v>
       </c>
       <c r="F183" s="4" t="n">
-        <v>557900</v>
+        <v>650600</v>
       </c>
       <c r="G183" s="5" t="n">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
       <c r="H183" t="n">
-        <v>29.4</v>
+        <v>34.29</v>
       </c>
       <c r="I183" s="6" t="inlineStr">
         <is>
@@ -8690,10 +8690,10 @@
         </is>
       </c>
       <c r="J183" s="2" t="n">
-        <v>1.822</v>
+        <v>0.724</v>
       </c>
       <c r="K183" s="2" t="n">
-        <v>1.962</v>
+        <v>0.744</v>
       </c>
       <c r="L183" t="inlineStr"/>
       <c r="M183" s="7" t="inlineStr"/>
@@ -8706,28 +8706,28 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>0293</t>
+          <t>5236</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>KJTS</t>
+          <t>MATRIX</t>
         </is>
       </c>
       <c r="D184" s="2" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="E184" s="9" t="n">
-        <v>0.0119</v>
+        <v>1.03</v>
+      </c>
+      <c r="E184" s="8" t="n">
+        <v>-0.019</v>
       </c>
       <c r="F184" s="4" t="n">
-        <v>548300</v>
+        <v>649700</v>
       </c>
       <c r="G184" s="5" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="H184" t="n">
-        <v>33.01</v>
+        <v>34.63</v>
       </c>
       <c r="I184" s="6" t="inlineStr">
         <is>
@@ -8735,10 +8735,10 @@
         </is>
       </c>
       <c r="J184" s="2" t="n">
-        <v>0.951</v>
+        <v>1.085</v>
       </c>
       <c r="K184" s="2" t="n">
-        <v>1.023</v>
+        <v>1.133</v>
       </c>
       <c r="L184" t="inlineStr"/>
       <c r="M184" s="7" t="inlineStr"/>
@@ -8751,39 +8751,39 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>0376</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>IAB</t>
+          <t>TAKAFUL</t>
         </is>
       </c>
       <c r="D185" s="2" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="E185" s="3" t="n">
-        <v>-0.028</v>
+        <v>2.86</v>
+      </c>
+      <c r="E185" s="8" t="n">
+        <v>-0.0138</v>
       </c>
       <c r="F185" s="4" t="n">
-        <v>547600</v>
+        <v>640700</v>
       </c>
       <c r="G185" s="5" t="n">
-        <v>0.22</v>
+        <v>0.5</v>
       </c>
       <c r="H185" t="n">
-        <v>33.46</v>
-      </c>
-      <c r="I185" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>34.01</v>
+      </c>
+      <c r="I185" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J185" s="2" t="n">
-        <v>1.196</v>
+        <v>2.927</v>
       </c>
       <c r="K185" s="2" t="n">
-        <v>1.291</v>
+        <v>3.063</v>
       </c>
       <c r="L185" t="inlineStr"/>
       <c r="M185" s="7" t="inlineStr"/>
@@ -8796,39 +8796,39 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>0359</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>SEG</t>
+          <t>HKB</t>
         </is>
       </c>
       <c r="D186" s="2" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E186" s="3" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.775</v>
+      </c>
+      <c r="E186" s="8" t="n">
+        <v>-0.0127</v>
       </c>
       <c r="F186" s="4" t="n">
-        <v>538500</v>
+        <v>634900</v>
       </c>
       <c r="G186" s="5" t="n">
-        <v>0.47</v>
+        <v>0.28</v>
       </c>
       <c r="H186" t="n">
-        <v>34.58</v>
-      </c>
-      <c r="I186" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>67.27</v>
+      </c>
+      <c r="I186" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J186" s="2" t="n">
-        <v>0.631</v>
+        <v>0.73</v>
       </c>
       <c r="K186" s="2" t="n">
-        <v>0.631</v>
+        <v>0.648</v>
       </c>
       <c r="L186" t="inlineStr"/>
       <c r="M186" s="7" t="inlineStr"/>
@@ -8841,39 +8841,39 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>4758</t>
+          <t>5212</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>ANCOMNY</t>
+          <t>PAVREIT</t>
         </is>
       </c>
       <c r="D187" s="2" t="n">
-        <v>0.8149999999999999</v>
-      </c>
-      <c r="E187" s="10" t="n">
-        <v>0</v>
+        <v>1.55</v>
+      </c>
+      <c r="E187" s="8" t="n">
+        <v>-0.0064</v>
       </c>
       <c r="F187" s="4" t="n">
-        <v>537200</v>
+        <v>577100</v>
       </c>
       <c r="G187" s="5" t="n">
-        <v>0.32</v>
+        <v>0.17</v>
       </c>
       <c r="H187" t="n">
-        <v>33.01</v>
-      </c>
-      <c r="I187" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>45.42</v>
+      </c>
+      <c r="I187" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J187" s="2" t="n">
-        <v>0.844</v>
+        <v>1.567</v>
       </c>
       <c r="K187" s="2" t="n">
-        <v>0.861</v>
+        <v>1.601</v>
       </c>
       <c r="L187" t="inlineStr"/>
       <c r="M187" s="7" t="inlineStr"/>
@@ -8886,28 +8886,28 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>0376</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>TSH</t>
+          <t>IAB</t>
         </is>
       </c>
       <c r="D188" s="2" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="E188" s="10" t="n">
-        <v>0</v>
+        <v>1.04</v>
+      </c>
+      <c r="E188" s="8" t="n">
+        <v>-0.028</v>
       </c>
       <c r="F188" s="4" t="n">
-        <v>500500</v>
+        <v>567600</v>
       </c>
       <c r="G188" s="5" t="n">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="H188" t="n">
-        <v>30.66</v>
+        <v>33.46</v>
       </c>
       <c r="I188" s="6" t="inlineStr">
         <is>
@@ -8915,16 +8915,286 @@
         </is>
       </c>
       <c r="J188" s="2" t="n">
-        <v>1.238</v>
+        <v>1.196</v>
       </c>
       <c r="K188" s="2" t="n">
-        <v>1.308</v>
+        <v>1.291</v>
       </c>
       <c r="L188" t="inlineStr"/>
       <c r="M188" s="7" t="inlineStr"/>
     </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>0293</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>KJTS</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E189" s="10" t="n">
+        <v>0.0119</v>
+      </c>
+      <c r="F189" s="4" t="n">
+        <v>548300</v>
+      </c>
+      <c r="G189" s="5" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H189" t="n">
+        <v>33.01</v>
+      </c>
+      <c r="I189" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J189" s="2" t="n">
+        <v>0.951</v>
+      </c>
+      <c r="K189" s="2" t="n">
+        <v>1.023</v>
+      </c>
+      <c r="L189" t="inlineStr"/>
+      <c r="M189" s="7" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>4758</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>ANCOMNY</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="E190" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F190" s="4" t="n">
+        <v>547200</v>
+      </c>
+      <c r="G190" s="5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H190" t="n">
+        <v>33.01</v>
+      </c>
+      <c r="I190" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J190" s="2" t="n">
+        <v>0.844</v>
+      </c>
+      <c r="K190" s="2" t="n">
+        <v>0.861</v>
+      </c>
+      <c r="L190" t="inlineStr"/>
+      <c r="M190" s="7" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>9792</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>SEG</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E191" s="8" t="n">
+        <v>-0.007900000000000001</v>
+      </c>
+      <c r="F191" s="4" t="n">
+        <v>538500</v>
+      </c>
+      <c r="G191" s="5" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="H191" t="n">
+        <v>34.58</v>
+      </c>
+      <c r="I191" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J191" s="2" t="n">
+        <v>0.631</v>
+      </c>
+      <c r="K191" s="2" t="n">
+        <v>0.631</v>
+      </c>
+      <c r="L191" t="inlineStr"/>
+      <c r="M191" s="7" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>9059</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>TSH</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="E192" s="8" t="n">
+        <v>-0.008500000000000001</v>
+      </c>
+      <c r="F192" s="4" t="n">
+        <v>526200</v>
+      </c>
+      <c r="G192" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H192" t="n">
+        <v>29.45</v>
+      </c>
+      <c r="I192" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J192" s="2" t="n">
+        <v>1.237</v>
+      </c>
+      <c r="K192" s="2" t="n">
+        <v>1.308</v>
+      </c>
+      <c r="L192" t="inlineStr"/>
+      <c r="M192" s="7" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>6633</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>LHI</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="E193" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F193" s="4" t="n">
+        <v>517800</v>
+      </c>
+      <c r="G193" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H193" t="n">
+        <v>46.64</v>
+      </c>
+      <c r="I193" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J193" s="2" t="n">
+        <v>0.732</v>
+      </c>
+      <c r="K193" s="2" t="n">
+        <v>0.745</v>
+      </c>
+      <c r="L193" t="inlineStr"/>
+      <c r="M193" s="7" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>0265</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>INFOM</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="E194" s="8" t="n">
+        <v>-0.0109</v>
+      </c>
+      <c r="F194" s="4" t="n">
+        <v>507300</v>
+      </c>
+      <c r="G194" s="5" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="H194" t="n">
+        <v>61.67</v>
+      </c>
+      <c r="I194" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J194" s="2" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="K194" s="2" t="n">
+        <v>1.647</v>
+      </c>
+      <c r="L194" t="inlineStr"/>
+      <c r="M194" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M188"/>
+  <autoFilter ref="A1:M194"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>